--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,67 +444,67 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>score_per_minute</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>deepswe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>terminal_bench_v2_1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>swe_atlas_qna</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cost_per_task_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_execution_time_sec</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>mean_steps</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_tokens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>input_tokens</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>output_tokens</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>cache_hit_rate</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>score_per_cost</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>score_per_1000_tokens</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>score_per_minute</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -547,40 +547,40 @@
       <c r="E2" t="n">
         <v>0.482993172759088</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.02639291776320254</v>
+      </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>0.545698924731183</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>3.451835432645762</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1098.006314631462</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>187.3635863586358</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>16229406.25687568</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>16083805.39493949</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>145600.8619361936</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.9661540316569817</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.1399235804207744</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>2.976037232135126e-05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.02639291776320254</v>
       </c>
       <c r="S2" t="n">
         <v>0.0004398819627200423</v>
@@ -616,40 +616,40 @@
       <c r="E3" t="n">
         <v>0.3874247758775307</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.02118927042627475</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>0.513440860215054</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.08278622901034095</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1097.040440044003</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>121.6666666666667</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>15350225.29922993</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>15269826.30913091</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>80398.9900990099</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.9869993314104538</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4.679821517527231</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2.523902863477623e-05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.02118927042627475</v>
       </c>
       <c r="S3" t="n">
         <v>0.0003531545071045792</v>
@@ -681,40 +681,40 @@
       <c r="E4" t="n">
         <v>0.588884131062264</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.02384313631717553</v>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>0.594086021505376</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>4.536492777821779</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1481.89598019802</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>78.55115511551155</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>6074134.495049492</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>6017554.665016501</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>56579.83003300329</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.9200611321722409</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0.1298104416568739</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>9.694947182058831e-05</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.02384313631717553</v>
       </c>
       <c r="S4" t="n">
         <v>0.0003973856052862588</v>
@@ -746,40 +746,40 @@
       <c r="E5" t="n">
         <v>0.6168255492406223</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.01722625087550708</v>
+      </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
         <v>0.658602150537635</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>7.89717336090483</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2148.438056655663</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>99.53685368536854</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>9691739.689768959</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>9590695.989548955</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>101043.700220022</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.9585129825583554</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0.07810713036821931</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>6.364446105499215e-05</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.01722625087550708</v>
       </c>
       <c r="S5" t="n">
         <v>0.0002871041812584513</v>
@@ -815,40 +815,40 @@
       <c r="E6" t="n">
         <v>0.54559127289644</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.02644871163008279</v>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>0.540322580645161</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>6.579795483718375</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1237.696445544555</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>116.3949394939494</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>10170136.63256324</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>10120981.25467547</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>49155.37788778878</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.9458037017976718</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.08291918407593353</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>5.364640541303439e-05</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.02644871163008279</v>
       </c>
       <c r="S6" t="n">
         <v>0.0004408118605013798</v>
@@ -884,40 +884,40 @@
       <c r="E7" t="n">
         <v>0.6222249615769457</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.01786377121119468</v>
+      </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
         <v>0.647849462365591</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>12.38809237513753</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>2089.900125412543</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>36.65676567656766</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>5715253.85918592</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5581622.259625964</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>133631.599559956</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.9159555838702423</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.05022766562717351</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0.0001088709227809481</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.01786377121119468</v>
       </c>
       <c r="S7" t="n">
         <v>0.0002977295201865781</v>
@@ -953,40 +953,40 @@
       <c r="E8" t="n">
         <v>0.519259105470924</v>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.008444738328521398</v>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>0.661290322580645</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5.047195443300332</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>3689.344194719472</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>173.3602860286028</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>8481121.533553353</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>8387890.666666667</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>93230.86688668867</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.9500000000000017</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.1028807208486825</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>6.12252876481737e-05</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.008444738328521398</v>
       </c>
       <c r="S8" t="n">
         <v>0.00014074563880869</v>
@@ -1022,40 +1022,40 @@
       <c r="E9" t="n">
         <v>0.5430273329930766</v>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.02943627526383025</v>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
         <v>0.594086021505376</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>3.977504096947204</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>1106.853353135313</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>185.2381738173817</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>16709444.57370737</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>16445971.06820682</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>263473.5055005501</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>0.9712826195905685</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>0.1365246445402428</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>3.24982276100033e-05</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.02943627526383025</v>
       </c>
       <c r="S9" t="n">
         <v>0.0004906045877305042</v>
@@ -1091,40 +1091,40 @@
       <c r="E10" t="n">
         <v>0.4186315529449987</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.03574427079166177</v>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
         <v>0.451612903225807</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>2.467392200412544</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>702.7110253025301</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>188.4884488448845</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>13511073.15511551</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>13395246.74862486</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>115826.4064906491</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.8697428234581179</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.1696655897976026</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>3.098433027035294e-05</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.03574427079166177</v>
       </c>
       <c r="S10" t="n">
         <v>0.0005957378465276962</v>
@@ -1160,40 +1160,40 @@
       <c r="E11" t="n">
         <v>0.4326529641259874</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.006858597906636284</v>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
         <v>0.620967741935484</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3.488442380612681</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>3784.910298129812</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>110.1898874502835</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>8723306.44030633</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>8616277.132021666</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>107029.3082846746</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.9507585357339288</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.1240246840625758</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>4.959735933692525e-05</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.006858597906636284</v>
       </c>
       <c r="S11" t="n">
         <v>0.0001143099651106047</v>
@@ -1229,40 +1229,40 @@
       <c r="E12" t="n">
         <v>0.5972636729844837</v>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.01426406965584376</v>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
         <v>0.620967741935484</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>10.78915469925741</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>2512.313893839384</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>151.9246424642464</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>11352813.1688669</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>11216237.69361936</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>136575.4752475248</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.9698121456131864</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.05535778192387877</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>5.260931049428126e-05</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.01426406965584376</v>
       </c>
       <c r="S12" t="n">
         <v>0.0002377344942640626</v>
@@ -1298,40 +1298,40 @@
       <c r="E13" t="n">
         <v>0.5355484140097326</v>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.01112652294860106</v>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
         <v>0.594086021505376</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>4.241385833751375</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>2887.955652365237</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>107.049504950495</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>14276424.42684269</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14202165.16611661</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>74259.26072607259</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0.9745705628087887</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0.1262673180421449</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>3.751278317299032e-05</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.01112652294860106</v>
       </c>
       <c r="S13" t="n">
         <v>0.000185442049143351</v>
@@ -1367,40 +1367,40 @@
       <c r="E14" t="n">
         <v>0.6164504498789397</v>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.02097258358166011</v>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
         <v>0.618279569892473</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>7.474426621246558</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1763.589442794279</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>39.41089108910891</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3349533.576637992</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3302421.489675197</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>47112.08696279464</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0.9339048285192524</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0.08247461392244296</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>0.0001840406838069932</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.02097258358166011</v>
       </c>
       <c r="S14" t="n">
         <v>0.0003495430596943351</v>
@@ -1436,40 +1436,40 @@
       <c r="E15" t="n">
         <v>0.4696895205744764</v>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.02414155383854575</v>
+      </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>3.570143280528054</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>1167.338748074809</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>112.0616061606161</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>5543624.597359739</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>5487669.762376238</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>55954.83498349835</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>0.9057792630165156</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>0.1315604119129374</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>8.472606907729202e-05</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.02414155383854575</v>
       </c>
       <c r="S15" t="n">
         <v>0.0004023592306424291</v>
@@ -1505,40 +1505,40 @@
       <c r="E16" t="n">
         <v>0.4305203524444174</v>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.01069344533174493</v>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
         <v>0.618279569892473</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.2380768615165014</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>2415.612587458747</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>138.1430143014302</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>24183653.94004401</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>24067169.90924092</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>116484.0308030803</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>0.9898479195143476</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>1.808325049742717</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>1.780212177662487e-05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.01069344533174493</v>
       </c>
       <c r="S16" t="n">
         <v>0.0001782240888624156</v>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coding Agents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +548,7 @@
         <v>0.482993172759088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02639291776320254</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -556,109 +556,105 @@
         <v>0.545698924731183</v>
       </c>
       <c r="J2" t="n">
-        <v>3.451835432645762</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K2" t="n">
-        <v>1098.006314631462</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L2" t="n">
-        <v>187.3635863586358</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M2" t="n">
-        <v>16229406.25687568</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N2" t="n">
-        <v>16083805.39493949</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O2" t="n">
-        <v>145600.8619361936</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9661540316569817</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1399235804207744</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R2" t="n">
-        <v>2.976037232135126e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004398819627200423</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T2" t="n">
-        <v>7.146758230405675</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U2" t="n">
-        <v>14780.79501056691</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.513440860215054</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08278622901034095</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K3" t="n">
-        <v>1097.040440044003</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L3" t="n">
-        <v>121.6666666666667</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M3" t="n">
-        <v>15350225.29922993</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N3" t="n">
-        <v>15269826.30913091</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O3" t="n">
-        <v>80398.9900990099</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.679821517527231</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T3" t="n">
-        <v>0.213683362977567</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U3" t="n">
-        <v>13992.39694264526</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="4">
@@ -669,7 +665,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -679,116 +675,120 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.588884131062264</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.594086021505376</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J4" t="n">
-        <v>4.536492777821779</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K4" t="n">
-        <v>1481.89598019802</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L4" t="n">
-        <v>78.55115511551155</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M4" t="n">
-        <v>6074134.495049492</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N4" t="n">
-        <v>6017554.665016501</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O4" t="n">
-        <v>56579.83003300329</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R4" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T4" t="n">
-        <v>7.703540541394086</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U4" t="n">
-        <v>4098.893968413241</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>GPT-5.6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01722625087550708</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.658602150537635</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J5" t="n">
-        <v>7.89717336090483</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K5" t="n">
-        <v>2148.438056655663</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L5" t="n">
-        <v>99.53685368536854</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M5" t="n">
-        <v>9691739.689768959</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N5" t="n">
-        <v>9590695.989548955</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O5" t="n">
-        <v>101043.700220022</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9585129825583554</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07810713036821931</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R5" t="n">
-        <v>6.364446105499215e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002871041812584513</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T5" t="n">
-        <v>12.80292843029458</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U5" t="n">
-        <v>4511.063123158167</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="6">
@@ -799,7 +799,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -809,607 +809,607 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.54559127289644</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.540322580645161</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J6" t="n">
-        <v>6.579795483718375</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K6" t="n">
-        <v>1237.696445544555</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L6" t="n">
-        <v>116.3949394939494</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M6" t="n">
-        <v>10170136.63256324</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N6" t="n">
-        <v>10120981.25467547</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O6" t="n">
-        <v>49155.37788778878</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08291918407593353</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R6" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T6" t="n">
-        <v>12.05993535928003</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U6" t="n">
-        <v>8216.987831849709</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.647849462365591</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J7" t="n">
-        <v>12.38809237513753</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K7" t="n">
-        <v>2089.900125412543</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L7" t="n">
-        <v>36.65676567656766</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M7" t="n">
-        <v>5715253.85918592</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N7" t="n">
-        <v>5581622.259625964</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O7" t="n">
-        <v>133631.599559956</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001088709227809481</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T7" t="n">
-        <v>19.90934652274569</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U7" t="n">
-        <v>2734.701907373559</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.519259105470924</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.661290322580645</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J8" t="n">
-        <v>5.047195443300332</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K8" t="n">
-        <v>3689.344194719472</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L8" t="n">
-        <v>173.3602860286028</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M8" t="n">
-        <v>8481121.533553353</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N8" t="n">
-        <v>8387890.666666667</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O8" t="n">
-        <v>93230.86688668867</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R8" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T8" t="n">
-        <v>9.719994103373407</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U8" t="n">
-        <v>2298.815476661763</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>3.977504096947204</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K9" t="n">
-        <v>1106.853353135313</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L9" t="n">
-        <v>185.2381738173817</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M9" t="n">
-        <v>16709444.57370737</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N9" t="n">
-        <v>16445971.06820682</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O9" t="n">
-        <v>263473.5055005501</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R9" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T9" t="n">
-        <v>7.32468488284717</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U9" t="n">
-        <v>15096.34905687875</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.451612903225807</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J10" t="n">
-        <v>2.467392200412544</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K10" t="n">
-        <v>702.7110253025301</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L10" t="n">
-        <v>188.4884488448845</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M10" t="n">
-        <v>13511073.15511551</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N10" t="n">
-        <v>13395246.74862486</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O10" t="n">
-        <v>115826.4064906491</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R10" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T10" t="n">
-        <v>5.893947035417844</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U10" t="n">
-        <v>19227.06869342024</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006858597906636284</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.620967741935484</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J11" t="n">
-        <v>3.488442380612681</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K11" t="n">
-        <v>3784.910298129812</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L11" t="n">
-        <v>110.1898874502835</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M11" t="n">
-        <v>8723306.44030633</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N11" t="n">
-        <v>8616277.132021666</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O11" t="n">
-        <v>107029.3082846746</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9507585357339288</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1240246840625758</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R11" t="n">
-        <v>4.959735933692525e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0001143099651106047</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T11" t="n">
-        <v>8.062911085469544</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U11" t="n">
-        <v>2304.759096831611</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01426406965584376</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.620967741935484</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J12" t="n">
-        <v>10.78915469925741</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K12" t="n">
-        <v>2512.313893839384</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L12" t="n">
-        <v>151.9246424642464</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M12" t="n">
-        <v>11352813.1688669</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N12" t="n">
-        <v>11216237.69361936</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O12" t="n">
-        <v>136575.4752475248</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9698121456131864</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R12" t="n">
-        <v>5.260931049428126e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002377344942640626</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T12" t="n">
-        <v>18.06430758687328</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U12" t="n">
-        <v>4518.867326533482</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.594086021505376</v>
+        <v>0.647849462365591</v>
       </c>
       <c r="J13" t="n">
-        <v>4.241385833751375</v>
+        <v>12.38809237513753</v>
       </c>
       <c r="K13" t="n">
-        <v>2887.955652365237</v>
+        <v>2089.900125412543</v>
       </c>
       <c r="L13" t="n">
-        <v>107.049504950495</v>
+        <v>36.65676567656766</v>
       </c>
       <c r="M13" t="n">
-        <v>14276424.42684269</v>
+        <v>5715253.85918592</v>
       </c>
       <c r="N13" t="n">
-        <v>14202165.16611661</v>
+        <v>5581622.259625964</v>
       </c>
       <c r="O13" t="n">
-        <v>74259.26072607259</v>
+        <v>133631.599559956</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9159555838702423</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.05022766562717351</v>
       </c>
       <c r="R13" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>0.0001088709227809481</v>
       </c>
       <c r="S13" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.0002977295201865781</v>
       </c>
       <c r="T13" t="n">
-        <v>7.919705712496602</v>
+        <v>19.90934652274569</v>
       </c>
       <c r="U13" t="n">
-        <v>4943.436169163572</v>
+        <v>2734.701907373559</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02097258358166011</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.618279569892473</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J14" t="n">
-        <v>7.474426621246558</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K14" t="n">
-        <v>1763.589442794279</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L14" t="n">
-        <v>39.41089108910891</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M14" t="n">
-        <v>3349533.576637992</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N14" t="n">
-        <v>3302421.489675197</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O14" t="n">
-        <v>47112.08696279464</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9339048285192524</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.08247461392244296</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0001840406838069932</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003495430596943351</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T14" t="n">
-        <v>12.12494308782548</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U14" t="n">
-        <v>1899.270598564539</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="15">
@@ -1506,7 +1506,7 @@
         <v>0.4305203524444174</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01069344533174493</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -1514,40 +1514,40 @@
         <v>0.618279569892473</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2380768615165014</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K16" t="n">
-        <v>2415.612587458747</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L16" t="n">
-        <v>138.1430143014302</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M16" t="n">
-        <v>24183653.94004401</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N16" t="n">
-        <v>24067169.90924092</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O16" t="n">
-        <v>116484.0308030803</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9898479195143476</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.808325049742717</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R16" t="n">
-        <v>1.780212177662487e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0001782240888624156</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5529979248710164</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U16" t="n">
-        <v>10011.39589419241</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,131 +595,139 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.594086021505376</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J3" t="n">
-        <v>4.536492777821779</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K3" t="n">
-        <v>1481.89598019802</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L3" t="n">
-        <v>78.55115511551155</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M3" t="n">
-        <v>6074134.495049492</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N3" t="n">
-        <v>6017554.665016501</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O3" t="n">
-        <v>56579.83003300329</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1298104416568739</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R3" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T3" t="n">
-        <v>7.703540541394086</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U3" t="n">
-        <v>4098.893968413241</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Opus 5 (max)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.658602150537635</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J4" t="n">
-        <v>7.897126985217273</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K4" t="n">
-        <v>2146.992089658964</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L4" t="n">
-        <v>99.53135313531354</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M4" t="n">
-        <v>9691548.173817372</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N4" t="n">
-        <v>9590504.44719472</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O4" t="n">
-        <v>101043.7266226623</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R4" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T4" t="n">
-        <v>12.802853245848</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U4" t="n">
-        <v>4514.012054584146</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="5">
@@ -794,760 +802,1097 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.513440860215054</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08506419165060494</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K6" t="n">
-        <v>1097.040440044003</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L6" t="n">
-        <v>121.6666666666667</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M6" t="n">
-        <v>15350225.29922993</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N6" t="n">
-        <v>15269826.30913091</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O6" t="n">
-        <v>80398.9900990099</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.554499000811647</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R6" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2195631176605357</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U6" t="n">
-        <v>13992.39694264526</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J7" t="n">
-        <v>3.977504096947204</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K7" t="n">
-        <v>1106.853353135313</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L7" t="n">
-        <v>185.2381738173817</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M7" t="n">
-        <v>16709444.57370737</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N7" t="n">
-        <v>16445971.06820682</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O7" t="n">
-        <v>263473.5055005501</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R7" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T7" t="n">
-        <v>7.32468488284717</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U7" t="n">
-        <v>15096.34905687875</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.451612903225807</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J8" t="n">
-        <v>2.467392200412544</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K8" t="n">
-        <v>702.7110253025301</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L8" t="n">
-        <v>188.4884488448845</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M8" t="n">
-        <v>13511073.15511551</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N8" t="n">
-        <v>13395246.74862486</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O8" t="n">
-        <v>115826.4064906491</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R8" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T8" t="n">
-        <v>5.893947035417844</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U8" t="n">
-        <v>19227.06869342024</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J9" t="n">
-        <v>3.478965577837015</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K9" t="n">
-        <v>3784.416073707372</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L9" t="n">
-        <v>110.0367013624439</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M9" t="n">
-        <v>8706893.798112892</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N9" t="n">
-        <v>8600561.252779894</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O9" t="n">
-        <v>106332.5453329948</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1243625308862589</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R9" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T9" t="n">
-        <v>8.041007149609982</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U9" t="n">
-        <v>2300.723183849934</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.620967741935484</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J10" t="n">
-        <v>10.78915469925741</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K10" t="n">
-        <v>2515.540235973597</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L10" t="n">
-        <v>152.1303630363036</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M10" t="n">
-        <v>11374850.48899891</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N10" t="n">
-        <v>11238194.40979098</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O10" t="n">
-        <v>136656.0792079208</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.05535778192387877</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R10" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T10" t="n">
-        <v>18.06430758687328</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U10" t="n">
-        <v>4521.832060697078</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.618279569892473</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J11" t="n">
-        <v>7.46709735138597</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K11" t="n">
-        <v>1762.03302640264</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L11" t="n">
-        <v>39.37843784378438</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M11" t="n">
-        <v>3346611.012209417</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N11" t="n">
-        <v>3299549.915435806</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O11" t="n">
-        <v>47061.09677361179</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001842014048331127</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T11" t="n">
-        <v>12.11305361664085</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U11" t="n">
-        <v>1899.289605849129</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.519259105470924</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.661290322580645</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>5.047195443300332</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K12" t="n">
-        <v>3689.344194719472</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L12" t="n">
-        <v>173.3602860286028</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M12" t="n">
-        <v>8481121.533553353</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N12" t="n">
-        <v>8387890.666666667</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O12" t="n">
-        <v>93230.86688668867</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R12" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T12" t="n">
-        <v>9.719994103373407</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U12" t="n">
-        <v>2298.815476661763</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.647849462365591</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J13" t="n">
-        <v>12.38809237513753</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K13" t="n">
-        <v>2089.900125412543</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L13" t="n">
-        <v>36.65676567656766</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M13" t="n">
-        <v>5715253.85918592</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N13" t="n">
-        <v>5581622.259625964</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O13" t="n">
-        <v>133631.599559956</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001088709227809481</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T13" t="n">
-        <v>19.90934652274569</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U13" t="n">
-        <v>2734.701907373559</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.594086021505376</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J14" t="n">
-        <v>4.241385833751375</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K14" t="n">
-        <v>2887.955652365237</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L14" t="n">
-        <v>107.049504950495</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M14" t="n">
-        <v>14276424.42684269</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N14" t="n">
-        <v>14202165.16611661</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O14" t="n">
-        <v>74259.26072607259</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R14" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S14" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T14" t="n">
-        <v>7.919705712496602</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U14" t="n">
-        <v>4943.436169163572</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.583333333333333</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J15" t="n">
-        <v>3.570143280528054</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K15" t="n">
-        <v>1167.338748074809</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L15" t="n">
-        <v>112.0616061606161</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M15" t="n">
-        <v>5543624.597359739</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N15" t="n">
-        <v>5487669.762376238</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O15" t="n">
-        <v>55954.83498349835</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R15" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T15" t="n">
-        <v>7.601070758745943</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U15" t="n">
-        <v>4748.942504052369</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.618279569892473</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2380461072079206</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K16" t="n">
-        <v>2417.550009900991</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L16" t="n">
-        <v>138.1463146314632</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M16" t="n">
-        <v>24180108.02805281</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N16" t="n">
-        <v>24063625.6270627</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O16" t="n">
-        <v>116482.400990099</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.808558675855097</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R16" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5529264896684616</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U16" t="n">
-        <v>10001.90603256356</v>
+        <v>19227.06869342024</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Muse Code</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Muse Spark 1.3 (max)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5430273329930766</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.02943627526383025</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0.594086021505376</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.977504096947204</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1106.853353135313</v>
+      </c>
+      <c r="L17" t="n">
+        <v>185.2381738173817</v>
+      </c>
+      <c r="M17" t="n">
+        <v>16709444.57370737</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16445971.06820682</v>
+      </c>
+      <c r="O17" t="n">
+        <v>263473.5055005501</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9712826195905685</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1365246445402428</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.24982276100033e-05</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.0004906045877305042</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.32468488284717</v>
+      </c>
+      <c r="U17" t="n">
+        <v>15096.34905687875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Grok 4.7 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5626764360706693</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01433955552408987</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0.629032258064516</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.817468730473037</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2354.367686468646</v>
+      </c>
+      <c r="L18" t="n">
+        <v>162.6457645764577</v>
+      </c>
+      <c r="M18" t="n">
+        <v>14324724.28382839</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14201447.9559956</v>
+      </c>
+      <c r="O18" t="n">
+        <v>123276.3278327833</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.938882976190201</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.06381382835258244</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.928008839275821e-05</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.0002389925920681645</v>
+      </c>
+      <c r="T18" t="n">
+        <v>15.67058466504826</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6084.319100265209</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fable 5.1 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6222249615769457</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01786377121119468</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O19" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T19" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13.03638341842683</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3867.092341034102</v>
+      </c>
+      <c r="L20" t="n">
+        <v>155.0957095709571</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15551383.220022</v>
+      </c>
+      <c r="N20" t="n">
+        <v>15218206.4180418</v>
+      </c>
+      <c r="O20" t="n">
+        <v>333176.801980198</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9500106599458848</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.05061877833513936</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.243261150555715e-05</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.0001706413357517016</v>
+      </c>
+      <c r="T20" t="n">
+        <v>19.75551431484872</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4021.466737425617</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Opencode</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GLM-5.3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Opencode</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>zai</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5355484140097326</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.01112652294860106</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>0.594086021505376</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.241385833751375</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2887.955652365237</v>
+      </c>
+      <c r="L21" t="n">
+        <v>107.049504950495</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14276424.42684269</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14202165.16611661</v>
+      </c>
+      <c r="O21" t="n">
+        <v>74259.26072607259</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9745705628087887</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1262673180421449</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.751278317299032e-05</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.000185442049143351</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.919705712496602</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4943.436169163572</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -614,664 +614,664 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.618279569892473</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K3" t="n">
-        <v>2417.550009900991</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L3" t="n">
-        <v>138.1463146314632</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>24180108.02805281</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N3" t="n">
-        <v>24063625.6270627</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O3" t="n">
-        <v>116482.400990099</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.808558675855097</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R3" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5529264896684616</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U3" t="n">
-        <v>10001.90603256356</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J4" t="n">
-        <v>10.78915469925741</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K4" t="n">
-        <v>2515.540235973597</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L4" t="n">
-        <v>152.1303630363036</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M4" t="n">
-        <v>11374850.48899891</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N4" t="n">
-        <v>11238194.40979098</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O4" t="n">
-        <v>136656.0792079208</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05535778192387877</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R4" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T4" t="n">
-        <v>18.06430758687328</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U4" t="n">
-        <v>4521.832060697078</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.54559127289644</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.540322580645161</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J5" t="n">
-        <v>6.353318230693071</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K5" t="n">
-        <v>1237.696445544555</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L5" t="n">
-        <v>116.3949394939494</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M5" t="n">
-        <v>10170136.63256324</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N5" t="n">
-        <v>10120981.25467547</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O5" t="n">
-        <v>49155.37788778878</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R5" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T5" t="n">
-        <v>11.64483111499294</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U5" t="n">
-        <v>8216.987831849709</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.658602150537635</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J6" t="n">
-        <v>7.897126985217273</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K6" t="n">
-        <v>2146.992089658964</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L6" t="n">
-        <v>99.53135313531354</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M6" t="n">
-        <v>9691548.173817372</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N6" t="n">
-        <v>9590504.44719472</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O6" t="n">
-        <v>101043.7266226623</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R6" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T6" t="n">
-        <v>12.802853245848</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U6" t="n">
-        <v>4514.012054584146</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J7" t="n">
-        <v>3.478965577837015</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K7" t="n">
-        <v>3784.416073707372</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L7" t="n">
-        <v>110.0367013624439</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M7" t="n">
-        <v>8706893.798112892</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N7" t="n">
-        <v>8600561.252779894</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O7" t="n">
-        <v>106332.5453329948</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R7" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T7" t="n">
-        <v>8.041007149609982</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U7" t="n">
-        <v>2300.723183849934</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>GPT-5.6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.588884131062264</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.594086021505376</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J8" t="n">
-        <v>4.536492777821779</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K8" t="n">
-        <v>1481.89598019802</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L8" t="n">
-        <v>78.55115511551155</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M8" t="n">
-        <v>6074134.495049492</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N8" t="n">
-        <v>6017554.665016501</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O8" t="n">
-        <v>56579.83003300329</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R8" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T8" t="n">
-        <v>7.703540541394086</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U8" t="n">
-        <v>4098.893968413241</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.443548387096774</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1759117230445546</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K9" t="n">
-        <v>1285.926851485148</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L9" t="n">
-        <v>88.64301430143014</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M9" t="n">
-        <v>10218069.24807481</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N9" t="n">
-        <v>10119727.86413641</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O9" t="n">
-        <v>98341.38393839383</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.334943267525058</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R9" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4282759302584503</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U9" t="n">
-        <v>7946.073477098422</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.513440860215054</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08506419165060494</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K10" t="n">
-        <v>1097.040440044003</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L10" t="n">
-        <v>121.6666666666667</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M10" t="n">
-        <v>15350225.29922993</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N10" t="n">
-        <v>15269826.30913091</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O10" t="n">
-        <v>80398.9900990099</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.554499000811647</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R10" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2195631176605357</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U10" t="n">
-        <v>13992.39694264526</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.519259105470924</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.661290322580645</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>5.047195443300332</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K11" t="n">
-        <v>3689.344194719472</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L11" t="n">
-        <v>173.3602860286028</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M11" t="n">
-        <v>8481121.533553353</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N11" t="n">
-        <v>8387890.666666667</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O11" t="n">
-        <v>93230.86688668867</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R11" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T11" t="n">
-        <v>9.719994103373407</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U11" t="n">
-        <v>2298.815476661763</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.583333333333333</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J12" t="n">
-        <v>3.570143280528054</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K12" t="n">
-        <v>1167.338748074809</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L12" t="n">
-        <v>112.0616061606161</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M12" t="n">
-        <v>5543624.597359739</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N12" t="n">
-        <v>5487669.762376238</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O12" t="n">
-        <v>55954.83498349835</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R12" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T12" t="n">
-        <v>7.601070758745943</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U12" t="n">
-        <v>4748.942504052369</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="13">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1292,193 +1292,193 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.486559139784946</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4380225639383938</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K13" t="n">
-        <v>1412.260883388339</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L13" t="n">
-        <v>121.5137513751375</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M13" t="n">
-        <v>14854524.53905389</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N13" t="n">
-        <v>14783219.74807481</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O13" t="n">
-        <v>71304.79097909792</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P13" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9868141561395799</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R13" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T13" t="n">
-        <v>1.013362033548448</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U13" t="n">
-        <v>10518.2581446386</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.618279569892473</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J14" t="n">
-        <v>7.46709735138597</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K14" t="n">
-        <v>1762.03302640264</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L14" t="n">
-        <v>39.37843784378438</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M14" t="n">
-        <v>3346611.012209417</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N14" t="n">
-        <v>3299549.915435806</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O14" t="n">
-        <v>47061.09677361179</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0001842014048331127</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T14" t="n">
-        <v>12.11305361664085</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U14" t="n">
-        <v>1899.289605849129</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.575268817204301</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J15" t="n">
-        <v>2.989729004180416</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K15" t="n">
-        <v>1338.052705170518</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L15" t="n">
-        <v>86.55005500550054</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M15" t="n">
-        <v>9840777.763476355</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N15" t="n">
-        <v>9778602.140814083</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O15" t="n">
-        <v>62175.62266226623</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R15" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T15" t="n">
-        <v>5.276371829924331</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U15" t="n">
-        <v>7354.551674571196</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="16">
@@ -1553,139 +1553,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.594086021505376</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J17" t="n">
-        <v>3.977504096947204</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K17" t="n">
-        <v>1106.853353135313</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L17" t="n">
-        <v>185.2381738173817</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M17" t="n">
-        <v>16709444.57370737</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N17" t="n">
-        <v>16445971.06820682</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O17" t="n">
-        <v>263473.5055005501</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R17" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T17" t="n">
-        <v>7.32468488284717</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U17" t="n">
-        <v>15096.34905687875</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J18" t="n">
-        <v>8.817468730473037</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K18" t="n">
-        <v>2354.367686468646</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L18" t="n">
-        <v>162.6457645764577</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M18" t="n">
-        <v>14324724.28382839</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N18" t="n">
-        <v>14201447.9559956</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O18" t="n">
-        <v>123276.3278327833</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P18" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R18" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T18" t="n">
-        <v>15.67058466504826</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U18" t="n">
-        <v>6084.319100265209</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="19">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,70 +526,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.482993172759088</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.545698924731183</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J2" t="n">
-        <v>3.467754041474145</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K2" t="n">
-        <v>1098.202911991198</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L2" t="n">
-        <v>187.4895489548955</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>16237094.3520352</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N2" t="n">
-        <v>16091465.1039604</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O2" t="n">
-        <v>145629.2480748075</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1392812659094378</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R2" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T2" t="n">
-        <v>7.179716478526343</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U2" t="n">
-        <v>14785.14960645573</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -610,530 +610,530 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.513440860215054</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08506419165060494</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K3" t="n">
-        <v>1097.040440044003</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L3" t="n">
-        <v>121.6666666666667</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M3" t="n">
-        <v>15350225.29922993</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N3" t="n">
-        <v>15269826.30913091</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O3" t="n">
-        <v>80398.9900990099</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.554499000811647</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195631176605357</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U3" t="n">
-        <v>13992.39694264526</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.443548387096774</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1759117230445546</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K4" t="n">
-        <v>1285.926851485148</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L4" t="n">
-        <v>88.64301430143014</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M4" t="n">
-        <v>10218069.24807481</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N4" t="n">
-        <v>10119727.86413641</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O4" t="n">
-        <v>98341.38393839383</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R4" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U4" t="n">
-        <v>7946.073477098422</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J5" t="n">
-        <v>4.536492777821779</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K5" t="n">
-        <v>1481.89598019802</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L5" t="n">
-        <v>78.55115511551155</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M5" t="n">
-        <v>6074134.495049492</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N5" t="n">
-        <v>6017554.665016501</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O5" t="n">
-        <v>56579.83003300329</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R5" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T5" t="n">
-        <v>7.703540541394086</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U5" t="n">
-        <v>4098.893968413241</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J6" t="n">
-        <v>3.478965577837015</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K6" t="n">
-        <v>3784.416073707372</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L6" t="n">
-        <v>110.0367013624439</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M6" t="n">
-        <v>8706893.798112892</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N6" t="n">
-        <v>8600561.252779894</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O6" t="n">
-        <v>106332.5453329948</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R6" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T6" t="n">
-        <v>8.041007149609982</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U6" t="n">
-        <v>2300.723183849934</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>GPT-5.6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.658602150537635</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J7" t="n">
-        <v>7.897126985217273</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K7" t="n">
-        <v>2146.992089658964</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L7" t="n">
-        <v>99.53135313531354</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M7" t="n">
-        <v>9691548.173817372</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N7" t="n">
-        <v>9590504.44719472</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O7" t="n">
-        <v>101043.7266226623</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R7" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T7" t="n">
-        <v>12.802853245848</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U7" t="n">
-        <v>4514.012054584146</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.54559127289644</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.540322580645161</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J8" t="n">
-        <v>6.353318230693071</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K8" t="n">
-        <v>1237.696445544555</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L8" t="n">
-        <v>116.3949394939494</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M8" t="n">
-        <v>10170136.63256324</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N8" t="n">
-        <v>10120981.25467547</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O8" t="n">
-        <v>49155.37788778878</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R8" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T8" t="n">
-        <v>11.64483111499294</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U8" t="n">
-        <v>8216.987831849709</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J9" t="n">
-        <v>10.78915469925741</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K9" t="n">
-        <v>2515.540235973597</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L9" t="n">
-        <v>152.1303630363036</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M9" t="n">
-        <v>11374850.48899891</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N9" t="n">
-        <v>11238194.40979098</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O9" t="n">
-        <v>136656.0792079208</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R9" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T9" t="n">
-        <v>18.06430758687328</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U9" t="n">
-        <v>4521.832060697078</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.519259105470924</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.661290322580645</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J10" t="n">
-        <v>5.047195443300332</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K10" t="n">
-        <v>3689.344194719472</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L10" t="n">
-        <v>173.3602860286028</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M10" t="n">
-        <v>8481121.533553353</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N10" t="n">
-        <v>8387890.666666667</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O10" t="n">
-        <v>93230.86688668867</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R10" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T10" t="n">
-        <v>9.719994103373407</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U10" t="n">
-        <v>2298.815476661763</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="11">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,599 +541,599 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.513440860215054</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08506419165060494</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K2" t="n">
-        <v>1097.040440044003</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L2" t="n">
-        <v>121.6666666666667</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M2" t="n">
-        <v>15350225.29922993</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N2" t="n">
-        <v>15269826.30913091</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O2" t="n">
-        <v>80398.9900990099</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.554499000811647</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R2" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2195631176605357</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U2" t="n">
-        <v>13992.39694264526</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.443548387096774</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1759117230445546</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K3" t="n">
-        <v>1285.926851485148</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L3" t="n">
-        <v>88.64301430143014</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M3" t="n">
-        <v>10218069.24807481</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N3" t="n">
-        <v>10119727.86413641</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O3" t="n">
-        <v>98341.38393839383</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R3" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U3" t="n">
-        <v>7946.073477098422</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J4" t="n">
-        <v>4.536492777821779</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K4" t="n">
-        <v>1481.89598019802</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L4" t="n">
-        <v>78.55115511551155</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M4" t="n">
-        <v>6074134.495049492</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N4" t="n">
-        <v>6017554.665016501</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O4" t="n">
-        <v>56579.83003300329</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R4" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T4" t="n">
-        <v>7.703540541394086</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U4" t="n">
-        <v>4098.893968413241</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478965577837015</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K5" t="n">
-        <v>3784.416073707372</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L5" t="n">
-        <v>110.0367013624439</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M5" t="n">
-        <v>8706893.798112892</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N5" t="n">
-        <v>8600561.252779894</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O5" t="n">
-        <v>106332.5453329948</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R5" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T5" t="n">
-        <v>8.041007149609982</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U5" t="n">
-        <v>2300.723183849934</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>GPT-5.6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.658602150537635</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J6" t="n">
-        <v>7.897126985217273</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K6" t="n">
-        <v>2146.992089658964</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L6" t="n">
-        <v>99.53135313531354</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M6" t="n">
-        <v>9691548.173817372</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N6" t="n">
-        <v>9590504.44719472</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O6" t="n">
-        <v>101043.7266226623</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R6" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T6" t="n">
-        <v>12.802853245848</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U6" t="n">
-        <v>4514.012054584146</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.54559127289644</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.540322580645161</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J7" t="n">
-        <v>6.353318230693071</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K7" t="n">
-        <v>1237.696445544555</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L7" t="n">
-        <v>116.3949394939494</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M7" t="n">
-        <v>10170136.63256324</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N7" t="n">
-        <v>10120981.25467547</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O7" t="n">
-        <v>49155.37788778878</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R7" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T7" t="n">
-        <v>11.64483111499294</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U7" t="n">
-        <v>8216.987831849709</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.620967741935484</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J8" t="n">
-        <v>10.78915469925741</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K8" t="n">
-        <v>2515.540235973597</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L8" t="n">
-        <v>152.1303630363036</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>11374850.48899891</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N8" t="n">
-        <v>11238194.40979098</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O8" t="n">
-        <v>136656.0792079208</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05535778192387877</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R8" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T8" t="n">
-        <v>18.06430758687328</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U8" t="n">
-        <v>4521.832060697078</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.519259105470924</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.661290322580645</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J9" t="n">
-        <v>5.047195443300332</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K9" t="n">
-        <v>3689.344194719472</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L9" t="n">
-        <v>173.3602860286028</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M9" t="n">
-        <v>8481121.533553353</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N9" t="n">
-        <v>8387890.666666667</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O9" t="n">
-        <v>93230.86688668867</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R9" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T9" t="n">
-        <v>9.719994103373407</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U9" t="n">
-        <v>2298.815476661763</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.482993172759088</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.545698924731183</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J10" t="n">
-        <v>3.467754041474145</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K10" t="n">
-        <v>1098.202911991198</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L10" t="n">
-        <v>187.4895489548955</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M10" t="n">
-        <v>16237094.3520352</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N10" t="n">
-        <v>16091465.1039604</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O10" t="n">
-        <v>145629.2480748075</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R10" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T10" t="n">
-        <v>7.179716478526343</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U10" t="n">
-        <v>14785.14960645573</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="11">
@@ -1256,7 +1256,7 @@
         <v>71304.79097909792</v>
       </c>
       <c r="P12" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9718803286808345</v>
       </c>
       <c r="Q12" t="n">
         <v>0.9868141561395799</v>
@@ -1346,208 +1346,208 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.629032258064516</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J14" t="n">
-        <v>8.817468730473037</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K14" t="n">
-        <v>2354.367686468646</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L14" t="n">
-        <v>162.6457645764577</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M14" t="n">
-        <v>14324724.28382839</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N14" t="n">
-        <v>14201447.9559956</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O14" t="n">
-        <v>123276.3278327833</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P14" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R14" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T14" t="n">
-        <v>15.67058466504826</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U14" t="n">
-        <v>6084.319100265209</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.594086021505376</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J15" t="n">
-        <v>3.977504096947204</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K15" t="n">
-        <v>1106.853353135313</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L15" t="n">
-        <v>185.2381738173817</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M15" t="n">
-        <v>16709444.57370737</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N15" t="n">
-        <v>16445971.06820682</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O15" t="n">
-        <v>263473.5055005501</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R15" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T15" t="n">
-        <v>7.32468488284717</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U15" t="n">
-        <v>15096.34905687875</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.451612903225807</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J16" t="n">
-        <v>2.467392200412544</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K16" t="n">
-        <v>702.7110253025301</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L16" t="n">
-        <v>188.4884488448845</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M16" t="n">
-        <v>13511073.15511551</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N16" t="n">
-        <v>13395246.74862486</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O16" t="n">
-        <v>115826.4064906491</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R16" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T16" t="n">
-        <v>5.893947035417844</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U16" t="n">
-        <v>19227.06869342024</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="17">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,120 +1572,120 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.575268817204301</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J17" t="n">
-        <v>2.989729004180416</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K17" t="n">
-        <v>1338.052705170518</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L17" t="n">
-        <v>86.55005500550054</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M17" t="n">
-        <v>9840777.763476355</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N17" t="n">
-        <v>9778602.140814083</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O17" t="n">
-        <v>62175.62266226623</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.18952417157726</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R17" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T17" t="n">
-        <v>5.276371829924331</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U17" t="n">
-        <v>7354.551674571196</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.618279569892473</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J18" t="n">
-        <v>7.46709735138597</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K18" t="n">
-        <v>1762.03302640264</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L18" t="n">
-        <v>39.37843784378438</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M18" t="n">
-        <v>3346611.012209417</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N18" t="n">
-        <v>3299549.915435806</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O18" t="n">
-        <v>47061.09677361179</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0001842014048331127</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T18" t="n">
-        <v>12.11305361664085</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U18" t="n">
-        <v>1899.289605849129</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="19">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,461 +541,461 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.443548387096774</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1759117230445546</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K2" t="n">
-        <v>1285.926851485148</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L2" t="n">
-        <v>88.64301430143014</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>10218069.24807481</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N2" t="n">
-        <v>10119727.86413641</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O2" t="n">
-        <v>98341.38393839383</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.334943267525058</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R2" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4282759302584503</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U2" t="n">
-        <v>7946.073477098422</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>GPT-6 Luna (max)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.594086021505376</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J3" t="n">
-        <v>4.536492777821779</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K3" t="n">
-        <v>1481.89598019802</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L3" t="n">
-        <v>78.55115511551155</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M3" t="n">
-        <v>6074134.495049492</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N3" t="n">
-        <v>6017554.665016501</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O3" t="n">
-        <v>56579.83003300329</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1298104416568739</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R3" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T3" t="n">
-        <v>7.703540541394086</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U3" t="n">
-        <v>4098.893968413241</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.620967741935484</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J4" t="n">
-        <v>3.478965577837015</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K4" t="n">
-        <v>3784.416073707372</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L4" t="n">
-        <v>110.0367013624439</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M4" t="n">
-        <v>8706893.798112892</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N4" t="n">
-        <v>8600561.252779894</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O4" t="n">
-        <v>106332.5453329948</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R4" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T4" t="n">
-        <v>8.041007149609982</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U4" t="n">
-        <v>2300.723183849934</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.658602150537635</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J5" t="n">
-        <v>7.897126985217273</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K5" t="n">
-        <v>2146.992089658964</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L5" t="n">
-        <v>99.53135313531354</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M5" t="n">
-        <v>9691548.173817372</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N5" t="n">
-        <v>9590504.44719472</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O5" t="n">
-        <v>101043.7266226623</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R5" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T5" t="n">
-        <v>12.802853245848</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U5" t="n">
-        <v>4514.012054584146</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.54559127289644</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.540322580645161</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J6" t="n">
-        <v>6.353318230693071</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K6" t="n">
-        <v>1237.696445544555</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L6" t="n">
-        <v>116.3949394939494</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M6" t="n">
-        <v>10170136.63256324</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N6" t="n">
-        <v>10120981.25467547</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O6" t="n">
-        <v>49155.37788778878</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R6" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T6" t="n">
-        <v>11.64483111499294</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U6" t="n">
-        <v>8216.987831849709</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.620967741935484</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J7" t="n">
-        <v>10.78915469925741</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K7" t="n">
-        <v>2515.540235973597</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L7" t="n">
-        <v>152.1303630363036</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M7" t="n">
-        <v>11374850.48899891</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N7" t="n">
-        <v>11238194.40979098</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O7" t="n">
-        <v>136656.0792079208</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R7" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T7" t="n">
-        <v>18.06430758687328</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U7" t="n">
-        <v>4521.832060697078</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.513440860215054</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08506419165060494</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K8" t="n">
-        <v>1097.040440044003</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L8" t="n">
-        <v>121.6666666666667</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M8" t="n">
-        <v>15350225.29922993</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N8" t="n">
-        <v>15269826.30913091</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O8" t="n">
-        <v>80398.9900990099</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.554499000811647</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R8" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2195631176605357</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U8" t="n">
-        <v>13992.39694264526</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="9">
@@ -1256,7 +1256,7 @@
         <v>71304.79097909792</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q12" t="n">
         <v>0.9868141561395799</v>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,461 +541,461 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.513440860215054</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08506419165060494</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K2" t="n">
-        <v>1097.040440044003</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L2" t="n">
-        <v>121.6666666666667</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M2" t="n">
-        <v>15350225.29922993</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N2" t="n">
-        <v>15269826.30913091</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O2" t="n">
-        <v>80398.9900990099</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.554499000811647</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R2" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2195631176605357</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U2" t="n">
-        <v>13992.39694264526</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.443548387096774</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1759117230445546</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K3" t="n">
-        <v>1285.926851485148</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L3" t="n">
-        <v>88.64301430143014</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M3" t="n">
-        <v>10218069.24807481</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N3" t="n">
-        <v>10119727.86413641</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O3" t="n">
-        <v>98341.38393839383</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R3" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U3" t="n">
-        <v>7946.073477098422</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J4" t="n">
-        <v>4.536492777821779</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K4" t="n">
-        <v>1481.89598019802</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L4" t="n">
-        <v>78.55115511551155</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M4" t="n">
-        <v>6074134.495049492</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N4" t="n">
-        <v>6017554.665016501</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O4" t="n">
-        <v>56579.83003300329</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R4" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T4" t="n">
-        <v>7.703540541394086</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U4" t="n">
-        <v>4098.893968413241</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478965577837015</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K5" t="n">
-        <v>3784.416073707372</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L5" t="n">
-        <v>110.0367013624439</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M5" t="n">
-        <v>8706893.798112892</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N5" t="n">
-        <v>8600561.252779894</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O5" t="n">
-        <v>106332.5453329948</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R5" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T5" t="n">
-        <v>8.041007149609982</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U5" t="n">
-        <v>2300.723183849934</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>GPT-5.6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.658602150537635</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J6" t="n">
-        <v>7.897126985217273</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K6" t="n">
-        <v>2146.992089658964</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L6" t="n">
-        <v>99.53135313531354</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M6" t="n">
-        <v>9691548.173817372</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N6" t="n">
-        <v>9590504.44719472</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O6" t="n">
-        <v>101043.7266226623</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R6" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T6" t="n">
-        <v>12.802853245848</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U6" t="n">
-        <v>4514.012054584146</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.54559127289644</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.540322580645161</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J7" t="n">
-        <v>6.353318230693071</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K7" t="n">
-        <v>1237.696445544555</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L7" t="n">
-        <v>116.3949394939494</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M7" t="n">
-        <v>10170136.63256324</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N7" t="n">
-        <v>10120981.25467547</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O7" t="n">
-        <v>49155.37788778878</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R7" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T7" t="n">
-        <v>11.64483111499294</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U7" t="n">
-        <v>8216.987831849709</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.620967741935484</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J8" t="n">
-        <v>10.78915469925741</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K8" t="n">
-        <v>2515.540235973597</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L8" t="n">
-        <v>152.1303630363036</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>11374850.48899891</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N8" t="n">
-        <v>11238194.40979098</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O8" t="n">
-        <v>136656.0792079208</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05535778192387877</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R8" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T8" t="n">
-        <v>18.06430758687328</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U8" t="n">
-        <v>4521.832060697078</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="9">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,683 +526,683 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.443548387096774</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1759117230445546</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K2" t="n">
-        <v>1285.926851485148</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L2" t="n">
-        <v>88.64301430143014</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M2" t="n">
-        <v>10218069.24807481</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N2" t="n">
-        <v>10119727.86413641</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O2" t="n">
-        <v>98341.38393839383</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R2" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U2" t="n">
-        <v>7946.073477098422</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J3" t="n">
-        <v>4.536492777821779</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K3" t="n">
-        <v>1481.89598019802</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L3" t="n">
-        <v>78.55115511551155</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M3" t="n">
-        <v>6074134.495049492</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N3" t="n">
-        <v>6017554.665016501</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O3" t="n">
-        <v>56579.83003300329</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R3" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T3" t="n">
-        <v>7.703540541394086</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U3" t="n">
-        <v>4098.893968413241</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.620967741935484</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J4" t="n">
-        <v>3.478965577837015</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K4" t="n">
-        <v>3784.416073707372</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L4" t="n">
-        <v>110.0367013624439</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M4" t="n">
-        <v>8706893.798112892</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N4" t="n">
-        <v>8600561.252779894</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O4" t="n">
-        <v>106332.5453329948</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R4" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T4" t="n">
-        <v>8.041007149609982</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U4" t="n">
-        <v>2300.723183849934</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>GLM-5.3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Opencode</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.658602150537635</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J5" t="n">
-        <v>7.897126985217273</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K5" t="n">
-        <v>2146.992089658964</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L5" t="n">
-        <v>99.53135313531354</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M5" t="n">
-        <v>9691548.173817372</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N5" t="n">
-        <v>9590504.44719472</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O5" t="n">
-        <v>101043.7266226623</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R5" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T5" t="n">
-        <v>12.802853245848</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U5" t="n">
-        <v>4514.012054584146</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.54559127289644</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.540322580645161</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J6" t="n">
-        <v>6.353318230693071</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K6" t="n">
-        <v>1237.696445544555</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L6" t="n">
-        <v>116.3949394939494</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M6" t="n">
-        <v>10170136.63256324</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N6" t="n">
-        <v>10120981.25467547</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O6" t="n">
-        <v>49155.37788778878</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R6" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T6" t="n">
-        <v>11.64483111499294</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U6" t="n">
-        <v>8216.987831849709</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.620967741935484</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J7" t="n">
-        <v>10.78915469925741</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K7" t="n">
-        <v>2515.540235973597</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L7" t="n">
-        <v>152.1303630363036</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M7" t="n">
-        <v>11374850.48899891</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N7" t="n">
-        <v>11238194.40979098</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O7" t="n">
-        <v>136656.0792079208</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05535778192387877</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R7" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T7" t="n">
-        <v>18.06430758687328</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U7" t="n">
-        <v>4521.832060697078</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.513440860215054</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08506419165060494</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K8" t="n">
-        <v>1097.040440044003</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L8" t="n">
-        <v>121.6666666666667</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M8" t="n">
-        <v>15350225.29922993</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N8" t="n">
-        <v>15269826.30913091</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O8" t="n">
-        <v>80398.9900990099</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.554499000811647</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R8" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2195631176605357</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U8" t="n">
-        <v>13992.39694264526</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.482993172759088</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.545698924731183</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>3.467754041474145</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K9" t="n">
-        <v>1098.202911991198</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L9" t="n">
-        <v>187.4895489548955</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M9" t="n">
-        <v>16237094.3520352</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N9" t="n">
-        <v>16091465.1039604</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O9" t="n">
-        <v>145629.2480748075</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R9" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T9" t="n">
-        <v>7.179716478526343</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U9" t="n">
-        <v>14785.14960645573</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.519259105470924</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.661290322580645</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J10" t="n">
-        <v>5.047195443300332</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K10" t="n">
-        <v>3689.344194719472</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L10" t="n">
-        <v>173.3602860286028</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M10" t="n">
-        <v>8481121.533553353</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N10" t="n">
-        <v>8387890.666666667</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O10" t="n">
-        <v>93230.86688668867</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1028807208486825</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R10" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T10" t="n">
-        <v>9.719994103373407</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U10" t="n">
-        <v>2298.815476661763</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.583333333333333</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J11" t="n">
-        <v>3.570143280528054</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K11" t="n">
-        <v>1167.338748074809</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L11" t="n">
-        <v>112.0616061606161</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M11" t="n">
-        <v>5543624.597359739</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N11" t="n">
-        <v>5487669.762376238</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O11" t="n">
-        <v>55954.83498349835</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R11" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T11" t="n">
-        <v>7.601070758745943</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U11" t="n">
-        <v>4748.942504052369</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="12">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1227,327 +1227,327 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.486559139784946</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4380225639383938</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K12" t="n">
-        <v>1412.260883388339</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L12" t="n">
-        <v>121.5137513751375</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M12" t="n">
-        <v>14854524.53905389</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N12" t="n">
-        <v>14783219.74807481</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O12" t="n">
-        <v>71304.79097909792</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P12" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R12" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T12" t="n">
-        <v>1.013362033548448</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U12" t="n">
-        <v>10518.2581446386</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.618279569892473</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2380461072079206</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K13" t="n">
-        <v>2417.550009900991</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L13" t="n">
-        <v>138.1463146314632</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M13" t="n">
-        <v>24180108.02805281</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N13" t="n">
-        <v>24063625.6270627</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O13" t="n">
-        <v>116482.400990099</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.808558675855097</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R13" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5529264896684616</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U13" t="n">
-        <v>10001.90603256356</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.594086021505376</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J14" t="n">
-        <v>3.977504096947204</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K14" t="n">
-        <v>1106.853353135313</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L14" t="n">
-        <v>185.2381738173817</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M14" t="n">
-        <v>16709444.57370737</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N14" t="n">
-        <v>16445971.06820682</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O14" t="n">
-        <v>263473.5055005501</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R14" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T14" t="n">
-        <v>7.32468488284717</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U14" t="n">
-        <v>15096.34905687875</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.451612903225807</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J15" t="n">
-        <v>2.467392200412544</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K15" t="n">
-        <v>702.7110253025301</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L15" t="n">
-        <v>188.4884488448845</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M15" t="n">
-        <v>13511073.15511551</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N15" t="n">
-        <v>13395246.74862486</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O15" t="n">
-        <v>115826.4064906491</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R15" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T15" t="n">
-        <v>5.893947035417844</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U15" t="n">
-        <v>19227.06869342024</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.575268817204301</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>2.989729004180416</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K16" t="n">
-        <v>1338.052705170518</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L16" t="n">
-        <v>86.55005500550054</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M16" t="n">
-        <v>9840777.763476355</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N16" t="n">
-        <v>9778602.140814083</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O16" t="n">
-        <v>62175.62266226623</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R16" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T16" t="n">
-        <v>5.276371829924331</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U16" t="n">
-        <v>7354.551674571196</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="17">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,120 +1572,120 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.618279569892473</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J17" t="n">
-        <v>7.46709735138597</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K17" t="n">
-        <v>1762.03302640264</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L17" t="n">
-        <v>39.37843784378438</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M17" t="n">
-        <v>3346611.012209417</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N17" t="n">
-        <v>3299549.915435806</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O17" t="n">
-        <v>47061.09677361179</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9718803286808345</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0001842014048331127</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T17" t="n">
-        <v>12.11305361664085</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U17" t="n">
-        <v>1899.289605849129</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J18" t="n">
-        <v>8.817468730473037</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K18" t="n">
-        <v>2354.367686468646</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L18" t="n">
-        <v>162.6457645764577</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M18" t="n">
-        <v>14324724.28382839</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N18" t="n">
-        <v>14201447.9559956</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O18" t="n">
-        <v>123276.3278327833</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P18" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.06381382835258244</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R18" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T18" t="n">
-        <v>15.67058466504826</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U18" t="n">
-        <v>6084.319100265209</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="19">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1710,51 +1710,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.647849462365591</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J19" t="n">
-        <v>12.38809237513753</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K19" t="n">
-        <v>2089.900125412543</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L19" t="n">
-        <v>36.65676567656766</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M19" t="n">
-        <v>5715253.85918592</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N19" t="n">
-        <v>5581622.259625964</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O19" t="n">
-        <v>133631.599559956</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0001088709227809481</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T19" t="n">
-        <v>19.90934652274569</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U19" t="n">
-        <v>2734.701907373559</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="20">
@@ -1829,70 +1829,415 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O21" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Grok 4.7 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5626764360706693</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.01433955552408987</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0.629032258064516</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8.817468730473037</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2354.367686468646</v>
+      </c>
+      <c r="L22" t="n">
+        <v>162.6457645764577</v>
+      </c>
+      <c r="M22" t="n">
+        <v>14324724.28382839</v>
+      </c>
+      <c r="N22" t="n">
+        <v>14201447.9559956</v>
+      </c>
+      <c r="O22" t="n">
+        <v>123276.3278327833</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.938882976190201</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.06381382835258244</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.928008839275821e-05</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.0002389925920681645</v>
+      </c>
+      <c r="T22" t="n">
+        <v>15.67058466504826</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6084.319100265209</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Muse Code</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Muse Spark 1.3 (max)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5430273329930766</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.02943627526383025</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
         <v>0.594086021505376</v>
       </c>
-      <c r="J21" t="n">
-        <v>4.241385833751375</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2887.955652365237</v>
-      </c>
-      <c r="L21" t="n">
-        <v>107.049504950495</v>
-      </c>
-      <c r="M21" t="n">
-        <v>14276424.42684269</v>
-      </c>
-      <c r="N21" t="n">
-        <v>14202165.16611661</v>
-      </c>
-      <c r="O21" t="n">
-        <v>74259.26072607259</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.9745705628087887</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.1262673180421449</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.751278317299032e-05</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.000185442049143351</v>
-      </c>
-      <c r="T21" t="n">
-        <v>7.919705712496602</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4943.436169163572</v>
+      <c r="J23" t="n">
+        <v>3.977504096947204</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1106.853353135313</v>
+      </c>
+      <c r="L23" t="n">
+        <v>185.2381738173817</v>
+      </c>
+      <c r="M23" t="n">
+        <v>16709444.57370737</v>
+      </c>
+      <c r="N23" t="n">
+        <v>16445971.06820682</v>
+      </c>
+      <c r="O23" t="n">
+        <v>263473.5055005501</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9712826195905685</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1365246445402428</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.24982276100033e-05</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0004906045877305042</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7.32468488284717</v>
+      </c>
+      <c r="U23" t="n">
+        <v>15096.34905687875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Antigravity SDK v0.1.12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gemini 3.8 Flash (high)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4186315529449987</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.03574427079166177</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>0.451612903225807</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.467392200412544</v>
+      </c>
+      <c r="K24" t="n">
+        <v>702.7110253025301</v>
+      </c>
+      <c r="L24" t="n">
+        <v>188.4884488448845</v>
+      </c>
+      <c r="M24" t="n">
+        <v>13511073.15511551</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13395246.74862486</v>
+      </c>
+      <c r="O24" t="n">
+        <v>115826.4064906491</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.8697428234581179</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1696655897976026</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.098433027035294e-05</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0005957378465276962</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5.893947035417844</v>
+      </c>
+      <c r="U24" t="n">
+        <v>19227.06869342024</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GPT-6 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5666259127577997</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02540823290001526</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>0.575268817204301</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.989729004180416</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1338.052705170518</v>
+      </c>
+      <c r="L25" t="n">
+        <v>86.55005500550054</v>
+      </c>
+      <c r="M25" t="n">
+        <v>9840777.763476355</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9778602.140814083</v>
+      </c>
+      <c r="O25" t="n">
+        <v>62175.62266226623</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9640119921972632</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.18952417157726</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5.757938309112199e-05</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0004234705483335876</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5.276371829924331</v>
+      </c>
+      <c r="U25" t="n">
+        <v>7354.551674571196</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (max)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6164504498789397</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0209911088149403</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>0.618279569892473</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7.46709735138597</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1762.03302640264</v>
+      </c>
+      <c r="L26" t="n">
+        <v>39.37843784378438</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3346611.012209417</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3299549.915435806</v>
+      </c>
+      <c r="O26" t="n">
+        <v>47061.09677361179</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9335591564904552</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.08255556622206355</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.0001842014048331127</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0003498518135823383</v>
+      </c>
+      <c r="T26" t="n">
+        <v>12.11305361664085</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1899.289605849129</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,411 +526,411 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Sonnet 5.5 (high)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.588884131062264</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.594086021505376</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J2" t="n">
-        <v>4.536492777821779</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K2" t="n">
-        <v>1481.89598019802</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L2" t="n">
-        <v>78.55115511551155</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M2" t="n">
-        <v>6074134.495049492</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N2" t="n">
-        <v>6017554.665016501</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O2" t="n">
-        <v>56579.83003300329</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R2" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T2" t="n">
-        <v>7.703540541394086</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U2" t="n">
-        <v>4098.893968413241</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.620967741935484</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J3" t="n">
-        <v>3.478965577837015</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K3" t="n">
-        <v>3784.416073707372</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L3" t="n">
-        <v>110.0367013624439</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M3" t="n">
-        <v>8706893.798112892</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N3" t="n">
-        <v>8600561.252779894</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O3" t="n">
-        <v>106332.5453329948</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R3" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T3" t="n">
-        <v>8.041007149609982</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U3" t="n">
-        <v>2300.723183849934</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.482993172759088</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.545698924731183</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J4" t="n">
-        <v>3.467754041474145</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K4" t="n">
-        <v>1098.202911991198</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L4" t="n">
-        <v>187.4895489548955</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>16237094.3520352</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N4" t="n">
-        <v>16091465.1039604</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O4" t="n">
-        <v>145629.2480748075</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1392812659094378</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R4" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T4" t="n">
-        <v>7.179716478526343</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U4" t="n">
-        <v>14785.14960645573</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J5" t="n">
-        <v>4.241385833751375</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K5" t="n">
-        <v>2887.955652365237</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L5" t="n">
-        <v>107.049504950495</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M5" t="n">
-        <v>14276424.42684269</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N5" t="n">
-        <v>14202165.16611661</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O5" t="n">
-        <v>74259.26072607259</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R5" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T5" t="n">
-        <v>7.919705712496602</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U5" t="n">
-        <v>4943.436169163572</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.519259105470924</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.661290322580645</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J6" t="n">
-        <v>5.047195443300332</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K6" t="n">
-        <v>3689.344194719472</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L6" t="n">
-        <v>173.3602860286028</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M6" t="n">
-        <v>8481121.533553353</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N6" t="n">
-        <v>8387890.666666667</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O6" t="n">
-        <v>93230.86688668867</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1028807208486825</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R6" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T6" t="n">
-        <v>9.719994103373407</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U6" t="n">
-        <v>2298.815476661763</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.513440860215054</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08506419165060494</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K7" t="n">
-        <v>1097.040440044003</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L7" t="n">
-        <v>121.6666666666667</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M7" t="n">
-        <v>15350225.29922993</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N7" t="n">
-        <v>15269826.30913091</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O7" t="n">
-        <v>80398.9900990099</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.554499000811647</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R7" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2195631176605357</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U7" t="n">
-        <v>13992.39694264526</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="8">
@@ -941,7 +941,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -951,124 +951,120 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.564516129032258</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J8" t="n">
-        <v>1.235497127172719</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K8" t="n">
-        <v>735.1809878987912</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L8" t="n">
-        <v>36.77227722772277</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M8" t="n">
-        <v>2652380.565456549</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N8" t="n">
-        <v>2610884.190319032</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O8" t="n">
-        <v>41496.37513751376</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002074079836537043</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T8" t="n">
-        <v>2.245848381022551</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U8" t="n">
-        <v>3607.792651218138</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.628713868151493</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J9" t="n">
-        <v>3.333386534873489</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K9" t="n">
-        <v>1619.013470847085</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L9" t="n">
-        <v>78.31683168316832</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M9" t="n">
-        <v>7087678.3960396</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N9" t="n">
-        <v>6961982.357535753</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O9" t="n">
-        <v>125696.0385038504</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R9" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T9" t="n">
-        <v>5.30191348359169</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U9" t="n">
-        <v>4377.776049220426</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="10">
@@ -1079,7 +1075,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1093,116 +1089,120 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.443548387096774</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1759117230445546</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K10" t="n">
-        <v>1285.926851485148</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L10" t="n">
-        <v>88.64301430143014</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M10" t="n">
-        <v>10218069.24807481</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N10" t="n">
-        <v>10119727.86413641</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O10" t="n">
-        <v>98341.38393839383</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.334943267525058</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R10" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4282759302584503</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U10" t="n">
-        <v>7946.073477098422</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>GPT-6.1 Sol (medium)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.658602150537635</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J11" t="n">
-        <v>7.897126985217273</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K11" t="n">
-        <v>2146.992089658964</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L11" t="n">
-        <v>99.53135313531354</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M11" t="n">
-        <v>9691548.173817372</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N11" t="n">
-        <v>9590504.44719472</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O11" t="n">
-        <v>101043.7266226623</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R11" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T11" t="n">
-        <v>12.802853245848</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U11" t="n">
-        <v>4514.012054584146</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="12">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1227,51 +1227,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.54559127289644</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.540322580645161</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J12" t="n">
-        <v>6.353318230693071</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K12" t="n">
-        <v>1237.696445544555</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L12" t="n">
-        <v>116.3949394939494</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M12" t="n">
-        <v>10170136.63256324</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N12" t="n">
-        <v>10120981.25467547</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O12" t="n">
-        <v>49155.37788778878</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R12" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T12" t="n">
-        <v>11.64483111499294</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U12" t="n">
-        <v>8216.987831849709</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="13">
@@ -1484,70 +1484,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.583333333333333</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J16" t="n">
-        <v>3.570143280528054</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K16" t="n">
-        <v>1167.338748074809</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L16" t="n">
-        <v>112.0616061606161</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M16" t="n">
-        <v>5543624.597359739</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N16" t="n">
-        <v>5487669.762376238</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O16" t="n">
-        <v>55954.83498349835</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R16" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T16" t="n">
-        <v>7.601070758745943</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U16" t="n">
-        <v>4748.942504052369</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="17">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,51 +1572,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.486559139784946</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4380225639383938</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K17" t="n">
-        <v>1412.260883388339</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L17" t="n">
-        <v>121.5137513751375</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M17" t="n">
-        <v>14854524.53905389</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N17" t="n">
-        <v>14783219.74807481</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O17" t="n">
-        <v>71304.79097909792</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.9278388366571143</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R17" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T17" t="n">
-        <v>1.013362033548448</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U17" t="n">
-        <v>10518.2581446386</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="18">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1637,607 +1637,952 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.618279569892473</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K18" t="n">
-        <v>2417.550009900991</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L18" t="n">
-        <v>138.1463146314632</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M18" t="n">
-        <v>24180108.02805281</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N18" t="n">
-        <v>24063625.6270627</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O18" t="n">
-        <v>116482.400990099</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.808558675855097</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R18" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5529264896684616</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U18" t="n">
-        <v>10001.90603256356</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F19" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.669354838709677</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J19" t="n">
-        <v>14.19080079636965</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K19" t="n">
-        <v>5244.965372937293</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L19" t="n">
-        <v>265.9306930693069</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M19" t="n">
-        <v>27742337.2337734</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N19" t="n">
-        <v>27141368.95929593</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O19" t="n">
-        <v>600968.2744774478</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R19" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T19" t="n">
-        <v>20.75958236310095</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U19" t="n">
-        <v>5289.327051979582</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.659885802549234</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.663978494623656</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J20" t="n">
-        <v>13.03638341842683</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K20" t="n">
-        <v>3867.092341034102</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L20" t="n">
-        <v>155.0957095709571</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M20" t="n">
-        <v>15551383.220022</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N20" t="n">
-        <v>15218206.4180418</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O20" t="n">
-        <v>333176.801980198</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R20" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T20" t="n">
-        <v>19.75551431484872</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U20" t="n">
-        <v>4021.466737425617</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.647849462365591</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J21" t="n">
-        <v>12.38809237513753</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K21" t="n">
-        <v>2089.900125412543</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L21" t="n">
-        <v>36.65676567656766</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M21" t="n">
-        <v>5715253.85918592</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N21" t="n">
-        <v>5581622.259625964</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O21" t="n">
-        <v>133631.599559956</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0001088709227809481</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T21" t="n">
-        <v>19.90934652274569</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U21" t="n">
-        <v>2734.701907373559</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.629032258064516</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J22" t="n">
-        <v>8.817468730473037</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K22" t="n">
-        <v>2354.367686468646</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L22" t="n">
-        <v>162.6457645764577</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M22" t="n">
-        <v>14324724.28382839</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N22" t="n">
-        <v>14201447.9559956</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O22" t="n">
-        <v>123276.3278327833</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P22" t="n">
-        <v>0.938882976190201</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R22" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T22" t="n">
-        <v>15.67058466504826</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U22" t="n">
-        <v>6084.319100265209</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.594086021505376</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J23" t="n">
-        <v>3.977504096947204</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K23" t="n">
-        <v>1106.853353135313</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L23" t="n">
-        <v>185.2381738173817</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M23" t="n">
-        <v>16709444.57370737</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N23" t="n">
-        <v>16445971.06820682</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O23" t="n">
-        <v>263473.5055005501</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1365246445402428</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T23" t="n">
-        <v>7.32468488284717</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U23" t="n">
-        <v>15096.34905687875</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.451612903225807</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J24" t="n">
-        <v>2.467392200412544</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K24" t="n">
-        <v>702.7110253025301</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L24" t="n">
-        <v>188.4884488448845</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M24" t="n">
-        <v>13511073.15511551</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N24" t="n">
-        <v>13395246.74862486</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O24" t="n">
-        <v>115826.4064906491</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R24" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T24" t="n">
-        <v>5.893947035417844</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U24" t="n">
-        <v>19227.06869342024</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.575268817204301</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J25" t="n">
-        <v>2.989729004180416</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K25" t="n">
-        <v>1338.052705170518</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L25" t="n">
-        <v>86.55005500550054</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M25" t="n">
-        <v>9840777.763476355</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N25" t="n">
-        <v>9778602.140814083</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O25" t="n">
-        <v>62175.62266226623</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R25" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T25" t="n">
-        <v>5.276371829924331</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U25" t="n">
-        <v>7354.551674571196</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
+        <v>0.669354838709677</v>
+      </c>
+      <c r="J26" t="n">
+        <v>14.19080079636965</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5244.965372937293</v>
+      </c>
+      <c r="L26" t="n">
+        <v>265.9306930693069</v>
+      </c>
+      <c r="M26" t="n">
+        <v>27742337.2337734</v>
+      </c>
+      <c r="N26" t="n">
+        <v>27141368.95929593</v>
+      </c>
+      <c r="O26" t="n">
+        <v>600968.2744774478</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9506214943317096</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.04817052590506091</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.464025765438745e-05</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0001303303813790985</v>
+      </c>
+      <c r="T26" t="n">
+        <v>20.75958236310095</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5289.327051979582</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Grok 4.7 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5626764360706693</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.01433955552408987</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0.629032258064516</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8.817468730473037</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2354.367686468646</v>
+      </c>
+      <c r="L27" t="n">
+        <v>162.6457645764577</v>
+      </c>
+      <c r="M27" t="n">
+        <v>14324724.28382839</v>
+      </c>
+      <c r="N27" t="n">
+        <v>14201447.9559956</v>
+      </c>
+      <c r="O27" t="n">
+        <v>123276.3278327833</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.938882976190201</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.06381382835258244</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.928008839275821e-05</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0002389925920681645</v>
+      </c>
+      <c r="T27" t="n">
+        <v>15.67058466504826</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6084.319100265209</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (max)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6164504498789397</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0209911088149403</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
         <v>0.618279569892473</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J28" t="n">
         <v>7.46709735138597</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K28" t="n">
         <v>1762.03302640264</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L28" t="n">
         <v>39.37843784378438</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>3346611.012209417</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>3299549.915435806</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>47061.09677361179</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>0.9335591564904552</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>0.08255556622206355</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>0.0001842014048331127</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>0.0003498518135823383</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>12.11305361664085</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>1899.289605849129</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fable 5.1 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6222249615769457</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.01786377121119468</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L29" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O29" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T29" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J30" t="n">
+        <v>13.03638341842683</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3867.092341034102</v>
+      </c>
+      <c r="L30" t="n">
+        <v>155.0957095709571</v>
+      </c>
+      <c r="M30" t="n">
+        <v>15551383.220022</v>
+      </c>
+      <c r="N30" t="n">
+        <v>15218206.4180418</v>
+      </c>
+      <c r="O30" t="n">
+        <v>333176.801980198</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9500106599458848</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.05061877833513936</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4.243261150555715e-05</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.0001706413357517016</v>
+      </c>
+      <c r="T30" t="n">
+        <v>19.75551431484872</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4021.466737425617</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GPT-6.1 Sol (xhigh)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6290776736822983</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.04052542124850751</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0.610215053763441</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.039708101440963</v>
+      </c>
+      <c r="K31" t="n">
+        <v>931.3823091309132</v>
+      </c>
+      <c r="L31" t="n">
+        <v>40.05500550055005</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3212528.109451931</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3177125.49569875</v>
+      </c>
+      <c r="O31" t="n">
+        <v>35402.61375317859</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9327572280083256</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.6050521995648973</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.0001958201305169657</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.0006754236874751251</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.652749962266257</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3449.204561819077</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,208 +526,208 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.564516129032258</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J2" t="n">
-        <v>1.235497127172719</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K2" t="n">
-        <v>735.1809878987912</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L2" t="n">
-        <v>36.77227722772277</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M2" t="n">
-        <v>2652380.565456549</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N2" t="n">
-        <v>2610884.190319032</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O2" t="n">
-        <v>41496.37513751376</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002074079836537043</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T2" t="n">
-        <v>2.245848381022551</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U2" t="n">
-        <v>3607.792651218138</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.482993172759088</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.545698924731183</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J3" t="n">
-        <v>3.467754041474145</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K3" t="n">
-        <v>1098.202911991198</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L3" t="n">
-        <v>187.4895489548955</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>16237094.3520352</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N3" t="n">
-        <v>16091465.1039604</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O3" t="n">
-        <v>145629.2480748075</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1392812659094378</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R3" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T3" t="n">
-        <v>7.179716478526343</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U3" t="n">
-        <v>14785.14960645573</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.513440860215054</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08506419165060494</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K4" t="n">
-        <v>1097.040440044003</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L4" t="n">
-        <v>121.6666666666667</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M4" t="n">
-        <v>15350225.29922993</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N4" t="n">
-        <v>15269826.30913091</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O4" t="n">
-        <v>80398.9900990099</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.554499000811647</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R4" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2195631176605357</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U4" t="n">
-        <v>13992.39694264526</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="5">
@@ -871,269 +871,269 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Gemini 3.8 Flash (high)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.594086021505376</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J7" t="n">
-        <v>4.536492777821779</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K7" t="n">
-        <v>1481.89598019802</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L7" t="n">
-        <v>78.55115511551155</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M7" t="n">
-        <v>6074134.495049492</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N7" t="n">
-        <v>6017554.665016501</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O7" t="n">
-        <v>56579.83003300329</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R7" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T7" t="n">
-        <v>7.703540541394086</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U7" t="n">
-        <v>4098.893968413241</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.620967741935484</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J8" t="n">
-        <v>3.478965577837015</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K8" t="n">
-        <v>3784.416073707372</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L8" t="n">
-        <v>110.0367013624439</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M8" t="n">
-        <v>8706893.798112892</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N8" t="n">
-        <v>8600561.252779894</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O8" t="n">
-        <v>106332.5453329948</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R8" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T8" t="n">
-        <v>8.041007149609982</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U8" t="n">
-        <v>2300.723183849934</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Qwen3.8 Max</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.658602150537635</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>7.897126985217273</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K9" t="n">
-        <v>2146.992089658964</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L9" t="n">
-        <v>99.53135313531354</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M9" t="n">
-        <v>9691548.173817372</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N9" t="n">
-        <v>9590504.44719472</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O9" t="n">
-        <v>101043.7266226623</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R9" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T9" t="n">
-        <v>12.802853245848</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U9" t="n">
-        <v>4514.012054584146</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.54559127289644</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.540322580645161</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J10" t="n">
-        <v>6.353318230693071</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K10" t="n">
-        <v>1237.696445544555</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L10" t="n">
-        <v>116.3949394939494</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M10" t="n">
-        <v>10170136.63256324</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N10" t="n">
-        <v>10120981.25467547</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O10" t="n">
-        <v>49155.37788778878</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R10" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T10" t="n">
-        <v>11.64483111499294</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U10" t="n">
-        <v>8216.987831849709</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="11">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1158,51 +1158,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.60752688172043</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7046746644898908</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K11" t="n">
-        <v>651.3228668866898</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L11" t="n">
-        <v>37.98899889988999</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M11" t="n">
-        <v>2298278.745423723</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N11" t="n">
-        <v>2275866.51440062</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O11" t="n">
-        <v>22412.23102310231</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0002672206192482065</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T11" t="n">
-        <v>1.147403025201837</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U11" t="n">
-        <v>3528.632053730048</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="12">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1227,120 +1227,120 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.577956989247312</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J12" t="n">
-        <v>1.554119528390054</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K12" t="n">
-        <v>1463.046422442244</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L12" t="n">
-        <v>40.45654565456545</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M12" t="n">
-        <v>3999501.610795507</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N12" t="n">
-        <v>3937843.056466302</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O12" t="n">
-        <v>61658.55432920342</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R12" t="n">
-        <v>0.000150387505484869</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T12" t="n">
-        <v>2.583846953587535</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U12" t="n">
-        <v>2733.680592389675</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.620967741935484</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J13" t="n">
-        <v>10.78915469925741</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K13" t="n">
-        <v>2515.540235973597</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L13" t="n">
-        <v>152.1303630363036</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M13" t="n">
-        <v>11374850.48899891</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N13" t="n">
-        <v>11238194.40979098</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O13" t="n">
-        <v>136656.0792079208</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R13" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T13" t="n">
-        <v>18.06430758687328</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U13" t="n">
-        <v>4521.832060697078</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="14">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1365,51 +1365,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.420593075103495</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.389784946236559</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4831101147414734</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K14" t="n">
-        <v>380.8561793179318</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L14" t="n">
-        <v>18.57865786578658</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M14" t="n">
-        <v>977284.7700770069</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N14" t="n">
-        <v>961481.2431243125</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O14" t="n">
-        <v>15803.52695269527</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0004303690060271313</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T14" t="n">
-        <v>1.148640201987622</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U14" t="n">
-        <v>2566.020516792475</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="15">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1434,120 +1434,120 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.448924731182796</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K15" t="n">
-        <v>510.7721826182621</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L15" t="n">
-        <v>22.20902090209021</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M15" t="n">
-        <v>1253351.492849284</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N15" t="n">
-        <v>1232830.718371837</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O15" t="n">
-        <v>20520.77447744774</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T15" t="n">
-        <v>1.348511698390355</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U15" t="n">
-        <v>2453.836633045474</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.575268817204301</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J16" t="n">
-        <v>2.989729004180416</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K16" t="n">
-        <v>1338.052705170518</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L16" t="n">
-        <v>86.55005500550054</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M16" t="n">
-        <v>9840777.763476355</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N16" t="n">
-        <v>9778602.140814083</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O16" t="n">
-        <v>62175.62266226623</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.18952417157726</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R16" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T16" t="n">
-        <v>5.276371829924331</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U16" t="n">
-        <v>7354.551674571196</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="17">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,51 +1572,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.599462365591398</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8892413135295484</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K17" t="n">
-        <v>799.7652123212325</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L17" t="n">
-        <v>38.97909790979098</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M17" t="n">
-        <v>2819911.990351496</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N17" t="n">
-        <v>2791163.254864831</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O17" t="n">
-        <v>28748.73548666342</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278388366571143</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6764107362832188</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0002133018241973586</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T17" t="n">
-        <v>1.478391672927692</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U17" t="n">
-        <v>3525.924792561313</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="18">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1641,327 +1641,327 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.551075268817204</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4988036451027072</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K18" t="n">
-        <v>517.8138943894386</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L18" t="n">
-        <v>35.74037403740374</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M18" t="n">
-        <v>1713818.918195099</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N18" t="n">
-        <v>1699123.860141752</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O18" t="n">
-        <v>14695.05805334632</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9278388366571141</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.147071598051071</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8717851629305855</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U18" t="n">
-        <v>3309.719837116163</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Moonshot AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.519259105470924</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.661290322580645</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J19" t="n">
-        <v>5.047195443300332</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K19" t="n">
-        <v>3689.344194719472</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L19" t="n">
-        <v>173.3602860286028</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M19" t="n">
-        <v>8481121.533553353</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N19" t="n">
-        <v>8387890.666666667</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O19" t="n">
-        <v>93230.86688668867</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1028807208486825</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R19" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S19" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T19" t="n">
-        <v>9.719994103373407</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U19" t="n">
-        <v>2298.815476661763</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Moonshot AI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.594086021505376</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J20" t="n">
-        <v>4.241385833751375</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K20" t="n">
-        <v>2887.955652365237</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L20" t="n">
-        <v>107.049504950495</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M20" t="n">
-        <v>14276424.42684269</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N20" t="n">
-        <v>14202165.16611661</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O20" t="n">
-        <v>74259.26072607259</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R20" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T20" t="n">
-        <v>7.919705712496602</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U20" t="n">
-        <v>4943.436169163572</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.583333333333333</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J21" t="n">
-        <v>3.570143280528054</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K21" t="n">
-        <v>1167.338748074809</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L21" t="n">
-        <v>112.0616061606161</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M21" t="n">
-        <v>5543624.597359739</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N21" t="n">
-        <v>5487669.762376238</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O21" t="n">
-        <v>55954.83498349835</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R21" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T21" t="n">
-        <v>7.601070758745943</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U21" t="n">
-        <v>4748.942504052369</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.486559139784946</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4380225639383938</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K22" t="n">
-        <v>1412.260883388339</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L22" t="n">
-        <v>121.5137513751375</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M22" t="n">
-        <v>14854524.53905389</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N22" t="n">
-        <v>14783219.74807481</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O22" t="n">
-        <v>71304.79097909792</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P22" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R22" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T22" t="n">
-        <v>1.013362033548448</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U22" t="n">
-        <v>10518.2581446386</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="23">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1982,469 +1982,469 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.618279569892473</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K23" t="n">
-        <v>2417.550009900991</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L23" t="n">
-        <v>138.1463146314632</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M23" t="n">
-        <v>24180108.02805281</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N23" t="n">
-        <v>24063625.6270627</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O23" t="n">
-        <v>116482.400990099</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9718803286808345</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.808558675855097</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R23" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5529264896684616</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U23" t="n">
-        <v>10001.90603256356</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.594086021505376</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J24" t="n">
-        <v>3.977504096947204</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K24" t="n">
-        <v>1106.853353135313</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L24" t="n">
-        <v>185.2381738173817</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M24" t="n">
-        <v>16709444.57370737</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N24" t="n">
-        <v>16445971.06820682</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O24" t="n">
-        <v>263473.5055005501</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1365246445402428</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R24" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T24" t="n">
-        <v>7.32468488284717</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U24" t="n">
-        <v>15096.34905687875</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.451612903225807</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J25" t="n">
-        <v>2.467392200412544</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K25" t="n">
-        <v>702.7110253025301</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L25" t="n">
-        <v>188.4884488448845</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M25" t="n">
-        <v>13511073.15511551</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N25" t="n">
-        <v>13395246.74862486</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O25" t="n">
-        <v>115826.4064906491</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R25" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T25" t="n">
-        <v>5.893947035417844</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U25" t="n">
-        <v>19227.06869342024</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.669354838709677</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J26" t="n">
-        <v>14.19080079636965</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K26" t="n">
-        <v>5244.965372937293</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L26" t="n">
-        <v>265.9306930693069</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M26" t="n">
-        <v>27742337.2337734</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N26" t="n">
-        <v>27141368.95929593</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O26" t="n">
-        <v>600968.2744774478</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R26" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T26" t="n">
-        <v>20.75958236310095</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U26" t="n">
-        <v>5289.327051979582</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.629032258064516</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J27" t="n">
-        <v>8.817468730473037</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K27" t="n">
-        <v>2354.367686468646</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L27" t="n">
-        <v>162.6457645764577</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M27" t="n">
-        <v>14324724.28382839</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N27" t="n">
-        <v>14201447.9559956</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O27" t="n">
-        <v>123276.3278327833</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P27" t="n">
-        <v>0.938882976190201</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R27" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T27" t="n">
-        <v>15.67058466504826</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U27" t="n">
-        <v>6084.319100265209</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.618279569892473</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J28" t="n">
-        <v>7.46709735138597</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K28" t="n">
-        <v>1762.03302640264</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L28" t="n">
-        <v>39.37843784378438</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M28" t="n">
-        <v>3346611.012209417</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N28" t="n">
-        <v>3299549.915435806</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O28" t="n">
-        <v>47061.09677361179</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001842014048331127</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T28" t="n">
-        <v>12.11305361664085</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U28" t="n">
-        <v>1899.289605849129</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.647849462365591</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J29" t="n">
-        <v>12.38809237513753</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K29" t="n">
-        <v>2089.900125412543</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L29" t="n">
-        <v>36.65676567656766</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M29" t="n">
-        <v>5715253.85918592</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N29" t="n">
-        <v>5581622.259625964</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O29" t="n">
-        <v>133631.599559956</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0001088709227809481</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T29" t="n">
-        <v>19.90934652274569</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U29" t="n">
-        <v>2734.701907373559</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="30">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2469,119 +2469,188 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.659885802549234</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.663978494623656</v>
+        <v>0.647849462365591</v>
       </c>
       <c r="J30" t="n">
-        <v>13.03638341842683</v>
+        <v>12.38809237513753</v>
       </c>
       <c r="K30" t="n">
-        <v>3867.092341034102</v>
+        <v>2089.900125412543</v>
       </c>
       <c r="L30" t="n">
-        <v>155.0957095709571</v>
+        <v>36.65676567656766</v>
       </c>
       <c r="M30" t="n">
-        <v>15551383.220022</v>
+        <v>5715253.85918592</v>
       </c>
       <c r="N30" t="n">
-        <v>15218206.4180418</v>
+        <v>5581622.259625964</v>
       </c>
       <c r="O30" t="n">
-        <v>333176.801980198</v>
+        <v>133631.599559956</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.9159555838702423</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.05022766562717351</v>
       </c>
       <c r="R30" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>0.0001088709227809481</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.0002977295201865781</v>
       </c>
       <c r="T30" t="n">
-        <v>19.75551431484872</v>
+        <v>19.90934652274569</v>
       </c>
       <c r="U30" t="n">
-        <v>4021.466737425617</v>
+        <v>2734.701907373559</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Opus 5.5 (max)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.659885802549234</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.0102384801451021</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J31" t="n">
+        <v>13.03638341842683</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3867.092341034102</v>
+      </c>
+      <c r="L31" t="n">
+        <v>155.0957095709571</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15551383.220022</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15218206.4180418</v>
+      </c>
+      <c r="O31" t="n">
+        <v>333176.801980198</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9500106599458848</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.05061877833513936</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4.243261150555715e-05</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.0001706413357517016</v>
+      </c>
+      <c r="T31" t="n">
+        <v>19.75551431484872</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4021.466737425617</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GPT-6.1 Sol (xhigh)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6290776736822983</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.04052542124850751</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
         <v>0.610215053763441</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>1.039708101440963</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>931.3823091309132</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>40.05500550055005</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>3212528.109451931</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N32" t="n">
         <v>3177125.49569875</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O32" t="n">
         <v>35402.61375317859</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P32" t="n">
         <v>0.9327572280083256</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>0.6050521995648973</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>0.0001958201305169657</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>0.0006754236874751251</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>1.652749962266257</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>3449.204561819077</v>
       </c>
     </row>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -610,55 +610,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.513440860215054</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08506419165060494</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K3" t="n">
-        <v>1097.040440044003</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L3" t="n">
-        <v>121.6666666666667</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M3" t="n">
-        <v>15350225.29922993</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N3" t="n">
-        <v>15269826.30913091</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O3" t="n">
-        <v>80398.9900990099</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.554499000811647</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195631176605357</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U3" t="n">
-        <v>13992.39694264526</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="4">
@@ -669,7 +669,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,51 +683,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.564516129032258</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235497127172719</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K4" t="n">
-        <v>735.1809878987912</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L4" t="n">
-        <v>36.77227722772277</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M4" t="n">
-        <v>2652380.565456549</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N4" t="n">
-        <v>2610884.190319032</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O4" t="n">
-        <v>41496.37513751376</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002074079836537043</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T4" t="n">
-        <v>2.245848381022551</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U4" t="n">
-        <v>3607.792651218138</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +738,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -752,323 +752,327 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.628713868151493</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.620967741935484</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J5" t="n">
-        <v>3.333386534873489</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K5" t="n">
-        <v>1619.013470847085</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L5" t="n">
-        <v>78.31683168316832</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M5" t="n">
-        <v>7087678.3960396</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N5" t="n">
-        <v>6961982.357535753</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O5" t="n">
-        <v>125696.0385038504</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R5" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T5" t="n">
-        <v>5.30191348359169</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U5" t="n">
-        <v>4377.776049220426</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.443548387096774</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1759117230445546</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K6" t="n">
-        <v>1285.926851485148</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L6" t="n">
-        <v>88.64301430143014</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M6" t="n">
-        <v>10218069.24807481</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N6" t="n">
-        <v>10119727.86413641</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O6" t="n">
-        <v>98341.38393839383</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.334943267525058</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R6" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4282759302584503</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U6" t="n">
-        <v>7946.073477098422</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.451612903225807</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J7" t="n">
-        <v>2.467392200412544</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K7" t="n">
-        <v>702.7110253025301</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L7" t="n">
-        <v>188.4884488448845</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M7" t="n">
-        <v>13511073.15511551</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N7" t="n">
-        <v>13395246.74862486</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O7" t="n">
-        <v>115826.4064906491</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R7" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T7" t="n">
-        <v>5.893947035417844</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U7" t="n">
-        <v>19227.06869342024</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>GPT-6.1 Sol (medium)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.588884131062264</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.594086021505376</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J8" t="n">
-        <v>4.536492777821779</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K8" t="n">
-        <v>1481.89598019802</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L8" t="n">
-        <v>78.55115511551155</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M8" t="n">
-        <v>6074134.495049492</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N8" t="n">
-        <v>6017554.665016501</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O8" t="n">
-        <v>56579.83003300329</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R8" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T8" t="n">
-        <v>7.703540541394086</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U8" t="n">
-        <v>4098.893968413241</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J9" t="n">
-        <v>3.478965577837015</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K9" t="n">
-        <v>3784.416073707372</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L9" t="n">
-        <v>110.0367013624439</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M9" t="n">
-        <v>8706893.798112892</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N9" t="n">
-        <v>8600561.252779894</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O9" t="n">
-        <v>106332.5453329948</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R9" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T9" t="n">
-        <v>8.041007149609982</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U9" t="n">
-        <v>2300.723183849934</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="10">
@@ -1139,277 +1143,273 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.54559127289644</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.540322580645161</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J11" t="n">
-        <v>6.353318230693071</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K11" t="n">
-        <v>1237.696445544555</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L11" t="n">
-        <v>116.3949394939494</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M11" t="n">
-        <v>10170136.63256324</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N11" t="n">
-        <v>10120981.25467547</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O11" t="n">
-        <v>49155.37788778878</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R11" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T11" t="n">
-        <v>11.64483111499294</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U11" t="n">
-        <v>8216.987831849709</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.60752688172043</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7046746644898908</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K12" t="n">
-        <v>651.3228668866898</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L12" t="n">
-        <v>37.98899889988999</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M12" t="n">
-        <v>2298278.745423723</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N12" t="n">
-        <v>2275866.51440062</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O12" t="n">
-        <v>22412.23102310231</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002672206192482065</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T12" t="n">
-        <v>1.147403025201837</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U12" t="n">
-        <v>3528.632053730048</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.577956989247312</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J13" t="n">
-        <v>1.554119528390054</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K13" t="n">
-        <v>1463.046422442244</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L13" t="n">
-        <v>40.45654565456545</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M13" t="n">
-        <v>3999501.610795507</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N13" t="n">
-        <v>3937843.056466302</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O13" t="n">
-        <v>61658.55432920342</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R13" t="n">
-        <v>0.000150387505484869</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T13" t="n">
-        <v>2.583846953587535</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U13" t="n">
-        <v>2733.680592389675</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J14" t="n">
-        <v>10.78915469925741</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K14" t="n">
-        <v>2515.540235973597</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L14" t="n">
-        <v>152.1303630363036</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M14" t="n">
-        <v>11374850.48899891</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N14" t="n">
-        <v>11238194.40979098</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O14" t="n">
-        <v>136656.0792079208</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.05535778192387877</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R14" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T14" t="n">
-        <v>18.06430758687328</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U14" t="n">
-        <v>4521.832060697078</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="15">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1434,51 +1434,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.420593075103495</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.389784946236559</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4831101147414734</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K15" t="n">
-        <v>380.8561793179318</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L15" t="n">
-        <v>18.57865786578658</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M15" t="n">
-        <v>977284.7700770069</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N15" t="n">
-        <v>961481.2431243125</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O15" t="n">
-        <v>15803.52695269527</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004303690060271313</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T15" t="n">
-        <v>1.148640201987622</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U15" t="n">
-        <v>2566.020516792475</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="16">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1503,51 +1503,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.448924731182796</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6187507753025301</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K16" t="n">
-        <v>510.7721826182621</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L16" t="n">
-        <v>22.20902090209021</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M16" t="n">
-        <v>1253351.492849284</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N16" t="n">
-        <v>1232830.718371837</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O16" t="n">
-        <v>20520.77447744774</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T16" t="n">
-        <v>1.348511698390355</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U16" t="n">
-        <v>2453.836633045474</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="17">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1568,55 +1568,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.575268817204301</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J17" t="n">
-        <v>2.989729004180416</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K17" t="n">
-        <v>1338.052705170518</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L17" t="n">
-        <v>86.55005500550054</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M17" t="n">
-        <v>9840777.763476355</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N17" t="n">
-        <v>9778602.140814083</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O17" t="n">
-        <v>62175.62266226623</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.18952417157726</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R17" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T17" t="n">
-        <v>5.276371829924331</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U17" t="n">
-        <v>7354.551674571196</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="18">
@@ -2105,139 +2105,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J25" t="n">
-        <v>8.817468730473037</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K25" t="n">
-        <v>2354.367686468646</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L25" t="n">
-        <v>162.6457645764577</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M25" t="n">
-        <v>14324724.28382839</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N25" t="n">
-        <v>14201447.9559956</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O25" t="n">
-        <v>123276.3278327833</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P25" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R25" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T25" t="n">
-        <v>15.67058466504826</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U25" t="n">
-        <v>6084.319100265209</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.594086021505376</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J26" t="n">
-        <v>3.977504096947204</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K26" t="n">
-        <v>1106.853353135313</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L26" t="n">
-        <v>185.2381738173817</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M26" t="n">
-        <v>16709444.57370737</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N26" t="n">
-        <v>16445971.06820682</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O26" t="n">
-        <v>263473.5055005501</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R26" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T26" t="n">
-        <v>7.32468488284717</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U26" t="n">
-        <v>15096.34905687875</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="27">
@@ -2273,7 +2273,7 @@
         <v>0.564516129032258</v>
       </c>
       <c r="J27" t="n">
-        <v>5.843905389444815</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K27" t="n">
         <v>2070.168603200884</v>
@@ -2294,7 +2294,7 @@
         <v>0.8700000000000004</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1091012876743977</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R27" t="n">
         <v>4.642399712573407e-05</v>
@@ -2303,7 +2303,7 @@
         <v>0.0003079834183795285</v>
       </c>
       <c r="T27" t="n">
-        <v>9.165794660319715</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U27" t="n">
         <v>6634.142629842724</v>
@@ -2312,139 +2312,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F28" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.669354838709677</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J28" t="n">
-        <v>14.19080079636965</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K28" t="n">
-        <v>5244.965372937293</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L28" t="n">
-        <v>265.9306930693069</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M28" t="n">
-        <v>27742337.2337734</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N28" t="n">
-        <v>27141368.95929593</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O28" t="n">
-        <v>600968.2744774478</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R28" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T28" t="n">
-        <v>20.75958236310095</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U28" t="n">
-        <v>5289.327051979582</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.618279569892473</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J29" t="n">
-        <v>7.46709735138597</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K29" t="n">
-        <v>1762.03302640264</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L29" t="n">
-        <v>39.37843784378438</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M29" t="n">
-        <v>3346611.012209417</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N29" t="n">
-        <v>3299549.915435806</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O29" t="n">
-        <v>47061.09677361179</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0001842014048331127</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T29" t="n">
-        <v>12.11305361664085</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U29" t="n">
-        <v>1899.289605849129</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="30">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,208 +526,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.545698924731183</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J2" t="n">
-        <v>3.467754041474145</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K2" t="n">
-        <v>1098.202911991198</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L2" t="n">
-        <v>187.4895489548955</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M2" t="n">
-        <v>16237094.3520352</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N2" t="n">
-        <v>16091465.1039604</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O2" t="n">
-        <v>145629.2480748075</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1392812659094378</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R2" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T2" t="n">
-        <v>7.179716478526343</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U2" t="n">
-        <v>14785.14960645573</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.575268817204301</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J3" t="n">
-        <v>2.989729004180416</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K3" t="n">
-        <v>1338.052705170518</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L3" t="n">
-        <v>86.55005500550054</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M3" t="n">
-        <v>9840777.763476355</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N3" t="n">
-        <v>9778602.140814083</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O3" t="n">
-        <v>62175.62266226623</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R3" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T3" t="n">
-        <v>5.276371829924331</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U3" t="n">
-        <v>7354.551674571196</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.448924731182796</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6187507753025301</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K4" t="n">
-        <v>510.7721826182621</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L4" t="n">
-        <v>22.20902090209021</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M4" t="n">
-        <v>1253351.492849284</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N4" t="n">
-        <v>1232830.718371837</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O4" t="n">
-        <v>20520.77447744774</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003660902437453124</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T4" t="n">
-        <v>1.348511698390355</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U4" t="n">
-        <v>2453.836633045474</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +734,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -748,124 +744,120 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.420593075103495</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.389784946236559</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4831101147414734</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K5" t="n">
-        <v>380.8561793179318</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L5" t="n">
-        <v>18.57865786578658</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M5" t="n">
-        <v>977284.7700770069</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N5" t="n">
-        <v>961481.2431243125</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O5" t="n">
-        <v>15803.52695269527</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0004303690060271313</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T5" t="n">
-        <v>1.148640201987622</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U5" t="n">
-        <v>2566.020516792475</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J6" t="n">
-        <v>10.78915469925741</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K6" t="n">
-        <v>2515.540235973597</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L6" t="n">
-        <v>152.1303630363036</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M6" t="n">
-        <v>11374850.48899891</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N6" t="n">
-        <v>11238194.40979098</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O6" t="n">
-        <v>136656.0792079208</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R6" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T6" t="n">
-        <v>18.06430758687328</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U6" t="n">
-        <v>4521.832060697078</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="7">
@@ -876,7 +868,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -890,51 +882,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.577956989247312</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J7" t="n">
-        <v>1.554119528390054</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K7" t="n">
-        <v>1463.046422442244</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L7" t="n">
-        <v>40.45654565456545</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M7" t="n">
-        <v>3999501.610795507</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N7" t="n">
-        <v>3937843.056466302</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O7" t="n">
-        <v>61658.55432920342</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000150387505484869</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T7" t="n">
-        <v>2.583846953587535</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U7" t="n">
-        <v>2733.680592389675</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="8">
@@ -1009,135 +1001,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.54559127289644</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.540322580645161</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J9" t="n">
-        <v>6.353318230693071</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K9" t="n">
-        <v>1237.696445544555</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L9" t="n">
-        <v>116.3949394939494</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M9" t="n">
-        <v>10170136.63256324</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N9" t="n">
-        <v>10120981.25467547</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O9" t="n">
-        <v>49155.37788778878</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R9" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T9" t="n">
-        <v>11.64483111499294</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U9" t="n">
-        <v>8216.987831849709</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>GPT-6.1 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.658602150537635</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J10" t="n">
-        <v>7.897126985217273</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K10" t="n">
-        <v>2146.992089658964</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L10" t="n">
-        <v>99.53135313531354</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M10" t="n">
-        <v>9691548.173817372</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N10" t="n">
-        <v>9590504.44719472</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O10" t="n">
-        <v>101043.7266226623</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R10" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T10" t="n">
-        <v>12.802853245848</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U10" t="n">
-        <v>4514.012054584146</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="11">
@@ -1148,7 +1144,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1158,14 +1154,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -1173,174 +1169,178 @@
         <v>0.620967741935484</v>
       </c>
       <c r="J11" t="n">
-        <v>3.478965577837015</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K11" t="n">
-        <v>3784.416073707372</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L11" t="n">
-        <v>110.0367013624439</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M11" t="n">
-        <v>8706893.798112892</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N11" t="n">
-        <v>8600561.252779894</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O11" t="n">
-        <v>106332.5453329948</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R11" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T11" t="n">
-        <v>8.041007149609982</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U11" t="n">
-        <v>2300.723183849934</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Sonnet 5.5 (low)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.588884131062264</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.594086021505376</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J12" t="n">
-        <v>4.536492777821779</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K12" t="n">
-        <v>1481.89598019802</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L12" t="n">
-        <v>78.55115511551155</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M12" t="n">
-        <v>6074134.495049492</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N12" t="n">
-        <v>6017554.665016501</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O12" t="n">
-        <v>56579.83003300329</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R12" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T12" t="n">
-        <v>7.703540541394086</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U12" t="n">
-        <v>4098.893968413241</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.451612903225807</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J13" t="n">
-        <v>2.467392200412544</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K13" t="n">
-        <v>702.7110253025301</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L13" t="n">
-        <v>188.4884488448845</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M13" t="n">
-        <v>13511073.15511551</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N13" t="n">
-        <v>13395246.74862486</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O13" t="n">
-        <v>115826.4064906491</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R13" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T13" t="n">
-        <v>5.893947035417844</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U13" t="n">
-        <v>19227.06869342024</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="14">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1365,51 +1365,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.443548387096774</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1759117230445546</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K14" t="n">
-        <v>1285.926851485148</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L14" t="n">
-        <v>88.64301430143014</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M14" t="n">
-        <v>10218069.24807481</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N14" t="n">
-        <v>10119727.86413641</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O14" t="n">
-        <v>98341.38393839383</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.334943267525058</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R14" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4282759302584503</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U14" t="n">
-        <v>7946.073477098422</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="15">
@@ -1670,7 +1670,7 @@
         <v>28748.73548666342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278388366571141</v>
+        <v>0.9278388366571143</v>
       </c>
       <c r="Q18" t="n">
         <v>0.6764107362832188</v>
@@ -2015,7 +2015,7 @@
         <v>71304.79097909792</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q23" t="n">
         <v>0.9868141561395799</v>
@@ -2105,70 +2105,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.618279569892473</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J25" t="n">
-        <v>7.46709735138597</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K25" t="n">
-        <v>1762.03302640264</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L25" t="n">
-        <v>39.37843784378438</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M25" t="n">
-        <v>3346611.012209417</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N25" t="n">
-        <v>3299549.915435806</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O25" t="n">
-        <v>47061.09677361179</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0001842014048331127</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T25" t="n">
-        <v>12.11305361664085</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U25" t="n">
-        <v>1899.289605849129</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="26">
@@ -2243,70 +2243,70 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.637577603035782</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.564516129032258</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J27" t="n">
-        <v>5.84390538944481</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K27" t="n">
-        <v>2070.168603200884</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L27" t="n">
-        <v>149.1832229580574</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M27" t="n">
-        <v>13733793.78145695</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N27" t="n">
-        <v>13621672.65011038</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O27" t="n">
-        <v>112121.1313465784</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R27" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T27" t="n">
-        <v>9.165794660319708</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U27" t="n">
-        <v>6634.142629842724</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="28">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -534,11 +534,7 @@
           <t>GPT-6 Luna (max)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>openai</t>
@@ -603,11 +599,7 @@
           <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>google</t>
@@ -737,11 +729,7 @@
           <t>Qwen3.8 Max</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>alibaba_cloud</t>
@@ -871,11 +859,7 @@
           <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>openai</t>
@@ -940,11 +924,7 @@
           <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>openai</t>
@@ -1009,11 +989,7 @@
           <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>meta</t>
@@ -1078,11 +1054,7 @@
           <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>openai</t>
@@ -1147,11 +1119,7 @@
           <t>Opus 5 (max)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -1216,11 +1184,7 @@
           <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -1285,11 +1249,7 @@
           <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -1354,11 +1314,7 @@
           <t>GPT-6 Sol (max)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>openai</t>
@@ -1423,11 +1379,7 @@
           <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -1492,11 +1444,7 @@
           <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -1561,11 +1509,7 @@
           <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>deepseek</t>
@@ -1630,11 +1574,7 @@
           <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>openai</t>
@@ -1670,7 +1610,7 @@
         <v>28748.73548666342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278388366571143</v>
+        <v>0.9278388366571144</v>
       </c>
       <c r="Q18" t="n">
         <v>0.6764107362832188</v>
@@ -1699,11 +1639,7 @@
           <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>openai</t>
@@ -1768,11 +1704,7 @@
           <t>Kimi K3</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Moonshot AI</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>moonshotai</t>
@@ -1837,11 +1769,7 @@
           <t>GLM-5.3</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Opencode</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>zai</t>
@@ -1906,11 +1834,7 @@
           <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>xai</t>
@@ -1975,11 +1899,7 @@
           <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>openai</t>
@@ -2015,7 +1935,7 @@
         <v>71304.79097909792</v>
       </c>
       <c r="P23" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9718803286808345</v>
       </c>
       <c r="Q23" t="n">
         <v>0.9868141561395799</v>
@@ -2044,11 +1964,7 @@
           <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>deepseek</t>
@@ -2113,11 +2029,7 @@
           <t>Gemini 4 Argon</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>google</t>
@@ -2135,7 +2047,7 @@
         <v>0.564516129032258</v>
       </c>
       <c r="J25" t="n">
-        <v>5.843905389444815</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K25" t="n">
         <v>2070.168603200884</v>
@@ -2156,7 +2068,7 @@
         <v>0.8700000000000004</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1091012876743977</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R25" t="n">
         <v>4.642399712573407e-05</v>
@@ -2165,7 +2077,7 @@
         <v>0.0003079834183795285</v>
       </c>
       <c r="T25" t="n">
-        <v>9.165794660319715</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U25" t="n">
         <v>6634.142629842724</v>
@@ -2182,11 +2094,7 @@
           <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -2251,11 +2159,7 @@
           <t>GPT-6 Astra (max)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>openai</t>
@@ -2320,11 +2224,7 @@
           <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>meta</t>
@@ -2389,11 +2289,7 @@
           <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>xAI</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>xai</t>
@@ -2458,11 +2354,7 @@
           <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -2527,11 +2419,7 @@
           <t>Opus 5.5 (max)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>anthropic</t>
@@ -2596,11 +2484,7 @@
           <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>openai</t>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,196 +526,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.443548387096774</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1759117230445546</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K2" t="n">
-        <v>1285.926851485148</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L2" t="n">
-        <v>88.64301430143014</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M2" t="n">
-        <v>10218069.24807481</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N2" t="n">
-        <v>10119727.86413641</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O2" t="n">
-        <v>98341.38393839383</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R2" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U2" t="n">
-        <v>7946.073477098422</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.451612903225807</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J3" t="n">
-        <v>2.467392200412544</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K3" t="n">
-        <v>702.7110253025301</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L3" t="n">
-        <v>188.4884488448845</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>13511073.15511551</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N3" t="n">
-        <v>13395246.74862486</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O3" t="n">
-        <v>115826.4064906491</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1696655897976026</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R3" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T3" t="n">
-        <v>5.893947035417844</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U3" t="n">
-        <v>19227.06869342024</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.588884131062264</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.594086021505376</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J4" t="n">
-        <v>4.536492777821779</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K4" t="n">
-        <v>1481.89598019802</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L4" t="n">
-        <v>78.55115511551155</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M4" t="n">
-        <v>6074134.495049492</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N4" t="n">
-        <v>6017554.665016501</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O4" t="n">
-        <v>56579.83003300329</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R4" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T4" t="n">
-        <v>7.703540541394086</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U4" t="n">
-        <v>4098.893968413241</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="5">
@@ -726,20 +726,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -747,625 +747,625 @@
         <v>0.620967741935484</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478965577837015</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K5" t="n">
-        <v>3784.416073707372</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L5" t="n">
-        <v>110.0367013624439</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M5" t="n">
-        <v>8706893.798112892</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N5" t="n">
-        <v>8600561.252779894</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O5" t="n">
-        <v>106332.5453329948</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R5" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T5" t="n">
-        <v>8.041007149609982</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U5" t="n">
-        <v>2300.723183849934</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.658602150537635</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J6" t="n">
-        <v>7.897126985217273</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K6" t="n">
-        <v>2146.992089658964</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L6" t="n">
-        <v>99.53135313531354</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M6" t="n">
-        <v>9691548.173817372</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N6" t="n">
-        <v>9590504.44719472</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O6" t="n">
-        <v>101043.7266226623</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07810758905045663</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R6" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T6" t="n">
-        <v>12.802853245848</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U6" t="n">
-        <v>4514.012054584146</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.54559127289644</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.540322580645161</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J7" t="n">
-        <v>6.353318230693071</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K7" t="n">
-        <v>1237.696445544555</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L7" t="n">
-        <v>116.3949394939494</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M7" t="n">
-        <v>10170136.63256324</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N7" t="n">
-        <v>10120981.25467547</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O7" t="n">
-        <v>49155.37788778878</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R7" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T7" t="n">
-        <v>11.64483111499294</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U7" t="n">
-        <v>8216.987831849709</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.60752688172043</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7046746644898908</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K8" t="n">
-        <v>651.3228668866898</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L8" t="n">
-        <v>37.98899889988999</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M8" t="n">
-        <v>2298278.745423723</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N8" t="n">
-        <v>2275866.51440062</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O8" t="n">
-        <v>22412.23102310231</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002672206192482065</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T8" t="n">
-        <v>1.147403025201837</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U8" t="n">
-        <v>3528.632053730048</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.545698924731183</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>3.467754041474145</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K9" t="n">
-        <v>1098.202911991198</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L9" t="n">
-        <v>187.4895489548955</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M9" t="n">
-        <v>16237094.3520352</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N9" t="n">
-        <v>16091465.1039604</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O9" t="n">
-        <v>145629.2480748075</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R9" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T9" t="n">
-        <v>7.179716478526343</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U9" t="n">
-        <v>14785.14960645573</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.577956989247312</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J10" t="n">
-        <v>1.554119528390054</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K10" t="n">
-        <v>1463.046422442244</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L10" t="n">
-        <v>40.45654565456545</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M10" t="n">
-        <v>3999501.610795507</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N10" t="n">
-        <v>3937843.056466302</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O10" t="n">
-        <v>61658.55432920342</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R10" t="n">
-        <v>0.000150387505484869</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T10" t="n">
-        <v>2.583846953587535</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U10" t="n">
-        <v>2733.680592389675</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.620967741935484</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J11" t="n">
-        <v>10.78915469925741</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K11" t="n">
-        <v>2515.540235973597</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L11" t="n">
-        <v>152.1303630363036</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M11" t="n">
-        <v>11374850.48899891</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N11" t="n">
-        <v>11238194.40979098</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O11" t="n">
-        <v>136656.0792079208</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R11" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T11" t="n">
-        <v>18.06430758687328</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U11" t="n">
-        <v>4521.832060697078</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.420593075103495</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.389784946236559</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4831101147414734</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K12" t="n">
-        <v>380.8561793179318</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L12" t="n">
-        <v>18.57865786578658</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M12" t="n">
-        <v>977284.7700770069</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N12" t="n">
-        <v>961481.2431243125</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O12" t="n">
-        <v>15803.52695269527</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0004303690060271313</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T12" t="n">
-        <v>1.148640201987622</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U12" t="n">
-        <v>2566.020516792475</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.448924731182796</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6187507753025301</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K13" t="n">
-        <v>510.7721826182621</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L13" t="n">
-        <v>22.20902090209021</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M13" t="n">
-        <v>1253351.492849284</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N13" t="n">
-        <v>1232830.718371837</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O13" t="n">
-        <v>20520.77447744774</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T13" t="n">
-        <v>1.348511698390355</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U13" t="n">
-        <v>2453.836633045474</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.575268817204301</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J14" t="n">
-        <v>2.989729004180416</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K14" t="n">
-        <v>1338.052705170518</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L14" t="n">
-        <v>86.55005500550054</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M14" t="n">
-        <v>9840777.763476355</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N14" t="n">
-        <v>9778602.140814083</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O14" t="n">
-        <v>62175.62266226623</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.18952417157726</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R14" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T14" t="n">
-        <v>5.276371829924331</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U14" t="n">
-        <v>7354.551674571196</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1386,51 +1386,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.628713868151493</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.620967741935484</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J15" t="n">
-        <v>3.333386534873489</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K15" t="n">
-        <v>1619.013470847085</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L15" t="n">
-        <v>78.31683168316832</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M15" t="n">
-        <v>7087678.3960396</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N15" t="n">
-        <v>6961982.357535753</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O15" t="n">
-        <v>125696.0385038504</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R15" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S15" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T15" t="n">
-        <v>5.30191348359169</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U15" t="n">
-        <v>4377.776049220427</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="16">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1451,51 +1451,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.564516129032258</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J16" t="n">
-        <v>1.235497127172719</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K16" t="n">
-        <v>735.1809878987912</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L16" t="n">
-        <v>36.77227722772277</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M16" t="n">
-        <v>2652380.565456549</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N16" t="n">
-        <v>2610884.190319032</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O16" t="n">
-        <v>41496.37513751376</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0002074079836537043</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T16" t="n">
-        <v>2.245848381022551</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U16" t="n">
-        <v>3607.792651218138</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="17">
@@ -1506,61 +1506,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.513440860215054</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08506419165060494</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K17" t="n">
-        <v>1097.040440044003</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L17" t="n">
-        <v>121.6666666666667</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M17" t="n">
-        <v>15350225.29922993</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N17" t="n">
-        <v>15269826.30913091</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O17" t="n">
-        <v>80398.9900990099</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.554499000811647</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R17" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2195631176605357</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U17" t="n">
-        <v>13992.39694264526</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="18">
@@ -1610,7 +1610,7 @@
         <v>28748.73548666342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278388366571144</v>
+        <v>0.9278388366571141</v>
       </c>
       <c r="Q18" t="n">
         <v>0.6764107362832188</v>
@@ -2021,326 +2021,326 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.637577603035782</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.564516129032258</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J25" t="n">
-        <v>5.84390538944481</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K25" t="n">
-        <v>2070.168603200884</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L25" t="n">
-        <v>149.1832229580574</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M25" t="n">
-        <v>13733793.78145695</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N25" t="n">
-        <v>13621672.65011038</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O25" t="n">
-        <v>112121.1313465784</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R25" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T25" t="n">
-        <v>9.165794660319708</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U25" t="n">
-        <v>6634.142629842724</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.669354838709677</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J26" t="n">
-        <v>14.19080079636965</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K26" t="n">
-        <v>5244.965372937293</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L26" t="n">
-        <v>265.9306930693069</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M26" t="n">
-        <v>27742337.2337734</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N26" t="n">
-        <v>27141368.95929593</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O26" t="n">
-        <v>600968.2744774478</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R26" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T26" t="n">
-        <v>20.75958236310095</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U26" t="n">
-        <v>5289.327051979582</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.618279569892473</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J27" t="n">
-        <v>7.46709735138597</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K27" t="n">
-        <v>1762.03302640264</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L27" t="n">
-        <v>39.37843784378438</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M27" t="n">
-        <v>3346611.012209417</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N27" t="n">
-        <v>3299549.915435806</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O27" t="n">
-        <v>47061.09677361179</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0001842014048331127</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T27" t="n">
-        <v>12.11305361664085</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U27" t="n">
-        <v>1899.289605849129</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.594086021505376</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J28" t="n">
-        <v>3.977504096947204</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K28" t="n">
-        <v>1106.853353135313</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L28" t="n">
-        <v>185.2381738173817</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M28" t="n">
-        <v>16709444.57370737</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N28" t="n">
-        <v>16445971.06820682</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O28" t="n">
-        <v>263473.5055005501</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R28" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T28" t="n">
-        <v>7.32468488284717</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U28" t="n">
-        <v>15096.34905687875</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J29" t="n">
-        <v>8.817468730473037</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K29" t="n">
-        <v>2354.367686468646</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L29" t="n">
-        <v>162.6457645764577</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M29" t="n">
-        <v>14324724.28382839</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N29" t="n">
-        <v>14201447.9559956</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O29" t="n">
-        <v>123276.3278327833</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P29" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R29" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T29" t="n">
-        <v>15.67058466504826</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U29" t="n">
-        <v>6084.319100265209</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="30">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -774,13 +774,13 @@
         <v>8.870519132228135e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T5" t="n">
         <v>5.30191348359169</v>
       </c>
       <c r="U5" t="n">
-        <v>4377.776049220426</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="6">
@@ -1610,7 +1610,7 @@
         <v>28748.73548666342</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278388366571141</v>
+        <v>0.9278388366571143</v>
       </c>
       <c r="Q18" t="n">
         <v>0.6764107362832188</v>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,13 +774,13 @@
         <v>8.870519132228135e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T5" t="n">
         <v>5.30191348359169</v>
       </c>
       <c r="U5" t="n">
-        <v>4377.776049220427</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="6">
@@ -986,256 +986,256 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J9" t="n">
-        <v>3.478965577837015</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K9" t="n">
-        <v>3784.416073707372</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L9" t="n">
-        <v>110.0367013624439</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M9" t="n">
-        <v>8706893.798112892</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N9" t="n">
-        <v>8600561.252779894</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O9" t="n">
-        <v>106332.5453329948</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R9" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T9" t="n">
-        <v>8.041007149609982</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U9" t="n">
-        <v>2300.723183849934</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.658602150537635</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J10" t="n">
-        <v>7.897126985217273</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K10" t="n">
-        <v>2146.992089658964</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L10" t="n">
-        <v>99.53135313531354</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M10" t="n">
-        <v>9691548.173817372</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N10" t="n">
-        <v>9590504.44719472</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O10" t="n">
-        <v>101043.7266226623</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R10" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T10" t="n">
-        <v>12.802853245848</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U10" t="n">
-        <v>4514.012054584146</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.54559127289644</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.540322580645161</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J11" t="n">
-        <v>6.353318230693071</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K11" t="n">
-        <v>1237.696445544555</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L11" t="n">
-        <v>116.3949394939494</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M11" t="n">
-        <v>10170136.63256324</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N11" t="n">
-        <v>10120981.25467547</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O11" t="n">
-        <v>49155.37788778878</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R11" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T11" t="n">
-        <v>11.64483111499294</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U11" t="n">
-        <v>8216.987831849709</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.60752688172043</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7046746644898908</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K12" t="n">
-        <v>651.3228668866898</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L12" t="n">
-        <v>37.98899889988999</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M12" t="n">
-        <v>2298278.745423723</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N12" t="n">
-        <v>2275866.51440062</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O12" t="n">
-        <v>22412.23102310231</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002672206192482065</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T12" t="n">
-        <v>1.147403025201837</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U12" t="n">
-        <v>3528.632053730048</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1256,116 +1256,116 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.577956989247312</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J13" t="n">
-        <v>1.554119528390054</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K13" t="n">
-        <v>1463.046422442244</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L13" t="n">
-        <v>40.45654565456545</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M13" t="n">
-        <v>3999501.610795507</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N13" t="n">
-        <v>3937843.056466302</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O13" t="n">
-        <v>61658.55432920342</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R13" t="n">
-        <v>0.000150387505484869</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T13" t="n">
-        <v>2.583846953587535</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U13" t="n">
-        <v>2733.680592389675</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.620967741935484</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J14" t="n">
-        <v>10.78915469925741</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K14" t="n">
-        <v>2515.540235973597</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L14" t="n">
-        <v>152.1303630363036</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M14" t="n">
-        <v>11374850.48899891</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N14" t="n">
-        <v>11238194.40979098</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O14" t="n">
-        <v>136656.0792079208</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R14" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T14" t="n">
-        <v>18.06430758687328</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U14" t="n">
-        <v>4521.832060697078</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1386,506 +1386,506 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.420593075103495</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.389784946236559</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4831101147414734</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K15" t="n">
-        <v>380.8561793179318</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L15" t="n">
-        <v>18.57865786578658</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M15" t="n">
-        <v>977284.7700770069</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N15" t="n">
-        <v>961481.2431243125</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O15" t="n">
-        <v>15803.52695269527</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8705946372672551</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004303690060271313</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T15" t="n">
-        <v>1.148640201987622</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U15" t="n">
-        <v>2566.020516792475</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.448924731182796</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6187507753025301</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K16" t="n">
-        <v>510.7721826182621</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L16" t="n">
-        <v>22.20902090209021</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M16" t="n">
-        <v>1253351.492849284</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N16" t="n">
-        <v>1232830.718371837</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O16" t="n">
-        <v>20520.77447744774</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T16" t="n">
-        <v>1.348511698390355</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U16" t="n">
-        <v>2453.836633045474</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.575268817204301</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J17" t="n">
-        <v>2.989729004180416</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K17" t="n">
-        <v>1338.052705170518</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L17" t="n">
-        <v>86.55005500550054</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M17" t="n">
-        <v>9840777.763476355</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N17" t="n">
-        <v>9778602.140814083</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O17" t="n">
-        <v>62175.62266226623</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.18952417157726</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R17" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T17" t="n">
-        <v>5.276371829924331</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U17" t="n">
-        <v>7354.551674571196</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.599462365591398</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8892413135295484</v>
+        <v>1.662176316336634</v>
       </c>
       <c r="K18" t="n">
-        <v>799.7652123212325</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L18" t="n">
-        <v>38.97909790979098</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M18" t="n">
-        <v>2819911.990351496</v>
+        <v>21745500.3729373</v>
       </c>
       <c r="N18" t="n">
-        <v>2791163.254864831</v>
+        <v>21619498.96754675</v>
       </c>
       <c r="O18" t="n">
-        <v>28748.73548666342</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278388366571143</v>
+        <v>0.9870371536731076</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6764107362832188</v>
+        <v>0.308057109248377</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0002133018241973586</v>
+        <v>2.354718090134314e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T18" t="n">
-        <v>1.478391672927692</v>
+        <v>3.246151346547015</v>
       </c>
       <c r="U18" t="n">
-        <v>3525.924792561313</v>
+        <v>6431.165378693666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.551075268817204</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4988036451027072</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K19" t="n">
-        <v>517.8138943894386</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L19" t="n">
-        <v>35.74037403740374</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M19" t="n">
-        <v>1713818.918195099</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N19" t="n">
-        <v>1699123.860141752</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O19" t="n">
-        <v>14695.05805334632</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.147071598051071</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8717851629305855</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U19" t="n">
-        <v>3309.719837116163</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.519259105470924</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F20" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.661290322580645</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J20" t="n">
-        <v>5.047195443300332</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K20" t="n">
-        <v>3689.344194719472</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L20" t="n">
-        <v>173.3602860286028</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M20" t="n">
-        <v>8481121.533553353</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N20" t="n">
-        <v>8387890.666666667</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O20" t="n">
-        <v>93230.86688668867</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R20" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S20" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T20" t="n">
-        <v>9.719994103373407</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U20" t="n">
-        <v>2298.815476661763</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.594086021505376</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J21" t="n">
-        <v>4.241385833751375</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K21" t="n">
-        <v>2887.955652365237</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L21" t="n">
-        <v>107.049504950495</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M21" t="n">
-        <v>14276424.42684269</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N21" t="n">
-        <v>14202165.16611661</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O21" t="n">
-        <v>74259.26072607259</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R21" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T21" t="n">
-        <v>7.919705712496602</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U21" t="n">
-        <v>4943.436169163572</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.583333333333333</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J22" t="n">
-        <v>3.570143280528054</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K22" t="n">
-        <v>1167.338748074809</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L22" t="n">
-        <v>112.0616061606161</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M22" t="n">
-        <v>5543624.597359739</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N22" t="n">
-        <v>5487669.762376238</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O22" t="n">
-        <v>55954.83498349835</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R22" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0004023592306424291</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T22" t="n">
-        <v>7.601070758745943</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U22" t="n">
-        <v>4748.942504052369</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="23">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1906,311 +1906,311 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.486559139784946</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4380225639383938</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K23" t="n">
-        <v>1412.260883388339</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L23" t="n">
-        <v>121.5137513751375</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M23" t="n">
-        <v>14854524.53905389</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N23" t="n">
-        <v>14783219.74807481</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O23" t="n">
-        <v>71304.79097909792</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.9278388366571146</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R23" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T23" t="n">
-        <v>1.013362033548448</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U23" t="n">
-        <v>10518.2581446386</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.618279569892473</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K24" t="n">
-        <v>2417.550009900991</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L24" t="n">
-        <v>138.1463146314632</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M24" t="n">
-        <v>24180108.02805281</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N24" t="n">
-        <v>24063625.6270627</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O24" t="n">
-        <v>116482.400990099</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.808558675855097</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R24" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5529264896684616</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U24" t="n">
-        <v>10001.90603256356</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.594086021505376</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J25" t="n">
-        <v>3.977504096947204</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K25" t="n">
-        <v>1106.853353135313</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L25" t="n">
-        <v>185.2381738173817</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M25" t="n">
-        <v>16709444.57370737</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N25" t="n">
-        <v>16445971.06820682</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O25" t="n">
-        <v>263473.5055005501</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1365246445402428</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R25" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T25" t="n">
-        <v>7.32468488284717</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U25" t="n">
-        <v>15096.34905687875</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.637577603035782</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.564516129032258</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J26" t="n">
-        <v>5.84390538944481</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K26" t="n">
-        <v>2070.168603200884</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L26" t="n">
-        <v>149.1832229580574</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M26" t="n">
-        <v>13733793.78145695</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N26" t="n">
-        <v>13621672.65011038</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O26" t="n">
-        <v>112121.1313465784</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R26" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T26" t="n">
-        <v>9.165794660319708</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U26" t="n">
-        <v>6634.142629842724</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F27" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.669354838709677</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J27" t="n">
-        <v>14.19080079636965</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K27" t="n">
-        <v>5244.965372937293</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L27" t="n">
-        <v>265.9306930693069</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M27" t="n">
-        <v>27742337.2337734</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N27" t="n">
-        <v>27141368.95929593</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O27" t="n">
-        <v>600968.2744774478</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R27" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T27" t="n">
-        <v>20.75958236310095</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U27" t="n">
-        <v>5289.327051979582</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="28">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2231,51 +2231,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.629032258064516</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>8.817468730473037</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K28" t="n">
-        <v>2354.367686468646</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L28" t="n">
-        <v>162.6457645764577</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M28" t="n">
-        <v>14324724.28382839</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N28" t="n">
-        <v>14201447.9559956</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O28" t="n">
-        <v>123276.3278327833</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P28" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R28" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T28" t="n">
-        <v>15.67058466504826</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U28" t="n">
-        <v>6084.319100265209</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="29">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2296,245 +2296,635 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.618279569892473</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J29" t="n">
-        <v>7.46709735138597</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K29" t="n">
-        <v>1762.03302640264</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L29" t="n">
-        <v>39.37843784378438</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M29" t="n">
-        <v>3346611.012209417</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N29" t="n">
-        <v>3299549.915435806</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O29" t="n">
-        <v>47061.09677361179</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0001842014048331127</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T29" t="n">
-        <v>12.11305361664085</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U29" t="n">
-        <v>1899.289605849129</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.647849462365591</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J30" t="n">
-        <v>12.38809237513753</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K30" t="n">
-        <v>2089.900125412543</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L30" t="n">
-        <v>36.65676567656766</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M30" t="n">
-        <v>5715253.85918592</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N30" t="n">
-        <v>5581622.259625964</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O30" t="n">
-        <v>133631.599559956</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.05022766562717351</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001088709227809481</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T30" t="n">
-        <v>19.90934652274569</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U30" t="n">
-        <v>2734.701907373559</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.659885802549234</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.663978494623656</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J31" t="n">
-        <v>13.03638341842683</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K31" t="n">
-        <v>3867.092341034102</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L31" t="n">
-        <v>155.0957095709571</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M31" t="n">
-        <v>15551383.220022</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N31" t="n">
-        <v>15218206.4180418</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O31" t="n">
-        <v>333176.801980198</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R31" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T31" t="n">
-        <v>19.75551431484872</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U31" t="n">
-        <v>4021.466737425617</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
+        <v>0.594086021505376</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.977504096947204</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1106.853353135313</v>
+      </c>
+      <c r="L32" t="n">
+        <v>185.2381738173817</v>
+      </c>
+      <c r="M32" t="n">
+        <v>16709444.57370737</v>
+      </c>
+      <c r="N32" t="n">
+        <v>16445971.06820682</v>
+      </c>
+      <c r="O32" t="n">
+        <v>263473.5055005501</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9712826195905685</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.1365246445402428</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.24982276100033e-05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.0004906045877305042</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7.32468488284717</v>
+      </c>
+      <c r="U32" t="n">
+        <v>15096.34905687875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Antigravity CLI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gemini 4 Argon</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.637577603035782</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.01847900510277171</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0.564516129032258</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.84390538944481</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2070.168603200884</v>
+      </c>
+      <c r="L33" t="n">
+        <v>149.1832229580574</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13733793.78145695</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13621672.65011038</v>
+      </c>
+      <c r="O33" t="n">
+        <v>112121.1313465784</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8700000000000004</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1091012876743978</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4.642399712573407e-05</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.0003079834183795285</v>
+      </c>
+      <c r="T33" t="n">
+        <v>9.165794660319708</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6634.142629842724</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sonnet 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6835783373750831</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.007819822882745912</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0.669354838709677</v>
+      </c>
+      <c r="J34" t="n">
+        <v>14.19080079636965</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5244.965372937293</v>
+      </c>
+      <c r="L34" t="n">
+        <v>265.9306930693069</v>
+      </c>
+      <c r="M34" t="n">
+        <v>27742337.2337734</v>
+      </c>
+      <c r="N34" t="n">
+        <v>27141368.95929593</v>
+      </c>
+      <c r="O34" t="n">
+        <v>600968.2744774478</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9506214943317096</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.04817052590506091</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.464025765438745e-05</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.0001303303813790985</v>
+      </c>
+      <c r="T34" t="n">
+        <v>20.75958236310095</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5289.327051979582</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (max)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6164504498789397</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0209911088149403</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.618279569892473</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7.46709735138597</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1762.03302640264</v>
+      </c>
+      <c r="L35" t="n">
+        <v>39.37843784378438</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3346611.012209417</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3299549.915435806</v>
+      </c>
+      <c r="O35" t="n">
+        <v>47061.09677361179</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.9335591564904552</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.08255556622206355</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.0001842014048331127</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0003498518135823383</v>
+      </c>
+      <c r="T35" t="n">
+        <v>12.11305361664085</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1899.289605849129</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fable 5.1 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6222249615769457</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01786377121119468</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J36" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L36" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O36" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T36" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J37" t="n">
+        <v>13.03638341842683</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3867.092341034102</v>
+      </c>
+      <c r="L37" t="n">
+        <v>155.0957095709571</v>
+      </c>
+      <c r="M37" t="n">
+        <v>15551383.220022</v>
+      </c>
+      <c r="N37" t="n">
+        <v>15218206.4180418</v>
+      </c>
+      <c r="O37" t="n">
+        <v>333176.801980198</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.9500106599458848</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.05061877833513936</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4.243261150555715e-05</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.0001706413357517016</v>
+      </c>
+      <c r="T37" t="n">
+        <v>19.75551431484872</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4021.466737425617</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GPT-6.1 Sol (xhigh)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6290776736822983</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.04052542124850751</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
         <v>0.610215053763441</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J38" t="n">
         <v>1.039708101440963</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K38" t="n">
         <v>931.3823091309132</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L38" t="n">
         <v>40.05500550055005</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M38" t="n">
         <v>3212528.109451931</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N38" t="n">
         <v>3177125.49569875</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O38" t="n">
         <v>35402.61375317859</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P38" t="n">
         <v>0.9327572280083256</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q38" t="n">
         <v>0.6050521995648973</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R38" t="n">
         <v>0.0001958201305169657</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S38" t="n">
         <v>0.0006754236874751251</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T38" t="n">
         <v>1.652749962266257</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U38" t="n">
         <v>3449.204561819077</v>
       </c>
     </row>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,131 +526,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.545698924731183</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J2" t="n">
-        <v>3.467754041474145</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K2" t="n">
-        <v>1098.202911991198</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L2" t="n">
-        <v>187.4895489548955</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M2" t="n">
-        <v>16237094.3520352</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N2" t="n">
-        <v>16091465.1039604</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O2" t="n">
-        <v>145629.2480748075</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1392812659094378</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R2" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T2" t="n">
-        <v>7.179716478526343</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U2" t="n">
-        <v>14785.14960645573</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.513440860215054</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08506419165060494</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K3" t="n">
-        <v>1097.040440044003</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L3" t="n">
-        <v>121.6666666666667</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M3" t="n">
-        <v>15350225.29922993</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N3" t="n">
-        <v>15269826.30913091</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O3" t="n">
-        <v>80398.9900990099</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.554499000811647</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195631176605357</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U3" t="n">
-        <v>13992.39694264526</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -671,116 +671,116 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.564516129032258</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235497127172719</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K4" t="n">
-        <v>735.1809878987912</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L4" t="n">
-        <v>36.77227722772277</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M4" t="n">
-        <v>2652380.565456549</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N4" t="n">
-        <v>2610884.190319032</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O4" t="n">
-        <v>41496.37513751376</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002074079836537043</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T4" t="n">
-        <v>2.245848381022551</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U4" t="n">
-        <v>3607.792651218138</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.628713868151493</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J5" t="n">
-        <v>3.333386534873489</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K5" t="n">
-        <v>1619.013470847085</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L5" t="n">
-        <v>78.31683168316832</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M5" t="n">
-        <v>7087678.3960396</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N5" t="n">
-        <v>6961982.357535753</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O5" t="n">
-        <v>125696.0385038504</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R5" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T5" t="n">
-        <v>5.30191348359169</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U5" t="n">
-        <v>4377.776049220426</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="6">
@@ -791,7 +791,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -801,246 +801,246 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.443548387096774</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1759117230445546</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K6" t="n">
-        <v>1285.926851485148</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L6" t="n">
-        <v>88.64301430143014</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M6" t="n">
-        <v>10218069.24807481</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N6" t="n">
-        <v>10119727.86413641</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O6" t="n">
-        <v>98341.38393839383</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.334943267525058</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R6" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4282759302584503</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U6" t="n">
-        <v>7946.073477098422</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.451612903225807</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J7" t="n">
-        <v>2.467392200412544</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K7" t="n">
-        <v>702.7110253025301</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L7" t="n">
-        <v>188.4884488448845</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M7" t="n">
-        <v>13511073.15511551</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N7" t="n">
-        <v>13395246.74862486</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O7" t="n">
-        <v>115826.4064906491</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R7" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T7" t="n">
-        <v>5.893947035417844</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U7" t="n">
-        <v>19227.06869342024</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.588884131062264</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.594086021505376</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>4.536492777821779</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K8" t="n">
-        <v>1481.89598019802</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L8" t="n">
-        <v>78.55115511551155</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M8" t="n">
-        <v>6074134.495049492</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N8" t="n">
-        <v>6017554.665016501</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O8" t="n">
-        <v>56579.83003300329</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1298104416568739</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R8" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T8" t="n">
-        <v>7.703540541394086</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U8" t="n">
-        <v>4098.893968413241</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.350585020439431</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.46236559139785</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3646793423707372</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K9" t="n">
-        <v>1106.807743674368</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L9" t="n">
-        <v>58.5038503850385</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M9" t="n">
-        <v>5076190.689768974</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N9" t="n">
-        <v>4970717.200220022</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O9" t="n">
-        <v>105473.4895489549</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R9" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T9" t="n">
-        <v>1.040202293622358</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U9" t="n">
-        <v>4586.334635604457</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="10">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -1072,40 +1072,40 @@
         <v>0.620967741935484</v>
       </c>
       <c r="J10" t="n">
-        <v>3.478965577837015</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K10" t="n">
-        <v>3784.416073707372</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L10" t="n">
-        <v>110.0367013624439</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M10" t="n">
-        <v>8706893.798112892</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N10" t="n">
-        <v>8600561.252779894</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O10" t="n">
-        <v>106332.5453329948</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R10" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T10" t="n">
-        <v>8.041007149609982</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U10" t="n">
-        <v>2300.723183849934</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="11">
@@ -1116,191 +1116,191 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.414392761951997</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6104935163943895</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K11" t="n">
-        <v>1552.934440044002</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L11" t="n">
-        <v>75.22717271727173</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M11" t="n">
-        <v>7080866.402640261</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N11" t="n">
-        <v>6891342.883388339</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O11" t="n">
-        <v>189523.5192519252</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6787832316376182</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R11" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002668449815178645</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T11" t="n">
-        <v>1.473224371773918</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U11" t="n">
-        <v>4559.668599042484</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.658602150537635</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J12" t="n">
-        <v>7.897126985217273</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K12" t="n">
-        <v>2146.992089658964</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L12" t="n">
-        <v>99.53135313531354</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M12" t="n">
-        <v>9691548.173817372</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N12" t="n">
-        <v>9590504.44719472</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O12" t="n">
-        <v>101043.7266226623</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R12" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T12" t="n">
-        <v>12.802853245848</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U12" t="n">
-        <v>4514.012054584146</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.54559127289644</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.540322580645161</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J13" t="n">
-        <v>6.353318230693071</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K13" t="n">
-        <v>1237.696445544555</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L13" t="n">
-        <v>116.3949394939494</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M13" t="n">
-        <v>10170136.63256324</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N13" t="n">
-        <v>10120981.25467547</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O13" t="n">
-        <v>49155.37788778878</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R13" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T13" t="n">
-        <v>11.64483111499294</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U13" t="n">
-        <v>8216.987831849709</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="14">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1321,51 +1321,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.60752688172043</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7046746644898908</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K14" t="n">
-        <v>651.3228668866898</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L14" t="n">
-        <v>37.98899889988999</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M14" t="n">
-        <v>2298278.745423723</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N14" t="n">
-        <v>2275866.51440062</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O14" t="n">
-        <v>22412.23102310231</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0002672206192482065</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T14" t="n">
-        <v>1.147403025201837</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U14" t="n">
-        <v>3528.632053730048</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1386,441 +1386,441 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.335918178838533</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.416666666666667</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2263884094719471</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K15" t="n">
-        <v>837.3769053905384</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L15" t="n">
-        <v>44.01650165016502</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M15" t="n">
-        <v>3480808.845984597</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N15" t="n">
-        <v>3413192.581958196</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O15" t="n">
-        <v>67616.26402640264</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P15" t="n">
-        <v>0.95547252331787</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.483813502740997</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R15" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004011552942003655</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6739391427242943</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U15" t="n">
-        <v>4156.800627742662</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.577956989247312</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J16" t="n">
-        <v>1.554119528390054</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K16" t="n">
-        <v>1463.046422442244</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L16" t="n">
-        <v>40.45654565456545</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M16" t="n">
-        <v>3999501.610795507</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N16" t="n">
-        <v>3937843.056466302</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O16" t="n">
-        <v>61658.55432920342</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R16" t="n">
-        <v>0.000150387505484869</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T16" t="n">
-        <v>2.583846953587535</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U16" t="n">
-        <v>2733.680592389675</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.620967741935484</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J17" t="n">
-        <v>10.78915469925741</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K17" t="n">
-        <v>2515.540235973597</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L17" t="n">
-        <v>152.1303630363036</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M17" t="n">
-        <v>11374850.48899891</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N17" t="n">
-        <v>11238194.40979098</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O17" t="n">
-        <v>136656.0792079208</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R17" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T17" t="n">
-        <v>18.06430758687328</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U17" t="n">
-        <v>4521.832060697078</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F18" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.583333333333333</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J18" t="n">
-        <v>1.662176316336634</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K18" t="n">
-        <v>3381.269037953798</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5951595159516</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M18" t="n">
-        <v>21745500.3729373</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N18" t="n">
-        <v>21619498.96754675</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O18" t="n">
-        <v>126001.4053905391</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9870371536731076</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.308057109248377</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R18" t="n">
-        <v>2.354718090134314e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T18" t="n">
-        <v>3.246151346547015</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U18" t="n">
-        <v>6431.165378693666</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.420593075103495</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.389784946236559</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4831101147414734</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K19" t="n">
-        <v>380.8561793179318</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L19" t="n">
-        <v>18.57865786578658</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M19" t="n">
-        <v>977284.7700770069</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N19" t="n">
-        <v>961481.2431243125</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O19" t="n">
-        <v>15803.52695269527</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0004303690060271313</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T19" t="n">
-        <v>1.148640201987622</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U19" t="n">
-        <v>2566.020516792475</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.448924731182796</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K20" t="n">
-        <v>510.7721826182621</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L20" t="n">
-        <v>22.20902090209021</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M20" t="n">
-        <v>1253351.492849284</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N20" t="n">
-        <v>1232830.718371837</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O20" t="n">
-        <v>20520.77447744774</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7415582684181721</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0003660902437453124</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T20" t="n">
-        <v>1.348511698390355</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U20" t="n">
-        <v>2453.836633045474</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.575268817204301</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J21" t="n">
-        <v>2.989729004180416</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K21" t="n">
-        <v>1338.052705170518</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L21" t="n">
-        <v>86.55005500550054</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M21" t="n">
-        <v>9840777.763476355</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N21" t="n">
-        <v>9778602.140814083</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O21" t="n">
-        <v>62175.62266226623</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R21" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T21" t="n">
-        <v>5.276371829924331</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U21" t="n">
-        <v>7354.551674571196</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="22">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1841,51 +1841,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F22" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.336021505376344</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J22" t="n">
-        <v>2.580340961258277</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K22" t="n">
-        <v>5225.859279249448</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L22" t="n">
-        <v>120.9243929359824</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M22" t="n">
-        <v>13769015.17770419</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N22" t="n">
-        <v>12778720.50662252</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O22" t="n">
-        <v>990294.6710816775</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R22" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S22" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T22" t="n">
-        <v>7.074736286251795</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U22" t="n">
-        <v>2634.784911330742</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="23">
@@ -1896,451 +1896,451 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.599462365591398</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8892413135295484</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K23" t="n">
-        <v>799.7652123212325</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L23" t="n">
-        <v>38.97909790979098</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M23" t="n">
-        <v>2819911.990351496</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N23" t="n">
-        <v>2791163.254864831</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O23" t="n">
-        <v>28748.73548666342</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9278388366571146</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6764107362832188</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0002133018241973586</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T23" t="n">
-        <v>1.478391672927692</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U23" t="n">
-        <v>3525.924792561313</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (low)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2818428360106922</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02438275023528984</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.330645161290323</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1432474137843784</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K24" t="n">
-        <v>693.5464620462047</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L24" t="n">
-        <v>33.57535753575357</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M24" t="n">
-        <v>2412388.353135315</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N24" t="n">
-        <v>2364249.308030803</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O24" t="n">
-        <v>48139.04510451045</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9478942152323017</v>
+        <v>0.9278388366571141</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.967524778038458</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0001168314527983808</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004063791705881639</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5082528114319146</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U24" t="n">
-        <v>3478.337047553996</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.551075268817204</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4988036451027072</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K25" t="n">
-        <v>517.8138943894386</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L25" t="n">
-        <v>35.74037403740374</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M25" t="n">
-        <v>1713818.918195099</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N25" t="n">
-        <v>1699123.860141752</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O25" t="n">
-        <v>14695.05805334632</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.147071598051071</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S25" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8717851629305855</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U25" t="n">
-        <v>3309.719837116163</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.519259105470924</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F26" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.661290322580645</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J26" t="n">
-        <v>5.047195443300332</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K26" t="n">
-        <v>3689.344194719472</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L26" t="n">
-        <v>173.3602860286028</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M26" t="n">
-        <v>8481121.533553353</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N26" t="n">
-        <v>8387890.666666667</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O26" t="n">
-        <v>93230.86688668867</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1028807208486825</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R26" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S26" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T26" t="n">
-        <v>9.719994103373407</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U26" t="n">
-        <v>2298.815476661763</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.594086021505376</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J27" t="n">
-        <v>4.241385833751375</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K27" t="n">
-        <v>2887.955652365237</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L27" t="n">
-        <v>107.049504950495</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M27" t="n">
-        <v>14276424.42684269</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N27" t="n">
-        <v>14202165.16611661</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O27" t="n">
-        <v>74259.26072607259</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R27" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T27" t="n">
-        <v>7.919705712496602</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U27" t="n">
-        <v>4943.436169163572</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.583333333333333</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J28" t="n">
-        <v>3.570143280528054</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K28" t="n">
-        <v>1167.338748074809</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L28" t="n">
-        <v>112.0616061606161</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M28" t="n">
-        <v>5543624.597359739</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N28" t="n">
-        <v>5487669.762376238</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O28" t="n">
-        <v>55954.83498349835</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R28" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T28" t="n">
-        <v>7.601070758745943</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U28" t="n">
-        <v>4748.942504052369</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.486559139784946</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4380225639383938</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K29" t="n">
-        <v>1412.260883388339</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L29" t="n">
-        <v>121.5137513751375</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M29" t="n">
-        <v>14854524.53905389</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N29" t="n">
-        <v>14783219.74807481</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O29" t="n">
-        <v>71304.79097909792</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P29" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R29" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T29" t="n">
-        <v>1.013362033548448</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U29" t="n">
-        <v>10518.2581446386</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="30">
@@ -2351,451 +2351,451 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.618279569892473</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K30" t="n">
-        <v>2417.550009900991</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L30" t="n">
-        <v>138.1463146314632</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M30" t="n">
-        <v>24180108.02805281</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N30" t="n">
-        <v>24063625.6270627</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O30" t="n">
-        <v>116482.400990099</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9718803286808345</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.808558675855097</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R30" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T30" t="n">
-        <v>0.5529264896684616</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U30" t="n">
-        <v>10001.90603256356</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6290776736822983</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.04052542124850751</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.629032258064516</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J31" t="n">
-        <v>8.817468730473037</v>
+        <v>1.039708101440963</v>
       </c>
       <c r="K31" t="n">
-        <v>2354.367686468646</v>
+        <v>931.3823091309132</v>
       </c>
       <c r="L31" t="n">
-        <v>162.6457645764577</v>
+        <v>40.05500550055005</v>
       </c>
       <c r="M31" t="n">
-        <v>14324724.28382839</v>
+        <v>3212528.109451931</v>
       </c>
       <c r="N31" t="n">
-        <v>14201447.9559956</v>
+        <v>3177125.49569875</v>
       </c>
       <c r="O31" t="n">
-        <v>123276.3278327833</v>
+        <v>35402.61375317859</v>
       </c>
       <c r="P31" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9327572280083256</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.6050521995648973</v>
       </c>
       <c r="R31" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001958201305169657</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0006754236874751251</v>
       </c>
       <c r="T31" t="n">
-        <v>15.67058466504826</v>
+        <v>1.652749962266257</v>
       </c>
       <c r="U31" t="n">
-        <v>6084.319100265209</v>
+        <v>3449.204561819077</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.594086021505376</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J32" t="n">
-        <v>3.977504096947204</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K32" t="n">
-        <v>1106.853353135313</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L32" t="n">
-        <v>185.2381738173817</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M32" t="n">
-        <v>16709444.57370737</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N32" t="n">
-        <v>16445971.06820682</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O32" t="n">
-        <v>263473.5055005501</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R32" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T32" t="n">
-        <v>7.32468488284717</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U32" t="n">
-        <v>15096.34905687875</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.637577603035782</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.564516129032258</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J33" t="n">
-        <v>5.84390538944481</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K33" t="n">
-        <v>2070.168603200884</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L33" t="n">
-        <v>149.1832229580574</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M33" t="n">
-        <v>13733793.78145695</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N33" t="n">
-        <v>13621672.65011038</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O33" t="n">
-        <v>112121.1313465784</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R33" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T33" t="n">
-        <v>9.165794660319708</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U33" t="n">
-        <v>6634.142629842724</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F34" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.669354838709677</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J34" t="n">
-        <v>14.19080079636965</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K34" t="n">
-        <v>5244.965372937293</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L34" t="n">
-        <v>265.9306930693069</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M34" t="n">
-        <v>27742337.2337734</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N34" t="n">
-        <v>27141368.95929593</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O34" t="n">
-        <v>600968.2744774478</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R34" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T34" t="n">
-        <v>20.75958236310095</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U34" t="n">
-        <v>5289.327051979582</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.618279569892473</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J35" t="n">
-        <v>7.46709735138597</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K35" t="n">
-        <v>1762.03302640264</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L35" t="n">
-        <v>39.37843784378438</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M35" t="n">
-        <v>3346611.012209417</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N35" t="n">
-        <v>3299549.915435806</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O35" t="n">
-        <v>47061.09677361179</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0001842014048331127</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T35" t="n">
-        <v>12.11305361664085</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U35" t="n">
-        <v>1899.289605849129</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.647849462365591</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J36" t="n">
-        <v>12.38809237513753</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K36" t="n">
-        <v>2089.900125412543</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L36" t="n">
-        <v>36.65676567656766</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M36" t="n">
-        <v>5715253.85918592</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N36" t="n">
-        <v>5581622.259625964</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O36" t="n">
-        <v>133631.599559956</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0001088709227809481</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T36" t="n">
-        <v>19.90934652274569</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U36" t="n">
-        <v>2734.701907373559</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="37">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2816,116 +2816,116 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.659885802549234</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.663978494623656</v>
+        <v>0.647849462365591</v>
       </c>
       <c r="J37" t="n">
-        <v>13.03638341842683</v>
+        <v>12.38809237513753</v>
       </c>
       <c r="K37" t="n">
-        <v>3867.092341034102</v>
+        <v>2089.900125412543</v>
       </c>
       <c r="L37" t="n">
-        <v>155.0957095709571</v>
+        <v>36.65676567656766</v>
       </c>
       <c r="M37" t="n">
-        <v>15551383.220022</v>
+        <v>5715253.85918592</v>
       </c>
       <c r="N37" t="n">
-        <v>15218206.4180418</v>
+        <v>5581622.259625964</v>
       </c>
       <c r="O37" t="n">
-        <v>333176.801980198</v>
+        <v>133631.599559956</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.9159555838702423</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.05022766562717351</v>
       </c>
       <c r="R37" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>0.0001088709227809481</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.0002977295201865781</v>
       </c>
       <c r="T37" t="n">
-        <v>19.75551431484872</v>
+        <v>19.90934652274569</v>
       </c>
       <c r="U37" t="n">
-        <v>4021.466737425617</v>
+        <v>2734.701907373559</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Opus 5.5 (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.659885802549234</v>
       </c>
       <c r="F38" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.0102384801451021</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.610215053763441</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J38" t="n">
-        <v>1.039708101440963</v>
+        <v>13.03638341842683</v>
       </c>
       <c r="K38" t="n">
-        <v>931.3823091309132</v>
+        <v>3867.092341034102</v>
       </c>
       <c r="L38" t="n">
-        <v>40.05500550055005</v>
+        <v>155.0957095709571</v>
       </c>
       <c r="M38" t="n">
-        <v>3212528.109451931</v>
+        <v>15551383.220022</v>
       </c>
       <c r="N38" t="n">
-        <v>3177125.49569875</v>
+        <v>15218206.4180418</v>
       </c>
       <c r="O38" t="n">
-        <v>35402.61375317859</v>
+        <v>333176.801980198</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.9500106599458848</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6050521995648973</v>
+        <v>0.05061877833513936</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0001958201305169657</v>
+        <v>4.243261150555715e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0006754236874751251</v>
+        <v>0.0001706413357517016</v>
       </c>
       <c r="T38" t="n">
-        <v>1.652749962266257</v>
+        <v>19.75551431484872</v>
       </c>
       <c r="U38" t="n">
-        <v>3449.204561819077</v>
+        <v>4021.466737425617</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,66 +591,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.620967741935484</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J3" t="n">
-        <v>3.478965577837015</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K3" t="n">
-        <v>3784.416073707372</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L3" t="n">
-        <v>110.0367013624439</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M3" t="n">
-        <v>8706893.798112892</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N3" t="n">
-        <v>8600561.252779894</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O3" t="n">
-        <v>106332.5453329948</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R3" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T3" t="n">
-        <v>8.041007149609982</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U3" t="n">
-        <v>2300.723183849934</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -671,246 +671,246 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.414392761951997</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6104935163943895</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K4" t="n">
-        <v>1552.934440044002</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L4" t="n">
-        <v>75.22717271727173</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M4" t="n">
-        <v>7080866.402640261</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N4" t="n">
-        <v>6891342.883388339</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O4" t="n">
-        <v>189523.5192519252</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6787832316376182</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R4" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002668449815178645</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.473224371773918</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U4" t="n">
-        <v>4559.668599042484</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.658602150537635</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J5" t="n">
-        <v>7.897126985217273</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K5" t="n">
-        <v>2146.992089658964</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L5" t="n">
-        <v>99.53135313531354</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M5" t="n">
-        <v>9691548.173817372</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N5" t="n">
-        <v>9590504.44719472</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O5" t="n">
-        <v>101043.7266226623</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R5" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T5" t="n">
-        <v>12.802853245848</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U5" t="n">
-        <v>4514.012054584146</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.54559127289644</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.540322580645161</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J6" t="n">
-        <v>6.353318230693071</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K6" t="n">
-        <v>1237.696445544555</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L6" t="n">
-        <v>116.3949394939494</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M6" t="n">
-        <v>10170136.63256324</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N6" t="n">
-        <v>10120981.25467547</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O6" t="n">
-        <v>49155.37788778878</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R6" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T6" t="n">
-        <v>11.64483111499294</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U6" t="n">
-        <v>8216.987831849709</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.60752688172043</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7046746644898908</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K7" t="n">
-        <v>651.3228668866898</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L7" t="n">
-        <v>37.98899889988999</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M7" t="n">
-        <v>2298278.745423723</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N7" t="n">
-        <v>2275866.51440062</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O7" t="n">
-        <v>22412.23102310231</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002672206192482065</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T7" t="n">
-        <v>1.147403025201837</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U7" t="n">
-        <v>3528.632053730048</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="8">
@@ -921,191 +921,191 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.335918178838533</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.416666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2263884094719471</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K8" t="n">
-        <v>837.3769053905384</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L8" t="n">
-        <v>44.01650165016502</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M8" t="n">
-        <v>3480808.845984597</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N8" t="n">
-        <v>3413192.581958196</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O8" t="n">
-        <v>67616.26402640264</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P8" t="n">
-        <v>0.95547252331787</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.483813502740997</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R8" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004011552942003655</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6739391427242943</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U8" t="n">
-        <v>4156.800627742662</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.577956989247312</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>1.554119528390054</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K9" t="n">
-        <v>1463.046422442244</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L9" t="n">
-        <v>40.45654565456545</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M9" t="n">
-        <v>3999501.610795507</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N9" t="n">
-        <v>3937843.056466302</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O9" t="n">
-        <v>61658.55432920342</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000150387505484869</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T9" t="n">
-        <v>2.583846953587535</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U9" t="n">
-        <v>2733.680592389675</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.620967741935484</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J10" t="n">
-        <v>10.78915469925741</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K10" t="n">
-        <v>2515.540235973597</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L10" t="n">
-        <v>152.1303630363036</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M10" t="n">
-        <v>11374850.48899891</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N10" t="n">
-        <v>11238194.40979098</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O10" t="n">
-        <v>136656.0792079208</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R10" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T10" t="n">
-        <v>18.06430758687328</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U10" t="n">
-        <v>4521.832060697078</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="11">
@@ -1116,191 +1116,185 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.583333333333333</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J11" t="n">
-        <v>1.662215663091308</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K11" t="n">
-        <v>3381.269037953798</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L11" t="n">
-        <v>138.5951595159516</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M11" t="n">
-        <v>21745804.32343233</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N11" t="n">
-        <v>21619802.9180418</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O11" t="n">
-        <v>126001.4053905391</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3080498171455697</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R11" t="n">
-        <v>2.354685177223e-05</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T11" t="n">
-        <v>3.246228188888836</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U11" t="n">
-        <v>6431.255271125063</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.420593075103495</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.389784946236559</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.4831101147414734</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>380.8561793179318</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L12" t="n">
-        <v>18.57865786578658</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M12" t="n">
-        <v>977284.7700770069</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N12" t="n">
-        <v>961481.2431243125</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O12" t="n">
-        <v>15803.52695269527</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9307814644010347</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.8705946372672551</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0.0004303690060271313</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001104335699257203</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.148640201987622</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>2566.020516792475</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.448924731182796</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K13" t="n">
-        <v>510.7721826182621</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L13" t="n">
-        <v>22.20902090209021</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M13" t="n">
-        <v>1253351.492849284</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N13" t="n">
-        <v>1232830.718371837</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O13" t="n">
-        <v>20520.77447744774</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T13" t="n">
-        <v>1.348511698390355</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U13" t="n">
-        <v>2453.836633045474</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="14">
@@ -1311,7 +1305,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1321,116 +1315,116 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.575268817204301</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J14" t="n">
-        <v>2.989729004180416</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K14" t="n">
-        <v>1338.052705170518</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L14" t="n">
-        <v>86.55005500550054</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M14" t="n">
-        <v>9840777.763476355</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N14" t="n">
-        <v>9778602.140814083</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O14" t="n">
-        <v>62175.62266226623</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.18952417157726</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R14" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T14" t="n">
-        <v>5.276371829924331</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U14" t="n">
-        <v>7354.551674571196</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.336021505376344</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J15" t="n">
-        <v>2.580340961258277</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K15" t="n">
-        <v>5225.859279249448</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L15" t="n">
-        <v>120.9243929359824</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M15" t="n">
-        <v>13769015.17770419</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N15" t="n">
-        <v>12778720.50662252</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O15" t="n">
-        <v>990294.6710816775</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R15" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T15" t="n">
-        <v>7.074736286251795</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U15" t="n">
-        <v>2634.784911330742</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="16">
@@ -1441,7 +1435,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1451,376 +1445,376 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.350585020439431</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.46236559139785</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3646793423707372</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K16" t="n">
-        <v>1106.807743674368</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L16" t="n">
-        <v>58.5038503850385</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M16" t="n">
-        <v>5076190.689768974</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N16" t="n">
-        <v>4970717.200220022</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O16" t="n">
-        <v>105473.4895489549</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R16" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T16" t="n">
-        <v>1.040202293622358</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U16" t="n">
-        <v>4586.334635604457</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.545698924731183</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J17" t="n">
-        <v>3.467754041474145</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K17" t="n">
-        <v>1098.202911991198</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L17" t="n">
-        <v>187.4895489548955</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M17" t="n">
-        <v>16237094.3520352</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N17" t="n">
-        <v>16091465.1039604</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O17" t="n">
-        <v>145629.2480748075</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R17" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T17" t="n">
-        <v>7.179716478526343</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U17" t="n">
-        <v>14785.14960645573</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.588884131062264</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.594086021505376</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J18" t="n">
-        <v>4.536492777821779</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K18" t="n">
-        <v>1481.89598019802</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L18" t="n">
-        <v>78.55115511551155</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M18" t="n">
-        <v>6074134.495049492</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N18" t="n">
-        <v>6017554.665016501</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O18" t="n">
-        <v>56579.83003300329</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R18" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T18" t="n">
-        <v>7.703540541394086</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U18" t="n">
-        <v>4098.893968413241</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.451612903225807</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J19" t="n">
-        <v>2.467392200412544</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K19" t="n">
-        <v>702.7110253025301</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L19" t="n">
-        <v>188.4884488448845</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M19" t="n">
-        <v>13511073.15511551</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N19" t="n">
-        <v>13395246.74862486</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O19" t="n">
-        <v>115826.4064906491</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R19" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T19" t="n">
-        <v>5.893947035417844</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U19" t="n">
-        <v>19227.06869342024</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.443548387096774</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1759117230445546</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K20" t="n">
-        <v>1285.926851485148</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L20" t="n">
-        <v>88.64301430143014</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M20" t="n">
-        <v>10218069.24807481</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N20" t="n">
-        <v>10119727.86413641</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O20" t="n">
-        <v>98341.38393839383</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R20" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4282759302584503</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U20" t="n">
-        <v>7946.073477098422</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.628713868151493</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J21" t="n">
-        <v>3.333386534873489</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K21" t="n">
-        <v>1619.013470847085</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L21" t="n">
-        <v>78.31683168316832</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M21" t="n">
-        <v>7087678.3960396</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N21" t="n">
-        <v>6961982.357535753</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O21" t="n">
-        <v>125696.0385038504</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1886111501243448</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R21" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T21" t="n">
-        <v>5.30191348359169</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U21" t="n">
-        <v>4377.776049220426</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="22">
@@ -1831,7 +1825,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1841,246 +1835,246 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.564516129032258</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J22" t="n">
-        <v>1.235497127172719</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K22" t="n">
-        <v>735.1809878987912</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L22" t="n">
-        <v>36.77227722772277</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M22" t="n">
-        <v>2652380.565456549</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N22" t="n">
-        <v>2610884.190319032</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O22" t="n">
-        <v>41496.37513751376</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0002074079836537043</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T22" t="n">
-        <v>2.245848381022551</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U22" t="n">
-        <v>3607.792651218138</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.513440860215054</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08506419165060494</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K23" t="n">
-        <v>1097.040440044003</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L23" t="n">
-        <v>121.6666666666667</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M23" t="n">
-        <v>15350225.29922993</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N23" t="n">
-        <v>15269826.30913091</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O23" t="n">
-        <v>80398.9900990099</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.554499000811647</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R23" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2195631176605357</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U23" t="n">
-        <v>13992.39694264526</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.599462365591398</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8892413135295484</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K24" t="n">
-        <v>799.7652123212325</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L24" t="n">
-        <v>38.97909790979098</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M24" t="n">
-        <v>2819911.990351496</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N24" t="n">
-        <v>2791163.254864831</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O24" t="n">
-        <v>28748.73548666342</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9278388366571141</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6764107362832188</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0002133018241973586</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T24" t="n">
-        <v>1.478391672927692</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U24" t="n">
-        <v>3525.924792561313</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (low)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.2818428360106922</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02438275023528984</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.330645161290323</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1432474137843784</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K25" t="n">
-        <v>693.5464620462047</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L25" t="n">
-        <v>33.57535753575357</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M25" t="n">
-        <v>2412388.353135315</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N25" t="n">
-        <v>2364249.308030803</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O25" t="n">
-        <v>48139.04510451045</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9478942152323017</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.967524778038458</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0001168314527983808</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004063791705881639</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5082528114319146</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U25" t="n">
-        <v>3478.337047553996</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="26">
@@ -2091,7 +2085,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -2101,441 +2095,441 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.551075268817204</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4988036451027072</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K26" t="n">
-        <v>517.8138943894386</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L26" t="n">
-        <v>35.74037403740374</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M26" t="n">
-        <v>1713818.918195099</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N26" t="n">
-        <v>1699123.860141752</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O26" t="n">
-        <v>14695.05805334632</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9278388366571144</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.147071598051071</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8717851629305855</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U26" t="n">
-        <v>3309.719837116163</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.519259105470924</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F27" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.661290322580645</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J27" t="n">
-        <v>5.047195443300332</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K27" t="n">
-        <v>3689.344194719472</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L27" t="n">
-        <v>173.3602860286028</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M27" t="n">
-        <v>8481121.533553353</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N27" t="n">
-        <v>8387890.666666667</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O27" t="n">
-        <v>93230.86688668867</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1028807208486825</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R27" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S27" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T27" t="n">
-        <v>9.719994103373407</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U27" t="n">
-        <v>2298.815476661763</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.594086021505376</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J28" t="n">
-        <v>4.241385833751375</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K28" t="n">
-        <v>2887.955652365237</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L28" t="n">
-        <v>107.049504950495</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M28" t="n">
-        <v>14276424.42684269</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N28" t="n">
-        <v>14202165.16611661</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O28" t="n">
-        <v>74259.26072607259</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1262673180421449</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R28" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S28" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T28" t="n">
-        <v>7.919705712496602</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U28" t="n">
-        <v>4943.436169163572</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.583333333333333</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J29" t="n">
-        <v>3.570143280528054</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K29" t="n">
-        <v>1167.338748074809</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L29" t="n">
-        <v>112.0616061606161</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M29" t="n">
-        <v>5543624.597359739</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N29" t="n">
-        <v>5487669.762376238</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O29" t="n">
-        <v>55954.83498349835</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R29" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T29" t="n">
-        <v>7.601070758745943</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U29" t="n">
-        <v>4748.942504052369</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.486559139784946</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4380225639383938</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K30" t="n">
-        <v>1412.260883388339</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L30" t="n">
-        <v>121.5137513751375</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M30" t="n">
-        <v>14854524.53905389</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N30" t="n">
-        <v>14783219.74807481</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O30" t="n">
-        <v>71304.79097909792</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R30" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T30" t="n">
-        <v>1.013362033548448</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U30" t="n">
-        <v>10518.2581446386</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.610215053763441</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J31" t="n">
-        <v>1.039708101440963</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K31" t="n">
-        <v>931.3823091309132</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L31" t="n">
-        <v>40.05500550055005</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M31" t="n">
-        <v>3212528.109451931</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N31" t="n">
-        <v>3177125.49569875</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O31" t="n">
-        <v>35402.61375317859</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.6050521995648973</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0001958201305169657</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0006754236874751251</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T31" t="n">
-        <v>1.652749962266257</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U31" t="n">
-        <v>3449.204561819077</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F32" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.669354838709677</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J32" t="n">
-        <v>14.19080079636965</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K32" t="n">
-        <v>5244.965372937293</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L32" t="n">
-        <v>265.9306930693069</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M32" t="n">
-        <v>27742337.2337734</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N32" t="n">
-        <v>27141368.95929593</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O32" t="n">
-        <v>600968.2744774478</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R32" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T32" t="n">
-        <v>20.75958236310095</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U32" t="n">
-        <v>5289.327051979582</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="33">
@@ -2546,7 +2540,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2556,116 +2550,116 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6290776736822983</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.04052542124850751</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.618279569892473</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J33" t="n">
-        <v>7.46709735138597</v>
+        <v>1.039708101440963</v>
       </c>
       <c r="K33" t="n">
-        <v>1762.03302640264</v>
+        <v>931.3823091309132</v>
       </c>
       <c r="L33" t="n">
-        <v>39.37843784378438</v>
+        <v>40.05500550055005</v>
       </c>
       <c r="M33" t="n">
-        <v>3346611.012209417</v>
+        <v>3212528.109451931</v>
       </c>
       <c r="N33" t="n">
-        <v>3299549.915435806</v>
+        <v>3177125.49569875</v>
       </c>
       <c r="O33" t="n">
-        <v>47061.09677361179</v>
+        <v>35402.61375317859</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9327572280083256</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.6050521995648973</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0001842014048331127</v>
+        <v>0.0001958201305169657</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0006754236874751251</v>
       </c>
       <c r="T33" t="n">
-        <v>12.11305361664085</v>
+        <v>1.652749962266257</v>
       </c>
       <c r="U33" t="n">
-        <v>1899.289605849129</v>
+        <v>3449.204561819077</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.637577603035782</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.564516129032258</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J34" t="n">
-        <v>5.84390538944481</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K34" t="n">
-        <v>2070.168603200884</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L34" t="n">
-        <v>149.1832229580574</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M34" t="n">
-        <v>13733793.78145695</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N34" t="n">
-        <v>13621672.65011038</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O34" t="n">
-        <v>112121.1313465784</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R34" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T34" t="n">
-        <v>9.165794660319708</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U34" t="n">
-        <v>6634.142629842724</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="35">
@@ -2676,7 +2670,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2686,245 +2680,375 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.6349675266318143</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.02829093785912806</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.594086021505376</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J35" t="n">
-        <v>3.977504096947204</v>
+        <v>8.052232502530256</v>
       </c>
       <c r="K35" t="n">
-        <v>1106.853353135313</v>
+        <v>1346.652125412539</v>
       </c>
       <c r="L35" t="n">
-        <v>185.2381738173817</v>
+        <v>191.9551493610899</v>
       </c>
       <c r="M35" t="n">
-        <v>16709444.57370737</v>
+        <v>15016299.67931794</v>
       </c>
       <c r="N35" t="n">
-        <v>16445971.06820682</v>
+        <v>14926250.65016502</v>
       </c>
       <c r="O35" t="n">
-        <v>263473.5055005501</v>
+        <v>90049.02915291529</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.935735212525825</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.07885608449983135</v>
       </c>
       <c r="R35" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>4.228521940770533e-05</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0004715156309854677</v>
       </c>
       <c r="T35" t="n">
-        <v>7.32468488284717</v>
+        <v>12.68132961892292</v>
       </c>
       <c r="U35" t="n">
-        <v>15096.34905687875</v>
+        <v>11150.83798996551</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.629032258064516</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J36" t="n">
-        <v>8.817468730473037</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K36" t="n">
-        <v>2354.367686468646</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L36" t="n">
-        <v>162.6457645764577</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M36" t="n">
-        <v>14324724.28382839</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N36" t="n">
-        <v>14201447.9559956</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O36" t="n">
-        <v>123276.3278327833</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P36" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R36" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T36" t="n">
-        <v>15.67058466504826</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U36" t="n">
-        <v>6084.319100265209</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.647849462365591</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J37" t="n">
-        <v>12.38809237513753</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K37" t="n">
-        <v>2089.900125412543</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L37" t="n">
-        <v>36.65676567656766</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M37" t="n">
-        <v>5715253.85918592</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N37" t="n">
-        <v>5581622.259625964</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O37" t="n">
-        <v>133631.599559956</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0001088709227809481</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T37" t="n">
-        <v>19.90934652274569</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U37" t="n">
-        <v>2734.701907373559</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.659885802549234</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
+        <v>0.629032258064516</v>
+      </c>
+      <c r="J38" t="n">
+        <v>8.817468730473037</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2354.367686468646</v>
+      </c>
+      <c r="L38" t="n">
+        <v>162.6457645764577</v>
+      </c>
+      <c r="M38" t="n">
+        <v>14324724.28382839</v>
+      </c>
+      <c r="N38" t="n">
+        <v>14201447.9559956</v>
+      </c>
+      <c r="O38" t="n">
+        <v>123276.3278327833</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.938882976190201</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.06381382835258244</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.928008839275821e-05</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.0002389925920681645</v>
+      </c>
+      <c r="T38" t="n">
+        <v>15.67058466504826</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6084.319100265209</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fable 5.1 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6222249615769457</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.01786377121119468</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J39" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L39" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O39" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T39" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
         <v>0.663978494623656</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J40" t="n">
         <v>13.03638341842683</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K40" t="n">
         <v>3867.092341034102</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L40" t="n">
         <v>155.0957095709571</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M40" t="n">
         <v>15551383.220022</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N40" t="n">
         <v>15218206.4180418</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O40" t="n">
         <v>333176.801980198</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P40" t="n">
         <v>0.9500106599458848</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q40" t="n">
         <v>0.05061877833513936</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R40" t="n">
         <v>4.243261150555715e-05</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S40" t="n">
         <v>0.0001706413357517016</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T40" t="n">
         <v>19.75551431484872</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U40" t="n">
         <v>4021.466737425617</v>
       </c>
     </row>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,131 +526,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.618279569892473</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2380461072079206</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K2" t="n">
-        <v>2417.550009900991</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L2" t="n">
-        <v>138.1463146314632</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M2" t="n">
-        <v>24180108.02805281</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N2" t="n">
-        <v>24063625.6270627</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O2" t="n">
-        <v>116482.400990099</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.808558675855097</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R2" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5529264896684616</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U2" t="n">
-        <v>10001.90603256356</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.482993172759088</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.545698924731183</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J3" t="n">
-        <v>3.467754041474145</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K3" t="n">
-        <v>1098.202911991198</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L3" t="n">
-        <v>187.4895489548955</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M3" t="n">
-        <v>16237094.3520352</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N3" t="n">
-        <v>16091465.1039604</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O3" t="n">
-        <v>145629.2480748075</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R3" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T3" t="n">
-        <v>7.179716478526343</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U3" t="n">
-        <v>14785.14960645573</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -671,116 +671,116 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.336021505376344</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J4" t="n">
-        <v>2.580340961258277</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K4" t="n">
-        <v>5225.859279249448</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L4" t="n">
-        <v>120.9243929359824</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M4" t="n">
-        <v>13769015.17770419</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N4" t="n">
-        <v>12778720.50662252</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O4" t="n">
-        <v>990294.6710816775</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R4" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T4" t="n">
-        <v>7.074736286251795</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U4" t="n">
-        <v>2634.784911330742</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.575268817204301</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J5" t="n">
-        <v>2.989729004180416</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K5" t="n">
-        <v>1338.052705170518</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L5" t="n">
-        <v>86.55005500550054</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M5" t="n">
-        <v>9840777.763476355</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N5" t="n">
-        <v>9778602.140814083</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O5" t="n">
-        <v>62175.62266226623</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R5" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T5" t="n">
-        <v>5.276371829924331</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U5" t="n">
-        <v>7354.551674571196</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="6">
@@ -791,7 +791,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -801,311 +801,305 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.448924731182796</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K6" t="n">
-        <v>510.7721826182621</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L6" t="n">
-        <v>22.20902090209021</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M6" t="n">
-        <v>1253351.492849284</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N6" t="n">
-        <v>1232830.718371837</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O6" t="n">
-        <v>20520.77447744774</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003660902437453124</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T6" t="n">
-        <v>1.348511698390355</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U6" t="n">
-        <v>2453.836633045474</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.420593075103495</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.389784946236559</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4831101147414734</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K7" t="n">
-        <v>380.8561793179318</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L7" t="n">
-        <v>18.57865786578658</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M7" t="n">
-        <v>977284.7700770069</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N7" t="n">
-        <v>961481.2431243125</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O7" t="n">
-        <v>15803.52695269527</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004303690060271313</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T7" t="n">
-        <v>1.148640201987622</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U7" t="n">
-        <v>2566.020516792475</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.583333333333333</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J8" t="n">
-        <v>1.662215663091308</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K8" t="n">
-        <v>3381.269037953798</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L8" t="n">
-        <v>138.5951595159516</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M8" t="n">
-        <v>21745804.32343233</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N8" t="n">
-        <v>21619802.9180418</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O8" t="n">
-        <v>126001.4053905391</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R8" t="n">
-        <v>2.354685177223e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T8" t="n">
-        <v>3.246228188888836</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U8" t="n">
-        <v>6431.255271125063</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J9" t="n">
-        <v>10.78915469925741</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K9" t="n">
-        <v>2515.540235973597</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L9" t="n">
-        <v>152.1303630363036</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M9" t="n">
-        <v>11374850.48899891</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N9" t="n">
-        <v>11238194.40979098</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O9" t="n">
-        <v>136656.0792079208</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R9" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T9" t="n">
-        <v>18.06430758687328</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U9" t="n">
-        <v>4521.832060697078</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.577956989247312</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.554119528390054</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1463.046422442244</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L10" t="n">
-        <v>40.45654565456545</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M10" t="n">
-        <v>3999501.610795507</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N10" t="n">
-        <v>3937843.056466302</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O10" t="n">
-        <v>61658.55432920342</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9281954641245814</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.3870198266238458</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>0.000150387505484869</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004111114050818821</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.583846953587535</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>2733.680592389675</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="11">
@@ -1176,255 +1170,261 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6803093740718634</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02365082421477135</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.68010752688172</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>0.577956989247312</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.554119528390054</v>
+      </c>
       <c r="K12" t="n">
-        <v>1725.883295805741</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L12" t="n">
-        <v>194.9635761589404</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M12" t="n">
-        <v>15002315.66997792</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N12" t="n">
-        <v>14917198.82339956</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O12" t="n">
-        <v>85116.84657836644</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9637709553156532</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>0.9281954641245814</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3870198266238458</v>
+      </c>
       <c r="R12" t="n">
-        <v>4.534695769888867e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003941804035795226</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
+        <v>0.0004111114050818821</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.583846953587535</v>
+      </c>
       <c r="U12" t="n">
-        <v>8692.543526226078</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.60752688172043</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7046746644898908</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K13" t="n">
-        <v>651.3228668866898</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L13" t="n">
-        <v>37.98899889988999</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M13" t="n">
-        <v>2298278.745423723</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N13" t="n">
-        <v>2275866.51440062</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O13" t="n">
-        <v>22412.23102310231</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0002672206192482065</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T13" t="n">
-        <v>1.147403025201837</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U13" t="n">
-        <v>3528.632053730048</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.54559127289644</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.540322580645161</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>6.353318230693071</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K14" t="n">
-        <v>1237.696445544555</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L14" t="n">
-        <v>116.3949394939494</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M14" t="n">
-        <v>10170136.63256324</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N14" t="n">
-        <v>10120981.25467547</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O14" t="n">
-        <v>49155.37788778878</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R14" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T14" t="n">
-        <v>11.64483111499294</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U14" t="n">
-        <v>8216.987831849709</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.658602150537635</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J15" t="n">
-        <v>7.897126985217273</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K15" t="n">
-        <v>2146.992089658964</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L15" t="n">
-        <v>99.53135313531354</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M15" t="n">
-        <v>9691548.173817372</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N15" t="n">
-        <v>9590504.44719472</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O15" t="n">
-        <v>101043.7266226623</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R15" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T15" t="n">
-        <v>12.802853245848</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U15" t="n">
-        <v>4514.012054584146</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="16">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1445,116 +1445,116 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.414392761951997</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6104935163943895</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K16" t="n">
-        <v>1552.934440044002</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L16" t="n">
-        <v>75.22717271727173</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M16" t="n">
-        <v>7080866.402640261</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N16" t="n">
-        <v>6891342.883388339</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O16" t="n">
-        <v>189523.5192519252</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6787832316376182</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R16" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0002668449815178645</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T16" t="n">
-        <v>1.473224371773918</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U16" t="n">
-        <v>4559.668599042484</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.620967741935484</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J17" t="n">
-        <v>3.478965577837015</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K17" t="n">
-        <v>3784.416073707372</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L17" t="n">
-        <v>110.0367013624439</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M17" t="n">
-        <v>8706893.798112892</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N17" t="n">
-        <v>8600561.252779894</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O17" t="n">
-        <v>106332.5453329948</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R17" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T17" t="n">
-        <v>8.041007149609982</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U17" t="n">
-        <v>2300.723183849934</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="18">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1575,441 +1575,441 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.350585020439431</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.46236559139785</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3646793423707372</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K18" t="n">
-        <v>1106.807743674368</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L18" t="n">
-        <v>58.5038503850385</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M18" t="n">
-        <v>5076190.689768974</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N18" t="n">
-        <v>4970717.200220022</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O18" t="n">
-        <v>105473.4895489549</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R18" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0003167533137015853</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.040202293622358</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U18" t="n">
-        <v>4586.334635604457</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.588884131062264</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.594086021505376</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J19" t="n">
-        <v>4.536492777821779</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K19" t="n">
-        <v>1481.89598019802</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L19" t="n">
-        <v>78.55115511551155</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M19" t="n">
-        <v>6074134.495049492</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N19" t="n">
-        <v>6017554.665016501</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O19" t="n">
-        <v>56579.83003300329</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1298104416568739</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R19" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T19" t="n">
-        <v>7.703540541394086</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U19" t="n">
-        <v>4098.893968413241</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.451612903225807</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J20" t="n">
-        <v>2.467392200412544</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K20" t="n">
-        <v>702.7110253025301</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L20" t="n">
-        <v>188.4884488448845</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M20" t="n">
-        <v>13511073.15511551</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N20" t="n">
-        <v>13395246.74862486</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O20" t="n">
-        <v>115826.4064906491</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R20" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T20" t="n">
-        <v>5.893947035417844</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U20" t="n">
-        <v>19227.06869342024</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.443548387096774</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1759117230445546</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K21" t="n">
-        <v>1285.926851485148</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L21" t="n">
-        <v>88.64301430143014</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M21" t="n">
-        <v>10218069.24807481</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N21" t="n">
-        <v>10119727.86413641</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O21" t="n">
-        <v>98341.38393839383</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R21" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4282759302584503</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U21" t="n">
-        <v>7946.073477098422</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.628713868151493</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.620967741935484</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J22" t="n">
-        <v>3.333386534873489</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K22" t="n">
-        <v>1619.013470847085</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L22" t="n">
-        <v>78.31683168316832</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M22" t="n">
-        <v>7087678.3960396</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N22" t="n">
-        <v>6961982.357535753</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O22" t="n">
-        <v>125696.0385038504</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R22" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T22" t="n">
-        <v>5.30191348359169</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U22" t="n">
-        <v>4377.776049220427</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.594086021505376</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J23" t="n">
-        <v>3.977504096947204</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K23" t="n">
-        <v>1106.853353135313</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L23" t="n">
-        <v>185.2381738173817</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M23" t="n">
-        <v>16709444.57370737</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N23" t="n">
-        <v>16445971.06820682</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O23" t="n">
-        <v>263473.5055005501</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T23" t="n">
-        <v>7.32468488284717</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U23" t="n">
-        <v>15096.34905687875</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.564516129032258</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J24" t="n">
-        <v>1.235497127172719</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K24" t="n">
-        <v>735.1809878987912</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L24" t="n">
-        <v>36.77227722772277</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M24" t="n">
-        <v>2652380.565456549</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N24" t="n">
-        <v>2610884.190319032</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O24" t="n">
-        <v>41496.37513751376</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4452660332950404</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0002074079836537043</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T24" t="n">
-        <v>2.245848381022551</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U24" t="n">
-        <v>3607.792651218138</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="25">
@@ -2020,451 +2020,451 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.513440860215054</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J25" t="n">
-        <v>0.08506419165060494</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K25" t="n">
-        <v>1097.040440044003</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L25" t="n">
-        <v>121.6666666666667</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M25" t="n">
-        <v>15350225.29922993</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N25" t="n">
-        <v>15269826.30913091</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O25" t="n">
-        <v>80398.9900990099</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9278388366571146</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.554499000811647</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R25" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2195631176605357</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U25" t="n">
-        <v>13992.39694264526</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.599462365591398</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8892413135295484</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K26" t="n">
-        <v>799.7652123212325</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L26" t="n">
-        <v>38.97909790979098</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M26" t="n">
-        <v>2819911.990351496</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N26" t="n">
-        <v>2791163.254864831</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O26" t="n">
-        <v>28748.73548666342</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9278388366571144</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6764107362832188</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0002133018241973586</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T26" t="n">
-        <v>1.478391672927692</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U26" t="n">
-        <v>3525.924792561313</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (low)</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2818428360106922</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02438275023528984</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.330645161290323</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1432474137843784</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K27" t="n">
-        <v>693.5464620462047</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L27" t="n">
-        <v>33.57535753575357</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M27" t="n">
-        <v>2412388.353135315</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N27" t="n">
-        <v>2364249.308030803</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O27" t="n">
-        <v>48139.04510451045</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9478942152323017</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.967524778038458</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0001168314527983808</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0004063791705881639</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5082528114319146</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U27" t="n">
-        <v>3478.337047553996</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.551075268817204</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4988036451027072</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K28" t="n">
-        <v>517.8138943894386</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L28" t="n">
-        <v>35.74037403740374</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M28" t="n">
-        <v>1713818.918195099</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N28" t="n">
-        <v>1699123.860141752</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O28" t="n">
-        <v>14695.05805334632</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.147071598051071</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0003338529457384175</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8717851629305855</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U28" t="n">
-        <v>3309.719837116163</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.519259105470924</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.661290322580645</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J29" t="n">
-        <v>5.047195443300332</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K29" t="n">
-        <v>3689.344194719472</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L29" t="n">
-        <v>173.3602860286028</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M29" t="n">
-        <v>8481121.533553353</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N29" t="n">
-        <v>8387890.666666667</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O29" t="n">
-        <v>93230.86688668867</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R29" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T29" t="n">
-        <v>9.719994103373407</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U29" t="n">
-        <v>2298.815476661763</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.594086021505376</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J30" t="n">
-        <v>4.241385833751375</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K30" t="n">
-        <v>2887.955652365237</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L30" t="n">
-        <v>107.049504950495</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M30" t="n">
-        <v>14276424.42684269</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N30" t="n">
-        <v>14202165.16611661</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O30" t="n">
-        <v>74259.26072607259</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R30" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T30" t="n">
-        <v>7.919705712496602</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U30" t="n">
-        <v>4943.436169163572</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.583333333333333</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J31" t="n">
-        <v>3.570143280528054</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K31" t="n">
-        <v>1167.338748074809</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L31" t="n">
-        <v>112.0616061606161</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M31" t="n">
-        <v>5543624.597359739</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N31" t="n">
-        <v>5487669.762376238</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O31" t="n">
-        <v>55954.83498349835</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R31" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T31" t="n">
-        <v>7.601070758745943</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U31" t="n">
-        <v>4748.942504052369</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="32">
@@ -2475,191 +2475,191 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.486559139784946</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4380225639383938</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K32" t="n">
-        <v>1412.260883388339</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L32" t="n">
-        <v>121.5137513751375</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M32" t="n">
-        <v>14854524.53905389</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N32" t="n">
-        <v>14783219.74807481</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O32" t="n">
-        <v>71304.79097909792</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P32" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9868141561395799</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R32" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T32" t="n">
-        <v>1.013362033548448</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U32" t="n">
-        <v>10518.2581446386</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.610215053763441</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J33" t="n">
-        <v>1.039708101440963</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K33" t="n">
-        <v>931.3823091309132</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L33" t="n">
-        <v>40.05500550055005</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M33" t="n">
-        <v>3212528.109451931</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N33" t="n">
-        <v>3177125.49569875</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O33" t="n">
-        <v>35402.61375317859</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.6050521995648973</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0001958201305169657</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0006754236874751251</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T33" t="n">
-        <v>1.652749962266257</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U33" t="n">
-        <v>3449.204561819077</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.618279569892473</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J34" t="n">
-        <v>7.46709735138597</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K34" t="n">
-        <v>1762.03302640264</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L34" t="n">
-        <v>39.37843784378438</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M34" t="n">
-        <v>3346611.012209417</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N34" t="n">
-        <v>3299549.915435806</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O34" t="n">
-        <v>47061.09677361179</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0001842014048331127</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T34" t="n">
-        <v>12.11305361664085</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U34" t="n">
-        <v>1899.289605849129</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="35">
@@ -2730,196 +2730,196 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F36" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.669354838709677</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J36" t="n">
-        <v>14.19080079636965</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K36" t="n">
-        <v>5244.965372937293</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L36" t="n">
-        <v>265.9306930693069</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M36" t="n">
-        <v>27742337.2337734</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N36" t="n">
-        <v>27141368.95929593</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O36" t="n">
-        <v>600968.2744774478</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R36" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T36" t="n">
-        <v>20.75958236310095</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U36" t="n">
-        <v>5289.327051979582</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.637577603035782</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.564516129032258</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J37" t="n">
-        <v>5.843905389444815</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K37" t="n">
-        <v>2070.168603200884</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L37" t="n">
-        <v>149.1832229580574</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M37" t="n">
-        <v>13733793.78145695</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N37" t="n">
-        <v>13621672.65011038</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O37" t="n">
-        <v>112121.1313465784</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1091012876743977</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R37" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T37" t="n">
-        <v>9.165794660319715</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U37" t="n">
-        <v>6634.142629842724</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.629032258064516</v>
+        <v>0.647849462365591</v>
       </c>
       <c r="J38" t="n">
-        <v>8.817468730473037</v>
+        <v>12.38809237513753</v>
       </c>
       <c r="K38" t="n">
-        <v>2354.367686468646</v>
+        <v>2089.900125412543</v>
       </c>
       <c r="L38" t="n">
-        <v>162.6457645764577</v>
+        <v>36.65676567656766</v>
       </c>
       <c r="M38" t="n">
-        <v>14324724.28382839</v>
+        <v>5715253.85918592</v>
       </c>
       <c r="N38" t="n">
-        <v>14201447.9559956</v>
+        <v>5581622.259625964</v>
       </c>
       <c r="O38" t="n">
-        <v>123276.3278327833</v>
+        <v>133631.599559956</v>
       </c>
       <c r="P38" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9159555838702423</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.05022766562717351</v>
       </c>
       <c r="R38" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001088709227809481</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0002977295201865781</v>
       </c>
       <c r="T38" t="n">
-        <v>15.67058466504826</v>
+        <v>19.90934652274569</v>
       </c>
       <c r="U38" t="n">
-        <v>6084.319100265209</v>
+        <v>2734.701907373559</v>
       </c>
     </row>
     <row r="39">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Opus 5.5 (max)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2940,116 +2940,116 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.659885802549234</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.0102384801451021</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.647849462365591</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J39" t="n">
-        <v>12.38809237513753</v>
+        <v>13.03638341842683</v>
       </c>
       <c r="K39" t="n">
-        <v>2089.900125412543</v>
+        <v>3867.092341034102</v>
       </c>
       <c r="L39" t="n">
-        <v>36.65676567656766</v>
+        <v>155.0957095709571</v>
       </c>
       <c r="M39" t="n">
-        <v>5715253.85918592</v>
+        <v>15551383.220022</v>
       </c>
       <c r="N39" t="n">
-        <v>5581622.259625964</v>
+        <v>15218206.4180418</v>
       </c>
       <c r="O39" t="n">
-        <v>133631.599559956</v>
+        <v>333176.801980198</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9500106599458848</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.05061877833513936</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0001088709227809481</v>
+        <v>4.243261150555715e-05</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0001706413357517016</v>
       </c>
       <c r="T39" t="n">
-        <v>19.90934652274569</v>
+        <v>19.75551431484872</v>
       </c>
       <c r="U39" t="n">
-        <v>2734.701907373559</v>
+        <v>4021.466737425617</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.659885802549234</v>
+        <v>0.6290776736822983</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.04052542124850751</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.663978494623656</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J40" t="n">
-        <v>13.03638341842683</v>
+        <v>1.039708101440963</v>
       </c>
       <c r="K40" t="n">
-        <v>3867.092341034102</v>
+        <v>931.3823091309132</v>
       </c>
       <c r="L40" t="n">
-        <v>155.0957095709571</v>
+        <v>40.05500550055005</v>
       </c>
       <c r="M40" t="n">
-        <v>15551383.220022</v>
+        <v>3212528.109451931</v>
       </c>
       <c r="N40" t="n">
-        <v>15218206.4180418</v>
+        <v>3177125.49569875</v>
       </c>
       <c r="O40" t="n">
-        <v>333176.801980198</v>
+        <v>35402.61375317859</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.9327572280083256</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.6050521995648973</v>
       </c>
       <c r="R40" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>0.0001958201305169657</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.0006754236874751251</v>
       </c>
       <c r="T40" t="n">
-        <v>19.75551431484872</v>
+        <v>1.652749962266257</v>
       </c>
       <c r="U40" t="n">
-        <v>4021.466737425617</v>
+        <v>3449.204561819077</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,196 +526,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.451612903225807</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J2" t="n">
-        <v>2.467392200412544</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K2" t="n">
-        <v>702.7110253025301</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L2" t="n">
-        <v>188.4884488448845</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M2" t="n">
-        <v>13511073.15511551</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N2" t="n">
-        <v>13395246.74862486</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O2" t="n">
-        <v>115826.4064906491</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R2" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T2" t="n">
-        <v>5.893947035417844</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U2" t="n">
-        <v>19227.06869342024</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.588884131062264</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.594086021505376</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J3" t="n">
-        <v>4.536492777821779</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K3" t="n">
-        <v>1481.89598019802</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L3" t="n">
-        <v>78.55115511551155</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M3" t="n">
-        <v>6074134.495049492</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N3" t="n">
-        <v>6017554.665016501</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O3" t="n">
-        <v>56579.83003300329</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R3" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003973856052862588</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>7.703540541394086</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U3" t="n">
-        <v>4098.893968413241</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.350585020439431</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.46236559139785</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3646793423707372</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K4" t="n">
-        <v>1106.807743674368</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L4" t="n">
-        <v>58.5038503850385</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M4" t="n">
-        <v>5076190.689768974</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N4" t="n">
-        <v>4970717.200220022</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O4" t="n">
-        <v>105473.4895489549</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R4" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T4" t="n">
-        <v>1.040202293622358</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U4" t="n">
-        <v>4586.334635604457</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="5">
@@ -726,61 +726,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.620967741935484</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478965577837015</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K5" t="n">
-        <v>3784.416073707372</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L5" t="n">
-        <v>110.0367013624439</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M5" t="n">
-        <v>8706893.798112892</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N5" t="n">
-        <v>8600561.252779894</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O5" t="n">
-        <v>106332.5453329948</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R5" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T5" t="n">
-        <v>8.041007149609982</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U5" t="n">
-        <v>2300.723183849934</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="6">
@@ -791,7 +791,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -801,181 +801,181 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.414392761951997</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6104935163943895</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K6" t="n">
-        <v>1552.934440044002</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L6" t="n">
-        <v>75.22717271727173</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M6" t="n">
-        <v>7080866.402640261</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N6" t="n">
-        <v>6891342.883388339</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O6" t="n">
-        <v>189523.5192519252</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6787832316376182</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R6" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002668449815178645</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T6" t="n">
-        <v>1.473224371773918</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U6" t="n">
-        <v>4559.668599042484</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.658602150537635</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>7.897126985217273</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K7" t="n">
-        <v>2146.992089658964</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L7" t="n">
-        <v>99.53135313531354</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M7" t="n">
-        <v>9691548.173817372</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N7" t="n">
-        <v>9590504.44719472</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O7" t="n">
-        <v>101043.7266226623</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R7" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T7" t="n">
-        <v>12.802853245848</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U7" t="n">
-        <v>4514.012054584146</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.54559127289644</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.540322580645161</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J8" t="n">
-        <v>6.353318230693071</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K8" t="n">
-        <v>1237.696445544555</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L8" t="n">
-        <v>116.3949394939494</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M8" t="n">
-        <v>10170136.63256324</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N8" t="n">
-        <v>10120981.25467547</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O8" t="n">
-        <v>49155.37788778878</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R8" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T8" t="n">
-        <v>11.64483111499294</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U8" t="n">
-        <v>8216.987831849709</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="9">
@@ -986,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -996,175 +996,175 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.60752688172043</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7046746644898908</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K9" t="n">
-        <v>651.3228668866898</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L9" t="n">
-        <v>37.98899889988999</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M9" t="n">
-        <v>2298278.745423723</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N9" t="n">
-        <v>2275866.51440062</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O9" t="n">
-        <v>22412.23102310231</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002672206192482065</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S9" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T9" t="n">
-        <v>1.147403025201837</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U9" t="n">
-        <v>3528.632053730048</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6803093740718634</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02365082421477135</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.68010752688172</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2263884094719471</v>
+      </c>
       <c r="K10" t="n">
-        <v>1725.883295805741</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L10" t="n">
-        <v>194.9635761589404</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M10" t="n">
-        <v>15002315.66997792</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N10" t="n">
-        <v>14917198.82339956</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O10" t="n">
-        <v>85116.84657836644</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9637709553156532</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>0.95547252331787</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.483813502740997</v>
+      </c>
       <c r="R10" t="n">
-        <v>4.534695769888867e-05</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0003941804035795226</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
+        <v>0.0004011552942003655</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6739391427242943</v>
+      </c>
       <c r="U10" t="n">
-        <v>8692.543526226078</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.335918178838533</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.2263884094719471</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>837.3769053905384</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L11" t="n">
-        <v>44.01650165016502</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M11" t="n">
-        <v>3480808.845984597</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N11" t="n">
-        <v>3413192.581958196</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O11" t="n">
-        <v>67616.26402640264</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P11" t="n">
-        <v>0.95547252331787</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.483813502740997</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004011552942003655</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.6739391427242943</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>4156.800627742662</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="12">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1185,246 +1185,246 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.577956989247312</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J12" t="n">
-        <v>1.554119528390054</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K12" t="n">
-        <v>1463.046422442244</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L12" t="n">
-        <v>40.45654565456545</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M12" t="n">
-        <v>3999501.610795507</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N12" t="n">
-        <v>3937843.056466302</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O12" t="n">
-        <v>61658.55432920342</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R12" t="n">
-        <v>0.000150387505484869</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T12" t="n">
-        <v>2.583846953587535</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U12" t="n">
-        <v>2733.680592389675</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.620967741935484</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J13" t="n">
-        <v>10.78915469925741</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K13" t="n">
-        <v>2515.540235973597</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L13" t="n">
-        <v>152.1303630363036</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M13" t="n">
-        <v>11374850.48899891</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N13" t="n">
-        <v>11238194.40979098</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O13" t="n">
-        <v>136656.0792079208</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R13" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T13" t="n">
-        <v>18.06430758687328</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U13" t="n">
-        <v>4521.832060697078</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.583333333333333</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J14" t="n">
-        <v>1.662215663091308</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K14" t="n">
-        <v>3381.269037953798</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L14" t="n">
-        <v>138.5951595159516</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M14" t="n">
-        <v>21745804.32343233</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N14" t="n">
-        <v>21619802.9180418</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O14" t="n">
-        <v>126001.4053905391</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R14" t="n">
-        <v>2.354685177223e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T14" t="n">
-        <v>3.246228188888836</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U14" t="n">
-        <v>6431.255271125063</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.420593075103495</v>
+        <v>0.6810374657220217</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.0124204551066807</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.389784946236559</v>
+        <v>0.696236559139785</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4831101147414734</v>
+        <v>9.009237885244771</v>
       </c>
       <c r="K15" t="n">
-        <v>380.8561793179318</v>
+        <v>3289.915513751374</v>
       </c>
       <c r="L15" t="n">
-        <v>18.57865786578658</v>
+        <v>115.6490649064906</v>
       </c>
       <c r="M15" t="n">
-        <v>977284.7700770069</v>
+        <v>12806701.57480748</v>
       </c>
       <c r="N15" t="n">
-        <v>961481.2431243125</v>
+        <v>12511134.81463146</v>
       </c>
       <c r="O15" t="n">
-        <v>15803.52695269527</v>
+        <v>295566.7601760176</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.8712080457734013</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.07559323822910896</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004303690060271313</v>
+        <v>5.317820999762459e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.000207007585111345</v>
       </c>
       <c r="T15" t="n">
-        <v>1.148640201987622</v>
+        <v>13.2286964208252</v>
       </c>
       <c r="U15" t="n">
-        <v>2566.020516792475</v>
+        <v>3892.714424208558</v>
       </c>
     </row>
     <row r="16">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1445,116 +1445,116 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.448924731182796</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K16" t="n">
-        <v>510.7721826182621</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L16" t="n">
-        <v>22.20902090209021</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M16" t="n">
-        <v>1253351.492849284</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N16" t="n">
-        <v>1232830.718371837</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O16" t="n">
-        <v>20520.77447744774</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0003660902437453124</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T16" t="n">
-        <v>1.348511698390355</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U16" t="n">
-        <v>2453.836633045474</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.575268817204301</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J17" t="n">
-        <v>2.989729004180416</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K17" t="n">
-        <v>1338.052705170518</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L17" t="n">
-        <v>86.55005500550054</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M17" t="n">
-        <v>9840777.763476355</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N17" t="n">
-        <v>9778602.140814083</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O17" t="n">
-        <v>62175.62266226623</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R17" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T17" t="n">
-        <v>5.276371829924331</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U17" t="n">
-        <v>7354.551674571196</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="18">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1575,441 +1575,441 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.336021505376344</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J18" t="n">
-        <v>2.580340961258277</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K18" t="n">
-        <v>5225.859279249448</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L18" t="n">
-        <v>120.9243929359824</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M18" t="n">
-        <v>13769015.17770419</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N18" t="n">
-        <v>12778720.50662252</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O18" t="n">
-        <v>990294.6710816775</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R18" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T18" t="n">
-        <v>7.074736286251795</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U18" t="n">
-        <v>2634.784911330742</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.443548387096774</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1759117230445546</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K19" t="n">
-        <v>1285.926851485148</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L19" t="n">
-        <v>88.64301430143014</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M19" t="n">
-        <v>10218069.24807481</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N19" t="n">
-        <v>10119727.86413641</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O19" t="n">
-        <v>98341.38393839383</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R19" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U19" t="n">
-        <v>7946.073477098422</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.545698924731183</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J20" t="n">
-        <v>3.467754041474145</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K20" t="n">
-        <v>1098.202911991198</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L20" t="n">
-        <v>187.4895489548955</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M20" t="n">
-        <v>16237094.3520352</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N20" t="n">
-        <v>16091465.1039604</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O20" t="n">
-        <v>145629.2480748075</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R20" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T20" t="n">
-        <v>7.179716478526343</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U20" t="n">
-        <v>14785.14960645573</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.628713868151493</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J21" t="n">
-        <v>3.333386534873489</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K21" t="n">
-        <v>1619.013470847085</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L21" t="n">
-        <v>78.31683168316832</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M21" t="n">
-        <v>7087678.3960396</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N21" t="n">
-        <v>6961982.357535753</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O21" t="n">
-        <v>125696.0385038504</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1886111501243448</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R21" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T21" t="n">
-        <v>5.30191348359169</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U21" t="n">
-        <v>4377.776049220427</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J22" t="n">
-        <v>3.977504096947204</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K22" t="n">
-        <v>1106.853353135313</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L22" t="n">
-        <v>185.2381738173817</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M22" t="n">
-        <v>16709444.57370737</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N22" t="n">
-        <v>16445971.06820682</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O22" t="n">
-        <v>263473.5055005501</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R22" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T22" t="n">
-        <v>7.32468488284717</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U22" t="n">
-        <v>15096.34905687875</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.564516129032258</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J23" t="n">
-        <v>1.235497127172719</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K23" t="n">
-        <v>735.1809878987912</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L23" t="n">
-        <v>36.77227722772277</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M23" t="n">
-        <v>2652380.565456549</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N23" t="n">
-        <v>2610884.190319032</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O23" t="n">
-        <v>41496.37513751376</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0002074079836537043</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T23" t="n">
-        <v>2.245848381022551</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U23" t="n">
-        <v>3607.792651218138</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.513440860215054</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08506419165060494</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K24" t="n">
-        <v>1097.040440044003</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L24" t="n">
-        <v>121.6666666666667</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M24" t="n">
-        <v>15350225.29922993</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N24" t="n">
-        <v>15269826.30913091</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O24" t="n">
-        <v>80398.9900990099</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.554499000811647</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R24" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2195631176605357</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U24" t="n">
-        <v>13992.39694264526</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="25">
@@ -2020,451 +2020,451 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.599462365591398</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8892413135295484</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K25" t="n">
-        <v>799.7652123212325</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L25" t="n">
-        <v>38.97909790979098</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M25" t="n">
-        <v>2819911.990351496</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N25" t="n">
-        <v>2791163.254864831</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O25" t="n">
-        <v>28748.73548666342</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9278388366571146</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6764107362832188</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0002133018241973586</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T25" t="n">
-        <v>1.478391672927692</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U25" t="n">
-        <v>3525.924792561313</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (low)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.2818428360106922</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02438275023528984</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.330645161290323</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1432474137843784</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K26" t="n">
-        <v>693.5464620462047</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L26" t="n">
-        <v>33.57535753575357</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M26" t="n">
-        <v>2412388.353135315</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N26" t="n">
-        <v>2364249.308030803</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O26" t="n">
-        <v>48139.04510451045</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9478942152323017</v>
+        <v>0.9278388366571144</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.967524778038458</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0001168314527983808</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0004063791705881639</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5082528114319146</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U26" t="n">
-        <v>3478.337047553996</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.551075268817204</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4988036451027072</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K27" t="n">
-        <v>517.8138943894386</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L27" t="n">
-        <v>35.74037403740374</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M27" t="n">
-        <v>1713818.918195099</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N27" t="n">
-        <v>1699123.860141752</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O27" t="n">
-        <v>14695.05805334632</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.147071598051071</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S27" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8717851629305855</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U27" t="n">
-        <v>3309.719837116163</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.519259105470924</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F28" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.661290322580645</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J28" t="n">
-        <v>5.047195443300332</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K28" t="n">
-        <v>3689.344194719472</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L28" t="n">
-        <v>173.3602860286028</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M28" t="n">
-        <v>8481121.533553353</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N28" t="n">
-        <v>8387890.666666667</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O28" t="n">
-        <v>93230.86688668867</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1028807208486825</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R28" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S28" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T28" t="n">
-        <v>9.719994103373407</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U28" t="n">
-        <v>2298.815476661763</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.594086021505376</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J29" t="n">
-        <v>4.241385833751375</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K29" t="n">
-        <v>2887.955652365237</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L29" t="n">
-        <v>107.049504950495</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M29" t="n">
-        <v>14276424.42684269</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N29" t="n">
-        <v>14202165.16611661</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O29" t="n">
-        <v>74259.26072607259</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R29" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T29" t="n">
-        <v>7.919705712496602</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U29" t="n">
-        <v>4943.436169163572</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.583333333333333</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J30" t="n">
-        <v>3.570143280528054</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K30" t="n">
-        <v>1167.338748074809</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L30" t="n">
-        <v>112.0616061606161</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M30" t="n">
-        <v>5543624.597359739</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N30" t="n">
-        <v>5487669.762376238</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O30" t="n">
-        <v>55954.83498349835</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R30" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T30" t="n">
-        <v>7.601070758745943</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U30" t="n">
-        <v>4748.942504052369</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.486559139784946</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4380225639383938</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K31" t="n">
-        <v>1412.260883388339</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L31" t="n">
-        <v>121.5137513751375</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M31" t="n">
-        <v>14854524.53905389</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N31" t="n">
-        <v>14783219.74807481</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O31" t="n">
-        <v>71304.79097909792</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P31" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R31" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T31" t="n">
-        <v>1.013362033548448</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U31" t="n">
-        <v>10518.2581446386</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="32">
@@ -2475,581 +2475,646 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.618279569892473</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K32" t="n">
-        <v>2417.550009900991</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L32" t="n">
-        <v>138.1463146314632</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M32" t="n">
-        <v>24180108.02805281</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N32" t="n">
-        <v>24063625.6270627</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O32" t="n">
-        <v>116482.400990099</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.808558675855097</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R32" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5529264896684616</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U32" t="n">
-        <v>10001.90603256356</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.637577603035782</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.564516129032258</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J33" t="n">
-        <v>5.843905389444815</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K33" t="n">
-        <v>2070.168603200884</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L33" t="n">
-        <v>149.1832229580574</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M33" t="n">
-        <v>13733793.78145695</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N33" t="n">
-        <v>13621672.65011038</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O33" t="n">
-        <v>112121.1313465784</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1091012876743977</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R33" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T33" t="n">
-        <v>9.165794660319715</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U33" t="n">
-        <v>6634.142629842724</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.6290776736822983</v>
       </c>
       <c r="F34" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.04052542124850751</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.669354838709677</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J34" t="n">
-        <v>14.19080079636965</v>
+        <v>1.039708101440963</v>
       </c>
       <c r="K34" t="n">
-        <v>5244.965372937293</v>
+        <v>931.3823091309132</v>
       </c>
       <c r="L34" t="n">
-        <v>265.9306930693069</v>
+        <v>40.05500550055005</v>
       </c>
       <c r="M34" t="n">
-        <v>27742337.2337734</v>
+        <v>3212528.109451931</v>
       </c>
       <c r="N34" t="n">
-        <v>27141368.95929593</v>
+        <v>3177125.49569875</v>
       </c>
       <c r="O34" t="n">
-        <v>600968.2744774478</v>
+        <v>35402.61375317859</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9327572280083256</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.6050521995648973</v>
       </c>
       <c r="R34" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>0.0001958201305169657</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0006754236874751251</v>
       </c>
       <c r="T34" t="n">
-        <v>20.75958236310095</v>
+        <v>1.652749962266257</v>
       </c>
       <c r="U34" t="n">
-        <v>5289.327051979582</v>
+        <v>3449.204561819077</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6349675266318143</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02829093785912806</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.672043010752688</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J35" t="n">
-        <v>8.052232502530256</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K35" t="n">
-        <v>1346.652125412539</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L35" t="n">
-        <v>191.9551493610899</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M35" t="n">
-        <v>15016299.67931794</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N35" t="n">
-        <v>14926250.65016502</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O35" t="n">
-        <v>90049.02915291529</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P35" t="n">
-        <v>0.935735212525825</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.07885608449983135</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R35" t="n">
-        <v>4.228521940770533e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0004715156309854677</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T35" t="n">
-        <v>12.68132961892292</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U35" t="n">
-        <v>11150.83798996551</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6349675266318143</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.02829093785912806</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.618279569892473</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J36" t="n">
-        <v>7.46709735138597</v>
+        <v>8.052232502530256</v>
       </c>
       <c r="K36" t="n">
-        <v>1762.03302640264</v>
+        <v>1346.652125412539</v>
       </c>
       <c r="L36" t="n">
-        <v>39.37843784378438</v>
+        <v>191.9551493610899</v>
       </c>
       <c r="M36" t="n">
-        <v>3346611.012209417</v>
+        <v>15016299.67931794</v>
       </c>
       <c r="N36" t="n">
-        <v>3299549.915435806</v>
+        <v>14926250.65016502</v>
       </c>
       <c r="O36" t="n">
-        <v>47061.09677361179</v>
+        <v>90049.02915291529</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.935735212525825</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.07885608449983135</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0001842014048331127</v>
+        <v>4.228521940770533e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0004715156309854677</v>
       </c>
       <c r="T36" t="n">
-        <v>12.11305361664085</v>
+        <v>12.68132961892292</v>
       </c>
       <c r="U36" t="n">
-        <v>1899.289605849129</v>
+        <v>11150.83798996551</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.629032258064516</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J37" t="n">
-        <v>8.817468730473037</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K37" t="n">
-        <v>2354.367686468646</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L37" t="n">
-        <v>162.6457645764577</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M37" t="n">
-        <v>14324724.28382839</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N37" t="n">
-        <v>14201447.9559956</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O37" t="n">
-        <v>123276.3278327833</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P37" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R37" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T37" t="n">
-        <v>15.67058466504826</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U37" t="n">
-        <v>6084.319100265209</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.647849462365591</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J38" t="n">
-        <v>12.38809237513753</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K38" t="n">
-        <v>2089.900125412543</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L38" t="n">
-        <v>36.65676567656766</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M38" t="n">
-        <v>5715253.85918592</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N38" t="n">
-        <v>5581622.259625964</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O38" t="n">
-        <v>133631.599559956</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0001088709227809481</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T38" t="n">
-        <v>19.90934652274569</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U38" t="n">
-        <v>2734.701907373559</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.659885802549234</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.663978494623656</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J39" t="n">
-        <v>13.03638341842683</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K39" t="n">
-        <v>3867.092341034102</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L39" t="n">
-        <v>155.0957095709571</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M39" t="n">
-        <v>15551383.220022</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N39" t="n">
-        <v>15218206.4180418</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O39" t="n">
-        <v>333176.801980198</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R39" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T39" t="n">
-        <v>19.75551431484872</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U39" t="n">
-        <v>4021.466737425617</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.610215053763441</v>
+        <v>0.647849462365591</v>
       </c>
       <c r="J40" t="n">
-        <v>1.039708101440963</v>
+        <v>12.38809237513753</v>
       </c>
       <c r="K40" t="n">
-        <v>931.3823091309132</v>
+        <v>2089.900125412543</v>
       </c>
       <c r="L40" t="n">
-        <v>40.05500550055005</v>
+        <v>36.65676567656766</v>
       </c>
       <c r="M40" t="n">
-        <v>3212528.109451931</v>
+        <v>5715253.85918592</v>
       </c>
       <c r="N40" t="n">
-        <v>3177125.49569875</v>
+        <v>5581622.259625964</v>
       </c>
       <c r="O40" t="n">
-        <v>35402.61375317859</v>
+        <v>133631.599559956</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.9159555838702423</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6050521995648973</v>
+        <v>0.05022766562717351</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0001958201305169657</v>
+        <v>0.0001088709227809481</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0006754236874751251</v>
+        <v>0.0002977295201865781</v>
       </c>
       <c r="T40" t="n">
-        <v>1.652749962266257</v>
+        <v>19.90934652274569</v>
       </c>
       <c r="U40" t="n">
-        <v>3449.204561819077</v>
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J41" t="n">
+        <v>13.03638341842683</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3867.092341034102</v>
+      </c>
+      <c r="L41" t="n">
+        <v>155.0957095709571</v>
+      </c>
+      <c r="M41" t="n">
+        <v>15551383.220022</v>
+      </c>
+      <c r="N41" t="n">
+        <v>15218206.4180418</v>
+      </c>
+      <c r="O41" t="n">
+        <v>333176.801980198</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.9500106599458848</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.05061877833513936</v>
+      </c>
+      <c r="R41" t="n">
+        <v>4.243261150555715e-05</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.0001706413357517016</v>
+      </c>
+      <c r="T41" t="n">
+        <v>19.75551431484872</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4021.466737425617</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,196 +591,196 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.6290776736822983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.04052542124850751</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.336021505376344</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J3" t="n">
-        <v>2.580340961258277</v>
+        <v>1.039708101440963</v>
       </c>
       <c r="K3" t="n">
-        <v>5225.859279249448</v>
+        <v>931.3823091309132</v>
       </c>
       <c r="L3" t="n">
-        <v>120.9243929359824</v>
+        <v>40.05500550055005</v>
       </c>
       <c r="M3" t="n">
-        <v>13769015.17770419</v>
+        <v>3212528.109451931</v>
       </c>
       <c r="N3" t="n">
-        <v>12778720.50662252</v>
+        <v>3177125.49569875</v>
       </c>
       <c r="O3" t="n">
-        <v>990294.6710816775</v>
+        <v>35402.61375317859</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9327572280083256</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.6050521995648973</v>
       </c>
       <c r="R3" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>0.0001958201305169657</v>
       </c>
       <c r="S3" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0006754236874751251</v>
       </c>
       <c r="T3" t="n">
-        <v>7.074736286251795</v>
+        <v>1.652749962266257</v>
       </c>
       <c r="U3" t="n">
-        <v>2634.784911330742</v>
+        <v>3449.204561819077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.575268817204301</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J4" t="n">
-        <v>2.989729004180416</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K4" t="n">
-        <v>1338.052705170518</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L4" t="n">
-        <v>86.55005500550054</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M4" t="n">
-        <v>9840777.763476355</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N4" t="n">
-        <v>9778602.140814083</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O4" t="n">
-        <v>62175.62266226623</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.18952417157726</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R4" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004234705483335876</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>5.276371829924331</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U4" t="n">
-        <v>7354.551674571196</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.448924731182796</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6187507753025301</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K5" t="n">
-        <v>510.7721826182621</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L5" t="n">
-        <v>22.20902090209021</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M5" t="n">
-        <v>1253351.492849284</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N5" t="n">
-        <v>1232830.718371837</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O5" t="n">
-        <v>20520.77447744774</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003660902437453124</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T5" t="n">
-        <v>1.348511698390355</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U5" t="n">
-        <v>2453.836633045474</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="6">
@@ -791,7 +791,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -801,51 +801,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.420593075103495</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.389784946236559</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4831101147414734</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K6" t="n">
-        <v>380.8561793179318</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L6" t="n">
-        <v>18.57865786578658</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M6" t="n">
-        <v>977284.7700770069</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N6" t="n">
-        <v>961481.2431243125</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O6" t="n">
-        <v>15803.52695269527</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004303690060271313</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T6" t="n">
-        <v>1.148640201987622</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U6" t="n">
-        <v>2566.020516792475</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="7">
@@ -856,61 +856,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.583333333333333</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J7" t="n">
-        <v>1.662215663091308</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K7" t="n">
-        <v>3381.269037953798</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L7" t="n">
-        <v>138.5951595159516</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M7" t="n">
-        <v>21745804.32343233</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N7" t="n">
-        <v>21619802.9180418</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O7" t="n">
-        <v>126001.4053905391</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R7" t="n">
-        <v>2.354685177223e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T7" t="n">
-        <v>3.246228188888836</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U7" t="n">
-        <v>6431.255271125063</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="8">
@@ -921,126 +921,126 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.620967741935484</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>10.78915469925741</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K8" t="n">
-        <v>2515.540235973597</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L8" t="n">
-        <v>152.1303630363036</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M8" t="n">
-        <v>11374850.48899891</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N8" t="n">
-        <v>11238194.40979098</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O8" t="n">
-        <v>136656.0792079208</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.987035206105383</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R8" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T8" t="n">
-        <v>18.06430758687328</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U8" t="n">
-        <v>4521.832060697078</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.577956989247312</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J9" t="n">
-        <v>1.554119528390054</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K9" t="n">
-        <v>1463.046422442244</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L9" t="n">
-        <v>40.45654565456545</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M9" t="n">
-        <v>3999501.610795507</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N9" t="n">
-        <v>3937843.056466302</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O9" t="n">
-        <v>61658.55432920342</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000150387505484869</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T9" t="n">
-        <v>2.583846953587535</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U9" t="n">
-        <v>2733.680592389675</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="10">
@@ -1560,521 +1560,521 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.350585020439431</v>
+        <v>0.4117608187690975</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.01631992906626261</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.46236559139785</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3646793423707372</v>
+        <v>3.32599273971397</v>
       </c>
       <c r="K18" t="n">
-        <v>1106.807743674368</v>
+        <v>1513.833119361935</v>
       </c>
       <c r="L18" t="n">
-        <v>58.5038503850385</v>
+        <v>188.8080308030803</v>
       </c>
       <c r="M18" t="n">
-        <v>5076190.689768974</v>
+        <v>16314434.26072608</v>
       </c>
       <c r="N18" t="n">
-        <v>4970717.200220022</v>
+        <v>16209156.91639164</v>
       </c>
       <c r="O18" t="n">
-        <v>105473.4895489549</v>
+        <v>105277.3443344334</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9692708877835391</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.123800877209524</v>
       </c>
       <c r="R18" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>2.523904980023328e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0002719988177710436</v>
       </c>
       <c r="T18" t="n">
-        <v>1.040202293622358</v>
+        <v>8.077487191852224</v>
       </c>
       <c r="U18" t="n">
-        <v>4586.334635604457</v>
+        <v>10776.90404052095</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.588884131062264</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.594086021505376</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J19" t="n">
-        <v>4.536492777821779</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K19" t="n">
-        <v>1481.89598019802</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L19" t="n">
-        <v>78.55115511551155</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M19" t="n">
-        <v>6074134.495049492</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N19" t="n">
-        <v>6017554.665016501</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O19" t="n">
-        <v>56579.83003300329</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R19" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T19" t="n">
-        <v>7.703540541394086</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U19" t="n">
-        <v>4098.893968413241</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.451612903225807</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J20" t="n">
-        <v>2.467392200412544</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K20" t="n">
-        <v>702.7110253025301</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L20" t="n">
-        <v>188.4884488448845</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M20" t="n">
-        <v>13511073.15511551</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N20" t="n">
-        <v>13395246.74862486</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O20" t="n">
-        <v>115826.4064906491</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R20" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T20" t="n">
-        <v>5.893947035417844</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U20" t="n">
-        <v>19227.06869342024</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.443548387096774</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1759117230445546</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K21" t="n">
-        <v>1285.926851485148</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L21" t="n">
-        <v>88.64301430143014</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M21" t="n">
-        <v>10218069.24807481</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N21" t="n">
-        <v>10119727.86413641</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O21" t="n">
-        <v>98341.38393839383</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R21" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4282759302584503</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U21" t="n">
-        <v>7946.073477098422</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.628713868151493</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J22" t="n">
-        <v>3.333386534873489</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K22" t="n">
-        <v>1619.013470847085</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L22" t="n">
-        <v>78.31683168316832</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M22" t="n">
-        <v>7087678.3960396</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N22" t="n">
-        <v>6961982.357535753</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O22" t="n">
-        <v>125696.0385038504</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1886111501243448</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R22" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T22" t="n">
-        <v>5.30191348359169</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U22" t="n">
-        <v>4377.776049220427</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.594086021505376</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J23" t="n">
-        <v>3.977504096947204</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K23" t="n">
-        <v>1106.853353135313</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L23" t="n">
-        <v>185.2381738173817</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M23" t="n">
-        <v>16709444.57370737</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N23" t="n">
-        <v>16445971.06820682</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O23" t="n">
-        <v>263473.5055005501</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T23" t="n">
-        <v>7.32468488284717</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U23" t="n">
-        <v>15096.34905687875</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.564516129032258</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J24" t="n">
-        <v>1.235497127172719</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K24" t="n">
-        <v>735.1809878987912</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L24" t="n">
-        <v>36.77227722772277</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M24" t="n">
-        <v>2652380.565456549</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N24" t="n">
-        <v>2610884.190319032</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O24" t="n">
-        <v>41496.37513751376</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0002074079836537043</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T24" t="n">
-        <v>2.245848381022551</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U24" t="n">
-        <v>3607.792651218138</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.513440860215054</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J25" t="n">
-        <v>0.08506419165060494</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K25" t="n">
-        <v>1097.040440044003</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L25" t="n">
-        <v>121.6666666666667</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M25" t="n">
-        <v>15350225.29922993</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N25" t="n">
-        <v>15269826.30913091</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O25" t="n">
-        <v>80398.9900990099</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.554499000811647</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R25" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2195631176605357</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U25" t="n">
-        <v>13992.39694264526</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="26">
@@ -2085,451 +2085,451 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.599462365591398</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8892413135295484</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K26" t="n">
-        <v>799.7652123212325</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L26" t="n">
-        <v>38.97909790979098</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M26" t="n">
-        <v>2819911.990351496</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N26" t="n">
-        <v>2791163.254864831</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O26" t="n">
-        <v>28748.73548666342</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9278388366571144</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6764107362832188</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0002133018241973586</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T26" t="n">
-        <v>1.478391672927692</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U26" t="n">
-        <v>3525.924792561313</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (low)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2818428360106922</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02438275023528984</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.330645161290323</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1432474137843784</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K27" t="n">
-        <v>693.5464620462047</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L27" t="n">
-        <v>33.57535753575357</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M27" t="n">
-        <v>2412388.353135315</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N27" t="n">
-        <v>2364249.308030803</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O27" t="n">
-        <v>48139.04510451045</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9478942152323017</v>
+        <v>0.9278388366571141</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.967524778038458</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0001168314527983808</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0004063791705881639</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5082528114319146</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U27" t="n">
-        <v>3478.337047553996</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.551075268817204</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4988036451027072</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K28" t="n">
-        <v>517.8138943894386</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L28" t="n">
-        <v>35.74037403740374</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M28" t="n">
-        <v>1713818.918195099</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N28" t="n">
-        <v>1699123.860141752</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O28" t="n">
-        <v>14695.05805334632</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.147071598051071</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8717851629305855</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U28" t="n">
-        <v>3309.719837116163</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.519259105470924</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.661290322580645</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J29" t="n">
-        <v>5.047195443300332</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K29" t="n">
-        <v>3689.344194719472</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L29" t="n">
-        <v>173.3602860286028</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M29" t="n">
-        <v>8481121.533553353</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N29" t="n">
-        <v>8387890.666666667</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O29" t="n">
-        <v>93230.86688668867</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1028807208486825</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R29" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S29" t="n">
-        <v>0.00014074563880869</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T29" t="n">
-        <v>9.719994103373407</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U29" t="n">
-        <v>2298.815476661763</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.594086021505376</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J30" t="n">
-        <v>4.241385833751375</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K30" t="n">
-        <v>2887.955652365237</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L30" t="n">
-        <v>107.049504950495</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M30" t="n">
-        <v>14276424.42684269</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N30" t="n">
-        <v>14202165.16611661</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O30" t="n">
-        <v>74259.26072607259</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R30" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T30" t="n">
-        <v>7.919705712496602</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U30" t="n">
-        <v>4943.436169163572</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.583333333333333</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J31" t="n">
-        <v>3.570143280528054</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K31" t="n">
-        <v>1167.338748074809</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L31" t="n">
-        <v>112.0616061606161</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M31" t="n">
-        <v>5543624.597359739</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N31" t="n">
-        <v>5487669.762376238</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O31" t="n">
-        <v>55954.83498349835</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R31" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T31" t="n">
-        <v>7.601070758745943</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U31" t="n">
-        <v>4748.942504052369</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.486559139784946</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4380225639383938</v>
+        <v>3.570143280528054</v>
       </c>
       <c r="K32" t="n">
-        <v>1412.260883388339</v>
+        <v>1167.338748074809</v>
       </c>
       <c r="L32" t="n">
-        <v>121.5137513751375</v>
+        <v>112.0616061606161</v>
       </c>
       <c r="M32" t="n">
-        <v>14854524.53905389</v>
+        <v>5543624.597359739</v>
       </c>
       <c r="N32" t="n">
-        <v>14783219.74807481</v>
+        <v>5487669.762376238</v>
       </c>
       <c r="O32" t="n">
-        <v>71304.79097909792</v>
+        <v>55954.83498349835</v>
       </c>
       <c r="P32" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9057792630165156</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.1315604119129374</v>
       </c>
       <c r="R32" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>8.472606907729202e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0004023592306424291</v>
       </c>
       <c r="T32" t="n">
-        <v>1.013362033548448</v>
+        <v>7.601070758745943</v>
       </c>
       <c r="U32" t="n">
-        <v>10518.2581446386</v>
+        <v>4748.942504052369</v>
       </c>
     </row>
     <row r="33">
@@ -2540,61 +2540,61 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>GPT-5.6 Luna (max)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.4322468668029613</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.01836403763159828</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.618279569892473</v>
+        <v>0.486559139784946</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.4380225639383938</v>
       </c>
       <c r="K33" t="n">
-        <v>2417.550009900991</v>
+        <v>1412.260883388339</v>
       </c>
       <c r="L33" t="n">
-        <v>138.1463146314632</v>
+        <v>121.5137513751375</v>
       </c>
       <c r="M33" t="n">
-        <v>24180108.02805281</v>
+        <v>14854524.53905389</v>
       </c>
       <c r="N33" t="n">
-        <v>24063625.6270627</v>
+        <v>14783219.74807481</v>
       </c>
       <c r="O33" t="n">
-        <v>116482.400990099</v>
+        <v>71304.79097909792</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.808558675855097</v>
+        <v>0.9868141561395799</v>
       </c>
       <c r="R33" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>2.909866725565972e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0003060672938599712</v>
       </c>
       <c r="T33" t="n">
-        <v>0.5529264896684616</v>
+        <v>1.013362033548448</v>
       </c>
       <c r="U33" t="n">
-        <v>10001.90603256356</v>
+        <v>10518.2581446386</v>
       </c>
     </row>
     <row r="34">
@@ -2605,61 +2605,61 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.4305203524444174</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.01068487561410279</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.610215053763441</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J34" t="n">
-        <v>1.039708101440963</v>
+        <v>0.2380461072079206</v>
       </c>
       <c r="K34" t="n">
-        <v>931.3823091309132</v>
+        <v>2417.550009900991</v>
       </c>
       <c r="L34" t="n">
-        <v>40.05500550055005</v>
+        <v>138.1463146314632</v>
       </c>
       <c r="M34" t="n">
-        <v>3212528.109451931</v>
+        <v>24180108.02805281</v>
       </c>
       <c r="N34" t="n">
-        <v>3177125.49569875</v>
+        <v>24063625.6270627</v>
       </c>
       <c r="O34" t="n">
-        <v>35402.61375317859</v>
+        <v>116482.400990099</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.9898485564269163</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.6050521995648973</v>
+        <v>1.808558675855097</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0001958201305169657</v>
+        <v>1.780473238353379e-05</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0006754236874751251</v>
+        <v>0.0001780812602350464</v>
       </c>
       <c r="T34" t="n">
-        <v>1.652749962266257</v>
+        <v>0.5529264896684616</v>
       </c>
       <c r="U34" t="n">
-        <v>3449.204561819077</v>
+        <v>10001.90603256356</v>
       </c>
     </row>
     <row r="35">
@@ -2730,326 +2730,326 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6349675266318143</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02829093785912806</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.672043010752688</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J36" t="n">
-        <v>8.052232502530256</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K36" t="n">
-        <v>1346.652125412539</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L36" t="n">
-        <v>191.9551493610899</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M36" t="n">
-        <v>15016299.67931794</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N36" t="n">
-        <v>14926250.65016502</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O36" t="n">
-        <v>90049.02915291529</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P36" t="n">
-        <v>0.935735212525825</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.07885608449983135</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R36" t="n">
-        <v>4.228521940770533e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0004715156309854677</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T36" t="n">
-        <v>12.68132961892292</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U36" t="n">
-        <v>11150.83798996551</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.6349675266318143</v>
       </c>
       <c r="F37" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.02829093785912806</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.669354838709677</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J37" t="n">
-        <v>14.19080079636965</v>
+        <v>8.052232502530256</v>
       </c>
       <c r="K37" t="n">
-        <v>5244.965372937293</v>
+        <v>1346.652125412539</v>
       </c>
       <c r="L37" t="n">
-        <v>265.9306930693069</v>
+        <v>191.9551493610899</v>
       </c>
       <c r="M37" t="n">
-        <v>27742337.2337734</v>
+        <v>15016299.67931794</v>
       </c>
       <c r="N37" t="n">
-        <v>27141368.95929593</v>
+        <v>14926250.65016502</v>
       </c>
       <c r="O37" t="n">
-        <v>600968.2744774478</v>
+        <v>90049.02915291529</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.935735212525825</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.07885608449983135</v>
       </c>
       <c r="R37" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.228521940770533e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0004715156309854677</v>
       </c>
       <c r="T37" t="n">
-        <v>20.75958236310095</v>
+        <v>12.68132961892292</v>
       </c>
       <c r="U37" t="n">
-        <v>5289.327051979582</v>
+        <v>11150.83798996551</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.637577603035782</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.564516129032258</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J38" t="n">
-        <v>5.84390538944481</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K38" t="n">
-        <v>2070.168603200884</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L38" t="n">
-        <v>149.1832229580574</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M38" t="n">
-        <v>13733793.78145695</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N38" t="n">
-        <v>13621672.65011038</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O38" t="n">
-        <v>112121.1313465784</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R38" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T38" t="n">
-        <v>9.165794660319708</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U38" t="n">
-        <v>6634.142629842724</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.629032258064516</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J39" t="n">
-        <v>8.817468730473037</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K39" t="n">
-        <v>2354.367686468646</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L39" t="n">
-        <v>162.6457645764577</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M39" t="n">
-        <v>14324724.28382839</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N39" t="n">
-        <v>14201447.9559956</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O39" t="n">
-        <v>123276.3278327833</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P39" t="n">
-        <v>0.938882976190201</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R39" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T39" t="n">
-        <v>15.67058466504826</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U39" t="n">
-        <v>6084.319100265209</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.647849462365591</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J40" t="n">
-        <v>12.38809237513753</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K40" t="n">
-        <v>2089.900125412543</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L40" t="n">
-        <v>36.65676567656766</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M40" t="n">
-        <v>5715253.85918592</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N40" t="n">
-        <v>5581622.259625964</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O40" t="n">
-        <v>133631.599559956</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0001088709227809481</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T40" t="n">
-        <v>19.90934652274569</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U40" t="n">
-        <v>2734.701907373559</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="41">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -3070,50 +3070,115 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.659885802549234</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L41" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O41" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T41" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
         <v>0.663978494623656</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J42" t="n">
         <v>13.03638341842683</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>3867.092341034102</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L42" t="n">
         <v>155.0957095709571</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>15551383.220022</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N42" t="n">
         <v>15218206.4180418</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O42" t="n">
         <v>333176.801980198</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P42" t="n">
         <v>0.9500106599458848</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q42" t="n">
         <v>0.05061877833513936</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>4.243261150555715e-05</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S42" t="n">
         <v>0.0001706413357517016</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T42" t="n">
         <v>19.75551431484872</v>
       </c>
-      <c r="U41" t="n">
+      <c r="U42" t="n">
         <v>4021.466737425617</v>
       </c>
     </row>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,131 +526,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.545698924731183</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J2" t="n">
-        <v>3.467754041474145</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K2" t="n">
-        <v>1098.202911991198</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L2" t="n">
-        <v>187.4895489548955</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M2" t="n">
-        <v>16237094.3520352</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N2" t="n">
-        <v>16091465.1039604</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O2" t="n">
-        <v>145629.2480748075</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R2" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T2" t="n">
-        <v>7.179716478526343</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U2" t="n">
-        <v>14785.14960645573</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.513440860215054</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08506419165060494</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K3" t="n">
-        <v>1097.040440044003</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L3" t="n">
-        <v>121.6666666666667</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M3" t="n">
-        <v>15350225.29922993</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N3" t="n">
-        <v>15269826.30913091</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O3" t="n">
-        <v>80398.9900990099</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.554499000811647</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195631176605357</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U3" t="n">
-        <v>13992.39694264526</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -671,246 +671,246 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.564516129032258</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235497127172719</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K4" t="n">
-        <v>735.1809878987912</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L4" t="n">
-        <v>36.77227722772277</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M4" t="n">
-        <v>2652380.565456549</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N4" t="n">
-        <v>2610884.190319032</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O4" t="n">
-        <v>41496.37513751376</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002074079836537043</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T4" t="n">
-        <v>2.245848381022551</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U4" t="n">
-        <v>3607.792651218138</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.628713868151493</v>
+        <v>0.4117608187690975</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01631992906626261</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.620967741935484</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J5" t="n">
-        <v>3.333386534873489</v>
+        <v>3.32599273971397</v>
       </c>
       <c r="K5" t="n">
-        <v>1619.013470847085</v>
+        <v>1513.833119361935</v>
       </c>
       <c r="L5" t="n">
-        <v>78.31683168316832</v>
+        <v>188.8080308030803</v>
       </c>
       <c r="M5" t="n">
-        <v>7087678.3960396</v>
+        <v>16314434.26072608</v>
       </c>
       <c r="N5" t="n">
-        <v>6961982.357535753</v>
+        <v>16209156.91639164</v>
       </c>
       <c r="O5" t="n">
-        <v>125696.0385038504</v>
+        <v>105277.3443344334</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9692708877835391</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.123800877209524</v>
       </c>
       <c r="R5" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>2.523904980023328e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0002719988177710436</v>
       </c>
       <c r="T5" t="n">
-        <v>5.30191348359169</v>
+        <v>8.077487191852224</v>
       </c>
       <c r="U5" t="n">
-        <v>4377.776049220427</v>
+        <v>10776.90404052095</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.443548387096774</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1759117230445546</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K6" t="n">
-        <v>1285.926851485148</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L6" t="n">
-        <v>88.64301430143014</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M6" t="n">
-        <v>10218069.24807481</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N6" t="n">
-        <v>10119727.86413641</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O6" t="n">
-        <v>98341.38393839383</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R6" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4282759302584503</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U6" t="n">
-        <v>7946.073477098422</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.451612903225807</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J7" t="n">
-        <v>2.467392200412544</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K7" t="n">
-        <v>702.7110253025301</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L7" t="n">
-        <v>188.4884488448845</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M7" t="n">
-        <v>13511073.15511551</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N7" t="n">
-        <v>13395246.74862486</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O7" t="n">
-        <v>115826.4064906491</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R7" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T7" t="n">
-        <v>5.893947035417844</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U7" t="n">
-        <v>19227.06869342024</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="8">
@@ -921,7 +921,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -931,181 +931,181 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.588884131062264</v>
+        <v>0.6810374657220217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.0124204551066807</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.594086021505376</v>
+        <v>0.696236559139785</v>
       </c>
       <c r="J8" t="n">
-        <v>4.536492777821779</v>
+        <v>9.009237885244771</v>
       </c>
       <c r="K8" t="n">
-        <v>1481.89598019802</v>
+        <v>3289.915513751374</v>
       </c>
       <c r="L8" t="n">
-        <v>78.55115511551155</v>
+        <v>115.6490649064906</v>
       </c>
       <c r="M8" t="n">
-        <v>6074134.495049492</v>
+        <v>12806701.57480748</v>
       </c>
       <c r="N8" t="n">
-        <v>6017554.665016501</v>
+        <v>12511134.81463146</v>
       </c>
       <c r="O8" t="n">
-        <v>56579.83003300329</v>
+        <v>295566.7601760176</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.8712080457734013</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.07559323822910896</v>
       </c>
       <c r="R8" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>5.317820999762459e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.000207007585111345</v>
       </c>
       <c r="T8" t="n">
-        <v>7.703540541394086</v>
+        <v>13.2286964208252</v>
       </c>
       <c r="U8" t="n">
-        <v>4098.893968413241</v>
+        <v>3892.714424208558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J9" t="n">
-        <v>3.478965577837015</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K9" t="n">
-        <v>3784.416073707372</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L9" t="n">
-        <v>110.0367013624439</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M9" t="n">
-        <v>8706893.798112892</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N9" t="n">
-        <v>8600561.252779894</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O9" t="n">
-        <v>106332.5453329948</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R9" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T9" t="n">
-        <v>8.041007149609982</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U9" t="n">
-        <v>2300.723183849934</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.658602150537635</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J10" t="n">
-        <v>7.897126985217273</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K10" t="n">
-        <v>2146.992089658964</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L10" t="n">
-        <v>99.53135313531354</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M10" t="n">
-        <v>9691548.173817372</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N10" t="n">
-        <v>9590504.44719472</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O10" t="n">
-        <v>101043.7266226623</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R10" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T10" t="n">
-        <v>12.802853245848</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U10" t="n">
-        <v>4514.012054584146</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="11">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1126,246 +1126,234 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.54559127289644</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.540322580645161</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J11" t="n">
-        <v>6.353318230693071</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K11" t="n">
-        <v>1237.696445544555</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L11" t="n">
-        <v>116.3949394939494</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M11" t="n">
-        <v>10170136.63256324</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N11" t="n">
-        <v>10120981.25467547</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O11" t="n">
-        <v>49155.37788778878</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R11" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T11" t="n">
-        <v>11.64483111499294</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U11" t="n">
-        <v>8216.987831849709</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.60752688172043</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.7046746644898908</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>651.3228668866898</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L12" t="n">
-        <v>37.98899889988999</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M12" t="n">
-        <v>2298278.745423723</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N12" t="n">
-        <v>2275866.51440062</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O12" t="n">
-        <v>22412.23102310231</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9239660644436648</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.8715333479481563</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0.0002672206192482065</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.000942923242496814</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.147403025201837</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>3528.632053730048</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.577956989247312</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J13" t="n">
-        <v>1.554119528390054</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K13" t="n">
-        <v>1463.046422442244</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L13" t="n">
-        <v>40.45654565456545</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M13" t="n">
-        <v>3999501.610795507</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N13" t="n">
-        <v>3937843.056466302</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O13" t="n">
-        <v>61658.55432920342</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3870198266238458</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R13" t="n">
-        <v>0.000150387505484869</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T13" t="n">
-        <v>2.583846953587535</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U13" t="n">
-        <v>2733.680592389675</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.2771443620715672</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.006542828532467639</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.620967741935484</v>
-      </c>
-      <c r="J14" t="n">
-        <v>10.78915469925741</v>
-      </c>
+        <v>0.397849462365591</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>2515.540235973597</v>
+        <v>2541.509630242825</v>
       </c>
       <c r="L14" t="n">
-        <v>152.1303630363036</v>
+        <v>95.90949227373069</v>
       </c>
       <c r="M14" t="n">
-        <v>11374850.48899891</v>
+        <v>5065557.310154528</v>
       </c>
       <c r="N14" t="n">
-        <v>11238194.40979098</v>
+        <v>5026647.232891832</v>
       </c>
       <c r="O14" t="n">
-        <v>136656.0792079208</v>
+        <v>38910.07726269315</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9698258997320075</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.05535778192387877</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>5.471152434027297e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002374295844857846</v>
-      </c>
-      <c r="T14" t="n">
-        <v>18.06430758687328</v>
-      </c>
+        <v>0.000109047142207794</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>4521.832060697078</v>
+        <v>1993.129299954904</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1364,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1386,51 +1374,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.420593075103495</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.389784946236559</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4831101147414734</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K15" t="n">
-        <v>380.8561793179318</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L15" t="n">
-        <v>18.57865786578658</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M15" t="n">
-        <v>977284.7700770069</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N15" t="n">
-        <v>961481.2431243125</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O15" t="n">
-        <v>15803.52695269527</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004303690060271313</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T15" t="n">
-        <v>1.148640201987622</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U15" t="n">
-        <v>2566.020516792475</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="16">
@@ -1441,191 +1429,191 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.448924731182796</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6187507753025301</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K16" t="n">
-        <v>510.7721826182621</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L16" t="n">
-        <v>22.20902090209021</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M16" t="n">
-        <v>1253351.492849284</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N16" t="n">
-        <v>1232830.718371837</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O16" t="n">
-        <v>20520.77447744774</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0003660902437453124</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T16" t="n">
-        <v>1.348511698390355</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U16" t="n">
-        <v>2453.836633045474</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.575268817204301</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J17" t="n">
-        <v>2.989729004180416</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K17" t="n">
-        <v>1338.052705170518</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L17" t="n">
-        <v>86.55005500550054</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M17" t="n">
-        <v>9840777.763476355</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N17" t="n">
-        <v>9778602.140814083</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O17" t="n">
-        <v>62175.62266226623</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.18952417157726</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R17" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T17" t="n">
-        <v>5.276371829924331</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U17" t="n">
-        <v>7354.551674571196</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.599462365591398</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8892413135295484</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K18" t="n">
-        <v>799.7652123212325</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L18" t="n">
-        <v>38.97909790979098</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M18" t="n">
-        <v>2819911.990351496</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N18" t="n">
-        <v>2791163.254864831</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O18" t="n">
-        <v>28748.73548666342</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278388366571143</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6764107362832188</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0002133018241973586</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T18" t="n">
-        <v>1.478391672927692</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U18" t="n">
-        <v>3525.924792561313</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="19">
@@ -1636,7 +1624,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (low)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1646,636 +1634,636 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5721634943016617</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06629758303140638</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.551075268817204</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4988036451027072</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K19" t="n">
-        <v>517.8138943894386</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L19" t="n">
-        <v>35.74037403740374</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M19" t="n">
-        <v>1713818.918195099</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N19" t="n">
-        <v>1699123.860141752</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O19" t="n">
-        <v>14695.05805334632</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.147071598051071</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0003338529457384175</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001104959717190106</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8717851629305855</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U19" t="n">
-        <v>3309.719837116163</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.519259105470924</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F20" t="n">
-        <v>0.008444738328521398</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.661290322580645</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J20" t="n">
-        <v>5.047195443300332</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K20" t="n">
-        <v>3689.344194719472</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L20" t="n">
-        <v>173.3602860286028</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M20" t="n">
-        <v>8481121.533553353</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N20" t="n">
-        <v>8387890.666666667</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O20" t="n">
-        <v>93230.86688668867</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9500000000000017</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1028807208486825</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R20" t="n">
-        <v>6.12252876481737e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.00014074563880869</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T20" t="n">
-        <v>9.719994103373407</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U20" t="n">
-        <v>2298.815476661763</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5355484140097326</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01112652294860106</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.594086021505376</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J21" t="n">
-        <v>4.241385833751375</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K21" t="n">
-        <v>2887.955652365237</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L21" t="n">
-        <v>107.049504950495</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M21" t="n">
-        <v>14276424.42684269</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N21" t="n">
-        <v>14202165.16611661</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O21" t="n">
-        <v>74259.26072607259</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9745705628087887</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1262673180421449</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R21" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.000185442049143351</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T21" t="n">
-        <v>7.919705712496602</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U21" t="n">
-        <v>4943.436169163572</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grok 4.6 (xhigh)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4696895205744764</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02414155383854575</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.583333333333333</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J22" t="n">
-        <v>3.570143280528054</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K22" t="n">
-        <v>1167.338748074809</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L22" t="n">
-        <v>112.0616061606161</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M22" t="n">
-        <v>5543624.597359739</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N22" t="n">
-        <v>5487669.762376238</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O22" t="n">
-        <v>55954.83498349835</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9057792630165156</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1315604119129374</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R22" t="n">
-        <v>8.472606907729202e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0004023592306424291</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T22" t="n">
-        <v>7.601070758745943</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U22" t="n">
-        <v>4748.942504052369</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna (max)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.4322468668029613</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01836403763159828</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.486559139784946</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4380225639383938</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K23" t="n">
-        <v>1412.260883388339</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L23" t="n">
-        <v>121.5137513751375</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M23" t="n">
-        <v>14854524.53905389</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N23" t="n">
-        <v>14783219.74807481</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O23" t="n">
-        <v>71304.79097909792</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R23" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0003060672938599712</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T23" t="n">
-        <v>1.013362033548448</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U23" t="n">
-        <v>10518.2581446386</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro 0813 (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4305203524444174</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01068487561410279</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.618279569892473</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2380461072079206</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K24" t="n">
-        <v>2417.550009900991</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L24" t="n">
-        <v>138.1463146314632</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M24" t="n">
-        <v>24180108.02805281</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N24" t="n">
-        <v>24063625.6270627</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O24" t="n">
-        <v>116482.400990099</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.808558675855097</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R24" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0001780812602350464</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5529264896684616</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U24" t="n">
-        <v>10001.90603256356</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.594086021505376</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J25" t="n">
-        <v>3.977504096947204</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K25" t="n">
-        <v>1106.853353135313</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L25" t="n">
-        <v>185.2381738173817</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M25" t="n">
-        <v>16709444.57370737</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N25" t="n">
-        <v>16445971.06820682</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O25" t="n">
-        <v>263473.5055005501</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R25" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T25" t="n">
-        <v>7.32468488284717</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U25" t="n">
-        <v>15096.34905687875</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.637577603035782</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.564516129032258</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J26" t="n">
-        <v>5.84390538944481</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K26" t="n">
-        <v>2070.168603200884</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L26" t="n">
-        <v>149.1832229580574</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M26" t="n">
-        <v>13733793.78145695</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N26" t="n">
-        <v>13621672.65011038</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O26" t="n">
-        <v>112121.1313465784</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1091012876743978</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R26" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T26" t="n">
-        <v>9.165794660319708</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U26" t="n">
-        <v>6634.142629842724</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F27" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.669354838709677</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J27" t="n">
-        <v>14.19080079636965</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K27" t="n">
-        <v>5244.965372937293</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L27" t="n">
-        <v>265.9306930693069</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M27" t="n">
-        <v>27742337.2337734</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N27" t="n">
-        <v>27141368.95929593</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O27" t="n">
-        <v>600968.2744774478</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9278388366571143</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R27" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T27" t="n">
-        <v>20.75958236310095</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U27" t="n">
-        <v>5289.327051979582</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Haiku 5.5 (low)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.2818428360106922</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.02438275023528984</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.629032258064516</v>
+        <v>0.330645161290323</v>
       </c>
       <c r="J28" t="n">
-        <v>8.817468730473037</v>
+        <v>0.1432474137843784</v>
       </c>
       <c r="K28" t="n">
-        <v>2354.367686468646</v>
+        <v>693.5464620462047</v>
       </c>
       <c r="L28" t="n">
-        <v>162.6457645764577</v>
+        <v>33.57535753575357</v>
       </c>
       <c r="M28" t="n">
-        <v>14324724.28382839</v>
+        <v>2412388.353135315</v>
       </c>
       <c r="N28" t="n">
-        <v>14201447.9559956</v>
+        <v>2364249.308030803</v>
       </c>
       <c r="O28" t="n">
-        <v>123276.3278327833</v>
+        <v>48139.04510451045</v>
       </c>
       <c r="P28" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9478942152323017</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.06381382835258244</v>
+        <v>1.967524778038458</v>
       </c>
       <c r="R28" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001168314527983808</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0004063791705881639</v>
       </c>
       <c r="T28" t="n">
-        <v>15.67058466504826</v>
+        <v>0.5082528114319146</v>
       </c>
       <c r="U28" t="n">
-        <v>6084.319100265209</v>
+        <v>3478.337047553996</v>
       </c>
     </row>
     <row r="29">
@@ -2286,7 +2274,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-6.1 Sol (low)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2296,246 +2284,961 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5721634943016617</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.06629758303140638</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.618279569892473</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J29" t="n">
-        <v>7.46709735138597</v>
+        <v>0.4988036451027072</v>
       </c>
       <c r="K29" t="n">
-        <v>1762.03302640264</v>
+        <v>517.8138943894386</v>
       </c>
       <c r="L29" t="n">
-        <v>39.37843784378438</v>
+        <v>35.74037403740374</v>
       </c>
       <c r="M29" t="n">
-        <v>3346611.012209417</v>
+        <v>1713818.918195099</v>
       </c>
       <c r="N29" t="n">
-        <v>3299549.915435806</v>
+        <v>1699123.860141752</v>
       </c>
       <c r="O29" t="n">
-        <v>47061.09677361179</v>
+        <v>14695.05805334632</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9135762473536158</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.08255556622206355</v>
+        <v>1.147071598051071</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0001842014048331127</v>
+        <v>0.0003338529457384175</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.001104959717190106</v>
       </c>
       <c r="T29" t="n">
-        <v>12.11305361664085</v>
+        <v>0.8717851629305855</v>
       </c>
       <c r="U29" t="n">
-        <v>1899.289605849129</v>
+        <v>3309.719837116163</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.519259105470924</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.008444738328521398</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.647849462365591</v>
+        <v>0.661290322580645</v>
       </c>
       <c r="J30" t="n">
-        <v>12.38809237513753</v>
+        <v>5.047195443300332</v>
       </c>
       <c r="K30" t="n">
-        <v>2089.900125412543</v>
+        <v>3689.344194719472</v>
       </c>
       <c r="L30" t="n">
-        <v>36.65676567656766</v>
+        <v>173.3602860286028</v>
       </c>
       <c r="M30" t="n">
-        <v>5715253.85918592</v>
+        <v>8481121.533553353</v>
       </c>
       <c r="N30" t="n">
-        <v>5581622.259625964</v>
+        <v>8387890.666666667</v>
       </c>
       <c r="O30" t="n">
-        <v>133631.599559956</v>
+        <v>93230.86688668867</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.9500000000000017</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.1028807208486825</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001088709227809481</v>
+        <v>6.12252876481737e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.00014074563880869</v>
       </c>
       <c r="T30" t="n">
-        <v>19.90934652274569</v>
+        <v>9.719994103373407</v>
       </c>
       <c r="U30" t="n">
-        <v>2734.701907373559</v>
+        <v>2298.815476661763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.659885802549234</v>
+        <v>0.5355484140097326</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01112652294860106</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.663978494623656</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J31" t="n">
-        <v>13.03638341842683</v>
+        <v>4.241385833751375</v>
       </c>
       <c r="K31" t="n">
-        <v>3867.092341034102</v>
+        <v>2887.955652365237</v>
       </c>
       <c r="L31" t="n">
-        <v>155.0957095709571</v>
+        <v>107.049504950495</v>
       </c>
       <c r="M31" t="n">
-        <v>15551383.220022</v>
+        <v>14276424.42684269</v>
       </c>
       <c r="N31" t="n">
-        <v>15218206.4180418</v>
+        <v>14202165.16611661</v>
       </c>
       <c r="O31" t="n">
-        <v>333176.801980198</v>
+        <v>74259.26072607259</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9500106599458848</v>
+        <v>0.9745705628087887</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.05061877833513936</v>
+        <v>0.1262673180421449</v>
       </c>
       <c r="R31" t="n">
-        <v>4.243261150555715e-05</v>
+        <v>3.751278317299032e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0001706413357517016</v>
+        <v>0.000185442049143351</v>
       </c>
       <c r="T31" t="n">
-        <v>19.75551431484872</v>
+        <v>7.919705712496602</v>
       </c>
       <c r="U31" t="n">
-        <v>4021.466737425617</v>
+        <v>4943.436169163572</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>Grok 4.6 (xhigh)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.4696895205744764</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.02414155383854575</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.570143280528054</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1167.338748074809</v>
+      </c>
+      <c r="L32" t="n">
+        <v>112.0616061606161</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5543624.597359739</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5487669.762376238</v>
+      </c>
+      <c r="O32" t="n">
+        <v>55954.83498349835</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9057792630165156</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.1315604119129374</v>
+      </c>
+      <c r="R32" t="n">
+        <v>8.472606907729202e-05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.0004023592306424291</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7.601070758745943</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4748.942504052369</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna (max)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4322468668029613</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.01836403763159828</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0.486559139784946</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.4380225639383938</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1412.260883388339</v>
+      </c>
+      <c r="L33" t="n">
+        <v>121.5137513751375</v>
+      </c>
+      <c r="M33" t="n">
+        <v>14854524.53905389</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14783219.74807481</v>
+      </c>
+      <c r="O33" t="n">
+        <v>71304.79097909792</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9718803286808345</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.9868141561395799</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.909866725565972e-05</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.0003060672938599712</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.013362033548448</v>
+      </c>
+      <c r="U33" t="n">
+        <v>10518.2581446386</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro 0813 (max)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4305203524444174</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.01068487561410279</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0.618279569892473</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.2380461072079206</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2417.550009900991</v>
+      </c>
+      <c r="L34" t="n">
+        <v>138.1463146314632</v>
+      </c>
+      <c r="M34" t="n">
+        <v>24180108.02805281</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24063625.6270627</v>
+      </c>
+      <c r="O34" t="n">
+        <v>116482.400990099</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9898485564269163</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.808558675855097</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.780473238353379e-05</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.0001780812602350464</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.5529264896684616</v>
+      </c>
+      <c r="U34" t="n">
+        <v>10001.90603256356</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GPT-6.1 Sol (xhigh)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6290776736822983</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.04052542124850751</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
         <v>0.610215053763441</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J35" t="n">
         <v>1.039708101440963</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K35" t="n">
         <v>931.3823091309132</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L35" t="n">
         <v>40.05500550055005</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M35" t="n">
         <v>3212528.109451931</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N35" t="n">
         <v>3177125.49569875</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O35" t="n">
         <v>35402.61375317859</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P35" t="n">
         <v>0.9327572280083256</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q35" t="n">
         <v>0.6050521995648973</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R35" t="n">
         <v>0.0001958201305169657</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S35" t="n">
         <v>0.0006754236874751251</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T35" t="n">
         <v>1.652749962266257</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U35" t="n">
         <v>3449.204561819077</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Antigravity CLI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gemini 4 Argon</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.637577603035782</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01847900510277171</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0.564516129032258</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5.843905389444815</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2070.168603200884</v>
+      </c>
+      <c r="L36" t="n">
+        <v>149.1832229580574</v>
+      </c>
+      <c r="M36" t="n">
+        <v>13733793.78145695</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13621672.65011038</v>
+      </c>
+      <c r="O36" t="n">
+        <v>112121.1313465784</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.8700000000000004</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.1091012876743977</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4.642399712573407e-05</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.0003079834183795285</v>
+      </c>
+      <c r="T36" t="n">
+        <v>9.165794660319715</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6634.142629842724</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sonnet 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6835783373750831</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.007819822882745912</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>0.669354838709677</v>
+      </c>
+      <c r="J37" t="n">
+        <v>14.19080079636965</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5244.965372937293</v>
+      </c>
+      <c r="L37" t="n">
+        <v>265.9306930693069</v>
+      </c>
+      <c r="M37" t="n">
+        <v>27742337.2337734</v>
+      </c>
+      <c r="N37" t="n">
+        <v>27141368.95929593</v>
+      </c>
+      <c r="O37" t="n">
+        <v>600968.2744774478</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.9506214943317096</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.04817052590506091</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.464025765438745e-05</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.0001303303813790985</v>
+      </c>
+      <c r="T37" t="n">
+        <v>20.75958236310095</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5289.327051979582</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Muse Code</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Muse Wonder (max)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6349675266318143</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.02829093785912806</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>0.672043010752688</v>
+      </c>
+      <c r="J38" t="n">
+        <v>8.052232502530256</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1346.652125412539</v>
+      </c>
+      <c r="L38" t="n">
+        <v>191.9551493610899</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15016299.67931794</v>
+      </c>
+      <c r="N38" t="n">
+        <v>14926250.65016502</v>
+      </c>
+      <c r="O38" t="n">
+        <v>90049.02915291529</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.935735212525825</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.07885608449983135</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4.228521940770533e-05</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.0004715156309854677</v>
+      </c>
+      <c r="T38" t="n">
+        <v>12.68132961892292</v>
+      </c>
+      <c r="U38" t="n">
+        <v>11150.83798996551</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GPT-6.1 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6014750704302517</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.02466668430491293</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>0.577956989247312</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.554119528390054</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1463.046422442244</v>
+      </c>
+      <c r="L39" t="n">
+        <v>40.45654565456545</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3999501.610795507</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3937843.056466302</v>
+      </c>
+      <c r="O39" t="n">
+        <v>61658.55432920342</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9281954641245814</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3870198266238458</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.000150387505484869</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.0004111114050818821</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.583846953587535</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2733.680592389675</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (max)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6164504498789397</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0209911088149403</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>0.618279569892473</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7.46709735138597</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1762.03302640264</v>
+      </c>
+      <c r="L40" t="n">
+        <v>39.37843784378438</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3346611.012209417</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3299549.915435806</v>
+      </c>
+      <c r="O40" t="n">
+        <v>47061.09677361179</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.9335591564904552</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.08255556622206355</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.0001842014048331127</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.0003498518135823383</v>
+      </c>
+      <c r="T40" t="n">
+        <v>12.11305361664085</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1899.289605849129</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Grok 4.7 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5626764360706693</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.01433955552408987</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0.629032258064516</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8.817468730473037</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2354.367686468646</v>
+      </c>
+      <c r="L41" t="n">
+        <v>162.6457645764577</v>
+      </c>
+      <c r="M41" t="n">
+        <v>14324724.28382839</v>
+      </c>
+      <c r="N41" t="n">
+        <v>14201447.9559956</v>
+      </c>
+      <c r="O41" t="n">
+        <v>123276.3278327833</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.938882976190201</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.06381382835258244</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3.928008839275821e-05</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.0002389925920681645</v>
+      </c>
+      <c r="T41" t="n">
+        <v>15.67058466504826</v>
+      </c>
+      <c r="U41" t="n">
+        <v>6084.319100265209</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fable 5.1 (max) (with fallback)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6222249615769457</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.01786377121119468</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J42" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L42" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O42" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T42" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J43" t="n">
+        <v>13.03638341842683</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3867.092341034102</v>
+      </c>
+      <c r="L43" t="n">
+        <v>155.0957095709571</v>
+      </c>
+      <c r="M43" t="n">
+        <v>15551383.220022</v>
+      </c>
+      <c r="N43" t="n">
+        <v>15218206.4180418</v>
+      </c>
+      <c r="O43" t="n">
+        <v>333176.801980198</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.9500106599458848</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.05061877833513936</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4.243261150555715e-05</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.0001706413357517016</v>
+      </c>
+      <c r="T43" t="n">
+        <v>19.75551431484872</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4021.466737425617</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,131 +526,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.545698924731183</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J2" t="n">
-        <v>3.467754041474145</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K2" t="n">
-        <v>1098.202911991198</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L2" t="n">
-        <v>187.4895489548955</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M2" t="n">
-        <v>16237094.3520352</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N2" t="n">
-        <v>16091465.1039604</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O2" t="n">
-        <v>145629.2480748075</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R2" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T2" t="n">
-        <v>7.179716478526343</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U2" t="n">
-        <v>14785.14960645573</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (xhigh)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6290776736822983</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04052542124850751</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.610215053763441</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J3" t="n">
-        <v>1.039708101440963</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K3" t="n">
-        <v>931.3823091309132</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L3" t="n">
-        <v>40.05500550055005</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M3" t="n">
-        <v>3212528.109451931</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N3" t="n">
-        <v>3177125.49569875</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O3" t="n">
-        <v>35402.61375317859</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6050521995648973</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001958201305169657</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006754236874751251</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T3" t="n">
-        <v>1.652749962266257</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U3" t="n">
-        <v>3449.204561819077</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -671,116 +671,116 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.336021505376344</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J4" t="n">
-        <v>2.580340961258277</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K4" t="n">
-        <v>5225.859279249448</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L4" t="n">
-        <v>120.9243929359824</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M4" t="n">
-        <v>13769015.17770419</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N4" t="n">
-        <v>12778720.50662252</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O4" t="n">
-        <v>990294.6710816775</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R4" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T4" t="n">
-        <v>7.074736286251795</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U4" t="n">
-        <v>2634.784911330742</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.4117608187690975</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.01631992906626261</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.575268817204301</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J5" t="n">
-        <v>2.989729004180416</v>
+        <v>3.32599273971397</v>
       </c>
       <c r="K5" t="n">
-        <v>1338.052705170518</v>
+        <v>1513.833119361935</v>
       </c>
       <c r="L5" t="n">
-        <v>86.55005500550054</v>
+        <v>188.8080308030803</v>
       </c>
       <c r="M5" t="n">
-        <v>9840777.763476355</v>
+        <v>16314434.26072608</v>
       </c>
       <c r="N5" t="n">
-        <v>9778602.140814083</v>
+        <v>16209156.91639164</v>
       </c>
       <c r="O5" t="n">
-        <v>62175.62266226623</v>
+        <v>105277.3443344334</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9692708877835391</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.18952417157726</v>
+        <v>0.123800877209524</v>
       </c>
       <c r="R5" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>2.523904980023328e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0002719988177710436</v>
       </c>
       <c r="T5" t="n">
-        <v>5.276371829924331</v>
+        <v>8.077487191852224</v>
       </c>
       <c r="U5" t="n">
-        <v>7354.551674571196</v>
+        <v>10776.90404052095</v>
       </c>
     </row>
     <row r="6">
@@ -791,61 +791,61 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.448924731182796</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6187507753025301</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K6" t="n">
-        <v>510.7721826182621</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L6" t="n">
-        <v>22.20902090209021</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M6" t="n">
-        <v>1253351.492849284</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N6" t="n">
-        <v>1232830.718371837</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O6" t="n">
-        <v>20520.77447744774</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003660902437453124</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T6" t="n">
-        <v>1.348511698390355</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U6" t="n">
-        <v>2453.836633045474</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +856,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -866,565 +866,559 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.420593075103495</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.389784946236559</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4831101147414734</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K7" t="n">
-        <v>380.8561793179318</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L7" t="n">
-        <v>18.57865786578658</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M7" t="n">
-        <v>977284.7700770069</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N7" t="n">
-        <v>961481.2431243125</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O7" t="n">
-        <v>15803.52695269527</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004303690060271313</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T7" t="n">
-        <v>1.148640201987622</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U7" t="n">
-        <v>2566.020516792475</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.6810374657220217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.0124204551066807</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.583333333333333</v>
+        <v>0.696236559139785</v>
       </c>
       <c r="J8" t="n">
-        <v>1.662215663091308</v>
+        <v>9.009237885244771</v>
       </c>
       <c r="K8" t="n">
-        <v>3381.269037953798</v>
+        <v>3289.915513751374</v>
       </c>
       <c r="L8" t="n">
-        <v>138.5951595159516</v>
+        <v>115.6490649064906</v>
       </c>
       <c r="M8" t="n">
-        <v>21745804.32343233</v>
+        <v>12806701.57480748</v>
       </c>
       <c r="N8" t="n">
-        <v>21619802.9180418</v>
+        <v>12511134.81463146</v>
       </c>
       <c r="O8" t="n">
-        <v>126001.4053905391</v>
+        <v>295566.7601760176</v>
       </c>
       <c r="P8" t="n">
-        <v>0.987035206105383</v>
+        <v>0.8712080457734013</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.07559323822910896</v>
       </c>
       <c r="R8" t="n">
-        <v>2.354685177223e-05</v>
+        <v>5.317820999762459e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.000207007585111345</v>
       </c>
       <c r="T8" t="n">
-        <v>3.246228188888836</v>
+        <v>13.2286964208252</v>
       </c>
       <c r="U8" t="n">
-        <v>6431.255271125063</v>
+        <v>3892.714424208558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.620967741935484</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J9" t="n">
-        <v>10.78915469925741</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K9" t="n">
-        <v>2515.540235973597</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L9" t="n">
-        <v>152.1303630363036</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M9" t="n">
-        <v>11374850.48899891</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N9" t="n">
-        <v>11238194.40979098</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O9" t="n">
-        <v>136656.0792079208</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R9" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T9" t="n">
-        <v>18.06430758687328</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U9" t="n">
-        <v>4521.832060697078</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.335918178838533</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.416666666666667</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2263884094719471</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K10" t="n">
-        <v>837.3769053905384</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L10" t="n">
-        <v>44.01650165016502</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M10" t="n">
-        <v>3480808.845984597</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N10" t="n">
-        <v>3413192.581958196</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O10" t="n">
-        <v>67616.26402640264</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P10" t="n">
-        <v>0.95547252331787</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.483813502740997</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R10" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004011552942003655</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6739391427242943</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U10" t="n">
-        <v>4156.800627742662</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6803093740718634</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02365082421477135</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.68010752688172</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
+        <v>0.60752688172043</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7046746644898908</v>
+      </c>
       <c r="K11" t="n">
-        <v>1725.883295805741</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L11" t="n">
-        <v>194.9635761589404</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M11" t="n">
-        <v>15002315.66997792</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N11" t="n">
-        <v>14917198.82339956</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O11" t="n">
-        <v>85116.84657836644</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9637709553156532</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>0.9239660644436648</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.8715333479481563</v>
+      </c>
       <c r="R11" t="n">
-        <v>4.534695769888867e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003941804035795226</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
+        <v>0.000942923242496814</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.147403025201837</v>
+      </c>
       <c r="U11" t="n">
-        <v>8692.543526226078</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.60752688172043</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.7046746644898908</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>651.3228668866898</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L12" t="n">
-        <v>37.98899889988999</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M12" t="n">
-        <v>2298278.745423723</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N12" t="n">
-        <v>2275866.51440062</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O12" t="n">
-        <v>22412.23102310231</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9239660644436648</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.8715333479481563</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0.0002672206192482065</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.000942923242496814</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.147403025201837</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>3528.632053730048</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.54559127289644</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.540322580645161</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J13" t="n">
-        <v>6.353318230693071</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K13" t="n">
-        <v>1237.696445544555</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L13" t="n">
-        <v>116.3949394939494</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M13" t="n">
-        <v>10170136.63256324</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N13" t="n">
-        <v>10120981.25467547</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O13" t="n">
-        <v>49155.37788778878</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08587501099199978</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R13" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T13" t="n">
-        <v>11.64483111499294</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U13" t="n">
-        <v>8216.987831849709</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.2771443620715672</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.006542828532467639</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.658602150537635</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7.897126985217273</v>
-      </c>
+        <v>0.397849462365591</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>2146.992089658964</v>
+        <v>2541.509630242825</v>
       </c>
       <c r="L14" t="n">
-        <v>99.53135313531354</v>
+        <v>95.90949227373069</v>
       </c>
       <c r="M14" t="n">
-        <v>9691548.173817372</v>
+        <v>5065557.310154528</v>
       </c>
       <c r="N14" t="n">
-        <v>9590504.44719472</v>
+        <v>5026647.232891832</v>
       </c>
       <c r="O14" t="n">
-        <v>101043.7266226623</v>
+        <v>38910.07726269315</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9584900963367992</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.07810758905045663</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.471152434027297e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002872975416218702</v>
-      </c>
-      <c r="T14" t="n">
-        <v>12.802853245848</v>
-      </c>
+        <v>0.000109047142207794</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>4514.012054584146</v>
+        <v>1993.129299954904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6810374657220217</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0124204551066807</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.696236559139785</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J15" t="n">
-        <v>9.009237885244771</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K15" t="n">
-        <v>3289.915513751374</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L15" t="n">
-        <v>115.6490649064906</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M15" t="n">
-        <v>12806701.57480748</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N15" t="n">
-        <v>12511134.81463146</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O15" t="n">
-        <v>295566.7601760176</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8712080457734013</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07559323822910896</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R15" t="n">
-        <v>5.317820999762459e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.000207007585111345</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T15" t="n">
-        <v>13.2286964208252</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U15" t="n">
-        <v>3892.714424208558</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="16">
@@ -1435,61 +1429,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.414392761951997</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6104935163943895</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K16" t="n">
-        <v>1552.934440044002</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L16" t="n">
-        <v>75.22717271727173</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M16" t="n">
-        <v>7080866.402640261</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N16" t="n">
-        <v>6891342.883388339</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O16" t="n">
-        <v>189523.5192519252</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6787832316376182</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R16" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0002668449815178645</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T16" t="n">
-        <v>1.473224371773918</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U16" t="n">
-        <v>4559.668599042484</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="17">
@@ -1500,386 +1494,386 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.620967741935484</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J17" t="n">
-        <v>3.478965577837015</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K17" t="n">
-        <v>3784.416073707372</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L17" t="n">
-        <v>110.0367013624439</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M17" t="n">
-        <v>8706893.798112892</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N17" t="n">
-        <v>8600561.252779894</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O17" t="n">
-        <v>106332.5453329948</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R17" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T17" t="n">
-        <v>8.041007149609982</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U17" t="n">
-        <v>2300.723183849934</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4117608187690975</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01631992906626261</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.577956989247312</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J18" t="n">
-        <v>3.32599273971397</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K18" t="n">
-        <v>1513.833119361935</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L18" t="n">
-        <v>188.8080308030803</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M18" t="n">
-        <v>16314434.26072608</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N18" t="n">
-        <v>16209156.91639164</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O18" t="n">
-        <v>105277.3443344334</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9692708877835391</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.123800877209524</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R18" t="n">
-        <v>2.523904980023328e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002719988177710436</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T18" t="n">
-        <v>8.077487191852224</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U18" t="n">
-        <v>10776.90404052095</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.350585020439431</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.46236559139785</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3646793423707372</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K19" t="n">
-        <v>1106.807743674368</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L19" t="n">
-        <v>58.5038503850385</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M19" t="n">
-        <v>5076190.689768974</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N19" t="n">
-        <v>4970717.200220022</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O19" t="n">
-        <v>105473.4895489549</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R19" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T19" t="n">
-        <v>1.040202293622358</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U19" t="n">
-        <v>4586.334635604457</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.588884131062264</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.594086021505376</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J20" t="n">
-        <v>4.536492777821779</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K20" t="n">
-        <v>1481.89598019802</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L20" t="n">
-        <v>78.55115511551155</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M20" t="n">
-        <v>6074134.495049492</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N20" t="n">
-        <v>6017554.665016501</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O20" t="n">
-        <v>56579.83003300329</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R20" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0003973856052862588</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T20" t="n">
-        <v>7.703540541394086</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U20" t="n">
-        <v>4098.893968413241</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.451612903225807</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J21" t="n">
-        <v>2.467392200412544</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K21" t="n">
-        <v>702.7110253025301</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L21" t="n">
-        <v>188.4884488448845</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M21" t="n">
-        <v>13511073.15511551</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N21" t="n">
-        <v>13395246.74862486</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O21" t="n">
-        <v>115826.4064906491</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1696655897976026</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R21" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T21" t="n">
-        <v>5.893947035417844</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U21" t="n">
-        <v>19227.06869342024</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.443548387096774</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1759117230445546</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K22" t="n">
-        <v>1285.926851485148</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L22" t="n">
-        <v>88.64301430143014</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M22" t="n">
-        <v>10218069.24807481</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N22" t="n">
-        <v>10119727.86413641</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O22" t="n">
-        <v>98341.38393839383</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R22" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4282759302584503</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U22" t="n">
-        <v>7946.073477098422</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="23">
@@ -1938,13 +1932,13 @@
         <v>8.870519132228135e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T23" t="n">
         <v>5.30191348359169</v>
       </c>
       <c r="U23" t="n">
-        <v>4377.776049220427</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="24">
@@ -2189,7 +2183,7 @@
         <v>28748.73548666342</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9278388366571141</v>
+        <v>0.9278388366571143</v>
       </c>
       <c r="Q27" t="n">
         <v>0.6764107362832188</v>
@@ -2579,7 +2573,7 @@
         <v>71304.79097909792</v>
       </c>
       <c r="P33" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9718803286808345</v>
       </c>
       <c r="Q33" t="n">
         <v>0.9868141561395799</v>
@@ -2670,7 +2664,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-6.1 Sol (xhigh)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2680,441 +2674,441 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6290776736822983</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.04052542124850751</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.618279569892473</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J35" t="n">
-        <v>7.46709735138597</v>
+        <v>1.039708101440963</v>
       </c>
       <c r="K35" t="n">
-        <v>1762.03302640264</v>
+        <v>931.3823091309132</v>
       </c>
       <c r="L35" t="n">
-        <v>39.37843784378438</v>
+        <v>40.05500550055005</v>
       </c>
       <c r="M35" t="n">
-        <v>3346611.012209417</v>
+        <v>3212528.109451931</v>
       </c>
       <c r="N35" t="n">
-        <v>3299549.915435806</v>
+        <v>3177125.49569875</v>
       </c>
       <c r="O35" t="n">
-        <v>47061.09677361179</v>
+        <v>35402.61375317859</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9327572280083256</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.6050521995648973</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0001842014048331127</v>
+        <v>0.0001958201305169657</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0006754236874751251</v>
       </c>
       <c r="T35" t="n">
-        <v>12.11305361664085</v>
+        <v>1.652749962266257</v>
       </c>
       <c r="U35" t="n">
-        <v>1899.289605849129</v>
+        <v>3449.204561819077</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.577956989247312</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J36" t="n">
-        <v>1.554119528390054</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K36" t="n">
-        <v>1463.046422442244</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L36" t="n">
-        <v>40.45654565456545</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M36" t="n">
-        <v>3999501.610795507</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N36" t="n">
-        <v>3937843.056466302</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O36" t="n">
-        <v>61658.55432920342</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R36" t="n">
-        <v>0.000150387505484869</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T36" t="n">
-        <v>2.583846953587535</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U36" t="n">
-        <v>2733.680592389675</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6349675266318143</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02829093785912806</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.672043010752688</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J37" t="n">
-        <v>8.052232502530256</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K37" t="n">
-        <v>1346.652125412539</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L37" t="n">
-        <v>191.9551493610899</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M37" t="n">
-        <v>15016299.67931794</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N37" t="n">
-        <v>14926250.65016502</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O37" t="n">
-        <v>90049.02915291529</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P37" t="n">
-        <v>0.935735212525825</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.07885608449983135</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R37" t="n">
-        <v>4.228521940770533e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0004715156309854677</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T37" t="n">
-        <v>12.68132961892292</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U37" t="n">
-        <v>11150.83798996551</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.6349675266318143</v>
       </c>
       <c r="F38" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.02829093785912806</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.669354838709677</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J38" t="n">
-        <v>14.19080079636965</v>
+        <v>8.052232502530256</v>
       </c>
       <c r="K38" t="n">
-        <v>5244.965372937293</v>
+        <v>1346.652125412539</v>
       </c>
       <c r="L38" t="n">
-        <v>265.9306930693069</v>
+        <v>191.9551493610899</v>
       </c>
       <c r="M38" t="n">
-        <v>27742337.2337734</v>
+        <v>15016299.67931794</v>
       </c>
       <c r="N38" t="n">
-        <v>27141368.95929593</v>
+        <v>14926250.65016502</v>
       </c>
       <c r="O38" t="n">
-        <v>600968.2744774478</v>
+        <v>90049.02915291529</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.935735212525825</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.07885608449983135</v>
       </c>
       <c r="R38" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.228521940770533e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0004715156309854677</v>
       </c>
       <c r="T38" t="n">
-        <v>20.75958236310095</v>
+        <v>12.68132961892292</v>
       </c>
       <c r="U38" t="n">
-        <v>5289.327051979582</v>
+        <v>11150.83798996551</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.637577603035782</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.564516129032258</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J39" t="n">
-        <v>5.84390538944481</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K39" t="n">
-        <v>2070.168603200884</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L39" t="n">
-        <v>149.1832229580574</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M39" t="n">
-        <v>13733793.78145695</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N39" t="n">
-        <v>13621672.65011038</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O39" t="n">
-        <v>112121.1313465784</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R39" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T39" t="n">
-        <v>9.165794660319708</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U39" t="n">
-        <v>6634.142629842724</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J40" t="n">
-        <v>8.817468730473037</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K40" t="n">
-        <v>2354.367686468646</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L40" t="n">
-        <v>162.6457645764577</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M40" t="n">
-        <v>14324724.28382839</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N40" t="n">
-        <v>14201447.9559956</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O40" t="n">
-        <v>123276.3278327833</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P40" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R40" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T40" t="n">
-        <v>15.67058466504826</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U40" t="n">
-        <v>6084.319100265209</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6222249615769457</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01786377121119468</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.647849462365591</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J41" t="n">
-        <v>12.38809237513753</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K41" t="n">
-        <v>2089.900125412543</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L41" t="n">
-        <v>36.65676567656766</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M41" t="n">
-        <v>5715253.85918592</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N41" t="n">
-        <v>5581622.259625964</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O41" t="n">
-        <v>133631.599559956</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9159555838702423</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.05022766562717351</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0001088709227809481</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0002977295201865781</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T41" t="n">
-        <v>19.90934652274569</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U41" t="n">
-        <v>2734.701907373559</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="42">
@@ -3125,7 +3119,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -3135,50 +3129,115 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.659885802549234</v>
+        <v>0.6222249615769457</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0102384801451021</v>
+        <v>0.01786377121119468</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
+        <v>0.647849462365591</v>
+      </c>
+      <c r="J42" t="n">
+        <v>12.38809237513753</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2089.900125412543</v>
+      </c>
+      <c r="L42" t="n">
+        <v>36.65676567656766</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5715253.85918592</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5581622.259625964</v>
+      </c>
+      <c r="O42" t="n">
+        <v>133631.599559956</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.9159555838702423</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.05022766562717351</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.0001088709227809481</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.0002977295201865781</v>
+      </c>
+      <c r="T42" t="n">
+        <v>19.90934652274569</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2734.701907373559</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.659885802549234</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0102384801451021</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
         <v>0.663978494623656</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J43" t="n">
         <v>13.03638341842683</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K43" t="n">
         <v>3867.092341034102</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L43" t="n">
         <v>155.0957095709571</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>15551383.220022</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N43" t="n">
         <v>15218206.4180418</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O43" t="n">
         <v>333176.801980198</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P43" t="n">
         <v>0.9500106599458848</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q43" t="n">
         <v>0.05061877833513936</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>4.243261150555715e-05</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S43" t="n">
         <v>0.0001706413357517016</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T43" t="n">
         <v>19.75551431484872</v>
       </c>
-      <c r="U42" t="n">
+      <c r="U43" t="n">
         <v>4021.466737425617</v>
       </c>
     </row>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,131 +526,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.451612903225807</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J2" t="n">
-        <v>2.467392200412544</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K2" t="n">
-        <v>702.7110253025301</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L2" t="n">
-        <v>188.4884488448845</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M2" t="n">
-        <v>13511073.15511551</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N2" t="n">
-        <v>13395246.74862486</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O2" t="n">
-        <v>115826.4064906491</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9278388366571141</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R2" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T2" t="n">
-        <v>5.893947035417844</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U2" t="n">
-        <v>19227.06869342024</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.588884131062264</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.594086021505376</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J3" t="n">
-        <v>4.536492777821779</v>
+        <v>0.08506419165060494</v>
       </c>
       <c r="K3" t="n">
-        <v>1481.89598019802</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L3" t="n">
-        <v>78.55115511551155</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>6074134.495049492</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N3" t="n">
-        <v>6017554.665016501</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O3" t="n">
-        <v>56579.83003300329</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1298104416568739</v>
+        <v>4.554499000811647</v>
       </c>
       <c r="R3" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T3" t="n">
-        <v>7.703540541394086</v>
+        <v>0.2195631176605357</v>
       </c>
       <c r="U3" t="n">
-        <v>4098.893968413241</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -671,51 +671,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.350585020439431</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.46236559139785</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3646793423707372</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K4" t="n">
-        <v>1106.807743674368</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L4" t="n">
-        <v>58.5038503850385</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M4" t="n">
-        <v>5076190.689768974</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N4" t="n">
-        <v>4970717.200220022</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O4" t="n">
-        <v>105473.4895489549</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R4" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T4" t="n">
-        <v>1.040202293622358</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U4" t="n">
-        <v>4586.334635604457</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -736,51 +736,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4117608187690975</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01631992906626261</v>
+        <v>0.02943627526383025</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.577956989247312</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J5" t="n">
-        <v>3.32599273971397</v>
+        <v>3.977504096947204</v>
       </c>
       <c r="K5" t="n">
-        <v>1513.833119361935</v>
+        <v>1106.853353135313</v>
       </c>
       <c r="L5" t="n">
-        <v>188.8080308030803</v>
+        <v>185.2381738173817</v>
       </c>
       <c r="M5" t="n">
-        <v>16314434.26072608</v>
+        <v>16709444.57370737</v>
       </c>
       <c r="N5" t="n">
-        <v>16209156.91639164</v>
+        <v>16445971.06820682</v>
       </c>
       <c r="O5" t="n">
-        <v>105277.3443344334</v>
+        <v>263473.5055005501</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9692708877835391</v>
+        <v>0.9712826195905685</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.123800877209524</v>
+        <v>0.1365246445402428</v>
       </c>
       <c r="R5" t="n">
-        <v>2.523904980023328e-05</v>
+        <v>3.24982276100033e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002719988177710436</v>
+        <v>0.0004906045877305042</v>
       </c>
       <c r="T5" t="n">
-        <v>8.077487191852224</v>
+        <v>7.32468488284717</v>
       </c>
       <c r="U5" t="n">
-        <v>10776.90404052095</v>
+        <v>15096.34905687875</v>
       </c>
     </row>
     <row r="6">
@@ -791,20 +791,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -812,365 +812,365 @@
         <v>0.620967741935484</v>
       </c>
       <c r="J6" t="n">
-        <v>3.478965577837015</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K6" t="n">
-        <v>3784.416073707372</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L6" t="n">
-        <v>110.0367013624439</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M6" t="n">
-        <v>8706893.798112892</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N6" t="n">
-        <v>8600561.252779894</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O6" t="n">
-        <v>106332.5453329948</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R6" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T6" t="n">
-        <v>8.041007149609982</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U6" t="n">
-        <v>2300.723183849934</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.414392761951997</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6104935163943895</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K7" t="n">
-        <v>1552.934440044002</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L7" t="n">
-        <v>75.22717271727173</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M7" t="n">
-        <v>7080866.402640261</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N7" t="n">
-        <v>6891342.883388339</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O7" t="n">
-        <v>189523.5192519252</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6787832316376182</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R7" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002668449815178645</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T7" t="n">
-        <v>1.473224371773918</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U7" t="n">
-        <v>4559.668599042484</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6810374657220217</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0124204551066807</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.696236559139785</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J8" t="n">
-        <v>9.009237885244771</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K8" t="n">
-        <v>3289.915513751374</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L8" t="n">
-        <v>115.6490649064906</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M8" t="n">
-        <v>12806701.57480748</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N8" t="n">
-        <v>12511134.81463146</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O8" t="n">
-        <v>295566.7601760176</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8712080457734013</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07559323822910896</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R8" t="n">
-        <v>5.317820999762459e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000207007585111345</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T8" t="n">
-        <v>13.2286964208252</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U8" t="n">
-        <v>3892.714424208558</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.658602150537635</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J9" t="n">
-        <v>7.897126985217273</v>
+        <v>3.467754041474145</v>
       </c>
       <c r="K9" t="n">
-        <v>2146.992089658964</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L9" t="n">
-        <v>99.53135313531354</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M9" t="n">
-        <v>9691548.173817372</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N9" t="n">
-        <v>9590504.44719472</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O9" t="n">
-        <v>101043.7266226623</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1392812659094378</v>
       </c>
       <c r="R9" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T9" t="n">
-        <v>12.802853245848</v>
+        <v>7.179716478526343</v>
       </c>
       <c r="U9" t="n">
-        <v>4514.012054584146</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.54559127289644</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.02384313631717553</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.540322580645161</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J10" t="n">
-        <v>6.353318230693071</v>
+        <v>4.536492777821779</v>
       </c>
       <c r="K10" t="n">
-        <v>1237.696445544555</v>
+        <v>1481.89598019802</v>
       </c>
       <c r="L10" t="n">
-        <v>116.3949394939494</v>
+        <v>78.55115511551155</v>
       </c>
       <c r="M10" t="n">
-        <v>10170136.63256324</v>
+        <v>6074134.495049492</v>
       </c>
       <c r="N10" t="n">
-        <v>10120981.25467547</v>
+        <v>6017554.665016501</v>
       </c>
       <c r="O10" t="n">
-        <v>49155.37788778878</v>
+        <v>56579.83003300329</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9200611321722409</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.1298104416568739</v>
       </c>
       <c r="R10" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>9.694947182058831e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0003973856052862588</v>
       </c>
       <c r="T10" t="n">
-        <v>11.64483111499294</v>
+        <v>7.703540541394086</v>
       </c>
       <c r="U10" t="n">
-        <v>8216.987831849709</v>
+        <v>4098.893968413241</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.60752688172043</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7046746644898908</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K11" t="n">
-        <v>651.3228668866898</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L11" t="n">
-        <v>37.98899889988999</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M11" t="n">
-        <v>2298278.745423723</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N11" t="n">
-        <v>2275866.51440062</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O11" t="n">
-        <v>22412.23102310231</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0002672206192482065</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T11" t="n">
-        <v>1.147403025201837</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U11" t="n">
-        <v>3528.632053730048</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="12">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1191,45 +1191,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6803093740718634</v>
+        <v>0.4117608187690975</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02365082421477135</v>
+        <v>0.01631992906626261</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.68010752688172</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>0.577956989247312</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.32599273971397</v>
+      </c>
       <c r="K12" t="n">
-        <v>1725.883295805741</v>
+        <v>1513.833119361935</v>
       </c>
       <c r="L12" t="n">
-        <v>194.9635761589404</v>
+        <v>188.8080308030803</v>
       </c>
       <c r="M12" t="n">
-        <v>15002315.66997792</v>
+        <v>16314434.26072608</v>
       </c>
       <c r="N12" t="n">
-        <v>14917198.82339956</v>
+        <v>16209156.91639164</v>
       </c>
       <c r="O12" t="n">
-        <v>85116.84657836644</v>
+        <v>105277.3443344334</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9637709553156532</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>0.9692708877835391</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.123800877209524</v>
+      </c>
       <c r="R12" t="n">
-        <v>4.534695769888867e-05</v>
+        <v>2.523904980023328e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003941804035795226</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
+        <v>0.0002719988177710436</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8.077487191852224</v>
+      </c>
       <c r="U12" t="n">
-        <v>8692.543526226078</v>
+        <v>10776.90404052095</v>
       </c>
     </row>
     <row r="13">
@@ -1240,445 +1246,445 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.335918178838533</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.416666666666667</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2263884094719471</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K13" t="n">
-        <v>837.3769053905384</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L13" t="n">
-        <v>44.01650165016502</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M13" t="n">
-        <v>3480808.845984597</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N13" t="n">
-        <v>3413192.581958196</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O13" t="n">
-        <v>67616.26402640264</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P13" t="n">
-        <v>0.95547252331787</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.483813502740997</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R13" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004011552942003655</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6739391427242943</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U13" t="n">
-        <v>4156.800627742662</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2771443620715672</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006542828532467639</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.397849462365591</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>0.5161290322580649</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6104935163943895</v>
+      </c>
       <c r="K14" t="n">
-        <v>2541.509630242825</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L14" t="n">
-        <v>95.90949227373069</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M14" t="n">
-        <v>5065557.310154528</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N14" t="n">
-        <v>5026647.232891832</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O14" t="n">
-        <v>38910.07726269315</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>0.9502433850815568</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.6787832316376182</v>
+      </c>
       <c r="R14" t="n">
-        <v>5.471152434027297e-05</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.000109047142207794</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
+        <v>0.0002668449815178645</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.473224371773918</v>
+      </c>
       <c r="U14" t="n">
-        <v>1993.129299954904</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.6810374657220217</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.0124204551066807</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.620967741935484</v>
+        <v>0.696236559139785</v>
       </c>
       <c r="J15" t="n">
-        <v>10.78915469925741</v>
+        <v>9.009237885244771</v>
       </c>
       <c r="K15" t="n">
-        <v>2515.540235973597</v>
+        <v>3289.915513751374</v>
       </c>
       <c r="L15" t="n">
-        <v>152.1303630363036</v>
+        <v>115.6490649064906</v>
       </c>
       <c r="M15" t="n">
-        <v>11374850.48899891</v>
+        <v>12806701.57480748</v>
       </c>
       <c r="N15" t="n">
-        <v>11238194.40979098</v>
+        <v>12511134.81463146</v>
       </c>
       <c r="O15" t="n">
-        <v>136656.0792079208</v>
+        <v>295566.7601760176</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.8712080457734013</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.07559323822910896</v>
       </c>
       <c r="R15" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>5.317820999762459e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.000207007585111345</v>
       </c>
       <c r="T15" t="n">
-        <v>18.06430758687328</v>
+        <v>13.2286964208252</v>
       </c>
       <c r="U15" t="n">
-        <v>4521.832060697078</v>
+        <v>3892.714424208558</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.583333333333333</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J16" t="n">
-        <v>1.662215663091308</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K16" t="n">
-        <v>3381.269037953798</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L16" t="n">
-        <v>138.5951595159516</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M16" t="n">
-        <v>21745804.32343233</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N16" t="n">
-        <v>21619802.9180418</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O16" t="n">
-        <v>126001.4053905391</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R16" t="n">
-        <v>2.354685177223e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T16" t="n">
-        <v>3.246228188888836</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U16" t="n">
-        <v>6431.255271125063</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.420593075103495</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.389784946236559</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4831101147414734</v>
+        <v>6.353318230693071</v>
       </c>
       <c r="K17" t="n">
-        <v>380.8561793179318</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L17" t="n">
-        <v>18.57865786578658</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M17" t="n">
-        <v>977284.7700770069</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N17" t="n">
-        <v>961481.2431243125</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O17" t="n">
-        <v>15803.52695269527</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.08587501099199978</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0004303690060271313</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T17" t="n">
-        <v>1.148640201987622</v>
+        <v>11.64483111499294</v>
       </c>
       <c r="U17" t="n">
-        <v>2566.020516792475</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.448924731182796</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K18" t="n">
-        <v>510.7721826182621</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L18" t="n">
-        <v>22.20902090209021</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M18" t="n">
-        <v>1253351.492849284</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N18" t="n">
-        <v>1232830.718371837</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O18" t="n">
-        <v>20520.77447744774</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T18" t="n">
-        <v>1.348511698390355</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U18" t="n">
-        <v>2453.836633045474</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.575268817204301</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.989729004180416</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>1338.052705170518</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L19" t="n">
-        <v>86.55005500550054</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M19" t="n">
-        <v>9840777.763476355</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N19" t="n">
-        <v>9778602.140814083</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O19" t="n">
-        <v>62175.62266226623</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9640119921972632</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.18952417157726</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0004234705483335876</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5.276371829924331</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>7354.551674571196</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="20">
@@ -1689,7 +1695,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1699,181 +1705,175 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.336021505376344</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J20" t="n">
-        <v>2.580340961258277</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K20" t="n">
-        <v>5225.859279249448</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L20" t="n">
-        <v>120.9243929359824</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M20" t="n">
-        <v>13769015.17770419</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N20" t="n">
-        <v>12778720.50662252</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O20" t="n">
-        <v>990294.6710816775</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1413480247939816</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R20" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T20" t="n">
-        <v>7.074736286251795</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U20" t="n">
-        <v>2634.784911330742</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.2771443620715672</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.006542828532467639</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.443548387096774</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.1759117230445546</v>
-      </c>
+        <v>0.397849462365591</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>1285.926851485148</v>
+        <v>2541.509630242825</v>
       </c>
       <c r="L21" t="n">
-        <v>88.64301430143014</v>
+        <v>95.90949227373069</v>
       </c>
       <c r="M21" t="n">
-        <v>10218069.24807481</v>
+        <v>5065557.310154528</v>
       </c>
       <c r="N21" t="n">
-        <v>10119727.86413641</v>
+        <v>5026647.232891832</v>
       </c>
       <c r="O21" t="n">
-        <v>98341.38393839383</v>
+        <v>38910.07726269315</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9606438143896164</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.334943267525058</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>5.471152434027297e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0003194146641601249</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.4282759302584503</v>
-      </c>
+        <v>0.000109047142207794</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>7946.073477098422</v>
+        <v>1993.129299954904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.482993172759088</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.545698924731183</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J22" t="n">
-        <v>3.467754041474145</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K22" t="n">
-        <v>1098.202911991198</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L22" t="n">
-        <v>187.4895489548955</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M22" t="n">
-        <v>16237094.3520352</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N22" t="n">
-        <v>16091465.1039604</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O22" t="n">
-        <v>145629.2480748075</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R22" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T22" t="n">
-        <v>7.179716478526343</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U22" t="n">
-        <v>14785.14960645573</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="23">
@@ -1884,126 +1884,126 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.628713868151493</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.620967741935484</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>3.333386534873489</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K23" t="n">
-        <v>1619.013470847085</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L23" t="n">
-        <v>78.31683168316832</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M23" t="n">
-        <v>7087678.3960396</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N23" t="n">
-        <v>6961982.357535753</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O23" t="n">
-        <v>125696.0385038504</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.987035206105383</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R23" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T23" t="n">
-        <v>5.30191348359169</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U23" t="n">
-        <v>4377.776049220426</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.594086021505376</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J24" t="n">
-        <v>3.977504096947204</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K24" t="n">
-        <v>1106.853353135313</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L24" t="n">
-        <v>185.2381738173817</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M24" t="n">
-        <v>16709444.57370737</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N24" t="n">
-        <v>16445971.06820682</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O24" t="n">
-        <v>263473.5055005501</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R24" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T24" t="n">
-        <v>7.32468488284717</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U24" t="n">
-        <v>15096.34905687875</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="25">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2024,51 +2024,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.564516129032258</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J25" t="n">
-        <v>1.235497127172719</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K25" t="n">
-        <v>735.1809878987912</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L25" t="n">
-        <v>36.77227722772277</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M25" t="n">
-        <v>2652380.565456549</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N25" t="n">
-        <v>2610884.190319032</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O25" t="n">
-        <v>41496.37513751376</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0002074079836537043</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T25" t="n">
-        <v>2.245848381022551</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U25" t="n">
-        <v>3607.792651218138</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="26">
@@ -2079,126 +2079,126 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.513440860215054</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J26" t="n">
-        <v>0.08506419165060494</v>
+        <v>2.989729004180416</v>
       </c>
       <c r="K26" t="n">
-        <v>1097.040440044003</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L26" t="n">
-        <v>121.6666666666667</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M26" t="n">
-        <v>15350225.29922993</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N26" t="n">
-        <v>15269826.30913091</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O26" t="n">
-        <v>80398.9900990099</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9640119921972632</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.554499000811647</v>
+        <v>0.18952417157726</v>
       </c>
       <c r="R26" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2195631176605357</v>
+        <v>5.276371829924331</v>
       </c>
       <c r="U26" t="n">
-        <v>13992.39694264526</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.3647260981688613</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.004187553609992088</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.599462365591398</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8892413135295484</v>
+        <v>2.580340961258277</v>
       </c>
       <c r="K27" t="n">
-        <v>799.7652123212325</v>
+        <v>5225.859279249448</v>
       </c>
       <c r="L27" t="n">
-        <v>38.97909790979098</v>
+        <v>120.9243929359824</v>
       </c>
       <c r="M27" t="n">
-        <v>2819911.990351496</v>
+        <v>13769015.17770419</v>
       </c>
       <c r="N27" t="n">
-        <v>2791163.254864831</v>
+        <v>12778720.50662252</v>
       </c>
       <c r="O27" t="n">
-        <v>28748.73548666342</v>
+        <v>990294.6710816775</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9278388366571143</v>
+        <v>0.8918200950779239</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6764107362832188</v>
+        <v>0.1413480247939816</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0002133018241973586</v>
+        <v>2.648890232610483e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007520861902360213</v>
+        <v>6.979256016653481e-05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.478391672927692</v>
+        <v>7.074736286251795</v>
       </c>
       <c r="U27" t="n">
-        <v>3525.924792561313</v>
+        <v>2634.784911330742</v>
       </c>
     </row>
     <row r="28">
@@ -2573,7 +2573,7 @@
         <v>71304.79097909792</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9718803286808345</v>
+        <v>0.971880328680834</v>
       </c>
       <c r="Q33" t="n">
         <v>0.9868141561395799</v>
@@ -2724,261 +2724,261 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.637577603035782</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.564516129032258</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J36" t="n">
-        <v>5.843905389444815</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K36" t="n">
-        <v>2070.168603200884</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L36" t="n">
-        <v>149.1832229580574</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M36" t="n">
-        <v>13733793.78145695</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N36" t="n">
-        <v>13621672.65011038</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O36" t="n">
-        <v>112121.1313465784</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1091012876743977</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R36" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T36" t="n">
-        <v>9.165794660319715</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U36" t="n">
-        <v>6634.142629842724</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F37" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.669354838709677</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J37" t="n">
-        <v>14.19080079636965</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K37" t="n">
-        <v>5244.965372937293</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L37" t="n">
-        <v>265.9306930693069</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M37" t="n">
-        <v>27742337.2337734</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N37" t="n">
-        <v>27141368.95929593</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O37" t="n">
-        <v>600968.2744774478</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R37" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T37" t="n">
-        <v>20.75958236310095</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U37" t="n">
-        <v>5289.327051979582</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6349675266318143</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F38" t="n">
-        <v>0.02829093785912806</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.672043010752688</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J38" t="n">
-        <v>8.052232502530256</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K38" t="n">
-        <v>1346.652125412539</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L38" t="n">
-        <v>191.9551493610899</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M38" t="n">
-        <v>15016299.67931794</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N38" t="n">
-        <v>14926250.65016502</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O38" t="n">
-        <v>90049.02915291529</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P38" t="n">
-        <v>0.935735212525825</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.07885608449983135</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R38" t="n">
-        <v>4.228521940770533e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0004715156309854677</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T38" t="n">
-        <v>12.68132961892292</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U38" t="n">
-        <v>11150.83798996551</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6349675266318143</v>
       </c>
       <c r="F39" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02829093785912806</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.577956989247312</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J39" t="n">
-        <v>1.554119528390054</v>
+        <v>8.052232502530256</v>
       </c>
       <c r="K39" t="n">
-        <v>1463.046422442244</v>
+        <v>1346.652125412539</v>
       </c>
       <c r="L39" t="n">
-        <v>40.45654565456545</v>
+        <v>191.9551493610899</v>
       </c>
       <c r="M39" t="n">
-        <v>3999501.610795507</v>
+        <v>15016299.67931794</v>
       </c>
       <c r="N39" t="n">
-        <v>3937843.056466302</v>
+        <v>14926250.65016502</v>
       </c>
       <c r="O39" t="n">
-        <v>61658.55432920342</v>
+        <v>90049.02915291529</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.935735212525825</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.07885608449983135</v>
       </c>
       <c r="R39" t="n">
-        <v>0.000150387505484869</v>
+        <v>4.228521940770533e-05</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0004715156309854677</v>
       </c>
       <c r="T39" t="n">
-        <v>2.583846953587535</v>
+        <v>12.68132961892292</v>
       </c>
       <c r="U39" t="n">
-        <v>2733.680592389675</v>
+        <v>11150.83798996551</v>
       </c>
     </row>
     <row r="40">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2999,116 +2999,116 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.618279569892473</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J40" t="n">
-        <v>7.46709735138597</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K40" t="n">
-        <v>1762.03302640264</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L40" t="n">
-        <v>39.37843784378438</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M40" t="n">
-        <v>3346611.012209417</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N40" t="n">
-        <v>3299549.915435806</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O40" t="n">
-        <v>47061.09677361179</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0001842014048331127</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T40" t="n">
-        <v>12.11305361664085</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U40" t="n">
-        <v>1899.289605849129</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.0209911088149403</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J41" t="n">
-        <v>8.817468730473037</v>
+        <v>7.46709735138597</v>
       </c>
       <c r="K41" t="n">
-        <v>2354.367686468646</v>
+        <v>1762.03302640264</v>
       </c>
       <c r="L41" t="n">
-        <v>162.6457645764577</v>
+        <v>39.37843784378438</v>
       </c>
       <c r="M41" t="n">
-        <v>14324724.28382839</v>
+        <v>3346611.012209417</v>
       </c>
       <c r="N41" t="n">
-        <v>14201447.9559956</v>
+        <v>3299549.915435806</v>
       </c>
       <c r="O41" t="n">
-        <v>123276.3278327833</v>
+        <v>47061.09677361179</v>
       </c>
       <c r="P41" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9335591564904552</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.08255556622206355</v>
       </c>
       <c r="R41" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.0001842014048331127</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003498518135823383</v>
       </c>
       <c r="T41" t="n">
-        <v>15.67058466504826</v>
+        <v>12.11305361664085</v>
       </c>
       <c r="U41" t="n">
-        <v>6084.319100265209</v>
+        <v>1899.289605849129</v>
       </c>
     </row>
     <row r="42">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -570,7 +570,7 @@
         <v>28748.73548666342</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278388366571141</v>
+        <v>0.9278388366571144</v>
       </c>
       <c r="Q2" t="n">
         <v>0.6764107362832188</v>
@@ -1923,7 +1923,7 @@
         <v>126001.4053905391</v>
       </c>
       <c r="P23" t="n">
-        <v>0.987035206105383</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q23" t="n">
         <v>0.3080498171455697</v>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -541,506 +541,506 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.599462365591398</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8892413135295484</v>
+        <v>0.1759117230445546</v>
       </c>
       <c r="K2" t="n">
-        <v>799.7652123212325</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L2" t="n">
-        <v>38.97909790979098</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M2" t="n">
-        <v>2819911.990351496</v>
+        <v>10218069.24807481</v>
       </c>
       <c r="N2" t="n">
-        <v>2791163.254864831</v>
+        <v>10119727.86413641</v>
       </c>
       <c r="O2" t="n">
-        <v>28748.73548666342</v>
+        <v>98341.38393839383</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278388366571144</v>
+        <v>0.9606438143896164</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6764107362832188</v>
+        <v>2.334943267525058</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002133018241973586</v>
+        <v>4.019779896079717e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007520861902360213</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T2" t="n">
-        <v>1.478391672927692</v>
+        <v>0.4282759302584503</v>
       </c>
       <c r="U2" t="n">
-        <v>3525.924792561313</v>
+        <v>7946.073477098422</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.513440860215054</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08506419165060494</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K3" t="n">
-        <v>1097.040440044003</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L3" t="n">
-        <v>121.6666666666667</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M3" t="n">
-        <v>15350225.29922993</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N3" t="n">
-        <v>15269826.30913091</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O3" t="n">
-        <v>80398.9900990099</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.554499000811647</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R3" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195631176605357</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U3" t="n">
-        <v>13992.39694264526</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.02388219393348059</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.564516129032258</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235497127172719</v>
+        <v>4.550067759664887</v>
       </c>
       <c r="K4" t="n">
-        <v>735.1809878987912</v>
+        <v>1479.472445544554</v>
       </c>
       <c r="L4" t="n">
-        <v>36.77227722772277</v>
+        <v>78.7035795887281</v>
       </c>
       <c r="M4" t="n">
-        <v>2652380.565456549</v>
+        <v>6091041.658356591</v>
       </c>
       <c r="N4" t="n">
-        <v>2610884.190319032</v>
+        <v>6034282.405762883</v>
       </c>
       <c r="O4" t="n">
-        <v>41496.37513751376</v>
+        <v>56759.25259372091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9199281814192396</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.1294231563500134</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002074079836537043</v>
+        <v>9.668036504960456e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0003980365655580099</v>
       </c>
       <c r="T4" t="n">
-        <v>2.245848381022551</v>
+        <v>7.726592583599095</v>
       </c>
       <c r="U4" t="n">
-        <v>3607.792651218138</v>
+        <v>4117.036229163865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02943627526383025</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.594086021505376</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J5" t="n">
-        <v>3.977504096947204</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K5" t="n">
-        <v>1106.853353135313</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L5" t="n">
-        <v>185.2381738173817</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M5" t="n">
-        <v>16709444.57370737</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N5" t="n">
-        <v>16445971.06820682</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O5" t="n">
-        <v>263473.5055005501</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9712826195905685</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1365246445402428</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R5" t="n">
-        <v>3.24982276100033e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004906045877305042</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T5" t="n">
-        <v>7.32468488284717</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U5" t="n">
-        <v>15096.34905687875</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.628713868151493</v>
+        <v>0.4117608187690975</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.01631992906626261</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.620967741935484</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J6" t="n">
-        <v>3.333386534873489</v>
+        <v>3.32599273971397</v>
       </c>
       <c r="K6" t="n">
-        <v>1619.013470847085</v>
+        <v>1513.833119361935</v>
       </c>
       <c r="L6" t="n">
-        <v>78.31683168316832</v>
+        <v>188.8080308030803</v>
       </c>
       <c r="M6" t="n">
-        <v>7087678.3960396</v>
+        <v>16314434.26072608</v>
       </c>
       <c r="N6" t="n">
-        <v>6961982.357535753</v>
+        <v>16209156.91639164</v>
       </c>
       <c r="O6" t="n">
-        <v>125696.0385038504</v>
+        <v>105277.3443344334</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9692708877835391</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.123800877209524</v>
       </c>
       <c r="R6" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>2.523904980023328e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003883314620121989</v>
+        <v>0.0002719988177710436</v>
       </c>
       <c r="T6" t="n">
-        <v>5.30191348359169</v>
+        <v>8.077487191852224</v>
       </c>
       <c r="U6" t="n">
-        <v>4377.776049220426</v>
+        <v>10776.90404052095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.443548387096774</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1759117230445546</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K7" t="n">
-        <v>1285.926851485148</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L7" t="n">
-        <v>88.64301430143014</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M7" t="n">
-        <v>10218069.24807481</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N7" t="n">
-        <v>10119727.86413641</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O7" t="n">
-        <v>98341.38393839383</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.334943267525058</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R7" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4282759302584503</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U7" t="n">
-        <v>7946.073477098422</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.451612903225807</v>
+        <v>0.5161290322580649</v>
       </c>
       <c r="J8" t="n">
-        <v>2.467392200412544</v>
+        <v>0.6104935163943895</v>
       </c>
       <c r="K8" t="n">
-        <v>702.7110253025301</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L8" t="n">
-        <v>188.4884488448845</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M8" t="n">
-        <v>13511073.15511551</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N8" t="n">
-        <v>13395246.74862486</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O8" t="n">
-        <v>115826.4064906491</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9502433850815568</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1696655897976026</v>
+        <v>0.6787832316376182</v>
       </c>
       <c r="R8" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0002668449815178645</v>
       </c>
       <c r="T8" t="n">
-        <v>5.893947035417844</v>
+        <v>1.473224371773918</v>
       </c>
       <c r="U8" t="n">
-        <v>19227.06869342024</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.482993172759088</v>
+        <v>0.6818249100578531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.0124028028080503</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.545698924731183</v>
+        <v>0.693548387096774</v>
       </c>
       <c r="J9" t="n">
-        <v>3.467754041474145</v>
+        <v>9.022975002444996</v>
       </c>
       <c r="K9" t="n">
-        <v>1098.202911991198</v>
+        <v>3298.4072420242</v>
       </c>
       <c r="L9" t="n">
-        <v>187.4895489548955</v>
+        <v>115.9295929592959</v>
       </c>
       <c r="M9" t="n">
-        <v>16237094.3520352</v>
+        <v>12862715.57590757</v>
       </c>
       <c r="N9" t="n">
-        <v>16091465.1039604</v>
+        <v>12566463.30638064</v>
       </c>
       <c r="O9" t="n">
-        <v>145629.2480748075</v>
+        <v>296252.2695269527</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.8712620382241437</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1392812659094378</v>
+        <v>0.07556542159022893</v>
       </c>
       <c r="R9" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>5.300785094983683e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0002067133801341716</v>
       </c>
       <c r="T9" t="n">
-        <v>7.179716478526343</v>
+        <v>13.2335660802997</v>
       </c>
       <c r="U9" t="n">
-        <v>14785.14960645573</v>
+        <v>3899.67479213205</v>
       </c>
     </row>
     <row r="10">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1061,630 +1061,624 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.588884131062264</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02384313631717553</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.594086021505376</v>
+        <v>0.658602150537635</v>
       </c>
       <c r="J10" t="n">
-        <v>4.536492777821779</v>
+        <v>7.897126985217273</v>
       </c>
       <c r="K10" t="n">
-        <v>1481.89598019802</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L10" t="n">
-        <v>78.55115511551155</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M10" t="n">
-        <v>6074134.495049492</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N10" t="n">
-        <v>6017554.665016501</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O10" t="n">
-        <v>56579.83003300329</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9200611321722409</v>
+        <v>0.9584900963367992</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1298104416568739</v>
+        <v>0.07810758905045663</v>
       </c>
       <c r="R10" t="n">
-        <v>9.694947182058831e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0003973856052862588</v>
+        <v>0.0002872975416218702</v>
       </c>
       <c r="T10" t="n">
-        <v>7.703540541394086</v>
+        <v>12.802853245848</v>
       </c>
       <c r="U10" t="n">
-        <v>4098.893968413241</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.350585020439431</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.46236559139785</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3646793423707372</v>
+        <v>6.579795483718375</v>
       </c>
       <c r="K11" t="n">
-        <v>1106.807743674368</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L11" t="n">
-        <v>58.5038503850385</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M11" t="n">
-        <v>5076190.689768974</v>
+        <v>10170136.63256324</v>
       </c>
       <c r="N11" t="n">
-        <v>4970717.200220022</v>
+        <v>10120981.25467547</v>
       </c>
       <c r="O11" t="n">
-        <v>105473.4895489549</v>
+        <v>49155.37788778878</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9458037017976718</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.08291918407593353</v>
       </c>
       <c r="R11" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>5.364640541303439e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T11" t="n">
-        <v>1.040202293622358</v>
+        <v>12.05993535928003</v>
       </c>
       <c r="U11" t="n">
-        <v>4586.334635604457</v>
+        <v>8216.987831849709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4117608187690975</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01631992906626261</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.577956989247312</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J12" t="n">
-        <v>3.32599273971397</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K12" t="n">
-        <v>1513.833119361935</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L12" t="n">
-        <v>188.8080308030803</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M12" t="n">
-        <v>16314434.26072608</v>
+        <v>2298278.745423723</v>
       </c>
       <c r="N12" t="n">
-        <v>16209156.91639164</v>
+        <v>2275866.51440062</v>
       </c>
       <c r="O12" t="n">
-        <v>105277.3443344334</v>
+        <v>22412.23102310231</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9692708877835391</v>
+        <v>0.9239660644436648</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.123800877209524</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R12" t="n">
-        <v>2.523904980023328e-05</v>
+        <v>0.0002672206192482065</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002719988177710436</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T12" t="n">
-        <v>8.077487191852224</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U12" t="n">
-        <v>10776.90404052095</v>
+        <v>3528.632053730048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.620967741935484</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J13" t="n">
-        <v>3.478965577837015</v>
+        <v>3.453038002695267</v>
       </c>
       <c r="K13" t="n">
-        <v>3784.416073707372</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L13" t="n">
-        <v>110.0367013624439</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M13" t="n">
-        <v>8706893.798112892</v>
+        <v>16237094.3520352</v>
       </c>
       <c r="N13" t="n">
-        <v>8600561.252779894</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O13" t="n">
-        <v>106332.5453329948</v>
+        <v>145629.2480748075</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1243625308862589</v>
+        <v>0.1398748500254234</v>
       </c>
       <c r="R13" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>2.974628109484061e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T13" t="n">
-        <v>8.041007149609982</v>
+        <v>7.149248058662739</v>
       </c>
       <c r="U13" t="n">
-        <v>2300.723183849934</v>
+        <v>14785.14960645573</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.414392761951997</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.5161290322580649</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.6104935163943895</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>1552.934440044002</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L14" t="n">
-        <v>75.22717271727173</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M14" t="n">
-        <v>7080866.402640261</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N14" t="n">
-        <v>6891342.883388339</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O14" t="n">
-        <v>189523.5192519252</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9502433850815568</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.6787832316376182</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002668449815178645</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.473224371773918</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>4559.668599042484</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6810374657220217</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0124204551066807</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.696236559139785</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J15" t="n">
-        <v>9.009237885244771</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K15" t="n">
-        <v>3289.915513751374</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L15" t="n">
-        <v>115.6490649064906</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M15" t="n">
-        <v>12806701.57480748</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N15" t="n">
-        <v>12511134.81463146</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O15" t="n">
-        <v>295566.7601760176</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8712080457734013</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07559323822910896</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R15" t="n">
-        <v>5.317820999762459e-05</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.000207007585111345</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T15" t="n">
-        <v>13.2286964208252</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U15" t="n">
-        <v>3892.714424208558</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.2771443620715672</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.006542828532467639</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.658602150537635</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7.897126985217273</v>
-      </c>
+        <v>0.397849462365591</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>2146.992089658964</v>
+        <v>2541.509630242825</v>
       </c>
       <c r="L16" t="n">
-        <v>99.53135313531354</v>
+        <v>95.90949227373069</v>
       </c>
       <c r="M16" t="n">
-        <v>9691548.173817372</v>
+        <v>5065557.310154528</v>
       </c>
       <c r="N16" t="n">
-        <v>9590504.44719472</v>
+        <v>5026647.232891832</v>
       </c>
       <c r="O16" t="n">
-        <v>101043.7266226623</v>
+        <v>38910.07726269315</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9584900963367992</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.07810758905045663</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>5.471152434027297e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0002872975416218702</v>
-      </c>
-      <c r="T16" t="n">
-        <v>12.802853245848</v>
-      </c>
+        <v>0.000109047142207794</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>4514.012054584146</v>
+        <v>1993.129299954904</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.54559127289644</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.540322580645161</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J17" t="n">
-        <v>6.353318230693071</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K17" t="n">
-        <v>1237.696445544555</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L17" t="n">
-        <v>116.3949394939494</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M17" t="n">
-        <v>10170136.63256324</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N17" t="n">
-        <v>10120981.25467547</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O17" t="n">
-        <v>49155.37788778878</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.08587501099199978</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R17" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T17" t="n">
-        <v>11.64483111499294</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U17" t="n">
-        <v>8216.987831849709</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.60752688172043</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7046746644898908</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K18" t="n">
-        <v>651.3228668866898</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L18" t="n">
-        <v>37.98899889988999</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M18" t="n">
-        <v>2298278.745423723</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N18" t="n">
-        <v>2275866.51440062</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O18" t="n">
-        <v>22412.23102310231</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0002672206192482065</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T18" t="n">
-        <v>1.147403025201837</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U18" t="n">
-        <v>3528.632053730048</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.6803093740718634</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02365082421477135</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.68010752688172</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>0.389784946236559</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4831101147414734</v>
+      </c>
       <c r="K19" t="n">
-        <v>1725.883295805741</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L19" t="n">
-        <v>194.9635761589404</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M19" t="n">
-        <v>15002315.66997792</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N19" t="n">
-        <v>14917198.82339956</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O19" t="n">
-        <v>85116.84657836644</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9637709553156532</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>0.9307814644010347</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8705946372672551</v>
+      </c>
       <c r="R19" t="n">
-        <v>4.534695769888867e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003941804035795226</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
+        <v>0.001104335699257203</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.148640201987622</v>
+      </c>
       <c r="U19" t="n">
-        <v>8692.543526226078</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="20">
@@ -1695,7 +1689,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1705,110 +1699,116 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.335918178838533</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.416666666666667</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2263884094719471</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K20" t="n">
-        <v>837.3769053905384</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L20" t="n">
-        <v>44.01650165016502</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M20" t="n">
-        <v>3480808.845984597</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N20" t="n">
-        <v>3413192.581958196</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O20" t="n">
-        <v>67616.26402640264</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P20" t="n">
-        <v>0.95547252331787</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.483813502740997</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R20" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0004011552942003655</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6739391427242943</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U20" t="n">
-        <v>4156.800627742662</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.2771443620715672</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F21" t="n">
-        <v>0.006542828532467639</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.397849462365591</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>0.575268817204301</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.989729004180416</v>
+      </c>
       <c r="K21" t="n">
-        <v>2541.509630242825</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L21" t="n">
-        <v>95.90949227373069</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M21" t="n">
-        <v>5065557.310154528</v>
+        <v>9840777.763476355</v>
       </c>
       <c r="N21" t="n">
-        <v>5026647.232891832</v>
+        <v>9778602.140814083</v>
       </c>
       <c r="O21" t="n">
-        <v>38910.07726269315</v>
+        <v>62175.62266226623</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>0.9640119921972632</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.18952417157726</v>
+      </c>
       <c r="R21" t="n">
-        <v>5.471152434027297e-05</v>
+        <v>5.757938309112199e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.000109047142207794</v>
-      </c>
-      <c r="T21" t="inlineStr"/>
+        <v>0.0004234705483335876</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.276371829924331</v>
+      </c>
       <c r="U21" t="n">
-        <v>1993.129299954904</v>
+        <v>7354.551674571196</v>
       </c>
     </row>
     <row r="22">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1829,51 +1829,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.3680931015358647</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.004193675756950516</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.620967741935484</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J22" t="n">
-        <v>10.78915469925741</v>
+        <v>2.803197722050223</v>
       </c>
       <c r="K22" t="n">
-        <v>2515.540235973597</v>
+        <v>5266.402881898454</v>
       </c>
       <c r="L22" t="n">
-        <v>152.1303630363036</v>
+        <v>121.5060706401766</v>
       </c>
       <c r="M22" t="n">
-        <v>11374850.48899891</v>
+        <v>13843602.99834437</v>
       </c>
       <c r="N22" t="n">
-        <v>11238194.40979098</v>
+        <v>12842977.3995585</v>
       </c>
       <c r="O22" t="n">
-        <v>136656.0792079208</v>
+        <v>1000625.598785872</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.8914806265675513</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.1313118581113308</v>
       </c>
       <c r="R22" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>2.65894002868969e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0002374295844857846</v>
+        <v>6.989459594917527e-05</v>
       </c>
       <c r="T22" t="n">
-        <v>18.06430758687328</v>
+        <v>7.61545845427124</v>
       </c>
       <c r="U22" t="n">
-        <v>4521.832060697078</v>
+        <v>2628.663873386378</v>
       </c>
     </row>
     <row r="23">
@@ -1884,126 +1884,126 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F23" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.583333333333333</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J23" t="n">
-        <v>1.662215663091308</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K23" t="n">
-        <v>3381.269037953798</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L23" t="n">
-        <v>138.5951595159516</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M23" t="n">
-        <v>21745804.32343233</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N23" t="n">
-        <v>21619802.9180418</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O23" t="n">
-        <v>126001.4053905391</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R23" t="n">
-        <v>2.354685177223e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.000388331462012199</v>
       </c>
       <c r="T23" t="n">
-        <v>3.246228188888836</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U23" t="n">
-        <v>6431.255271125063</v>
+        <v>4377.776049220427</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.420593075103495</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.02952880696749936</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.389784946236559</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4831101147414734</v>
+        <v>3.832577882590769</v>
       </c>
       <c r="K24" t="n">
-        <v>380.8561793179318</v>
+        <v>1103.38490869087</v>
       </c>
       <c r="L24" t="n">
-        <v>18.57865786578658</v>
+        <v>184.4213421342134</v>
       </c>
       <c r="M24" t="n">
-        <v>977284.7700770069</v>
+        <v>16122474.14796479</v>
       </c>
       <c r="N24" t="n">
-        <v>961481.2431243125</v>
+        <v>15871228.38008801</v>
       </c>
       <c r="O24" t="n">
-        <v>15803.52695269527</v>
+        <v>251245.7678767877</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9307814644010347</v>
+        <v>0.9712771508508302</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8705946372672551</v>
+        <v>0.1416872271427914</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0004303690060271313</v>
+        <v>3.368138959376935e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.001104335699257203</v>
+        <v>0.000492146782791656</v>
       </c>
       <c r="T24" t="n">
-        <v>1.148640201987622</v>
+        <v>7.057799211443437</v>
       </c>
       <c r="U24" t="n">
-        <v>2566.020516792475</v>
+        <v>14611.83130290732</v>
       </c>
     </row>
     <row r="25">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2024,51 +2024,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.448924731182796</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6187507753025301</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K25" t="n">
-        <v>510.7721826182621</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L25" t="n">
-        <v>22.20902090209021</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M25" t="n">
-        <v>1253351.492849284</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N25" t="n">
-        <v>1232830.718371837</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O25" t="n">
-        <v>20520.77447744774</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.7415582684181721</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003660902437453124</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T25" t="n">
-        <v>1.348511698390355</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U25" t="n">
-        <v>2453.836633045474</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="26">
@@ -2079,126 +2079,126 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.575268817204301</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J26" t="n">
-        <v>2.989729004180416</v>
+        <v>0.08278622901034095</v>
       </c>
       <c r="K26" t="n">
-        <v>1338.052705170518</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L26" t="n">
-        <v>86.55005500550054</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M26" t="n">
-        <v>9840777.763476355</v>
+        <v>15350225.29922993</v>
       </c>
       <c r="N26" t="n">
-        <v>9778602.140814083</v>
+        <v>15269826.30913091</v>
       </c>
       <c r="O26" t="n">
-        <v>62175.62266226623</v>
+        <v>80398.9900990099</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9640119921972632</v>
+        <v>0.9869993314104538</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.18952417157726</v>
+        <v>4.679821517527231</v>
       </c>
       <c r="R26" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>2.523902863477623e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0004234705483335876</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T26" t="n">
-        <v>5.276371829924331</v>
+        <v>0.213683362977567</v>
       </c>
       <c r="U26" t="n">
-        <v>7354.551674571196</v>
+        <v>13992.39694264526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3647260981688613</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F27" t="n">
-        <v>0.004187553609992088</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.336021505376344</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J27" t="n">
-        <v>2.580340961258277</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K27" t="n">
-        <v>5225.859279249448</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L27" t="n">
-        <v>120.9243929359824</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M27" t="n">
-        <v>13769015.17770419</v>
+        <v>2819911.990351496</v>
       </c>
       <c r="N27" t="n">
-        <v>12778720.50662252</v>
+        <v>2791163.254864831</v>
       </c>
       <c r="O27" t="n">
-        <v>990294.6710816775</v>
+        <v>28748.73548666342</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8918200950779239</v>
+        <v>0.9278388366571141</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1413480247939816</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R27" t="n">
-        <v>2.648890232610483e-05</v>
+        <v>0.0002133018241973586</v>
       </c>
       <c r="S27" t="n">
-        <v>6.979256016653481e-05</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T27" t="n">
-        <v>7.074736286251795</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U27" t="n">
-        <v>2634.784911330742</v>
+        <v>3525.924792561313</v>
       </c>
     </row>
     <row r="28">
@@ -2724,261 +2724,261 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.629032258064516</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J36" t="n">
-        <v>8.817468730473037</v>
+        <v>5.84390538944481</v>
       </c>
       <c r="K36" t="n">
-        <v>2354.367686468646</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L36" t="n">
-        <v>162.6457645764577</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M36" t="n">
-        <v>14324724.28382839</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N36" t="n">
-        <v>14201447.9559956</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O36" t="n">
-        <v>123276.3278327833</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P36" t="n">
-        <v>0.938882976190201</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.1091012876743978</v>
       </c>
       <c r="R36" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T36" t="n">
-        <v>15.67058466504826</v>
+        <v>9.165794660319708</v>
       </c>
       <c r="U36" t="n">
-        <v>6084.319100265209</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.637577603035782</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.564516129032258</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J37" t="n">
-        <v>5.843905389444815</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K37" t="n">
-        <v>2070.168603200884</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L37" t="n">
-        <v>149.1832229580574</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M37" t="n">
-        <v>13733793.78145695</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N37" t="n">
-        <v>13621672.65011038</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O37" t="n">
-        <v>112121.1313465784</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1091012876743977</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R37" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T37" t="n">
-        <v>9.165794660319715</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U37" t="n">
-        <v>6634.142629842724</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.6366510283153159</v>
       </c>
       <c r="F38" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.02838675827210399</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.669354838709677</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J38" t="n">
-        <v>14.19080079636965</v>
+        <v>8.040007295049511</v>
       </c>
       <c r="K38" t="n">
-        <v>5244.965372937293</v>
+        <v>1345.664810781076</v>
       </c>
       <c r="L38" t="n">
-        <v>265.9306930693069</v>
+        <v>191.8814250655834</v>
       </c>
       <c r="M38" t="n">
-        <v>27742337.2337734</v>
+        <v>15007201.97854787</v>
       </c>
       <c r="N38" t="n">
-        <v>27141368.95929593</v>
+        <v>14917219.10011001</v>
       </c>
       <c r="O38" t="n">
-        <v>600968.2744774478</v>
+        <v>89982.87843784377</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.9358639622980014</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.07918537943458363</v>
       </c>
       <c r="R38" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.242303323600098e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0004731126378683998</v>
       </c>
       <c r="T38" t="n">
-        <v>20.75958236310095</v>
+        <v>12.62859390382939</v>
       </c>
       <c r="U38" t="n">
-        <v>5289.327051979582</v>
+        <v>11152.25861471187</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6349675266318143</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F39" t="n">
-        <v>0.02829093785912806</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.672043010752688</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J39" t="n">
-        <v>8.052232502530256</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K39" t="n">
-        <v>1346.652125412539</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L39" t="n">
-        <v>191.9551493610899</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M39" t="n">
-        <v>15016299.67931794</v>
+        <v>3999501.610795507</v>
       </c>
       <c r="N39" t="n">
-        <v>14926250.65016502</v>
+        <v>3937843.056466302</v>
       </c>
       <c r="O39" t="n">
-        <v>90049.02915291529</v>
+        <v>61658.55432920342</v>
       </c>
       <c r="P39" t="n">
-        <v>0.935735212525825</v>
+        <v>0.9281954641245814</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.07885608449983135</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R39" t="n">
-        <v>4.228521940770533e-05</v>
+        <v>0.000150387505484869</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0004715156309854677</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T39" t="n">
-        <v>12.68132961892292</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U39" t="n">
-        <v>11150.83798996551</v>
+        <v>2733.680592389675</v>
       </c>
     </row>
     <row r="40">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2999,116 +2999,116 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02100022628798557</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.577956989247312</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J40" t="n">
-        <v>1.554119528390054</v>
+        <v>7.46548537723855</v>
       </c>
       <c r="K40" t="n">
-        <v>1463.046422442244</v>
+        <v>1761.26802090209</v>
       </c>
       <c r="L40" t="n">
-        <v>40.45654565456545</v>
+        <v>39.37183718371837</v>
       </c>
       <c r="M40" t="n">
-        <v>3999501.610795507</v>
+        <v>3345996.469855181</v>
       </c>
       <c r="N40" t="n">
-        <v>3937843.056466302</v>
+        <v>3298947.014445707</v>
       </c>
       <c r="O40" t="n">
-        <v>61658.55432920342</v>
+        <v>47049.45540947537</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9335374217538733</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.08257339191346216</v>
       </c>
       <c r="R40" t="n">
-        <v>0.000150387505484869</v>
+        <v>0.0001842352361793198</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0003500037714664262</v>
       </c>
       <c r="T40" t="n">
-        <v>2.583846953587535</v>
+        <v>12.11043868765875</v>
       </c>
       <c r="U40" t="n">
-        <v>2733.680592389675</v>
+        <v>1899.765640519279</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0209911088149403</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.618279569892473</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J41" t="n">
-        <v>7.46709735138597</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K41" t="n">
-        <v>1762.03302640264</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L41" t="n">
-        <v>39.37843784378438</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M41" t="n">
-        <v>3346611.012209417</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N41" t="n">
-        <v>3299549.915435806</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O41" t="n">
-        <v>47061.09677361179</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9335591564904552</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.08255556622206355</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0001842014048331127</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0003498518135823383</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T41" t="n">
-        <v>12.11305361664085</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U41" t="n">
-        <v>1899.289605849129</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="42">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>GPT-6.1 Sol (high)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -541,506 +541,506 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4107438934016153</v>
+        <v>0.6014923716179784</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01916487984960749</v>
+        <v>0.04512517141416127</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.443548387096774</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1759117230445546</v>
+        <v>0.8892413135295484</v>
       </c>
       <c r="K2" t="n">
-        <v>1285.926851485148</v>
+        <v>799.7652123212325</v>
       </c>
       <c r="L2" t="n">
-        <v>88.64301430143014</v>
+        <v>38.97909790979098</v>
       </c>
       <c r="M2" t="n">
-        <v>10218069.24807481</v>
+        <v>2823739.651517614</v>
       </c>
       <c r="N2" t="n">
-        <v>10119727.86413641</v>
+        <v>2794938.554094754</v>
       </c>
       <c r="O2" t="n">
-        <v>98341.38393839383</v>
+        <v>28801.09742285704</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9606438143896164</v>
+        <v>0.9277866092003811</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.334943267525058</v>
+        <v>0.6764107362832188</v>
       </c>
       <c r="R2" t="n">
-        <v>4.019779896079717e-05</v>
+        <v>0.0002130126873753065</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003194146641601249</v>
+        <v>0.0007520861902360213</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4282759302584503</v>
+        <v>1.478391672927692</v>
       </c>
       <c r="U2" t="n">
-        <v>7946.073477098422</v>
+        <v>3530.710773630693</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>DeepSeek V4 Flash 0731 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4186315529449987</v>
+        <v>0.3874247758775307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03574427079166177</v>
+        <v>0.02118927042627475</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.451612903225807</v>
+        <v>0.513440860215054</v>
       </c>
       <c r="J3" t="n">
-        <v>2.467392200412544</v>
+        <v>0.08278836187722763</v>
       </c>
       <c r="K3" t="n">
-        <v>702.7110253025301</v>
+        <v>1097.040440044003</v>
       </c>
       <c r="L3" t="n">
-        <v>188.4884488448845</v>
+        <v>121.6666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>13511073.15511551</v>
+        <v>15350417.07370738</v>
       </c>
       <c r="N3" t="n">
-        <v>13395246.74862486</v>
+        <v>15270013.91089109</v>
       </c>
       <c r="O3" t="n">
-        <v>115826.4064906491</v>
+        <v>80403.16281628163</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8697428234581179</v>
+        <v>0.9869998448543432</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1696655897976026</v>
+        <v>4.679700951832682</v>
       </c>
       <c r="R3" t="n">
-        <v>3.098433027035294e-05</v>
+        <v>2.523871332076851e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005957378465276962</v>
+        <v>0.0003531545071045792</v>
       </c>
       <c r="T3" t="n">
-        <v>5.893947035417844</v>
+        <v>0.2136888682188925</v>
       </c>
       <c r="U3" t="n">
-        <v>19227.06869342024</v>
+        <v>13992.57175340925</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Sonnet 5.5 (high)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.588884131062264</v>
+        <v>0.5501249049636148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02388219393348059</v>
+        <v>0.04489709995378834</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.594086021505376</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J4" t="n">
-        <v>4.550067759664887</v>
+        <v>1.235497127172719</v>
       </c>
       <c r="K4" t="n">
-        <v>1479.472445544554</v>
+        <v>735.1809878987912</v>
       </c>
       <c r="L4" t="n">
-        <v>78.7035795887281</v>
+        <v>36.77227722772277</v>
       </c>
       <c r="M4" t="n">
-        <v>6091041.658356591</v>
+        <v>2652380.565456549</v>
       </c>
       <c r="N4" t="n">
-        <v>6034282.405762883</v>
+        <v>2610884.190319032</v>
       </c>
       <c r="O4" t="n">
-        <v>56759.25259372091</v>
+        <v>41496.37513751376</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9199281814192396</v>
+        <v>0.9477934370079523</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1294231563500134</v>
+        <v>0.4452660332950404</v>
       </c>
       <c r="R4" t="n">
-        <v>9.668036504960456e-05</v>
+        <v>0.0002074079836537043</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003980365655580099</v>
+        <v>0.0007482849992298058</v>
       </c>
       <c r="T4" t="n">
-        <v>7.726592583599095</v>
+        <v>2.245848381022551</v>
       </c>
       <c r="U4" t="n">
-        <v>4117.036229163865</v>
+        <v>3607.792651218138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (high)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.350585020439431</v>
+        <v>0.5430273329930766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01900519882209512</v>
+        <v>0.02952880696749936</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.46236559139785</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3646793423707372</v>
+        <v>3.385871461111111</v>
       </c>
       <c r="K5" t="n">
-        <v>1106.807743674368</v>
+        <v>1103.38490869087</v>
       </c>
       <c r="L5" t="n">
-        <v>58.5038503850385</v>
+        <v>184.4213421342134</v>
       </c>
       <c r="M5" t="n">
-        <v>5076190.689768974</v>
+        <v>16017366.75467545</v>
       </c>
       <c r="N5" t="n">
-        <v>4970717.200220022</v>
+        <v>15871228.38008801</v>
       </c>
       <c r="O5" t="n">
-        <v>105473.4895489549</v>
+        <v>146138.3745874587</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9561309602762921</v>
+        <v>0.9712771508508302</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9613514660861219</v>
+        <v>0.1603803745151259</v>
       </c>
       <c r="R5" t="n">
-        <v>6.906458836269343e-05</v>
+        <v>3.390240988485623e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003167533137015853</v>
+        <v>0.000492146782791656</v>
       </c>
       <c r="T5" t="n">
-        <v>1.040202293622358</v>
+        <v>6.235176860156834</v>
       </c>
       <c r="U5" t="n">
-        <v>4586.334635604457</v>
+        <v>14516.57225734539</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>Sonnet 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4117608187690975</v>
+        <v>0.628713868151493</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01631992906626261</v>
+        <v>0.02329988772073193</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.577956989247312</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J6" t="n">
-        <v>3.32599273971397</v>
+        <v>3.333386534873489</v>
       </c>
       <c r="K6" t="n">
-        <v>1513.833119361935</v>
+        <v>1619.013470847085</v>
       </c>
       <c r="L6" t="n">
-        <v>188.8080308030803</v>
+        <v>78.31683168316832</v>
       </c>
       <c r="M6" t="n">
-        <v>16314434.26072608</v>
+        <v>7087678.3960396</v>
       </c>
       <c r="N6" t="n">
-        <v>16209156.91639164</v>
+        <v>6961982.357535753</v>
       </c>
       <c r="O6" t="n">
-        <v>105277.3443344334</v>
+        <v>125696.0385038504</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9692708877835391</v>
+        <v>0.9574714756466342</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.123800877209524</v>
+        <v>0.1886111501243448</v>
       </c>
       <c r="R6" t="n">
-        <v>2.523904980023328e-05</v>
+        <v>8.870519132228135e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002719988177710436</v>
+        <v>0.0003883314620121989</v>
       </c>
       <c r="T6" t="n">
-        <v>8.077487191852224</v>
+        <v>5.30191348359169</v>
       </c>
       <c r="U6" t="n">
-        <v>10776.90404052095</v>
+        <v>4377.776049220426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4326529641259874</v>
+        <v>0.4107438934016153</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006859493602702238</v>
+        <v>0.01916487984960749</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.620967741935484</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J7" t="n">
-        <v>3.478965577837015</v>
+        <v>0.1776965431270624</v>
       </c>
       <c r="K7" t="n">
-        <v>3784.416073707372</v>
+        <v>1285.926851485148</v>
       </c>
       <c r="L7" t="n">
-        <v>110.0367013624439</v>
+        <v>88.64301430143014</v>
       </c>
       <c r="M7" t="n">
-        <v>8706893.798112892</v>
+        <v>10284265.05555557</v>
       </c>
       <c r="N7" t="n">
-        <v>8600561.252779894</v>
+        <v>10185187.97414742</v>
       </c>
       <c r="O7" t="n">
-        <v>106332.5453329948</v>
+        <v>99077.08140814082</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9507113544554301</v>
+        <v>0.9604662048734249</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1243625308862589</v>
+        <v>2.311490624259987</v>
       </c>
       <c r="R7" t="n">
-        <v>4.969085119882356e-05</v>
+        <v>3.993906138968395e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001143248933783706</v>
+        <v>0.0003194146641601249</v>
       </c>
       <c r="T7" t="n">
-        <v>8.041007149609982</v>
+        <v>0.4326212659072087</v>
       </c>
       <c r="U7" t="n">
-        <v>2300.723183849934</v>
+        <v>7997.550594482124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (xhigh)</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.414392761951997</v>
+        <v>0.4186315529449987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01601069889107187</v>
+        <v>0.03574427079166177</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.5161290322580649</v>
+        <v>0.451612903225807</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6104935163943895</v>
+        <v>2.467392200412544</v>
       </c>
       <c r="K8" t="n">
-        <v>1552.934440044002</v>
+        <v>702.7110253025301</v>
       </c>
       <c r="L8" t="n">
-        <v>75.22717271727173</v>
+        <v>188.4884488448845</v>
       </c>
       <c r="M8" t="n">
-        <v>7080866.402640261</v>
+        <v>13511073.15511551</v>
       </c>
       <c r="N8" t="n">
-        <v>6891342.883388339</v>
+        <v>13395246.74862486</v>
       </c>
       <c r="O8" t="n">
-        <v>189523.5192519252</v>
+        <v>115826.4064906491</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9502433850815568</v>
+        <v>0.8697428234581179</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6787832316376182</v>
+        <v>0.1696655897976026</v>
       </c>
       <c r="R8" t="n">
-        <v>5.85228894867274e-05</v>
+        <v>3.098433027035294e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0002668449815178645</v>
+        <v>0.0005957378465276962</v>
       </c>
       <c r="T8" t="n">
-        <v>1.473224371773918</v>
+        <v>5.893947035417844</v>
       </c>
       <c r="U8" t="n">
-        <v>4559.668599042484</v>
+        <v>19227.06869342024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Muse Code 1.0.2 RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Muse Spark 1.3 (xhigh)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6818249100578531</v>
+        <v>0.482993172759088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0124028028080503</v>
+        <v>0.02638819297337426</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.693548387096774</v>
+        <v>0.545698924731183</v>
       </c>
       <c r="J9" t="n">
-        <v>9.022975002444996</v>
+        <v>3.433046465566554</v>
       </c>
       <c r="K9" t="n">
-        <v>3298.4072420242</v>
+        <v>1098.202911991198</v>
       </c>
       <c r="L9" t="n">
-        <v>115.9295929592959</v>
+        <v>187.4895489548955</v>
       </c>
       <c r="M9" t="n">
-        <v>12862715.57590757</v>
+        <v>16232390.46094608</v>
       </c>
       <c r="N9" t="n">
-        <v>12566463.30638064</v>
+        <v>16091465.1039604</v>
       </c>
       <c r="O9" t="n">
-        <v>296252.2695269527</v>
+        <v>140925.3569856986</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8712620382241437</v>
+        <v>0.9661832360411203</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07556542159022893</v>
+        <v>0.1406893782544187</v>
       </c>
       <c r="R9" t="n">
-        <v>5.300785094983683e-05</v>
+        <v>2.975490109858641e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002067133801341716</v>
+        <v>0.0004398032162229042</v>
       </c>
       <c r="T9" t="n">
-        <v>13.2335660802997</v>
+        <v>7.107857127576671</v>
       </c>
       <c r="U9" t="n">
-        <v>3899.67479213205</v>
+        <v>14780.86634419358</v>
       </c>
     </row>
     <row r="10">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1061,624 +1061,630 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6168255492406223</v>
+        <v>0.588884131062264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01723785249731221</v>
+        <v>0.02388219393348059</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.658602150537635</v>
+        <v>0.594086021505376</v>
       </c>
       <c r="J10" t="n">
-        <v>7.897126985217273</v>
+        <v>4.550067759664887</v>
       </c>
       <c r="K10" t="n">
-        <v>2146.992089658964</v>
+        <v>1479.472445544554</v>
       </c>
       <c r="L10" t="n">
-        <v>99.53135313531354</v>
+        <v>78.7035795887281</v>
       </c>
       <c r="M10" t="n">
-        <v>9691548.173817372</v>
+        <v>6091041.658356591</v>
       </c>
       <c r="N10" t="n">
-        <v>9590504.44719472</v>
+        <v>6034282.405762883</v>
       </c>
       <c r="O10" t="n">
-        <v>101043.7266226623</v>
+        <v>56759.25259372091</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9584900963367992</v>
+        <v>0.9199281814192396</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07810758905045663</v>
+        <v>0.1294231563500134</v>
       </c>
       <c r="R10" t="n">
-        <v>6.364571874151485e-05</v>
+        <v>9.668036504960456e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002872975416218702</v>
+        <v>0.0003980365655580099</v>
       </c>
       <c r="T10" t="n">
-        <v>12.802853245848</v>
+        <v>7.726592583599095</v>
       </c>
       <c r="U10" t="n">
-        <v>4514.012054584146</v>
+        <v>4117.036229163865</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol (max)</t>
+          <t>Haiku 5.5 (high)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.54559127289644</v>
+        <v>0.350585020439431</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02644871163008279</v>
+        <v>0.01900519882209512</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.540322580645161</v>
+        <v>0.46236559139785</v>
       </c>
       <c r="J11" t="n">
-        <v>6.579795483718375</v>
+        <v>0.3646793423707372</v>
       </c>
       <c r="K11" t="n">
-        <v>1237.696445544555</v>
+        <v>1106.807743674368</v>
       </c>
       <c r="L11" t="n">
-        <v>116.3949394939494</v>
+        <v>58.5038503850385</v>
       </c>
       <c r="M11" t="n">
-        <v>10170136.63256324</v>
+        <v>5076190.689768974</v>
       </c>
       <c r="N11" t="n">
-        <v>10120981.25467547</v>
+        <v>4970717.200220022</v>
       </c>
       <c r="O11" t="n">
-        <v>49155.37788778878</v>
+        <v>105473.4895489549</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9458037017976718</v>
+        <v>0.9561309602762921</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08291918407593353</v>
+        <v>0.9613514660861219</v>
       </c>
       <c r="R11" t="n">
-        <v>5.364640541303439e-05</v>
+        <v>6.906458836269343e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004408118605013798</v>
+        <v>0.0003167533137015853</v>
       </c>
       <c r="T11" t="n">
-        <v>12.05993535928003</v>
+        <v>1.040202293622358</v>
       </c>
       <c r="U11" t="n">
-        <v>8216.987831849709</v>
+        <v>4586.334635604457</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (medium)</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6141474695571183</v>
+        <v>0.4117608187690975</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05657539454980884</v>
+        <v>0.01631992906626261</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.60752688172043</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7046746644898908</v>
+        <v>3.32599273971397</v>
       </c>
       <c r="K12" t="n">
-        <v>651.3228668866898</v>
+        <v>1513.833119361935</v>
       </c>
       <c r="L12" t="n">
-        <v>37.98899889988999</v>
+        <v>188.8080308030803</v>
       </c>
       <c r="M12" t="n">
-        <v>2298278.745423723</v>
+        <v>16314434.26072608</v>
       </c>
       <c r="N12" t="n">
-        <v>2275866.51440062</v>
+        <v>16209156.91639164</v>
       </c>
       <c r="O12" t="n">
-        <v>22412.23102310231</v>
+        <v>105277.3443344334</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9239660644436648</v>
+        <v>0.9692708877835391</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8715333479481563</v>
+        <v>0.123800877209524</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002672206192482065</v>
+        <v>2.523904980023328e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.000942923242496814</v>
+        <v>0.0002719988177710436</v>
       </c>
       <c r="T12" t="n">
-        <v>1.147403025201837</v>
+        <v>8.077487191852224</v>
       </c>
       <c r="U12" t="n">
-        <v>3528.632053730048</v>
+        <v>10776.90404052095</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muse Code 1.0.2 RC</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (xhigh)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.482993172759088</v>
+        <v>0.4326529641259874</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02638819297337426</v>
+        <v>0.006859493602702238</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.545698924731183</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J13" t="n">
-        <v>3.453038002695267</v>
+        <v>3.478965577837015</v>
       </c>
       <c r="K13" t="n">
-        <v>1098.202911991198</v>
+        <v>3784.416073707372</v>
       </c>
       <c r="L13" t="n">
-        <v>187.4895489548955</v>
+        <v>110.0367013624439</v>
       </c>
       <c r="M13" t="n">
-        <v>16237094.3520352</v>
+        <v>8706893.798112892</v>
       </c>
       <c r="N13" t="n">
-        <v>16091465.1039604</v>
+        <v>8600561.252779894</v>
       </c>
       <c r="O13" t="n">
-        <v>145629.2480748075</v>
+        <v>106332.5453329948</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9661832360411203</v>
+        <v>0.9507113544554301</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1398748500254234</v>
+        <v>0.1243625308862589</v>
       </c>
       <c r="R13" t="n">
-        <v>2.974628109484061e-05</v>
+        <v>4.969085119882356e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0004398032162229042</v>
+        <v>0.0001143248933783706</v>
       </c>
       <c r="T13" t="n">
-        <v>7.149248058662739</v>
+        <v>8.041007149609982</v>
       </c>
       <c r="U13" t="n">
-        <v>14785.14960645573</v>
+        <v>2300.723183849934</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>Haiku 5.5 (xhigh)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6803093740718634</v>
+        <v>0.414392761951997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02365082421477135</v>
+        <v>0.01601069889107187</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.68010752688172</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>0.5161290322580649</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6104935163943895</v>
+      </c>
       <c r="K14" t="n">
-        <v>1725.883295805741</v>
+        <v>1552.934440044002</v>
       </c>
       <c r="L14" t="n">
-        <v>194.9635761589404</v>
+        <v>75.22717271727173</v>
       </c>
       <c r="M14" t="n">
-        <v>15002315.66997792</v>
+        <v>7080866.402640261</v>
       </c>
       <c r="N14" t="n">
-        <v>14917198.82339956</v>
+        <v>6891342.883388339</v>
       </c>
       <c r="O14" t="n">
-        <v>85116.84657836644</v>
+        <v>189523.5192519252</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9637709553156532</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>0.9502433850815568</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.6787832316376182</v>
+      </c>
       <c r="R14" t="n">
-        <v>4.534695769888867e-05</v>
+        <v>5.85228894867274e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003941804035795226</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
+        <v>0.0002668449815178645</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.473224371773918</v>
+      </c>
       <c r="U14" t="n">
-        <v>8692.543526226078</v>
+        <v>4559.668599042484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (medium)</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.335918178838533</v>
+        <v>0.6818249100578531</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02406931765202193</v>
+        <v>0.0124028028080503</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.416666666666667</v>
+        <v>0.693548387096774</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2263884094719471</v>
+        <v>9.022975002444996</v>
       </c>
       <c r="K15" t="n">
-        <v>837.3769053905384</v>
+        <v>3298.4072420242</v>
       </c>
       <c r="L15" t="n">
-        <v>44.01650165016502</v>
+        <v>115.9295929592959</v>
       </c>
       <c r="M15" t="n">
-        <v>3480808.845984597</v>
+        <v>12862715.57590757</v>
       </c>
       <c r="N15" t="n">
-        <v>3413192.581958196</v>
+        <v>12566463.30638064</v>
       </c>
       <c r="O15" t="n">
-        <v>67616.26402640264</v>
+        <v>296252.2695269527</v>
       </c>
       <c r="P15" t="n">
-        <v>0.95547252331787</v>
+        <v>0.8712620382241437</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.483813502740997</v>
+        <v>0.07556542159022893</v>
       </c>
       <c r="R15" t="n">
-        <v>9.650578175990406e-05</v>
+        <v>5.300785094983683e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004011552942003655</v>
+        <v>0.0002067133801341716</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6739391427242943</v>
+        <v>13.2335660802997</v>
       </c>
       <c r="U15" t="n">
-        <v>4156.800627742662</v>
+        <v>3899.67479213205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2771443620715672</v>
+        <v>0.6168255492406223</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006542828532467639</v>
+        <v>0.01723785249731221</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.397849462365591</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>0.658602150537635</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.897126985217273</v>
+      </c>
       <c r="K16" t="n">
-        <v>2541.509630242825</v>
+        <v>2146.992089658964</v>
       </c>
       <c r="L16" t="n">
-        <v>95.90949227373069</v>
+        <v>99.53135313531354</v>
       </c>
       <c r="M16" t="n">
-        <v>5065557.310154528</v>
+        <v>9691548.173817372</v>
       </c>
       <c r="N16" t="n">
-        <v>5026647.232891832</v>
+        <v>9590504.44719472</v>
       </c>
       <c r="O16" t="n">
-        <v>38910.07726269315</v>
+        <v>101043.7266226623</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>0.9584900963367992</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.07810758905045663</v>
+      </c>
       <c r="R16" t="n">
-        <v>5.471152434027297e-05</v>
+        <v>6.364571874151485e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.000109047142207794</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
+        <v>0.0002872975416218702</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12.802853245848</v>
+      </c>
       <c r="U16" t="n">
-        <v>1993.129299954904</v>
+        <v>4514.012054584146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opus 5 (max)</t>
+          <t>GPT-5.6 Sol (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5972636729844837</v>
+        <v>0.54559127289644</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01424577506914708</v>
+        <v>0.02644871163008279</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.620967741935484</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J17" t="n">
-        <v>10.78915469925741</v>
+        <v>6.611131146754674</v>
       </c>
       <c r="K17" t="n">
-        <v>2515.540235973597</v>
+        <v>1237.696445544555</v>
       </c>
       <c r="L17" t="n">
-        <v>152.1303630363036</v>
+        <v>116.3949394939494</v>
       </c>
       <c r="M17" t="n">
-        <v>11374850.48899891</v>
+        <v>10214074.76347635</v>
       </c>
       <c r="N17" t="n">
-        <v>11238194.40979098</v>
+        <v>10164333.28822882</v>
       </c>
       <c r="O17" t="n">
-        <v>136656.0792079208</v>
+        <v>49741.47524752475</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9698258997320075</v>
+        <v>0.9460315340894812</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.05535778192387877</v>
+        <v>0.08252616092244129</v>
       </c>
       <c r="R17" t="n">
-        <v>5.250738667397188e-05</v>
+        <v>5.341563338143696e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0002374295844857846</v>
+        <v>0.0004408118605013798</v>
       </c>
       <c r="T17" t="n">
-        <v>18.06430758687328</v>
+        <v>12.11736967795954</v>
       </c>
       <c r="U17" t="n">
-        <v>4521.832060697078</v>
+        <v>8252.487756787905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>GPT-6.1 Sol (medium)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5120452310717793</v>
+        <v>0.6141474695571183</v>
       </c>
       <c r="F18" t="n">
-        <v>0.009086148874713283</v>
+        <v>0.05657539454980884</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.583333333333333</v>
+        <v>0.60752688172043</v>
       </c>
       <c r="J18" t="n">
-        <v>1.662215663091308</v>
+        <v>0.7046746644898908</v>
       </c>
       <c r="K18" t="n">
-        <v>3381.269037953798</v>
+        <v>651.3228668866898</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5951595159516</v>
+        <v>37.98899889988999</v>
       </c>
       <c r="M18" t="n">
-        <v>21745804.32343233</v>
+        <v>2301380.208570039</v>
       </c>
       <c r="N18" t="n">
-        <v>21619802.9180418</v>
+        <v>2278919.617810961</v>
       </c>
       <c r="O18" t="n">
-        <v>126001.4053905391</v>
+        <v>22460.59075907591</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9870352061053834</v>
+        <v>0.9239632669191677</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3080498171455697</v>
+        <v>0.8715333479481563</v>
       </c>
       <c r="R18" t="n">
-        <v>2.354685177223e-05</v>
+        <v>0.0002668604984392033</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001514358145785547</v>
+        <v>0.000942923242496814</v>
       </c>
       <c r="T18" t="n">
-        <v>3.246228188888836</v>
+        <v>1.147403025201837</v>
       </c>
       <c r="U18" t="n">
-        <v>6431.255271125063</v>
+        <v>3533.393844393319</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (low)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.420593075103495</v>
+        <v>0.6803093740718634</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06626014195543219</v>
+        <v>0.02365082421477135</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.389784946236559</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.4831101147414734</v>
-      </c>
+        <v>0.68010752688172</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>380.8561793179318</v>
+        <v>1725.883295805741</v>
       </c>
       <c r="L19" t="n">
-        <v>18.57865786578658</v>
+        <v>194.9635761589404</v>
       </c>
       <c r="M19" t="n">
-        <v>977284.7700770069</v>
+        <v>15002315.66997792</v>
       </c>
       <c r="N19" t="n">
-        <v>961481.2431243125</v>
+        <v>14917198.82339956</v>
       </c>
       <c r="O19" t="n">
-        <v>15803.52695269527</v>
+        <v>85116.84657836644</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9307814644010347</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.8705946372672551</v>
-      </c>
+        <v>0.9637709553156532</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>0.0004303690060271313</v>
+        <v>4.534695769888867e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.001104335699257203</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.148640201987622</v>
-      </c>
+        <v>0.0003941804035795226</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>2566.020516792475</v>
+        <v>8692.543526226078</v>
       </c>
     </row>
     <row r="20">
@@ -1689,7 +1695,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (medium)</t>
+          <t>Haiku 5.5 (medium)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1699,116 +1705,110 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4588397535157457</v>
+        <v>0.335918178838533</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05389953906616766</v>
+        <v>0.02406931765202193</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.448924731182796</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6187507753025301</v>
+        <v>0.2263884094719471</v>
       </c>
       <c r="K20" t="n">
-        <v>510.7721826182621</v>
+        <v>837.3769053905384</v>
       </c>
       <c r="L20" t="n">
-        <v>22.20902090209021</v>
+        <v>44.01650165016502</v>
       </c>
       <c r="M20" t="n">
-        <v>1253351.492849284</v>
+        <v>3480808.845984597</v>
       </c>
       <c r="N20" t="n">
-        <v>1232830.718371837</v>
+        <v>3413192.581958196</v>
       </c>
       <c r="O20" t="n">
-        <v>20520.77447744774</v>
+        <v>67616.26402640264</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9341009883549257</v>
+        <v>0.95547252331787</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7415582684181721</v>
+        <v>1.483813502740997</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0003660902437453124</v>
+        <v>9.650578175990406e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0008983256511027943</v>
+        <v>0.0004011552942003655</v>
       </c>
       <c r="T20" t="n">
-        <v>1.348511698390355</v>
+        <v>0.6739391427242943</v>
       </c>
       <c r="U20" t="n">
-        <v>2453.836633045474</v>
+        <v>4156.800627742662</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-6 Sol (max)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5666259127577997</v>
+        <v>0.2771443620715672</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02540823290001526</v>
+        <v>0.006542828532467639</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.575268817204301</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.989729004180416</v>
-      </c>
+        <v>0.397849462365591</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>1338.052705170518</v>
+        <v>2541.509630242825</v>
       </c>
       <c r="L21" t="n">
-        <v>86.55005500550054</v>
+        <v>95.90949227373069</v>
       </c>
       <c r="M21" t="n">
-        <v>9840777.763476355</v>
+        <v>5065557.310154528</v>
       </c>
       <c r="N21" t="n">
-        <v>9778602.140814083</v>
+        <v>5026647.232891832</v>
       </c>
       <c r="O21" t="n">
-        <v>62175.62266226623</v>
+        <v>38910.07726269315</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9640119921972632</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.18952417157726</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>5.757938309112199e-05</v>
+        <v>5.471152434027297e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0004234705483335876</v>
-      </c>
-      <c r="T21" t="n">
-        <v>5.276371829924331</v>
-      </c>
+        <v>0.000109047142207794</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>7354.551674571196</v>
+        <v>1993.129299954904</v>
       </c>
     </row>
     <row r="22">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Opus 5 (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1829,51 +1829,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3680931015358647</v>
+        <v>0.5972636729844837</v>
       </c>
       <c r="F22" t="n">
-        <v>0.004193675756950516</v>
+        <v>0.01424577506914708</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.336021505376344</v>
+        <v>0.620967741935484</v>
       </c>
       <c r="J22" t="n">
-        <v>2.803197722050223</v>
+        <v>10.78915469925741</v>
       </c>
       <c r="K22" t="n">
-        <v>5266.402881898454</v>
+        <v>2515.540235973597</v>
       </c>
       <c r="L22" t="n">
-        <v>121.5060706401766</v>
+        <v>152.1303630363036</v>
       </c>
       <c r="M22" t="n">
-        <v>13843602.99834437</v>
+        <v>11374850.48899891</v>
       </c>
       <c r="N22" t="n">
-        <v>12842977.3995585</v>
+        <v>11238194.40979098</v>
       </c>
       <c r="O22" t="n">
-        <v>1000625.598785872</v>
+        <v>136656.0792079208</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8914806265675513</v>
+        <v>0.9698258997320075</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1313118581113308</v>
+        <v>0.05535778192387877</v>
       </c>
       <c r="R22" t="n">
-        <v>2.65894002868969e-05</v>
+        <v>5.250738667397188e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>6.989459594917527e-05</v>
+        <v>0.0002374295844857846</v>
       </c>
       <c r="T22" t="n">
-        <v>7.61545845427124</v>
+        <v>18.06430758687328</v>
       </c>
       <c r="U22" t="n">
-        <v>2628.663873386378</v>
+        <v>4521.832060697078</v>
       </c>
     </row>
     <row r="23">
@@ -1884,126 +1884,126 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (xhigh)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.628713868151493</v>
+        <v>0.5120452310717793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02329988772073193</v>
+        <v>0.009086148874713283</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.620967741935484</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>3.333386534873489</v>
+        <v>1.662215663091308</v>
       </c>
       <c r="K23" t="n">
-        <v>1619.013470847085</v>
+        <v>3381.269037953798</v>
       </c>
       <c r="L23" t="n">
-        <v>78.31683168316832</v>
+        <v>138.5951595159516</v>
       </c>
       <c r="M23" t="n">
-        <v>7087678.3960396</v>
+        <v>21745804.32343233</v>
       </c>
       <c r="N23" t="n">
-        <v>6961982.357535753</v>
+        <v>21619802.9180418</v>
       </c>
       <c r="O23" t="n">
-        <v>125696.0385038504</v>
+        <v>126001.4053905391</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9574714756466342</v>
+        <v>0.9870352061053834</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1886111501243448</v>
+        <v>0.3080498171455697</v>
       </c>
       <c r="R23" t="n">
-        <v>8.870519132228135e-05</v>
+        <v>2.354685177223e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.000388331462012199</v>
+        <v>0.0001514358145785547</v>
       </c>
       <c r="T23" t="n">
-        <v>5.30191348359169</v>
+        <v>3.246228188888836</v>
       </c>
       <c r="U23" t="n">
-        <v>4377.776049220427</v>
+        <v>6431.255271125063</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Sonnet 5.5 (low)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5430273329930766</v>
+        <v>0.420593075103495</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02952880696749936</v>
+        <v>0.06626014195543219</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.594086021505376</v>
+        <v>0.389784946236559</v>
       </c>
       <c r="J24" t="n">
-        <v>3.832577882590769</v>
+        <v>0.4831101147414734</v>
       </c>
       <c r="K24" t="n">
-        <v>1103.38490869087</v>
+        <v>380.8561793179318</v>
       </c>
       <c r="L24" t="n">
-        <v>184.4213421342134</v>
+        <v>18.57865786578658</v>
       </c>
       <c r="M24" t="n">
-        <v>16122474.14796479</v>
+        <v>977284.7700770069</v>
       </c>
       <c r="N24" t="n">
-        <v>15871228.38008801</v>
+        <v>961481.2431243125</v>
       </c>
       <c r="O24" t="n">
-        <v>251245.7678767877</v>
+        <v>15803.52695269527</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9712771508508302</v>
+        <v>0.9307814644010347</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1416872271427914</v>
+        <v>0.8705946372672551</v>
       </c>
       <c r="R24" t="n">
-        <v>3.368138959376935e-05</v>
+        <v>0.0004303690060271313</v>
       </c>
       <c r="S24" t="n">
-        <v>0.000492146782791656</v>
+        <v>0.001104335699257203</v>
       </c>
       <c r="T24" t="n">
-        <v>7.057799211443437</v>
+        <v>1.148640201987622</v>
       </c>
       <c r="U24" t="n">
-        <v>14611.83130290732</v>
+        <v>2566.020516792475</v>
       </c>
     </row>
     <row r="25">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (high)</t>
+          <t>Sonnet 5.5 (medium)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2024,51 +2024,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5501249049636148</v>
+        <v>0.4588397535157457</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04489709995378834</v>
+        <v>0.05389953906616766</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.564516129032258</v>
+        <v>0.448924731182796</v>
       </c>
       <c r="J25" t="n">
-        <v>1.235497127172719</v>
+        <v>0.6187507753025301</v>
       </c>
       <c r="K25" t="n">
-        <v>735.1809878987912</v>
+        <v>510.7721826182621</v>
       </c>
       <c r="L25" t="n">
-        <v>36.77227722772277</v>
+        <v>22.20902090209021</v>
       </c>
       <c r="M25" t="n">
-        <v>2652380.565456549</v>
+        <v>1253351.492849284</v>
       </c>
       <c r="N25" t="n">
-        <v>2610884.190319032</v>
+        <v>1232830.718371837</v>
       </c>
       <c r="O25" t="n">
-        <v>41496.37513751376</v>
+        <v>20520.77447744774</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9477934370079523</v>
+        <v>0.9341009883549257</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4452660332950404</v>
+        <v>0.7415582684181721</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0002074079836537043</v>
+        <v>0.0003660902437453124</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0007482849992298058</v>
+        <v>0.0008983256511027943</v>
       </c>
       <c r="T25" t="n">
-        <v>2.245848381022551</v>
+        <v>1.348511698390355</v>
       </c>
       <c r="U25" t="n">
-        <v>3607.792651218138</v>
+        <v>2453.836633045474</v>
       </c>
     </row>
     <row r="26">
@@ -2079,126 +2079,126 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731 (max)</t>
+          <t>GPT-6 Sol (max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3874247758775307</v>
+        <v>0.5666259127577997</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02118927042627475</v>
+        <v>0.02540823290001526</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.513440860215054</v>
+        <v>0.575268817204301</v>
       </c>
       <c r="J26" t="n">
-        <v>0.08278622901034095</v>
+        <v>3.002959349284928</v>
       </c>
       <c r="K26" t="n">
-        <v>1097.040440044003</v>
+        <v>1338.052705170518</v>
       </c>
       <c r="L26" t="n">
-        <v>121.6666666666667</v>
+        <v>86.55005500550054</v>
       </c>
       <c r="M26" t="n">
-        <v>15350225.29922993</v>
+        <v>9865698.770077005</v>
       </c>
       <c r="N26" t="n">
-        <v>15269826.30913091</v>
+        <v>9803212.217821782</v>
       </c>
       <c r="O26" t="n">
-        <v>80398.9900990099</v>
+        <v>62486.55225522553</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9869993314104538</v>
+        <v>0.9639719451023205</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.679821517527231</v>
+        <v>0.1886891718639901</v>
       </c>
       <c r="R26" t="n">
-        <v>2.523902863477623e-05</v>
+        <v>5.743393610155574e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003531545071045792</v>
+        <v>0.0004234705483335876</v>
       </c>
       <c r="T26" t="n">
-        <v>0.213683362977567</v>
+        <v>5.299721177009641</v>
       </c>
       <c r="U26" t="n">
-        <v>13992.39694264526</v>
+        <v>7373.176506391609</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (high)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6014923716179784</v>
+        <v>0.3680931015358647</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04512517141416127</v>
+        <v>0.004193675756950516</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.599462365591398</v>
+        <v>0.336021505376344</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8892413135295484</v>
+        <v>2.803197722050223</v>
       </c>
       <c r="K27" t="n">
-        <v>799.7652123212325</v>
+        <v>5266.402881898454</v>
       </c>
       <c r="L27" t="n">
-        <v>38.97909790979098</v>
+        <v>121.5060706401766</v>
       </c>
       <c r="M27" t="n">
-        <v>2819911.990351496</v>
+        <v>13843602.99834437</v>
       </c>
       <c r="N27" t="n">
-        <v>2791163.254864831</v>
+        <v>12842977.3995585</v>
       </c>
       <c r="O27" t="n">
-        <v>28748.73548666342</v>
+        <v>1000625.598785872</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9278388366571141</v>
+        <v>0.8914806265675513</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6764107362832188</v>
+        <v>0.1313118581113308</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0002133018241973586</v>
+        <v>2.65894002868969e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007520861902360213</v>
+        <v>6.989459594917527e-05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.478391672927692</v>
+        <v>7.61545845427124</v>
       </c>
       <c r="U27" t="n">
-        <v>3525.924792561313</v>
+        <v>2628.663873386378</v>
       </c>
     </row>
     <row r="28">
@@ -2304,22 +2304,22 @@
         <v>35.74037403740374</v>
       </c>
       <c r="M29" t="n">
-        <v>1713818.918195099</v>
+        <v>1716621.760879366</v>
       </c>
       <c r="N29" t="n">
-        <v>1699123.860141752</v>
+        <v>1701895.339789717</v>
       </c>
       <c r="O29" t="n">
-        <v>14695.05805334632</v>
+        <v>14726.42108964995</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9135762473536158</v>
+        <v>0.9135252011157503</v>
       </c>
       <c r="Q29" t="n">
         <v>1.147071598051071</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0003338529457384175</v>
+        <v>0.0003333078417976958</v>
       </c>
       <c r="S29" t="n">
         <v>0.001104959717190106</v>
@@ -2328,7 +2328,7 @@
         <v>0.8717851629305855</v>
       </c>
       <c r="U29" t="n">
-        <v>3309.719837116163</v>
+        <v>3315.132675038506</v>
       </c>
     </row>
     <row r="30">
@@ -2425,7 +2425,7 @@
         <v>0.594086021505376</v>
       </c>
       <c r="J31" t="n">
-        <v>4.241385833751375</v>
+        <v>4.365025664334435</v>
       </c>
       <c r="K31" t="n">
         <v>2887.955652365237</v>
@@ -2434,31 +2434,31 @@
         <v>107.049504950495</v>
       </c>
       <c r="M31" t="n">
-        <v>14276424.42684269</v>
+        <v>14304524.38833882</v>
       </c>
       <c r="N31" t="n">
         <v>14202165.16611661</v>
       </c>
       <c r="O31" t="n">
-        <v>74259.26072607259</v>
+        <v>102359.2222222222</v>
       </c>
       <c r="P31" t="n">
         <v>0.9745705628087887</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1262673180421449</v>
+        <v>0.1226907824129349</v>
       </c>
       <c r="R31" t="n">
-        <v>3.751278317299032e-05</v>
+        <v>3.743909265842608e-05</v>
       </c>
       <c r="S31" t="n">
         <v>0.000185442049143351</v>
       </c>
       <c r="T31" t="n">
-        <v>7.919705712496602</v>
+        <v>8.150571545255492</v>
       </c>
       <c r="U31" t="n">
-        <v>4943.436169163572</v>
+        <v>4953.166222141745</v>
       </c>
     </row>
     <row r="32">
@@ -2555,7 +2555,7 @@
         <v>0.486559139784946</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4380225639383938</v>
+        <v>0.443044129009901</v>
       </c>
       <c r="K33" t="n">
         <v>1412.260883388339</v>
@@ -2564,31 +2564,31 @@
         <v>121.5137513751375</v>
       </c>
       <c r="M33" t="n">
-        <v>14854524.53905389</v>
+        <v>14946565.0330033</v>
       </c>
       <c r="N33" t="n">
-        <v>14783219.74807481</v>
+        <v>14873442.23762376</v>
       </c>
       <c r="O33" t="n">
-        <v>71304.79097909792</v>
+        <v>73122.79537953796</v>
       </c>
       <c r="P33" t="n">
-        <v>0.971880328680834</v>
+        <v>0.9718252606404379</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9868141561395799</v>
+        <v>0.9756293752699781</v>
       </c>
       <c r="R33" t="n">
-        <v>2.909866725565972e-05</v>
+        <v>2.891947854564062e-05</v>
       </c>
       <c r="S33" t="n">
         <v>0.0003060672938599712</v>
       </c>
       <c r="T33" t="n">
-        <v>1.013362033548448</v>
+        <v>1.024979388021479</v>
       </c>
       <c r="U33" t="n">
-        <v>10518.2581446386</v>
+        <v>10583.43058907293</v>
       </c>
     </row>
     <row r="34">
@@ -2620,7 +2620,7 @@
         <v>0.618279569892473</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2380461072079206</v>
+        <v>0.238053496393564</v>
       </c>
       <c r="K34" t="n">
         <v>2417.550009900991</v>
@@ -2629,31 +2629,31 @@
         <v>138.1463146314632</v>
       </c>
       <c r="M34" t="n">
-        <v>24180108.02805281</v>
+        <v>24180269.40869088</v>
       </c>
       <c r="N34" t="n">
-        <v>24063625.6270627</v>
+        <v>24063782.8349835</v>
       </c>
       <c r="O34" t="n">
-        <v>116482.400990099</v>
+        <v>116486.5737073707</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9898485564269163</v>
+        <v>0.9898483066299235</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.808558675855097</v>
+        <v>1.808502538154936</v>
       </c>
       <c r="R34" t="n">
-        <v>1.780473238353379e-05</v>
+        <v>1.780461355363062e-05</v>
       </c>
       <c r="S34" t="n">
         <v>0.0001780812602350464</v>
       </c>
       <c r="T34" t="n">
-        <v>0.5529264896684616</v>
+        <v>0.5529436530513341</v>
       </c>
       <c r="U34" t="n">
-        <v>10001.90603256356</v>
+        <v>10001.97278635868</v>
       </c>
     </row>
     <row r="35">
@@ -2694,22 +2694,22 @@
         <v>40.05500550055005</v>
       </c>
       <c r="M35" t="n">
-        <v>3212528.109451931</v>
+        <v>3219106.085393785</v>
       </c>
       <c r="N35" t="n">
-        <v>3177125.49569875</v>
+        <v>3183587.565258165</v>
       </c>
       <c r="O35" t="n">
-        <v>35402.61375317859</v>
+        <v>35518.52013562011</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9327572280083256</v>
+        <v>0.9327267746735622</v>
       </c>
       <c r="Q35" t="n">
         <v>0.6050521995648973</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0001958201305169657</v>
+        <v>0.0001954199883429268</v>
       </c>
       <c r="S35" t="n">
         <v>0.0006754236874751251</v>
@@ -2718,267 +2718,267 @@
         <v>1.652749962266257</v>
       </c>
       <c r="U35" t="n">
-        <v>3449.204561819077</v>
+        <v>3456.267156714176</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.637577603035782</v>
+        <v>0.5626764360706693</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01847900510277171</v>
+        <v>0.01433955552408987</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>0.564516129032258</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J36" t="n">
-        <v>5.84390538944481</v>
+        <v>8.817468730473037</v>
       </c>
       <c r="K36" t="n">
-        <v>2070.168603200884</v>
+        <v>2354.367686468646</v>
       </c>
       <c r="L36" t="n">
-        <v>149.1832229580574</v>
+        <v>162.6457645764577</v>
       </c>
       <c r="M36" t="n">
-        <v>13733793.78145695</v>
+        <v>14324724.28382839</v>
       </c>
       <c r="N36" t="n">
-        <v>13621672.65011038</v>
+        <v>14201447.9559956</v>
       </c>
       <c r="O36" t="n">
-        <v>112121.1313465784</v>
+        <v>123276.3278327833</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8700000000000004</v>
+        <v>0.938882976190201</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1091012876743978</v>
+        <v>0.06381382835258244</v>
       </c>
       <c r="R36" t="n">
-        <v>4.642399712573407e-05</v>
+        <v>3.928008839275821e-05</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0003079834183795285</v>
+        <v>0.0002389925920681645</v>
       </c>
       <c r="T36" t="n">
-        <v>9.165794660319708</v>
+        <v>15.67058466504826</v>
       </c>
       <c r="U36" t="n">
-        <v>6634.142629842724</v>
+        <v>6084.319100265209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6835783373750831</v>
+        <v>0.637577603035782</v>
       </c>
       <c r="F37" t="n">
-        <v>0.007819822882745912</v>
+        <v>0.01847900510277171</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0.669354838709677</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="J37" t="n">
-        <v>14.19080079636965</v>
+        <v>5.843905389444815</v>
       </c>
       <c r="K37" t="n">
-        <v>5244.965372937293</v>
+        <v>2070.168603200884</v>
       </c>
       <c r="L37" t="n">
-        <v>265.9306930693069</v>
+        <v>149.1832229580574</v>
       </c>
       <c r="M37" t="n">
-        <v>27742337.2337734</v>
+        <v>13733793.78145695</v>
       </c>
       <c r="N37" t="n">
-        <v>27141368.95929593</v>
+        <v>13621672.65011038</v>
       </c>
       <c r="O37" t="n">
-        <v>600968.2744774478</v>
+        <v>112121.1313465784</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9506214943317096</v>
+        <v>0.8700000000000004</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.04817052590506091</v>
+        <v>0.1091012876743977</v>
       </c>
       <c r="R37" t="n">
-        <v>2.464025765438745e-05</v>
+        <v>4.642399712573407e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0001303303813790985</v>
+        <v>0.0003079834183795285</v>
       </c>
       <c r="T37" t="n">
-        <v>20.75958236310095</v>
+        <v>9.165794660319715</v>
       </c>
       <c r="U37" t="n">
-        <v>5289.327051979582</v>
+        <v>6634.142629842724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6366510283153159</v>
+        <v>0.6835783373750831</v>
       </c>
       <c r="F38" t="n">
-        <v>0.02838675827210399</v>
+        <v>0.007819822882745912</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>0.672043010752688</v>
+        <v>0.669354838709677</v>
       </c>
       <c r="J38" t="n">
-        <v>8.040007295049511</v>
+        <v>14.19080079636965</v>
       </c>
       <c r="K38" t="n">
-        <v>1345.664810781076</v>
+        <v>5244.965372937293</v>
       </c>
       <c r="L38" t="n">
-        <v>191.8814250655834</v>
+        <v>265.9306930693069</v>
       </c>
       <c r="M38" t="n">
-        <v>15007201.97854787</v>
+        <v>27742337.2337734</v>
       </c>
       <c r="N38" t="n">
-        <v>14917219.10011001</v>
+        <v>27141368.95929593</v>
       </c>
       <c r="O38" t="n">
-        <v>89982.87843784377</v>
+        <v>600968.2744774478</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9358639622980014</v>
+        <v>0.9506214943317096</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.07918537943458363</v>
+        <v>0.04817052590506091</v>
       </c>
       <c r="R38" t="n">
-        <v>4.242303323600098e-05</v>
+        <v>2.464025765438745e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0004731126378683998</v>
+        <v>0.0001303303813790985</v>
       </c>
       <c r="T38" t="n">
-        <v>12.62859390382939</v>
+        <v>20.75958236310095</v>
       </c>
       <c r="U38" t="n">
-        <v>11152.25861471187</v>
+        <v>5289.327051979582</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6014750704302517</v>
+        <v>0.6366510283153159</v>
       </c>
       <c r="F39" t="n">
-        <v>0.02466668430491293</v>
+        <v>0.02838675827210399</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0.577956989247312</v>
+        <v>0.672043010752688</v>
       </c>
       <c r="J39" t="n">
-        <v>1.554119528390054</v>
+        <v>8.040007295049511</v>
       </c>
       <c r="K39" t="n">
-        <v>1463.046422442244</v>
+        <v>1345.664810781076</v>
       </c>
       <c r="L39" t="n">
-        <v>40.45654565456545</v>
+        <v>191.8814250655834</v>
       </c>
       <c r="M39" t="n">
-        <v>3999501.610795507</v>
+        <v>15007201.97854787</v>
       </c>
       <c r="N39" t="n">
-        <v>3937843.056466302</v>
+        <v>14917219.10011001</v>
       </c>
       <c r="O39" t="n">
-        <v>61658.55432920342</v>
+        <v>89982.87843784377</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9281954641245814</v>
+        <v>0.9358639622980014</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3870198266238458</v>
+        <v>0.07918537943458363</v>
       </c>
       <c r="R39" t="n">
-        <v>0.000150387505484869</v>
+        <v>4.242303323600098e-05</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0004111114050818821</v>
+        <v>0.0004731126378683998</v>
       </c>
       <c r="T39" t="n">
-        <v>2.583846953587535</v>
+        <v>12.62859390382939</v>
       </c>
       <c r="U39" t="n">
-        <v>2733.680592389675</v>
+        <v>11152.25861471187</v>
       </c>
     </row>
     <row r="40">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2999,116 +2999,116 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6164504498789397</v>
+        <v>0.6014750704302517</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02100022628798557</v>
+        <v>0.02466668430491293</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>0.618279569892473</v>
+        <v>0.577956989247312</v>
       </c>
       <c r="J40" t="n">
-        <v>7.46548537723855</v>
+        <v>1.554119528390054</v>
       </c>
       <c r="K40" t="n">
-        <v>1761.26802090209</v>
+        <v>1463.046422442244</v>
       </c>
       <c r="L40" t="n">
-        <v>39.37183718371837</v>
+        <v>40.45654565456545</v>
       </c>
       <c r="M40" t="n">
-        <v>3345996.469855181</v>
+        <v>4014041.761005608</v>
       </c>
       <c r="N40" t="n">
-        <v>3298947.014445707</v>
+        <v>3952115.763079586</v>
       </c>
       <c r="O40" t="n">
-        <v>47049.45540947537</v>
+        <v>61925.99792602211</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9335374217538733</v>
+        <v>0.9280414051904134</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.08257339191346216</v>
+        <v>0.3870198266238458</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0001842352361793198</v>
+        <v>0.0001498427535740357</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0003500037714664262</v>
+        <v>0.0004111114050818821</v>
       </c>
       <c r="T40" t="n">
-        <v>12.11043868765875</v>
+        <v>2.583846953587535</v>
       </c>
       <c r="U40" t="n">
-        <v>1899.765640519279</v>
+        <v>2743.618862281227</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.5626764360706693</v>
+        <v>0.6164504498789397</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01433955552408987</v>
+        <v>0.02100022628798557</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>0.629032258064516</v>
+        <v>0.618279569892473</v>
       </c>
       <c r="J41" t="n">
-        <v>8.817468730473037</v>
+        <v>7.497231868004842</v>
       </c>
       <c r="K41" t="n">
-        <v>2354.367686468646</v>
+        <v>1761.26802090209</v>
       </c>
       <c r="L41" t="n">
-        <v>162.6457645764577</v>
+        <v>39.37183718371837</v>
       </c>
       <c r="M41" t="n">
-        <v>14324724.28382839</v>
+        <v>3357139.803008172</v>
       </c>
       <c r="N41" t="n">
-        <v>14201447.9559956</v>
+        <v>3309837.764846976</v>
       </c>
       <c r="O41" t="n">
-        <v>123276.3278327833</v>
+        <v>47302.03816119317</v>
       </c>
       <c r="P41" t="n">
-        <v>0.938882976190201</v>
+        <v>0.9335199965570197</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.06381382835258244</v>
+        <v>0.08222374080621693</v>
       </c>
       <c r="R41" t="n">
-        <v>3.928008839275821e-05</v>
+        <v>0.000183623705312054</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0002389925920681645</v>
+        <v>0.0003500037714664262</v>
       </c>
       <c r="T41" t="n">
-        <v>15.67058466504826</v>
+        <v>12.16193754011725</v>
       </c>
       <c r="U41" t="n">
-        <v>6084.319100265209</v>
+        <v>1906.092521505447</v>
       </c>
     </row>
     <row r="42">

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -541,51 +541,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.373496050722277</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.338709677419355</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J2" t="n">
-        <v>2.67388407176395</v>
+        <v>11.5301045391259</v>
       </c>
       <c r="K2" t="n">
-        <v>4255.92477550559</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L2" t="n">
-        <v>114.307695231889</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M2" t="n">
-        <v>16053233.8058097</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N2" t="n">
-        <v>15314914.0867177</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O2" t="n">
-        <v>738319.719091995</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P2" t="n">
-        <v>0.918420370906708</v>
+        <v>0.923288749508769</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.04997354913195912</v>
       </c>
       <c r="R2" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>0.0002723640979209027</v>
       </c>
       <c r="T2" t="n">
-        <v>7.159069196563442</v>
+        <v>20.01058594736629</v>
       </c>
       <c r="U2" t="n">
-        <v>3771.973108688846</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="3">
@@ -656,155 +656,155 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.663978494623656</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J4" t="n">
-        <v>11.5301045391259</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K4" t="n">
-        <v>2115.55138904529</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L4" t="n">
-        <v>42.2762050613663</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M4" t="n">
-        <v>5989151.58443575</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N4" t="n">
-        <v>5863350.62589986</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O4" t="n">
-        <v>125800.958535897</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P4" t="n">
-        <v>0.923288749508769</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04997354913195912</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R4" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002723640979209027</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T4" t="n">
-        <v>20.01058594736629</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U4" t="n">
-        <v>2831.01210183249</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.489161690344303</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.586021505376344</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J5" t="n">
-        <v>5.23102713863476</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K5" t="n">
-        <v>3369.69557528728</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L5" t="n">
-        <v>111.53421852938</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M5" t="n">
-        <v>15908435.1191376</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N5" t="n">
-        <v>15798476.017074</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O5" t="n">
-        <v>109959.102063647</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P5" t="n">
-        <v>0.949845583680754</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09351159483220896</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R5" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001451649501906712</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T5" t="n">
-        <v>10.69386103182535</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U5" t="n">
-        <v>4721.030361260851</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.457077885630498</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -812,40 +812,40 @@
         <v>0.586021505376344</v>
       </c>
       <c r="J6" t="n">
-        <v>3.91029139020419</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K6" t="n">
-        <v>1398.49826969262</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L6" t="n">
-        <v>208.319377647442</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M6" t="n">
-        <v>17824340.6533789</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N6" t="n">
-        <v>17642872.3721332</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O6" t="n">
-        <v>181468.281245791</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P6" t="n">
-        <v>0.966617846464586</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1168910037690644</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R6" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000326834788098065</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T6" t="n">
-        <v>8.554978293929695</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U6" t="n">
-        <v>12745.34337271405</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="7">
@@ -856,137 +856,137 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>DeepSeek V4.1 Flash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.311260251113284</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.381720430107527</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J7" t="n">
-        <v>0.159155559086193</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K7" t="n">
-        <v>1275.79489619203</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L7" t="n">
-        <v>81.3609199522103</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M7" t="n">
-        <v>8885939.032378631</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N7" t="n">
-        <v>8794707.77057673</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O7" t="n">
-        <v>91231.26180188989</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P7" t="n">
-        <v>0.954514555274975</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95569826715708</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R7" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5113263210350233</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U7" t="n">
-        <v>6965.021618209341</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.431274491691105</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.586021505376344</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J8" t="n">
-        <v>1.84006320525524</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K8" t="n">
-        <v>3665.13740781145</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L8" t="n">
-        <v>142.091813837298</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M8" t="n">
-        <v>22141655.7546106</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N8" t="n">
-        <v>21997509.2781069</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O8" t="n">
-        <v>144146.476503747</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P8" t="n">
-        <v>0.984007673153142</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2343802595798777</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R8" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T8" t="n">
-        <v>4.266570921085596</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U8" t="n">
-        <v>6041.152974898141</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash</t>
+          <t>DeepSeek V4.1 Flash 1017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -996,565 +996,565 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.473001334419464</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.610215053763441</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38619359563592</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K9" t="n">
-        <v>2283.94687962311</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L9" t="n">
-        <v>142.882443792766</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M9" t="n">
-        <v>27235627.5942381</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N9" t="n">
-        <v>27078637.1644444</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O9" t="n">
-        <v>156990.429793635</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.22477777923946</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R9" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8164746429519335</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U9" t="n">
-        <v>11924.80781283864</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.33272301118714</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.443548387096774</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J10" t="n">
-        <v>2.51071545979138</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K10" t="n">
-        <v>786.045572632779</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L10" t="n">
-        <v>202.504982078853</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M10" t="n">
-        <v>14251510.9748887</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N10" t="n">
-        <v>14138882.8572119</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O10" t="n">
-        <v>112628.117676768</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1325211942634019</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R10" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T10" t="n">
-        <v>7.545962783978378</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U10" t="n">
-        <v>18130.64212950749</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.463051957532312</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.615591397849462</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J11" t="n">
-        <v>0.29627468390668</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K11" t="n">
-        <v>1284.94041000543</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L11" t="n">
-        <v>101.530045617465</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M11" t="n">
-        <v>16739365.2564321</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N11" t="n">
-        <v>16633748.9354947</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O11" t="n">
-        <v>105616.32093733</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P11" t="n">
-        <v>0.967966386781858</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56291435848148</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R11" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6398303237623303</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U11" t="n">
-        <v>13027.34751439669</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.530769734767025</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.602150537634409</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J12" t="n">
-        <v>4.33822148437056</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K12" t="n">
-        <v>1270.3477207201</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L12" t="n">
-        <v>58.8586738351254</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M12" t="n">
-        <v>3625399.81721408</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N12" t="n">
-        <v>3585782.97351906</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O12" t="n">
-        <v>39616.8436950147</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P12" t="n">
-        <v>0.91270190622461</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1223473113761584</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001464030897356012</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0004178145291323519</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>8.173453006461965</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U12" t="n">
-        <v>2853.864149226019</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.263007023894863</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.508064516129032</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J13" t="n">
-        <v>3.54324946048794</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K13" t="n">
-        <v>1558.86632482568</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L13" t="n">
-        <v>161.39889866406</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M13" t="n">
-        <v>13336678.8257109</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N13" t="n">
-        <v>13239522.4765722</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O13" t="n">
-        <v>97156.3491386988</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P13" t="n">
-        <v>0.951550733530632</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07422763393538889</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R13" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001687168551314198</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T13" t="n">
-        <v>13.47207161244619</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U13" t="n">
-        <v>8555.370408172921</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.392199207885305</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.561827956989248</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J14" t="n">
-        <v>3.79584401482699</v>
+        <v>8.19825160322711</v>
       </c>
       <c r="K14" t="n">
-        <v>4568.4135207125</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L14" t="n">
-        <v>114.796515026192</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M14" t="n">
-        <v>9153421.029330021</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N14" t="n">
-        <v>9032702.304066719</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O14" t="n">
-        <v>120718.725263303</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P14" t="n">
-        <v>0.947205701820927</v>
+        <v>0.957829308304356</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.07155416292954402</v>
       </c>
       <c r="R14" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>0.0002602951802888973</v>
       </c>
       <c r="T14" t="n">
-        <v>9.678357167761158</v>
+        <v>13.97542727157122</v>
       </c>
       <c r="U14" t="n">
-        <v>2003.632330530016</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.615117219506897</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.682795698924731</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7.99768820548534</v>
-      </c>
+        <v>0.376344086021506</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>3067.08119502552</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L15" t="n">
-        <v>99.46435538177469</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M15" t="n">
-        <v>10463266.3479852</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N15" t="n">
-        <v>10202564.6581949</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O15" t="n">
-        <v>260701.689790377</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P15" t="n">
-        <v>0.870466942043008</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.07691187799556992</v>
-      </c>
+        <v>0.319061166570896</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002005545925893816</v>
-      </c>
-      <c r="T15" t="n">
-        <v>13.00189289432771</v>
-      </c>
+        <v>8.82238133000263e-05</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>3411.473541996706</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.586619030954708</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.682795698924731</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J16" t="n">
-        <v>8.19825160322711</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K16" t="n">
-        <v>2253.66843252199</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L16" t="n">
-        <v>92.38415770609321</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M16" t="n">
-        <v>9809458.18526447</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N16" t="n">
-        <v>9713403.98470946</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O16" t="n">
-        <v>96054.2005550125</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P16" t="n">
-        <v>0.957829308304356</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.07155416292954402</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R16" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T16" t="n">
-        <v>13.97542727157122</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U16" t="n">
-        <v>4352.662549515813</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.20478987379168</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.376344086021506</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>0.338709677419355</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.67388407176395</v>
+      </c>
       <c r="K17" t="n">
-        <v>2321.25393509395</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L17" t="n">
-        <v>92.9845715216683</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M17" t="n">
-        <v>4890063.07487998</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N17" t="n">
-        <v>4852363.14787444</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O17" t="n">
-        <v>37699.9270055393</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P17" t="n">
-        <v>0.319061166570896</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>0.918420370906708</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1396829633215486</v>
+      </c>
       <c r="R17" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>8.82238133000263e-05</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
+        <v>8.775908185029112e-05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.159069196563442</v>
+      </c>
       <c r="U17" t="n">
-        <v>2106.647187948466</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="18">
@@ -1625,261 +1625,261 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5466356905615291</v>
+        <v>0.465968752688172</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02206122126132733</v>
+        <v>0.01302767878143769</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.591397849462366</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J19" t="n">
-        <v>7.03615822479963</v>
+        <v>9.479356533441949</v>
       </c>
       <c r="K19" t="n">
-        <v>1486.68747959053</v>
+        <v>2146.05576560009</v>
       </c>
       <c r="L19" t="n">
-        <v>39.3501020962311</v>
+        <v>169.916321277289</v>
       </c>
       <c r="M19" t="n">
-        <v>3228511.32437048</v>
+        <v>15914547.7950299</v>
       </c>
       <c r="N19" t="n">
-        <v>3187374.52012585</v>
+        <v>15798913.4163495</v>
       </c>
       <c r="O19" t="n">
-        <v>41136.8042446321</v>
+        <v>115634.378680352</v>
       </c>
       <c r="P19" t="n">
-        <v>0.928466255516987</v>
+        <v>0.9420679200051389</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.07768951082351416</v>
+        <v>0.04915615854771305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0001693150915826867</v>
+        <v>2.927942148841287e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003676870210221221</v>
+        <v>0.0002171279796906282</v>
       </c>
       <c r="T19" t="n">
-        <v>12.87175050273751</v>
+        <v>20.34333091812611</v>
       </c>
       <c r="U19" t="n">
-        <v>2171.613986592321</v>
+        <v>7415.719595981607</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.532462665363311</v>
+        <v>0.5466356905615291</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01534920015815749</v>
+        <v>0.02206122126132733</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.551075268817204</v>
+        <v>0.591397849462366</v>
       </c>
       <c r="J20" t="n">
-        <v>5.86148606882067</v>
+        <v>7.03615822479963</v>
       </c>
       <c r="K20" t="n">
-        <v>2081.39574652818</v>
+        <v>1486.68747959053</v>
       </c>
       <c r="L20" t="n">
-        <v>166.081847507331</v>
+        <v>39.3501020962311</v>
       </c>
       <c r="M20" t="n">
-        <v>13865930.859975</v>
+        <v>3228511.32437048</v>
       </c>
       <c r="N20" t="n">
-        <v>13756695.0153003</v>
+        <v>3187374.52012585</v>
       </c>
       <c r="O20" t="n">
-        <v>109235.844674704</v>
+        <v>41136.8042446321</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.928466255516987</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09084089923810779</v>
+        <v>0.07768951082351416</v>
       </c>
       <c r="R20" t="n">
-        <v>3.840078756632939e-05</v>
+        <v>0.0001693150915826867</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0002558200026359581</v>
+        <v>0.0003676870210221221</v>
       </c>
       <c r="T20" t="n">
-        <v>11.00825738612349</v>
+        <v>12.87175050273751</v>
       </c>
       <c r="U20" t="n">
-        <v>6661.842603985196</v>
+        <v>2171.613986592321</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.593374426631911</v>
+        <v>0.532462665363311</v>
       </c>
       <c r="F21" t="n">
-        <v>0.007440989482023622</v>
+        <v>0.01534920015815749</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.64247311827957</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J21" t="n">
-        <v>13.3015082635468</v>
+        <v>5.86148606882067</v>
       </c>
       <c r="K21" t="n">
-        <v>4784.64130125774</v>
+        <v>2081.39574652818</v>
       </c>
       <c r="L21" t="n">
-        <v>232.941984902791</v>
+        <v>166.081847507331</v>
       </c>
       <c r="M21" t="n">
-        <v>24129277.9119089</v>
+        <v>13865930.859975</v>
       </c>
       <c r="N21" t="n">
-        <v>23634722.0822716</v>
+        <v>13756695.0153003</v>
       </c>
       <c r="O21" t="n">
-        <v>494555.829637233</v>
+        <v>109235.844674704</v>
       </c>
       <c r="P21" t="n">
-        <v>0.952959879951284</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.04460955967362529</v>
+        <v>0.09084089923810779</v>
       </c>
       <c r="R21" t="n">
-        <v>2.459147052797024e-05</v>
+        <v>3.840078756632939e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001240164913670604</v>
+        <v>0.0002558200026359581</v>
       </c>
       <c r="T21" t="n">
-        <v>22.41671980885376</v>
+        <v>11.00825738612349</v>
       </c>
       <c r="U21" t="n">
-        <v>5043.069353091532</v>
+        <v>6661.842603985196</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.519768236993592</v>
+        <v>0.593374426631911</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02117889017131678</v>
+        <v>0.007440989482023622</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.615591397849462</v>
+        <v>0.64247311827957</v>
       </c>
       <c r="J22" t="n">
-        <v>8.04811220428196</v>
+        <v>13.3015082635468</v>
       </c>
       <c r="K22" t="n">
-        <v>1472.5084254817</v>
+        <v>4784.64130125774</v>
       </c>
       <c r="L22" t="n">
-        <v>200.877049903502</v>
+        <v>232.941984902791</v>
       </c>
       <c r="M22" t="n">
-        <v>14479705.3019539</v>
+        <v>24129277.9119089</v>
       </c>
       <c r="N22" t="n">
-        <v>14384183.420164</v>
+        <v>23634722.0822716</v>
       </c>
       <c r="O22" t="n">
-        <v>95521.8817899424</v>
+        <v>494555.829637233</v>
       </c>
       <c r="P22" t="n">
-        <v>0.939000029822895</v>
+        <v>0.952959879951284</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.06458262804997322</v>
+        <v>0.04460955967362529</v>
       </c>
       <c r="R22" t="n">
-        <v>3.589632704219845e-05</v>
+        <v>2.459147052797024e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0003529815028552796</v>
+        <v>0.0001240164913670604</v>
       </c>
       <c r="T22" t="n">
-        <v>15.48404006145759</v>
+        <v>22.41671980885376</v>
       </c>
       <c r="U22" t="n">
-        <v>9833.35989892022</v>
+        <v>5043.069353091532</v>
       </c>
     </row>
     <row r="23">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1900,175 +1900,175 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.588804489084392</v>
+        <v>0.519768236993592</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01685280599548879</v>
+        <v>0.02117889017131678</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.688172043010753</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>0.615591397849462</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8.04811220428196</v>
+      </c>
       <c r="K23" t="n">
-        <v>2096.2841057163</v>
+        <v>1472.5084254817</v>
       </c>
       <c r="L23" t="n">
-        <v>194.874971760617</v>
+        <v>200.877049903502</v>
       </c>
       <c r="M23" t="n">
-        <v>14497965.3172412</v>
+        <v>14479705.3019539</v>
       </c>
       <c r="N23" t="n">
-        <v>14414434.4559639</v>
+        <v>14384183.420164</v>
       </c>
       <c r="O23" t="n">
-        <v>83530.861277289</v>
+        <v>95521.8817899424</v>
       </c>
       <c r="P23" t="n">
-        <v>0.962325196630197</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>0.939000029822895</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.06458262804997322</v>
+      </c>
       <c r="R23" t="n">
-        <v>4.061290506635278e-05</v>
+        <v>3.589632704219845e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0002808800999248132</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
+        <v>0.0003529815028552796</v>
+      </c>
+      <c r="T23" t="n">
+        <v>15.48404006145759</v>
+      </c>
       <c r="U23" t="n">
-        <v>6916.030741113332</v>
+        <v>9833.35989892022</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.541279798631476</v>
+        <v>0.588804489084392</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02284798697058158</v>
+        <v>0.01685280599548879</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.599462365591398</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.5046389983744</v>
-      </c>
+        <v>0.688172043010753</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>1421.42885321603</v>
+        <v>2096.2841057163</v>
       </c>
       <c r="L24" t="n">
-        <v>40.6271304442272</v>
+        <v>194.874971760617</v>
       </c>
       <c r="M24" t="n">
-        <v>3944222.64509301</v>
+        <v>14497965.3172412</v>
       </c>
       <c r="N24" t="n">
-        <v>3888998.33558647</v>
+        <v>14414434.4559639</v>
       </c>
       <c r="O24" t="n">
-        <v>55224.3095065408</v>
+        <v>83530.861277289</v>
       </c>
       <c r="P24" t="n">
-        <v>0.921352278288341</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.3597406415866333</v>
-      </c>
+        <v>0.962325196630197</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>0.0001372335811987895</v>
+        <v>4.061290506635278e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0003807997828430263</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.779780442903275</v>
-      </c>
+        <v>0.0002808800999248132</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>2774.82945148403</v>
+        <v>6916.030741113332</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.465968752688172</v>
+        <v>0.541279798631476</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.02284798697058158</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.629032258064516</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J25" t="n">
-        <v>9.479356533441949</v>
+        <v>1.5046389983744</v>
       </c>
       <c r="K25" t="n">
-        <v>2146.05576560009</v>
+        <v>1421.42885321603</v>
       </c>
       <c r="L25" t="n">
-        <v>169.916321277289</v>
+        <v>40.6271304442272</v>
       </c>
       <c r="M25" t="n">
-        <v>15914547.7950299</v>
+        <v>3944222.64509301</v>
       </c>
       <c r="N25" t="n">
-        <v>15798913.4163495</v>
+        <v>3888998.33558647</v>
       </c>
       <c r="O25" t="n">
-        <v>115634.378680352</v>
+        <v>55224.3095065408</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.921352278288341</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.3597406415866333</v>
       </c>
       <c r="R25" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>0.0001372335811987895</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0003807997828430263</v>
       </c>
       <c r="T25" t="n">
-        <v>20.34333091812611</v>
+        <v>2.779780442903275</v>
       </c>
       <c r="U25" t="n">
-        <v>7415.719595981607</v>
+        <v>2774.82945148403</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,716 +526,716 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.41417319257087</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.006586839388819422</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.663978494623656</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J2" t="n">
-        <v>11.5301045391259</v>
+        <v>5.16526976917945</v>
       </c>
       <c r="K2" t="n">
-        <v>2115.55138904529</v>
+        <v>3772.73379345389</v>
       </c>
       <c r="L2" t="n">
-        <v>42.2762050613663</v>
+        <v>185.884007277072</v>
       </c>
       <c r="M2" t="n">
-        <v>5989151.58443575</v>
+        <v>9010345.58218855</v>
       </c>
       <c r="N2" t="n">
-        <v>5863350.62589986</v>
+        <v>8910048.672052789</v>
       </c>
       <c r="O2" t="n">
-        <v>125800.958535897</v>
+        <v>100296.910135766</v>
       </c>
       <c r="P2" t="n">
-        <v>0.923288749508769</v>
+        <v>0.9600647788144701</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04997354913195912</v>
+        <v>0.08018423259172099</v>
       </c>
       <c r="R2" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>4.596640481688052e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002723640979209027</v>
+        <v>0.0001097806564803237</v>
       </c>
       <c r="T2" t="n">
-        <v>20.01058594736629</v>
+        <v>12.47127979751034</v>
       </c>
       <c r="U2" t="n">
-        <v>2831.01210183249</v>
+        <v>2388.280243313879</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.41417319257087</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006586839388819422</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.599462365591398</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J3" t="n">
-        <v>5.16526976917945</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K3" t="n">
-        <v>3772.73379345389</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L3" t="n">
-        <v>185.884007277072</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M3" t="n">
-        <v>9010345.58218855</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N3" t="n">
-        <v>8910048.672052789</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O3" t="n">
-        <v>100296.910135766</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9600647788144701</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08018423259172099</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R3" t="n">
-        <v>4.596640481688052e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001097806564803237</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T3" t="n">
-        <v>12.47127979751034</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U3" t="n">
-        <v>2388.280243313879</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.457077885630498</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.586021505376344</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J4" t="n">
-        <v>3.91029139020419</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K4" t="n">
-        <v>1398.49826969262</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L4" t="n">
-        <v>208.319377647442</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M4" t="n">
-        <v>17824340.6533789</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N4" t="n">
-        <v>17642872.3721332</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O4" t="n">
-        <v>181468.281245791</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P4" t="n">
-        <v>0.966617846464586</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1168910037690644</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R4" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000326834788098065</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T4" t="n">
-        <v>8.554978293929695</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U4" t="n">
-        <v>12745.34337271405</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.311260251113284</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.381720430107527</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J5" t="n">
-        <v>0.159155559086193</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K5" t="n">
-        <v>1275.79489619203</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L5" t="n">
-        <v>81.3609199522103</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M5" t="n">
-        <v>8885939.032378631</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N5" t="n">
-        <v>8794707.77057673</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O5" t="n">
-        <v>91231.26180188989</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P5" t="n">
-        <v>0.954514555274975</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95569826715708</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R5" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5113263210350233</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U5" t="n">
-        <v>6965.021618209341</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>DeepSeek V4.1 Flash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.431274491691105</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.586021505376344</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J6" t="n">
-        <v>1.84006320525524</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K6" t="n">
-        <v>3665.13740781145</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L6" t="n">
-        <v>142.091813837298</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M6" t="n">
-        <v>22141655.7546106</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N6" t="n">
-        <v>21997509.2781069</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O6" t="n">
-        <v>144146.476503747</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P6" t="n">
-        <v>0.984007673153142</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2343802595798777</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R6" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T6" t="n">
-        <v>4.266570921085596</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U6" t="n">
-        <v>6041.152974898141</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.473001334419464</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.610215053763441</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.38619359563592</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K7" t="n">
-        <v>2283.94687962311</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L7" t="n">
-        <v>142.882443792766</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M7" t="n">
-        <v>27235627.5942381</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N7" t="n">
-        <v>27078637.1644444</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O7" t="n">
-        <v>156990.429793635</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.22477777923946</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R7" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8164746429519335</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U7" t="n">
-        <v>11924.80781283864</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>DeepSeek V4.1 Flash 1017</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.33272301118714</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.443548387096774</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J8" t="n">
-        <v>2.51071545979138</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K8" t="n">
-        <v>786.045572632779</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L8" t="n">
-        <v>202.504982078853</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M8" t="n">
-        <v>14251510.9748887</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N8" t="n">
-        <v>14138882.8572119</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O8" t="n">
-        <v>112628.117676768</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1325211942634019</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T8" t="n">
-        <v>7.545962783978378</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U8" t="n">
-        <v>18130.64212950749</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.463051957532312</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.615591397849462</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J9" t="n">
-        <v>0.29627468390668</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K9" t="n">
-        <v>1284.94041000543</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L9" t="n">
-        <v>101.530045617465</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M9" t="n">
-        <v>16739365.2564321</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N9" t="n">
-        <v>16633748.9354947</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O9" t="n">
-        <v>105616.32093733</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.967966386781858</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56291435848148</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R9" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6398303237623303</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U9" t="n">
-        <v>13027.34751439669</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.530769734767025</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.602150537634409</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J10" t="n">
-        <v>4.33822148437056</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K10" t="n">
-        <v>1270.3477207201</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L10" t="n">
-        <v>58.8586738351254</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M10" t="n">
-        <v>3625399.81721408</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N10" t="n">
-        <v>3585782.97351906</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O10" t="n">
-        <v>39616.8436950147</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P10" t="n">
-        <v>0.91270190622461</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1223473113761584</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001464030897356012</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T10" t="n">
-        <v>8.173453006461965</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U10" t="n">
-        <v>2853.864149226019</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.263007023894863</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.508064516129032</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J11" t="n">
-        <v>3.54324946048794</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K11" t="n">
-        <v>1558.86632482568</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L11" t="n">
-        <v>161.39889866406</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M11" t="n">
-        <v>13336678.8257109</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N11" t="n">
-        <v>13239522.4765722</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O11" t="n">
-        <v>97156.3491386988</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P11" t="n">
-        <v>0.951550733530632</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07422763393538889</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R11" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0001687168551314198</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>13.47207161244619</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U11" t="n">
-        <v>8555.370408172921</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.392199207885305</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.561827956989248</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J12" t="n">
-        <v>3.79584401482699</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K12" t="n">
-        <v>4568.4135207125</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L12" t="n">
-        <v>114.796515026192</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M12" t="n">
-        <v>9153421.029330021</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N12" t="n">
-        <v>9032702.304066719</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O12" t="n">
-        <v>120718.725263303</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P12" t="n">
-        <v>0.947205701820927</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R12" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T12" t="n">
-        <v>9.678357167761158</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U12" t="n">
-        <v>2003.632330530016</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.615117219506897</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1267,619 +1267,619 @@
         <v>0.682795698924731</v>
       </c>
       <c r="J13" t="n">
-        <v>7.99768820548534</v>
+        <v>8.19825160322711</v>
       </c>
       <c r="K13" t="n">
-        <v>3067.08119502552</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L13" t="n">
-        <v>99.46435538177469</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M13" t="n">
-        <v>10463266.3479852</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N13" t="n">
-        <v>10202564.6581949</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O13" t="n">
-        <v>260701.689790377</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P13" t="n">
-        <v>0.870466942043008</v>
+        <v>0.957829308304356</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07691187799556992</v>
+        <v>0.07155416292954402</v>
       </c>
       <c r="R13" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002005545925893816</v>
+        <v>0.0002602951802888973</v>
       </c>
       <c r="T13" t="n">
-        <v>13.00189289432771</v>
+        <v>13.97542727157122</v>
       </c>
       <c r="U13" t="n">
-        <v>3411.473541996706</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.586619030954708</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.682795698924731</v>
-      </c>
-      <c r="J14" t="n">
-        <v>8.19825160322711</v>
-      </c>
+        <v>0.376344086021506</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>2253.66843252199</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L14" t="n">
-        <v>92.38415770609321</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M14" t="n">
-        <v>9809458.18526447</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N14" t="n">
-        <v>9713403.98470946</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O14" t="n">
-        <v>96054.2005550125</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P14" t="n">
-        <v>0.957829308304356</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.07155416292954402</v>
-      </c>
+        <v>0.319061166570896</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002602951802888973</v>
-      </c>
-      <c r="T14" t="n">
-        <v>13.97542727157122</v>
-      </c>
+        <v>8.82238133000263e-05</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>4352.662549515813</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.20478987379168</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.376344086021506</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>0.663978494623656</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11.5301045391259</v>
+      </c>
       <c r="K15" t="n">
-        <v>2321.25393509395</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L15" t="n">
-        <v>92.9845715216683</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M15" t="n">
-        <v>4890063.07487998</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N15" t="n">
-        <v>4852363.14787444</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O15" t="n">
-        <v>37699.9270055393</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P15" t="n">
-        <v>0.319061166570896</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>0.923288749508769</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.04997354913195912</v>
+      </c>
       <c r="R15" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>8.82238133000263e-05</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+        <v>0.0002723640979209027</v>
+      </c>
+      <c r="T15" t="n">
+        <v>20.01058594736629</v>
+      </c>
       <c r="U15" t="n">
-        <v>2106.647187948466</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.489161690344303</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.586021505376344</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="J16" t="n">
-        <v>5.23102713863476</v>
+        <v>2.67388407176395</v>
       </c>
       <c r="K16" t="n">
-        <v>3369.69557528728</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L16" t="n">
-        <v>111.53421852938</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M16" t="n">
-        <v>15908435.1191376</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N16" t="n">
-        <v>15798476.017074</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O16" t="n">
-        <v>109959.102063647</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P16" t="n">
-        <v>0.949845583680754</v>
+        <v>0.918420370906708</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.09351159483220896</v>
+        <v>0.1396829633215486</v>
       </c>
       <c r="R16" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0001451649501906712</v>
+        <v>8.775908185029112e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>10.69386103182535</v>
+        <v>7.159069196563442</v>
       </c>
       <c r="U16" t="n">
-        <v>4721.030361260851</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.373496050722277</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.338709677419355</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J17" t="n">
-        <v>2.67388407176395</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K17" t="n">
-        <v>4255.92477550559</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L17" t="n">
-        <v>114.307695231889</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M17" t="n">
-        <v>16053233.8058097</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N17" t="n">
-        <v>15314914.0867177</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O17" t="n">
-        <v>738319.719091995</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P17" t="n">
-        <v>0.918420370906708</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R17" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T17" t="n">
-        <v>7.159069196563442</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U17" t="n">
-        <v>3771.973108688846</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.616528649505811</v>
+        <v>0.465968752688172</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01010368064401798</v>
+        <v>0.01302767878143769</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.658602150537634</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J18" t="n">
-        <v>11.4227202144224</v>
+        <v>9.479356533441949</v>
       </c>
       <c r="K18" t="n">
-        <v>3661.21221302161</v>
+        <v>2146.05576560009</v>
       </c>
       <c r="L18" t="n">
-        <v>146.351117627892</v>
+        <v>169.916321277289</v>
       </c>
       <c r="M18" t="n">
-        <v>14517552.0207549</v>
+        <v>15914547.7950299</v>
       </c>
       <c r="N18" t="n">
-        <v>14238131.763253</v>
+        <v>15798913.4163495</v>
       </c>
       <c r="O18" t="n">
-        <v>279420.257501901</v>
+        <v>115634.378680352</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9532457550498</v>
+        <v>0.9420679200051389</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.05397389045101341</v>
+        <v>0.04915615854771305</v>
       </c>
       <c r="R18" t="n">
-        <v>4.246781059398966e-05</v>
+        <v>2.927942148841287e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001683946774002996</v>
+        <v>0.0002171279796906282</v>
       </c>
       <c r="T18" t="n">
-        <v>18.5274767418813</v>
+        <v>20.34333091812611</v>
       </c>
       <c r="U18" t="n">
-        <v>3965.2309606969</v>
+        <v>7415.719595981607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.465968752688172</v>
+        <v>0.5466356905615291</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.02206122126132733</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.629032258064516</v>
+        <v>0.591397849462366</v>
       </c>
       <c r="J19" t="n">
-        <v>9.479356533441949</v>
+        <v>7.03615822479963</v>
       </c>
       <c r="K19" t="n">
-        <v>2146.05576560009</v>
+        <v>1486.68747959053</v>
       </c>
       <c r="L19" t="n">
-        <v>169.916321277289</v>
+        <v>39.3501020962311</v>
       </c>
       <c r="M19" t="n">
-        <v>15914547.7950299</v>
+        <v>3228511.32437048</v>
       </c>
       <c r="N19" t="n">
-        <v>15798913.4163495</v>
+        <v>3187374.52012585</v>
       </c>
       <c r="O19" t="n">
-        <v>115634.378680352</v>
+        <v>41136.8042446321</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.928466255516988</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.07768951082351416</v>
       </c>
       <c r="R19" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>0.0001693150915826867</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0003676870210221221</v>
       </c>
       <c r="T19" t="n">
-        <v>20.34333091812611</v>
+        <v>12.87175050273751</v>
       </c>
       <c r="U19" t="n">
-        <v>7415.719595981607</v>
+        <v>2171.613986592321</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5466356905615291</v>
+        <v>0.532462665363311</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02206122126132733</v>
+        <v>0.01534920015815749</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.591397849462366</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J20" t="n">
-        <v>7.03615822479963</v>
+        <v>5.86148606882067</v>
       </c>
       <c r="K20" t="n">
-        <v>1486.68747959053</v>
+        <v>2081.39574652818</v>
       </c>
       <c r="L20" t="n">
-        <v>39.3501020962311</v>
+        <v>166.081847507331</v>
       </c>
       <c r="M20" t="n">
-        <v>3228511.32437048</v>
+        <v>13865930.859975</v>
       </c>
       <c r="N20" t="n">
-        <v>3187374.52012585</v>
+        <v>13756695.0153003</v>
       </c>
       <c r="O20" t="n">
-        <v>41136.8042446321</v>
+        <v>109235.844674704</v>
       </c>
       <c r="P20" t="n">
-        <v>0.928466255516987</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.07768951082351416</v>
+        <v>0.09084089923810779</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0001693150915826867</v>
+        <v>3.840078756632939e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0003676870210221221</v>
+        <v>0.0002558200026359581</v>
       </c>
       <c r="T20" t="n">
-        <v>12.87175050273751</v>
+        <v>11.00825738612349</v>
       </c>
       <c r="U20" t="n">
-        <v>2171.613986592321</v>
+        <v>6661.842603985196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.532462665363311</v>
+        <v>0.593374426631911</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01534920015815749</v>
+        <v>0.007440989482023622</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.551075268817204</v>
+        <v>0.64247311827957</v>
       </c>
       <c r="J21" t="n">
-        <v>5.86148606882067</v>
+        <v>13.3015082635468</v>
       </c>
       <c r="K21" t="n">
-        <v>2081.39574652818</v>
+        <v>4784.64130125774</v>
       </c>
       <c r="L21" t="n">
-        <v>166.081847507331</v>
+        <v>232.941984902791</v>
       </c>
       <c r="M21" t="n">
-        <v>13865930.859975</v>
+        <v>24129277.9119089</v>
       </c>
       <c r="N21" t="n">
-        <v>13756695.0153003</v>
+        <v>23634722.0822716</v>
       </c>
       <c r="O21" t="n">
-        <v>109235.844674704</v>
+        <v>494555.829637233</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>0.952959879951284</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.09084089923810779</v>
+        <v>0.04460955967362529</v>
       </c>
       <c r="R21" t="n">
-        <v>3.840078756632939e-05</v>
+        <v>2.459147052797024e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0002558200026359581</v>
+        <v>0.0001240164913670604</v>
       </c>
       <c r="T21" t="n">
-        <v>11.00825738612349</v>
+        <v>22.41671980885376</v>
       </c>
       <c r="U21" t="n">
-        <v>6661.842603985196</v>
+        <v>5043.069353091532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Muse Wonder (max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.593374426631911</v>
+        <v>0.519768236993592</v>
       </c>
       <c r="F22" t="n">
-        <v>0.007440989482023622</v>
+        <v>0.02117889017131678</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.64247311827957</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J22" t="n">
-        <v>13.3015082635468</v>
+        <v>8.04811220428196</v>
       </c>
       <c r="K22" t="n">
-        <v>4784.64130125774</v>
+        <v>1472.5084254817</v>
       </c>
       <c r="L22" t="n">
-        <v>232.941984902791</v>
+        <v>200.877049903502</v>
       </c>
       <c r="M22" t="n">
-        <v>24129277.9119089</v>
+        <v>14479705.3019539</v>
       </c>
       <c r="N22" t="n">
-        <v>23634722.0822716</v>
+        <v>14384183.420164</v>
       </c>
       <c r="O22" t="n">
-        <v>494555.829637233</v>
+        <v>95521.8817899424</v>
       </c>
       <c r="P22" t="n">
-        <v>0.952959879951284</v>
+        <v>0.939000029822895</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.04460955967362529</v>
+        <v>0.06458262804997322</v>
       </c>
       <c r="R22" t="n">
-        <v>2.459147052797024e-05</v>
+        <v>3.589632704219845e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0001240164913670604</v>
+        <v>0.0003529815028552796</v>
       </c>
       <c r="T22" t="n">
-        <v>22.41671980885376</v>
+        <v>15.48404006145759</v>
       </c>
       <c r="U22" t="n">
-        <v>5043.069353091532</v>
+        <v>9833.35989892022</v>
       </c>
     </row>
     <row r="23">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>Muse Wonder Full (max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1900,175 +1900,175 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.519768236993592</v>
+        <v>0.588804489084392</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02117889017131678</v>
+        <v>0.01685280599548879</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.615591397849462</v>
-      </c>
-      <c r="J23" t="n">
-        <v>8.04811220428196</v>
-      </c>
+        <v>0.688172043010753</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>1472.5084254817</v>
+        <v>2096.2841057163</v>
       </c>
       <c r="L23" t="n">
-        <v>200.877049903502</v>
+        <v>194.874971760617</v>
       </c>
       <c r="M23" t="n">
-        <v>14479705.3019539</v>
+        <v>14497965.3172412</v>
       </c>
       <c r="N23" t="n">
-        <v>14384183.420164</v>
+        <v>14414434.4559639</v>
       </c>
       <c r="O23" t="n">
-        <v>95521.8817899424</v>
+        <v>83530.861277289</v>
       </c>
       <c r="P23" t="n">
-        <v>0.939000029822895</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.06458262804997322</v>
-      </c>
+        <v>0.962325196630197</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>3.589632704219845e-05</v>
+        <v>4.061290506635278e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0003529815028552796</v>
-      </c>
-      <c r="T23" t="n">
-        <v>15.48404006145759</v>
-      </c>
+        <v>0.0002808800999248132</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>9833.35989892022</v>
+        <v>6916.030741113332</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>GPT-6.1 Sol (max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.588804489084392</v>
+        <v>0.541279798631476</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01685280599548879</v>
+        <v>0.02284798697058158</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.688172043010753</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>0.599462365591398</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.5046389983744</v>
+      </c>
       <c r="K24" t="n">
-        <v>2096.2841057163</v>
+        <v>1421.42885321603</v>
       </c>
       <c r="L24" t="n">
-        <v>194.874971760617</v>
+        <v>40.6271304442272</v>
       </c>
       <c r="M24" t="n">
-        <v>14497965.3172412</v>
+        <v>3944222.64509301</v>
       </c>
       <c r="N24" t="n">
-        <v>14414434.4559639</v>
+        <v>3888998.33558647</v>
       </c>
       <c r="O24" t="n">
-        <v>83530.861277289</v>
+        <v>55224.3095065408</v>
       </c>
       <c r="P24" t="n">
-        <v>0.962325196630197</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>0.921352278288341</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3597406415866333</v>
+      </c>
       <c r="R24" t="n">
-        <v>4.061290506635278e-05</v>
+        <v>0.0001372335811987895</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0002808800999248132</v>
-      </c>
-      <c r="T24" t="inlineStr"/>
+        <v>0.0003807997828430263</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.779780442903275</v>
+      </c>
       <c r="U24" t="n">
-        <v>6916.030741113332</v>
+        <v>2774.82945148403</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Opus 5.5 (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.541279798631476</v>
+        <v>0.616528649505811</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02284798697058158</v>
+        <v>0.01010368064401798</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.599462365591398</v>
+        <v>0.658602150537634</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5046389983744</v>
+        <v>11.4227202144224</v>
       </c>
       <c r="K25" t="n">
-        <v>1421.42885321603</v>
+        <v>3661.21221302161</v>
       </c>
       <c r="L25" t="n">
-        <v>40.6271304442272</v>
+        <v>146.351117627892</v>
       </c>
       <c r="M25" t="n">
-        <v>3944222.64509301</v>
+        <v>14517552.0207549</v>
       </c>
       <c r="N25" t="n">
-        <v>3888998.33558647</v>
+        <v>14238131.763253</v>
       </c>
       <c r="O25" t="n">
-        <v>55224.3095065408</v>
+        <v>279420.257501901</v>
       </c>
       <c r="P25" t="n">
-        <v>0.921352278288341</v>
+        <v>0.9532457550498</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3597406415866333</v>
+        <v>0.05397389045101341</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0001372335811987895</v>
+        <v>4.246781059398966e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0003807997828430263</v>
+        <v>0.0001683946774002996</v>
       </c>
       <c r="T25" t="n">
-        <v>2.779780442903275</v>
+        <v>18.5274767418813</v>
       </c>
       <c r="U25" t="n">
-        <v>2774.82945148403</v>
+        <v>3965.2309606969</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,90 +526,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.41417319257087</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006586839388819422</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.599462365591398</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J2" t="n">
-        <v>5.16526976917945</v>
+        <v>11.5301045391259</v>
       </c>
       <c r="K2" t="n">
-        <v>3772.73379345389</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L2" t="n">
-        <v>185.884007277072</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M2" t="n">
-        <v>9010345.58218855</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N2" t="n">
-        <v>8910048.672052789</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O2" t="n">
-        <v>100296.910135766</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9600647788144701</v>
+        <v>0.923288749508769</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08018423259172099</v>
+        <v>0.04997354913195912</v>
       </c>
       <c r="R2" t="n">
-        <v>4.596640481688052e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001097806564803237</v>
+        <v>0.0002723640979209027</v>
       </c>
       <c r="T2" t="n">
-        <v>12.47127979751034</v>
+        <v>20.01058594736629</v>
       </c>
       <c r="U2" t="n">
-        <v>2388.280243313879</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.457077885630498</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -617,625 +617,625 @@
         <v>0.586021505376344</v>
       </c>
       <c r="J3" t="n">
-        <v>3.91029139020419</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K3" t="n">
-        <v>1398.49826969262</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L3" t="n">
-        <v>208.319377647442</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M3" t="n">
-        <v>17824340.6533789</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N3" t="n">
-        <v>17642872.3721332</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O3" t="n">
-        <v>181468.281245791</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P3" t="n">
-        <v>0.966617846464586</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1168910037690644</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R3" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000326834788098065</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T3" t="n">
-        <v>8.554978293929695</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U3" t="n">
-        <v>12745.34337271405</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.311260251113284</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.381720430107527</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J4" t="n">
-        <v>0.159155559086193</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K4" t="n">
-        <v>1275.79489619203</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L4" t="n">
-        <v>81.3609199522103</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M4" t="n">
-        <v>8885939.032378631</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N4" t="n">
-        <v>8794707.77057673</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O4" t="n">
-        <v>91231.26180188989</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P4" t="n">
-        <v>0.954514555274975</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95569826715708</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R4" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5113263210350233</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U4" t="n">
-        <v>6965.021618209341</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.431274491691105</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.586021505376344</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J5" t="n">
-        <v>1.84006320525524</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K5" t="n">
-        <v>3665.13740781145</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L5" t="n">
-        <v>142.091813837298</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M5" t="n">
-        <v>22141655.7546106</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N5" t="n">
-        <v>21997509.2781069</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O5" t="n">
-        <v>144146.476503747</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P5" t="n">
-        <v>0.984007673153142</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2343802595798777</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R5" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T5" t="n">
-        <v>4.266570921085596</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U5" t="n">
-        <v>6041.152974898141</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.473001334419464</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.610215053763441</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38619359563592</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K6" t="n">
-        <v>2283.94687962311</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L6" t="n">
-        <v>142.882443792766</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M6" t="n">
-        <v>27235627.5942381</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N6" t="n">
-        <v>27078637.1644444</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O6" t="n">
-        <v>156990.429793635</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.22477777923946</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R6" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8164746429519335</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U6" t="n">
-        <v>11924.80781283864</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>DeepSeek V4.1 Flash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.33272301118714</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.443548387096774</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J7" t="n">
-        <v>2.51071545979138</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K7" t="n">
-        <v>786.045572632779</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L7" t="n">
-        <v>202.504982078853</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M7" t="n">
-        <v>14251510.9748887</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N7" t="n">
-        <v>14138882.8572119</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O7" t="n">
-        <v>112628.117676768</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1325211942634019</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T7" t="n">
-        <v>7.545962783978378</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U7" t="n">
-        <v>18130.64212950749</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.463051957532312</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.615591397849462</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J8" t="n">
-        <v>0.29627468390668</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K8" t="n">
-        <v>1284.94041000543</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L8" t="n">
-        <v>101.530045617465</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M8" t="n">
-        <v>16739365.2564321</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N8" t="n">
-        <v>16633748.9354947</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O8" t="n">
-        <v>105616.32093733</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P8" t="n">
-        <v>0.967966386781858</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56291435848148</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R8" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6398303237623303</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U8" t="n">
-        <v>13027.34751439669</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>DeepSeek V4.1 Flash 1017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.530769734767025</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.602150537634409</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33822148437056</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K9" t="n">
-        <v>1270.3477207201</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L9" t="n">
-        <v>58.8586738351254</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M9" t="n">
-        <v>3625399.81721408</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N9" t="n">
-        <v>3585782.97351906</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O9" t="n">
-        <v>39616.8436950147</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P9" t="n">
-        <v>0.91270190622461</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1223473113761584</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001464030897356012</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T9" t="n">
-        <v>8.173453006461965</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U9" t="n">
-        <v>2853.864149226019</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.263007023894863</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.508064516129032</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J10" t="n">
-        <v>3.54324946048794</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K10" t="n">
-        <v>1558.86632482568</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L10" t="n">
-        <v>161.39889866406</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M10" t="n">
-        <v>13336678.8257109</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N10" t="n">
-        <v>13239522.4765722</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O10" t="n">
-        <v>97156.3491386988</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P10" t="n">
-        <v>0.951550733530632</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07422763393538889</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R10" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001687168551314198</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T10" t="n">
-        <v>13.47207161244619</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U10" t="n">
-        <v>8555.370408172921</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark Open (xhigh)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.392199207885305</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.561827956989248</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J11" t="n">
-        <v>3.79584401482699</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K11" t="n">
-        <v>4568.4135207125</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L11" t="n">
-        <v>114.796515026192</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M11" t="n">
-        <v>9153421.029330021</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N11" t="n">
-        <v>9032702.304066719</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O11" t="n">
-        <v>120718.725263303</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P11" t="n">
-        <v>0.947205701820927</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R11" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T11" t="n">
-        <v>9.678357167761158</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U11" t="n">
-        <v>2003.632330530016</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.615117219506897</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.682795698924731</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J12" t="n">
-        <v>7.99768820548534</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K12" t="n">
-        <v>3067.08119502552</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L12" t="n">
-        <v>99.46435538177469</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M12" t="n">
-        <v>10463266.3479852</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N12" t="n">
-        <v>10202564.6581949</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O12" t="n">
-        <v>260701.689790377</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P12" t="n">
-        <v>0.870466942043008</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07691187799556992</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R12" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002005545925893816</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>13.00189289432771</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U12" t="n">
-        <v>3411.473541996706</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.586619030954708</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1267,164 +1267,164 @@
         <v>0.682795698924731</v>
       </c>
       <c r="J13" t="n">
-        <v>8.19825160322711</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K13" t="n">
-        <v>2253.66843252199</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L13" t="n">
-        <v>92.38415770609321</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M13" t="n">
-        <v>9809458.18526447</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N13" t="n">
-        <v>9713403.98470946</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O13" t="n">
-        <v>96054.2005550125</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P13" t="n">
-        <v>0.957829308304356</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07155416292954402</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R13" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T13" t="n">
-        <v>13.97542727157122</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U13" t="n">
-        <v>4352.662549515813</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.20478987379168</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.376344086021506</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>0.682795698924731</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.19825160322711</v>
+      </c>
       <c r="K14" t="n">
-        <v>2321.25393509395</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L14" t="n">
-        <v>92.9845715216683</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M14" t="n">
-        <v>4890063.07487998</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N14" t="n">
-        <v>4852363.14787444</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O14" t="n">
-        <v>37699.9270055393</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P14" t="n">
-        <v>0.319061166570896</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>0.957829308304356</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.07155416292954402</v>
+      </c>
       <c r="R14" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>8.82238133000263e-05</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
+        <v>0.0002602951802888973</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13.97542727157122</v>
+      </c>
       <c r="U14" t="n">
-        <v>2106.647187948466</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.663978494623656</v>
-      </c>
-      <c r="J15" t="n">
-        <v>11.5301045391259</v>
-      </c>
+        <v>0.376344086021506</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>2115.55138904529</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L15" t="n">
-        <v>42.2762050613663</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M15" t="n">
-        <v>5989151.58443575</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N15" t="n">
-        <v>5863350.62589986</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O15" t="n">
-        <v>125800.958535897</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P15" t="n">
-        <v>0.923288749508769</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.04997354913195912</v>
-      </c>
+        <v>0.319061166570896</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002723640979209027</v>
-      </c>
-      <c r="T15" t="n">
-        <v>20.01058594736629</v>
-      </c>
+        <v>8.82238133000263e-05</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>2831.01210183249</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="16">
@@ -1495,131 +1495,131 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.489161690344303</v>
+        <v>0.41417319257087</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.006586839388819422</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.586021505376344</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J17" t="n">
-        <v>5.23102713863476</v>
+        <v>5.16526976917945</v>
       </c>
       <c r="K17" t="n">
-        <v>3369.69557528728</v>
+        <v>3772.73379345389</v>
       </c>
       <c r="L17" t="n">
-        <v>111.53421852938</v>
+        <v>185.884007277072</v>
       </c>
       <c r="M17" t="n">
-        <v>15908435.1191376</v>
+        <v>9010345.58218855</v>
       </c>
       <c r="N17" t="n">
-        <v>15798476.017074</v>
+        <v>8910048.672052789</v>
       </c>
       <c r="O17" t="n">
-        <v>109959.102063647</v>
+        <v>100296.910135766</v>
       </c>
       <c r="P17" t="n">
-        <v>0.949845583680754</v>
+        <v>0.9600647788144701</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.09351159483220896</v>
+        <v>0.08018423259172099</v>
       </c>
       <c r="R17" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>4.596640481688052e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001451649501906712</v>
+        <v>0.0001097806564803237</v>
       </c>
       <c r="T17" t="n">
-        <v>10.69386103182535</v>
+        <v>12.47127979751034</v>
       </c>
       <c r="U17" t="n">
-        <v>4721.030361260851</v>
+        <v>2388.280243313879</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Opus 5.5 (max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.465968752688172</v>
+        <v>0.616528649505811</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.01010368064401798</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.629032258064516</v>
+        <v>0.658602150537634</v>
       </c>
       <c r="J18" t="n">
-        <v>9.479356533441949</v>
+        <v>11.4227202144224</v>
       </c>
       <c r="K18" t="n">
-        <v>2146.05576560009</v>
+        <v>3661.21221302161</v>
       </c>
       <c r="L18" t="n">
-        <v>169.916321277289</v>
+        <v>146.351117627892</v>
       </c>
       <c r="M18" t="n">
-        <v>15914547.7950299</v>
+        <v>14517552.0207549</v>
       </c>
       <c r="N18" t="n">
-        <v>15798913.4163495</v>
+        <v>14238131.763253</v>
       </c>
       <c r="O18" t="n">
-        <v>115634.378680352</v>
+        <v>279420.257501901</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.9532457550498</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.05397389045101341</v>
       </c>
       <c r="R18" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>4.246781059398966e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0001683946774002996</v>
       </c>
       <c r="T18" t="n">
-        <v>20.34333091812611</v>
+        <v>18.5274767418813</v>
       </c>
       <c r="U18" t="n">
-        <v>7415.719595981607</v>
+        <v>3965.2309606969</v>
       </c>
     </row>
     <row r="19">
@@ -2009,66 +2009,66 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Grok 4.7 (xhigh)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.616528649505811</v>
+        <v>0.465968752688172</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01010368064401798</v>
+        <v>0.01302767878143769</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.658602150537634</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J25" t="n">
-        <v>11.4227202144224</v>
+        <v>9.479356533441949</v>
       </c>
       <c r="K25" t="n">
-        <v>3661.21221302161</v>
+        <v>2146.05576560009</v>
       </c>
       <c r="L25" t="n">
-        <v>146.351117627892</v>
+        <v>169.916321277289</v>
       </c>
       <c r="M25" t="n">
-        <v>14517552.0207549</v>
+        <v>15914547.7950299</v>
       </c>
       <c r="N25" t="n">
-        <v>14238131.763253</v>
+        <v>15798913.4163495</v>
       </c>
       <c r="O25" t="n">
-        <v>279420.257501901</v>
+        <v>115634.378680352</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9532457550498</v>
+        <v>0.9420679200051389</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.05397389045101341</v>
+        <v>0.04915615854771305</v>
       </c>
       <c r="R25" t="n">
-        <v>4.246781059398966e-05</v>
+        <v>2.927942148841287e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0001683946774002996</v>
+        <v>0.0002171279796906282</v>
       </c>
       <c r="T25" t="n">
-        <v>18.5274767418813</v>
+        <v>20.34333091812611</v>
       </c>
       <c r="U25" t="n">
-        <v>3965.2309606969</v>
+        <v>7415.719595981607</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,155 +526,155 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Muse Spark 1.3 (max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.663978494623656</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J2" t="n">
-        <v>11.5301045391259</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K2" t="n">
-        <v>2115.55138904529</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L2" t="n">
-        <v>42.2762050613663</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M2" t="n">
-        <v>5989151.58443575</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N2" t="n">
-        <v>5863350.62589986</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O2" t="n">
-        <v>125800.958535897</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P2" t="n">
-        <v>0.923288749508769</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04997354913195912</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R2" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002723640979209027</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T2" t="n">
-        <v>20.01058594736629</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U2" t="n">
-        <v>2831.01210183249</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GPT-6 Luna (max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.489161690344303</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.586021505376344</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J3" t="n">
-        <v>5.23102713863476</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K3" t="n">
-        <v>3369.69557528728</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L3" t="n">
-        <v>111.53421852938</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M3" t="n">
-        <v>15908435.1191376</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N3" t="n">
-        <v>15798476.017074</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O3" t="n">
-        <v>109959.102063647</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P3" t="n">
-        <v>0.949845583680754</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09351159483220896</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R3" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001451649501906712</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T3" t="n">
-        <v>10.69386103182535</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U3" t="n">
-        <v>4721.030361260851</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.457077885630498</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -682,40 +682,40 @@
         <v>0.586021505376344</v>
       </c>
       <c r="J4" t="n">
-        <v>3.91029139020419</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K4" t="n">
-        <v>1398.49826969262</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L4" t="n">
-        <v>208.319377647442</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M4" t="n">
-        <v>17824340.6533789</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N4" t="n">
-        <v>17642872.3721332</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O4" t="n">
-        <v>181468.281245791</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P4" t="n">
-        <v>0.966617846464586</v>
+        <v>0.984007673153141</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1168910037690644</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R4" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000326834788098065</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T4" t="n">
-        <v>8.554978293929695</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U4" t="n">
-        <v>12745.34337271405</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="5">
@@ -726,137 +726,137 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>DeepSeek V4.1 Flash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.311260251113284</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.381720430107527</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J5" t="n">
-        <v>0.159155559086193</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K5" t="n">
-        <v>1275.79489619203</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L5" t="n">
-        <v>81.3609199522103</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M5" t="n">
-        <v>8885939.032378631</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N5" t="n">
-        <v>8794707.77057673</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O5" t="n">
-        <v>91231.26180188989</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.954514555274975</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95569826715708</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R5" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5113263210350233</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U5" t="n">
-        <v>6965.021618209341</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Gemini 3.8 Flash (high)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.431274491691105</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.586021505376344</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J6" t="n">
-        <v>1.84006320525524</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K6" t="n">
-        <v>3665.13740781145</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L6" t="n">
-        <v>142.091813837298</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M6" t="n">
-        <v>22141655.7546106</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N6" t="n">
-        <v>21997509.2781069</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O6" t="n">
-        <v>144146.476503747</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P6" t="n">
-        <v>0.984007673153142</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2343802595798777</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R6" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T6" t="n">
-        <v>4.266570921085596</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U6" t="n">
-        <v>6041.152974898141</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash</t>
+          <t>DeepSeek V4.1 Flash 1017</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -866,246 +866,246 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.473001334419464</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.610215053763441</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J7" t="n">
-        <v>0.38619359563592</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K7" t="n">
-        <v>2283.94687962311</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L7" t="n">
-        <v>142.882443792766</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M7" t="n">
-        <v>27235627.5942381</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N7" t="n">
-        <v>27078637.1644444</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O7" t="n">
-        <v>156990.429793635</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.22477777923946</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R7" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8164746429519335</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U7" t="n">
-        <v>11924.80781283864</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>GPT-6.1 Terra (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.33272301118714</v>
+        <v>0.481004244053438</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.01839650049939798</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.443548387096774</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J8" t="n">
-        <v>2.51071545979138</v>
+        <v>1.24038465572461</v>
       </c>
       <c r="K8" t="n">
-        <v>786.045572632779</v>
+        <v>1568.79046882589</v>
       </c>
       <c r="L8" t="n">
-        <v>202.504982078853</v>
+        <v>100.428485934615</v>
       </c>
       <c r="M8" t="n">
-        <v>14251510.9748887</v>
+        <v>12280717.4101086</v>
       </c>
       <c r="N8" t="n">
-        <v>14138882.8572119</v>
+        <v>12207751.9070045</v>
       </c>
       <c r="O8" t="n">
-        <v>112628.117676768</v>
+        <v>72965.5031041599</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.967020333857851</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1325211942634019</v>
+        <v>0.3877863546872434</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>3.916743851279486e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.000306608341656633</v>
       </c>
       <c r="T8" t="n">
-        <v>7.545962783978378</v>
+        <v>2.578739524773938</v>
       </c>
       <c r="U8" t="n">
-        <v>18130.64212950749</v>
+        <v>7828.143817892839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.463051957532312</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.615591397849462</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J9" t="n">
-        <v>0.29627468390668</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K9" t="n">
-        <v>1284.94041000543</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L9" t="n">
-        <v>101.530045617465</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M9" t="n">
-        <v>16739365.2564321</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N9" t="n">
-        <v>16633748.9354947</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O9" t="n">
-        <v>105616.32093733</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.967966386781858</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56291435848148</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R9" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6398303237623303</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U9" t="n">
-        <v>13027.34751439669</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>GPT-6.1 Terra (low)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.530769734767025</v>
+        <v>0.3485683422396</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.05511407534171487</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.602150537634409</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="J10" t="n">
-        <v>4.33822148437056</v>
+        <v>0.198820047696481</v>
       </c>
       <c r="K10" t="n">
-        <v>1270.3477207201</v>
+        <v>379.469317133703</v>
       </c>
       <c r="L10" t="n">
-        <v>58.8586738351254</v>
+        <v>42.7471271858369</v>
       </c>
       <c r="M10" t="n">
-        <v>3625399.81721408</v>
+        <v>1886086.8732888</v>
       </c>
       <c r="N10" t="n">
-        <v>3585782.97351906</v>
+        <v>1877408.29673401</v>
       </c>
       <c r="O10" t="n">
-        <v>39616.8436950147</v>
+        <v>8678.576554795271</v>
       </c>
       <c r="P10" t="n">
-        <v>0.91270190622461</v>
+        <v>0.925808219461337</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1223473113761584</v>
+        <v>1.753185085096272</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001464030897356012</v>
+        <v>0.0001848103325335146</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0009185679223619145</v>
       </c>
       <c r="T10" t="n">
-        <v>8.173453006461965</v>
+        <v>0.5703904331042647</v>
       </c>
       <c r="U10" t="n">
-        <v>2853.864149226019</v>
+        <v>4970.327739631851</v>
       </c>
     </row>
     <row r="11">
@@ -1306,255 +1306,261 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GPT-6.1 Terra (none)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.586619030954708</v>
+        <v>0.392151614641034</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.04110338068613622</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.682795698924731</v>
+        <v>0.462365591397849</v>
       </c>
       <c r="J14" t="n">
-        <v>8.19825160322711</v>
+        <v>0.454255643441512</v>
       </c>
       <c r="K14" t="n">
-        <v>2253.66843252199</v>
+        <v>572.437023079179</v>
       </c>
       <c r="L14" t="n">
-        <v>92.38415770609321</v>
+        <v>81.50919734984249</v>
       </c>
       <c r="M14" t="n">
-        <v>9809458.18526447</v>
+        <v>5776354.240164</v>
       </c>
       <c r="N14" t="n">
-        <v>9713403.98470946</v>
+        <v>5762448.0127566</v>
       </c>
       <c r="O14" t="n">
-        <v>96054.2005550125</v>
+        <v>13906.2274074074</v>
       </c>
       <c r="P14" t="n">
-        <v>0.957829308304356</v>
+        <v>0.947531776215516</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07155416292954402</v>
+        <v>0.8632839686261944</v>
       </c>
       <c r="R14" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>6.788912146598201e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.000685056344768937</v>
       </c>
       <c r="T14" t="n">
-        <v>13.97542727157122</v>
+        <v>1.158367392819041</v>
       </c>
       <c r="U14" t="n">
-        <v>4352.662549515813</v>
+        <v>10090.81175269305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.20478987379168</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.376344086021506</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>0.682795698924731</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.19825160322711</v>
+      </c>
       <c r="K15" t="n">
-        <v>2321.25393509395</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L15" t="n">
-        <v>92.9845715216683</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M15" t="n">
-        <v>4890063.07487998</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N15" t="n">
-        <v>4852363.14787444</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O15" t="n">
-        <v>37699.9270055393</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P15" t="n">
-        <v>0.319061166570896</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>0.957829308304356</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.07155416292954402</v>
+      </c>
       <c r="R15" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>8.82238133000263e-05</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+        <v>0.0002602951802888973</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13.97542727157122</v>
+      </c>
       <c r="U15" t="n">
-        <v>2106.647187948466</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.373496050722277</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.338709677419355</v>
+        <v>0.376344086021506</v>
       </c>
       <c r="J16" t="n">
-        <v>2.67388407176395</v>
+        <v>0.319490234063365</v>
       </c>
       <c r="K16" t="n">
-        <v>4255.92477550559</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L16" t="n">
-        <v>114.307695231889</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M16" t="n">
-        <v>16053233.8058097</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N16" t="n">
-        <v>15314914.0867177</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O16" t="n">
-        <v>738319.719091995</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P16" t="n">
-        <v>0.918420370906708</v>
+        <v>0.95239449990423</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.6409894637063107</v>
       </c>
       <c r="R16" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>8.82238133000263e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>7.159069196563442</v>
+        <v>1.560088046093346</v>
       </c>
       <c r="U16" t="n">
-        <v>3771.973108688846</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>GPT-6.1 Terra (xhigh)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.41417319257087</v>
+        <v>0.482238344954925</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006586839388819422</v>
+        <v>0.02947324998862232</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.599462365591398</v>
+        <v>0.5376344086021499</v>
       </c>
       <c r="J17" t="n">
-        <v>5.16526976917945</v>
+        <v>0.690844449567775</v>
       </c>
       <c r="K17" t="n">
-        <v>3772.73379345389</v>
+        <v>981.713951073096</v>
       </c>
       <c r="L17" t="n">
-        <v>185.884007277072</v>
+        <v>71.9594569349408</v>
       </c>
       <c r="M17" t="n">
-        <v>9010345.58218855</v>
+        <v>6886239.03807863</v>
       </c>
       <c r="N17" t="n">
-        <v>8910048.672052789</v>
+        <v>6849711.54192788</v>
       </c>
       <c r="O17" t="n">
-        <v>100296.910135766</v>
+        <v>36527.4961507549</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9600647788144701</v>
+        <v>0.956934601768947</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.08018423259172099</v>
+        <v>0.6980418605905224</v>
       </c>
       <c r="R17" t="n">
-        <v>4.596640481688052e-05</v>
+        <v>7.002927756186012e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001097806564803237</v>
+        <v>0.0004912208331437053</v>
       </c>
       <c r="T17" t="n">
-        <v>12.47127979751034</v>
+        <v>1.432578841552611</v>
       </c>
       <c r="U17" t="n">
-        <v>2388.280243313879</v>
+        <v>7014.506649876363</v>
       </c>
     </row>
     <row r="18">
@@ -1565,7 +1571,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Haiku 5.5 (max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1575,500 +1581,890 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.616528649505811</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01010368064401798</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.658602150537634</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="J18" t="n">
-        <v>11.4227202144224</v>
+        <v>2.67388407176395</v>
       </c>
       <c r="K18" t="n">
-        <v>3661.21221302161</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L18" t="n">
-        <v>146.351117627892</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M18" t="n">
-        <v>14517552.0207549</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N18" t="n">
-        <v>14238131.763253</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O18" t="n">
-        <v>279420.257501901</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9532457550498</v>
+        <v>0.918420370906708</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.05397389045101341</v>
+        <v>0.1396829633215486</v>
       </c>
       <c r="R18" t="n">
-        <v>4.246781059398966e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001683946774002996</v>
+        <v>8.775908185029112e-05</v>
       </c>
       <c r="T18" t="n">
-        <v>18.5274767418813</v>
+        <v>7.159069196563442</v>
       </c>
       <c r="U18" t="n">
-        <v>3965.2309606969</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Kimi K3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5466356905615291</v>
+        <v>0.41417319257087</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02206122126132733</v>
+        <v>0.006586839388819422</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.591397849462366</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J19" t="n">
-        <v>7.03615822479963</v>
+        <v>5.16526976917945</v>
       </c>
       <c r="K19" t="n">
-        <v>1486.68747959053</v>
+        <v>3772.73379345389</v>
       </c>
       <c r="L19" t="n">
-        <v>39.3501020962311</v>
+        <v>185.884007277072</v>
       </c>
       <c r="M19" t="n">
-        <v>3228511.32437048</v>
+        <v>9010345.58218855</v>
       </c>
       <c r="N19" t="n">
-        <v>3187374.52012585</v>
+        <v>8910048.672052789</v>
       </c>
       <c r="O19" t="n">
-        <v>41136.8042446321</v>
+        <v>100296.910135766</v>
       </c>
       <c r="P19" t="n">
-        <v>0.928466255516988</v>
+        <v>0.9600647788144701</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.07768951082351416</v>
+        <v>0.08018423259172099</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0001693150915826867</v>
+        <v>4.596640481688052e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0003676870210221221</v>
+        <v>0.0001097806564803237</v>
       </c>
       <c r="T19" t="n">
-        <v>12.87175050273751</v>
+        <v>12.47127979751034</v>
       </c>
       <c r="U19" t="n">
-        <v>2171.613986592321</v>
+        <v>2388.280243313879</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Fable 5.1 (max) (with fallback)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.532462665363311</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01534920015815749</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.551075268817204</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J20" t="n">
-        <v>5.86148606882067</v>
+        <v>11.5301045391259</v>
       </c>
       <c r="K20" t="n">
-        <v>2081.39574652818</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L20" t="n">
-        <v>166.081847507331</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M20" t="n">
-        <v>13865930.859975</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N20" t="n">
-        <v>13756695.0153003</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O20" t="n">
-        <v>109235.844674704</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.923288749508769</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09084089923810779</v>
+        <v>0.04997354913195912</v>
       </c>
       <c r="R20" t="n">
-        <v>3.840078756632939e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0002558200026359581</v>
+        <v>0.0002723640979209027</v>
       </c>
       <c r="T20" t="n">
-        <v>11.00825738612349</v>
+        <v>20.01058594736629</v>
       </c>
       <c r="U20" t="n">
-        <v>6661.842603985196</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>GLM-5.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.593374426631911</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F21" t="n">
-        <v>0.007440989482023622</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.64247311827957</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J21" t="n">
-        <v>13.3015082635468</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K21" t="n">
-        <v>4784.64130125774</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L21" t="n">
-        <v>232.941984902791</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M21" t="n">
-        <v>24129277.9119089</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N21" t="n">
-        <v>23634722.0822716</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O21" t="n">
-        <v>494555.829637233</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P21" t="n">
-        <v>0.952959879951284</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.04460955967362529</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R21" t="n">
-        <v>2.459147052797024e-05</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001240164913670604</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T21" t="n">
-        <v>22.41671980885376</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U21" t="n">
-        <v>5043.069353091532</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>GPT-6.1 Terra (high)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.519768236993592</v>
+        <v>0.462787772238514</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02117889017131678</v>
+        <v>0.03657118285941164</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.615591397849462</v>
+        <v>0.529569892473118</v>
       </c>
       <c r="J22" t="n">
-        <v>8.04811220428196</v>
+        <v>0.544031579042956</v>
       </c>
       <c r="K22" t="n">
-        <v>1472.5084254817</v>
+        <v>759.266290102096</v>
       </c>
       <c r="L22" t="n">
-        <v>200.877049903502</v>
+        <v>66.77620831975671</v>
       </c>
       <c r="M22" t="n">
-        <v>14479705.3019539</v>
+        <v>5600133.87243293</v>
       </c>
       <c r="N22" t="n">
-        <v>14384183.420164</v>
+        <v>5573162.88381014</v>
       </c>
       <c r="O22" t="n">
-        <v>95521.8817899424</v>
+        <v>26970.988622787</v>
       </c>
       <c r="P22" t="n">
-        <v>0.939000029822895</v>
+        <v>0.949839928351402</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.06458262804997322</v>
+        <v>0.8506634358480373</v>
       </c>
       <c r="R22" t="n">
-        <v>3.589632704219845e-05</v>
+        <v>8.263869807052661e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0003529815028552796</v>
+        <v>0.0006095197143235273</v>
       </c>
       <c r="T22" t="n">
-        <v>15.48404006145759</v>
+        <v>1.175553054073715</v>
       </c>
       <c r="U22" t="n">
-        <v>9833.35989892022</v>
+        <v>7375.717775748873</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>GPT-6.1 Terra (medium)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.588804489084392</v>
+        <v>0.420492375909634</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01685280599548879</v>
+        <v>0.04130896078448847</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.688172043010753</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>0.470430107526882</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.394994482142174</v>
+      </c>
       <c r="K23" t="n">
-        <v>2096.2841057163</v>
+        <v>610.752293823178</v>
       </c>
       <c r="L23" t="n">
-        <v>194.874971760617</v>
+        <v>57.9985804279353</v>
       </c>
       <c r="M23" t="n">
-        <v>14497965.3172412</v>
+        <v>4075423.19637776</v>
       </c>
       <c r="N23" t="n">
-        <v>14414434.4559639</v>
+        <v>4056826.27165961</v>
       </c>
       <c r="O23" t="n">
-        <v>83530.861277289</v>
+        <v>18596.9247181492</v>
       </c>
       <c r="P23" t="n">
-        <v>0.962325196630197</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>0.9421388881635679</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.064552531542155</v>
+      </c>
       <c r="R23" t="n">
-        <v>4.061290506635278e-05</v>
+        <v>0.0001031775979199824</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0002808800999248132</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
+        <v>0.0006884826797414745</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.9393618166980995</v>
+      </c>
       <c r="U23" t="n">
-        <v>6916.030741113332</v>
+        <v>6672.792288452144</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>Gemini 4 Argon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.541279798631476</v>
+        <v>0.532462665363311</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02284798697058158</v>
+        <v>0.01534920015815749</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.599462365591398</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5046389983744</v>
+        <v>5.86148606882067</v>
       </c>
       <c r="K24" t="n">
-        <v>1421.42885321603</v>
+        <v>2081.39574652818</v>
       </c>
       <c r="L24" t="n">
-        <v>40.6271304442272</v>
+        <v>166.081847507331</v>
       </c>
       <c r="M24" t="n">
-        <v>3944222.64509301</v>
+        <v>13865930.859975</v>
       </c>
       <c r="N24" t="n">
-        <v>3888998.33558647</v>
+        <v>13756695.0153003</v>
       </c>
       <c r="O24" t="n">
-        <v>55224.3095065408</v>
+        <v>109235.844674704</v>
       </c>
       <c r="P24" t="n">
-        <v>0.921352278288341</v>
+        <v>0.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3597406415866333</v>
+        <v>0.09084089923810779</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0001372335811987895</v>
+        <v>3.840078756632939e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0003807997828430263</v>
+        <v>0.0002558200026359581</v>
       </c>
       <c r="T24" t="n">
-        <v>2.779780442903275</v>
+        <v>11.00825738612349</v>
       </c>
       <c r="U24" t="n">
-        <v>2774.82945148403</v>
+        <v>6661.842603985196</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>Sonnet 5.5 (max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.465968752688172</v>
+        <v>0.593374426631911</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.007440989482023622</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
+        <v>0.64247311827957</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13.3015082635468</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4784.64130125774</v>
+      </c>
+      <c r="L25" t="n">
+        <v>232.941984902791</v>
+      </c>
+      <c r="M25" t="n">
+        <v>24129277.9119089</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23634722.0822716</v>
+      </c>
+      <c r="O25" t="n">
+        <v>494555.829637233</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.952959879951284</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.04460955967362529</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.459147052797024e-05</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0001240164913670604</v>
+      </c>
+      <c r="T25" t="n">
+        <v>22.41671980885376</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5043.069353091532</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Muse Code</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Muse Wonder (max)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.519768236993592</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.02117889017131678</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>0.615591397849462</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8.04811220428196</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1472.5084254817</v>
+      </c>
+      <c r="L26" t="n">
+        <v>200.877049903502</v>
+      </c>
+      <c r="M26" t="n">
+        <v>14479705.3019539</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14384183.420164</v>
+      </c>
+      <c r="O26" t="n">
+        <v>95521.8817899424</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.939000029822895</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.06458262804997322</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.589632704219845e-05</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0003529815028552796</v>
+      </c>
+      <c r="T26" t="n">
+        <v>15.48404006145759</v>
+      </c>
+      <c r="U26" t="n">
+        <v>9833.35989892022</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Muse Code</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Muse Wonder Full (max)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.588804489084392</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.01685280599548879</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0.688172043010753</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>2096.2841057163</v>
+      </c>
+      <c r="L27" t="n">
+        <v>194.874971760617</v>
+      </c>
+      <c r="M27" t="n">
+        <v>14497965.3172412</v>
+      </c>
+      <c r="N27" t="n">
+        <v>14414434.4559639</v>
+      </c>
+      <c r="O27" t="n">
+        <v>83530.861277289</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.962325196630197</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>4.061290506635278e-05</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0002808800999248132</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>6916.030741113332</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GPT-6.1 Sol (max)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.541279798631476</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.02284798697058158</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>0.599462365591398</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.5046389983744</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1421.42885321603</v>
+      </c>
+      <c r="L28" t="n">
+        <v>40.6271304442272</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3944222.64509301</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3888998.33558647</v>
+      </c>
+      <c r="O28" t="n">
+        <v>55224.3095065408</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.921352278288341</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.3597406415866333</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.0001372335811987895</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.0003807997828430263</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.779780442903275</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2774.82945148403</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Grok 4.7 (xhigh)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.465968752688172</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.01302767878143769</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
         <v>0.629032258064516</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J29" t="n">
         <v>9.479356533441949</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K29" t="n">
         <v>2146.05576560009</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L29" t="n">
         <v>169.916321277289</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>15914547.7950299</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>15798913.4163495</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>115634.378680352</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>0.9420679200051389</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>0.04915615854771305</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>2.927942148841287e-05</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>0.0002171279796906282</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>20.34333091812611</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>7415.719595981607</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (max)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5466356905615291</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.02206122126132733</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.591397849462366</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7.03615822479963</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1486.68747959053</v>
+      </c>
+      <c r="L30" t="n">
+        <v>39.3501020962311</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3228511.32437048</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3187374.52012585</v>
+      </c>
+      <c r="O30" t="n">
+        <v>41136.8042446321</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.928466255516988</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.07768951082351416</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.0001693150915826867</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.0003676870210221221</v>
+      </c>
+      <c r="T30" t="n">
+        <v>12.87175050273751</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2171.613986592321</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Opus 5.5 (max)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.616528649505811</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.01010368064401798</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0.658602150537634</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11.4227202144224</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3661.21221302161</v>
+      </c>
+      <c r="L31" t="n">
+        <v>146.351117627892</v>
+      </c>
+      <c r="M31" t="n">
+        <v>14517552.0207549</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14238131.763253</v>
+      </c>
+      <c r="O31" t="n">
+        <v>279420.257501901</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9532457550498</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.05397389045101341</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4.246781059398966e-05</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.0001683946774002996</v>
+      </c>
+      <c r="T31" t="n">
+        <v>18.5274767418813</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3965.2309606969</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,391 +526,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (max)</t>
+          <t>GPT-6.1 Terra (Max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.457077885630498</v>
+        <v>0.481004244053438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.01839650049939798</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.586021505376344</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J2" t="n">
-        <v>3.91029139020419</v>
+        <v>1.24038465572461</v>
       </c>
       <c r="K2" t="n">
-        <v>1398.49826969262</v>
+        <v>1568.79046882589</v>
       </c>
       <c r="L2" t="n">
-        <v>208.319377647442</v>
+        <v>100.428485934615</v>
       </c>
       <c r="M2" t="n">
-        <v>17824340.6533789</v>
+        <v>12280717.4101086</v>
       </c>
       <c r="N2" t="n">
-        <v>17642872.3721332</v>
+        <v>12207751.9070045</v>
       </c>
       <c r="O2" t="n">
-        <v>181468.281245791</v>
+        <v>72965.5031041599</v>
       </c>
       <c r="P2" t="n">
-        <v>0.966617846464586</v>
+        <v>0.967020333857851</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1168910037690644</v>
+        <v>0.3877863546872434</v>
       </c>
       <c r="R2" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>3.916743851279486e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000326834788098065</v>
+        <v>0.000306608341656633</v>
       </c>
       <c r="T2" t="n">
-        <v>8.554978293929695</v>
+        <v>2.578739524773938</v>
       </c>
       <c r="U2" t="n">
-        <v>12745.34337271405</v>
+        <v>7828.143817892839</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.311260251113284</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.381720430107527</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J3" t="n">
-        <v>0.159155559086193</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K3" t="n">
-        <v>1275.79489619203</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L3" t="n">
-        <v>81.3609199522103</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M3" t="n">
-        <v>8885939.032378631</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N3" t="n">
-        <v>8794707.77057673</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O3" t="n">
-        <v>91231.26180188989</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P3" t="n">
-        <v>0.954514555274975</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95569826715708</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R3" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5113263210350233</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U3" t="n">
-        <v>6965.021618209341</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>DeepSeek V4.1 Flash (Max)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.431274491691105</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.586021505376344</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J4" t="n">
-        <v>1.84006320525524</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K4" t="n">
-        <v>3665.13740781145</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L4" t="n">
-        <v>142.091813837298</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M4" t="n">
-        <v>22141655.7546106</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N4" t="n">
-        <v>21997509.2781069</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O4" t="n">
-        <v>144146.476503747</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P4" t="n">
-        <v>0.984007673153141</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2343802595798777</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R4" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T4" t="n">
-        <v>4.266570921085596</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U4" t="n">
-        <v>6041.152974898141</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash</t>
+          <t>Gemini 3.8 Flash (High)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.473001334419464</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.610215053763441</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J5" t="n">
-        <v>0.38619359563592</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K5" t="n">
-        <v>2283.94687962311</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L5" t="n">
-        <v>142.882443792766</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M5" t="n">
-        <v>27235627.5942381</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N5" t="n">
-        <v>27078637.1644444</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O5" t="n">
-        <v>156990.429793635</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.22477777923946</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R5" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8164746429519335</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U5" t="n">
-        <v>11924.80781283864</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (high)</t>
+          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.33272301118714</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.443548387096774</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J6" t="n">
-        <v>2.51071545979138</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K6" t="n">
-        <v>786.045572632779</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L6" t="n">
-        <v>202.504982078853</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M6" t="n">
-        <v>14251510.9748887</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N6" t="n">
-        <v>14138882.8572119</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O6" t="n">
-        <v>112628.117676768</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1325211942634019</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R6" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T6" t="n">
-        <v>7.545962783978378</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U6" t="n">
-        <v>18130.64212950749</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.463051957532312</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.615591397849462</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J7" t="n">
-        <v>0.29627468390668</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K7" t="n">
-        <v>1284.94041000543</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L7" t="n">
-        <v>101.530045617465</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M7" t="n">
-        <v>16739365.2564321</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N7" t="n">
-        <v>16633748.9354947</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O7" t="n">
-        <v>105616.32093733</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P7" t="n">
-        <v>0.967966386781858</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56291435848148</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R7" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6398303237623303</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U7" t="n">
-        <v>13027.34751439669</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="8">
@@ -921,7 +921,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (max)</t>
+          <t>GPT-6.1 Terra (Low)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -931,311 +931,311 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.481004244053438</v>
+        <v>0.3485683422396</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01839650049939798</v>
+        <v>0.05511407534171487</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.540322580645161</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="J8" t="n">
-        <v>1.24038465572461</v>
+        <v>0.198820047696481</v>
       </c>
       <c r="K8" t="n">
-        <v>1568.79046882589</v>
+        <v>379.469317133703</v>
       </c>
       <c r="L8" t="n">
-        <v>100.428485934615</v>
+        <v>42.7471271858369</v>
       </c>
       <c r="M8" t="n">
-        <v>12280717.4101086</v>
+        <v>1886086.8732888</v>
       </c>
       <c r="N8" t="n">
-        <v>12207751.9070045</v>
+        <v>1877408.29673401</v>
       </c>
       <c r="O8" t="n">
-        <v>72965.5031041599</v>
+        <v>8678.576554795271</v>
       </c>
       <c r="P8" t="n">
-        <v>0.967020333857851</v>
+        <v>0.925808219461337</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3877863546872434</v>
+        <v>1.753185085096272</v>
       </c>
       <c r="R8" t="n">
-        <v>3.916743851279486e-05</v>
+        <v>0.0001848103325335146</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000306608341656633</v>
+        <v>0.0009185679223619145</v>
       </c>
       <c r="T8" t="n">
-        <v>2.578739524773938</v>
+        <v>0.5703904331042647</v>
       </c>
       <c r="U8" t="n">
-        <v>7828.143817892839</v>
+        <v>4970.327739631851</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Muse Spark Open (Xhigh)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.530769734767025</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.602150537634409</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33822148437056</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K9" t="n">
-        <v>1270.3477207201</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L9" t="n">
-        <v>58.8586738351254</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M9" t="n">
-        <v>3625399.81721408</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N9" t="n">
-        <v>3585782.97351906</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O9" t="n">
-        <v>39616.8436950147</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P9" t="n">
-        <v>0.91270190622461</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1223473113761584</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001464030897356012</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T9" t="n">
-        <v>8.173453006461965</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U9" t="n">
-        <v>2853.864149226019</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (low)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3485683422396</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05511407534171487</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.387096774193548</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J10" t="n">
-        <v>0.198820047696481</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K10" t="n">
-        <v>379.469317133703</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L10" t="n">
-        <v>42.7471271858369</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M10" t="n">
-        <v>1886086.8732888</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N10" t="n">
-        <v>1877408.29673401</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O10" t="n">
-        <v>8678.576554795271</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P10" t="n">
-        <v>0.925808219461337</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.753185085096272</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001848103325335146</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0009185679223619145</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5703904331042647</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U10" t="n">
-        <v>4970.327739631851</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muse Spark Open (xhigh)</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.263007023894863</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.508064516129032</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J11" t="n">
-        <v>3.54324946048794</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K11" t="n">
-        <v>1558.86632482568</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L11" t="n">
-        <v>161.39889866406</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M11" t="n">
-        <v>13336678.8257109</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N11" t="n">
-        <v>13239522.4765722</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O11" t="n">
-        <v>97156.3491386988</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P11" t="n">
-        <v>0.951550733530632</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07422763393538889</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R11" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0001687168551314198</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T11" t="n">
-        <v>13.47207161244619</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U11" t="n">
-        <v>8555.370408172921</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>GPT-6.1 Terra (Non-reasoning)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.392199207885305</v>
+        <v>0.392151614641034</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.04110338068613622</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.561827956989248</v>
+        <v>0.462365591397849</v>
       </c>
       <c r="J12" t="n">
-        <v>3.79584401482699</v>
+        <v>0.454255643441512</v>
       </c>
       <c r="K12" t="n">
-        <v>4568.4135207125</v>
+        <v>572.437023079179</v>
       </c>
       <c r="L12" t="n">
-        <v>114.796515026192</v>
+        <v>81.50919734984249</v>
       </c>
       <c r="M12" t="n">
-        <v>9153421.029330021</v>
+        <v>5776354.240164</v>
       </c>
       <c r="N12" t="n">
-        <v>9032702.304066719</v>
+        <v>5762448.0127566</v>
       </c>
       <c r="O12" t="n">
-        <v>120718.725263303</v>
+        <v>13906.2274074074</v>
       </c>
       <c r="P12" t="n">
-        <v>0.947205701820927</v>
+        <v>0.947531776215516</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.8632839686261944</v>
       </c>
       <c r="R12" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>6.788912146598201e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>0.000685056344768937</v>
       </c>
       <c r="T12" t="n">
-        <v>9.678357167761158</v>
+        <v>1.158367392819041</v>
       </c>
       <c r="U12" t="n">
-        <v>2003.632330530016</v>
+        <v>10090.81175269305</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.615117219506897</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1267,235 +1267,235 @@
         <v>0.682795698924731</v>
       </c>
       <c r="J13" t="n">
-        <v>7.99768820548534</v>
+        <v>8.19825160322711</v>
       </c>
       <c r="K13" t="n">
-        <v>3067.08119502552</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L13" t="n">
-        <v>99.46435538177469</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M13" t="n">
-        <v>10463266.3479852</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N13" t="n">
-        <v>10202564.6581949</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O13" t="n">
-        <v>260701.689790377</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P13" t="n">
-        <v>0.870466942043008</v>
+        <v>0.957829308304356</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07691187799556992</v>
+        <v>0.07155416292954402</v>
       </c>
       <c r="R13" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002005545925893816</v>
+        <v>0.0002602951802888973</v>
       </c>
       <c r="T13" t="n">
-        <v>13.00189289432771</v>
+        <v>13.97542727157122</v>
       </c>
       <c r="U13" t="n">
-        <v>3411.473541996706</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (none)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.392151614641034</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04110338068613622</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.462365591397849</v>
+        <v>0.376344086021506</v>
       </c>
       <c r="J14" t="n">
-        <v>0.454255643441512</v>
+        <v>0.319490234063365</v>
       </c>
       <c r="K14" t="n">
-        <v>572.437023079179</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L14" t="n">
-        <v>81.50919734984249</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M14" t="n">
-        <v>5776354.240164</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N14" t="n">
-        <v>5762448.0127566</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O14" t="n">
-        <v>13906.2274074074</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P14" t="n">
-        <v>0.947531776215516</v>
+        <v>0.95239449990423</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8632839686261944</v>
+        <v>0.6409894637063107</v>
       </c>
       <c r="R14" t="n">
-        <v>6.788912146598201e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.000685056344768937</v>
+        <v>8.82238133000263e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.158367392819041</v>
+        <v>1.560088046093346</v>
       </c>
       <c r="U14" t="n">
-        <v>10090.81175269305</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>GPT-6.1 Terra (Xhigh)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.586619030954708</v>
+        <v>0.482238344954925</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.02947324998862232</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.682795698924731</v>
+        <v>0.5376344086021499</v>
       </c>
       <c r="J15" t="n">
-        <v>8.19825160322711</v>
+        <v>0.690844449567775</v>
       </c>
       <c r="K15" t="n">
-        <v>2253.66843252199</v>
+        <v>981.713951073096</v>
       </c>
       <c r="L15" t="n">
-        <v>92.38415770609321</v>
+        <v>71.9594569349408</v>
       </c>
       <c r="M15" t="n">
-        <v>9809458.18526447</v>
+        <v>6886239.03807863</v>
       </c>
       <c r="N15" t="n">
-        <v>9713403.98470946</v>
+        <v>6849711.54192788</v>
       </c>
       <c r="O15" t="n">
-        <v>96054.2005550125</v>
+        <v>36527.4961507549</v>
       </c>
       <c r="P15" t="n">
-        <v>0.957829308304356</v>
+        <v>0.956934601768947</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07155416292954402</v>
+        <v>0.6980418605905224</v>
       </c>
       <c r="R15" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>7.002927756186012e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.0004912208331437053</v>
       </c>
       <c r="T15" t="n">
-        <v>13.97542727157122</v>
+        <v>1.432578841552611</v>
       </c>
       <c r="U15" t="n">
-        <v>4352.662549515813</v>
+        <v>7014.506649876363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>Claude Haiku 5.5 (Max)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.20478987379168</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.376344086021506</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="J16" t="n">
-        <v>0.319490234063365</v>
+        <v>2.67388407176395</v>
       </c>
       <c r="K16" t="n">
-        <v>2321.25393509395</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L16" t="n">
-        <v>92.9845715216683</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M16" t="n">
-        <v>4890063.07487998</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N16" t="n">
-        <v>4852363.14787444</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O16" t="n">
-        <v>37699.9270055393</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P16" t="n">
-        <v>0.95239449990423</v>
+        <v>0.918420370906708</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6409894637063107</v>
+        <v>0.1396829633215486</v>
       </c>
       <c r="R16" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>8.82238133000263e-05</v>
+        <v>8.775908185029112e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.560088046093346</v>
+        <v>7.159069196563442</v>
       </c>
       <c r="U16" t="n">
-        <v>2106.647187948466</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="17">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (xhigh)</t>
+          <t>GPT-6 Luna (Max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1516,116 +1516,116 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.482238344954925</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02947324998862232</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.5376344086021499</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J17" t="n">
-        <v>0.690844449567775</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K17" t="n">
-        <v>981.713951073096</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L17" t="n">
-        <v>71.9594569349408</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M17" t="n">
-        <v>6886239.03807863</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N17" t="n">
-        <v>6849711.54192788</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O17" t="n">
-        <v>36527.4961507549</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P17" t="n">
-        <v>0.956934601768947</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6980418605905224</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R17" t="n">
-        <v>7.002927756186012e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0004912208331437053</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T17" t="n">
-        <v>1.432578841552611</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U17" t="n">
-        <v>7014.506649876363</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Haiku 5.5 (max)</t>
+          <t>Muse Spark 1.3 (Max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.373496050722277</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.338709677419355</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J18" t="n">
-        <v>2.67388407176395</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K18" t="n">
-        <v>4255.92477550559</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L18" t="n">
-        <v>114.307695231889</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M18" t="n">
-        <v>16053233.8058097</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N18" t="n">
-        <v>15314914.0867177</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O18" t="n">
-        <v>738319.719091995</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P18" t="n">
-        <v>0.918420370906708</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R18" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T18" t="n">
-        <v>7.159069196563442</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U18" t="n">
-        <v>3771.973108688846</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="19">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kimi K3</t>
+          <t>Kimi K3 (Max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fable 5.1 (max) (with fallback)</t>
+          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GLM-5.3</t>
+          <t>GLM-5.3 (Max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (high)</t>
+          <t>GPT-6.1 Terra (High)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (medium)</t>
+          <t>GPT-6.1 Terra (Medium)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon</t>
+          <t>Gemini 4 Argon (High)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sonnet 5.5 (max)</t>
+          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Muse Wonder (max)</t>
+          <t>Muse Wonder (Max)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (max)</t>
+          <t>Muse Wonder Full (Max)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (max)</t>
+          <t>GPT-6.1 Sol (Max)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2275,131 +2275,131 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grok 4.7 (xhigh)</t>
+          <t>GPT-6 Astra (Max)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.465968752688172</v>
+        <v>0.5466356905615291</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.02206122126132733</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.629032258064516</v>
+        <v>0.591397849462366</v>
       </c>
       <c r="J29" t="n">
-        <v>9.479356533441949</v>
+        <v>7.03615822479963</v>
       </c>
       <c r="K29" t="n">
-        <v>2146.05576560009</v>
+        <v>1486.68747959053</v>
       </c>
       <c r="L29" t="n">
-        <v>169.916321277289</v>
+        <v>39.3501020962311</v>
       </c>
       <c r="M29" t="n">
-        <v>15914547.7950299</v>
+        <v>3228511.32437048</v>
       </c>
       <c r="N29" t="n">
-        <v>15798913.4163495</v>
+        <v>3187374.52012585</v>
       </c>
       <c r="O29" t="n">
-        <v>115634.378680352</v>
+        <v>41136.8042446321</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.928466255516987</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.07768951082351416</v>
       </c>
       <c r="R29" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>0.0001693150915826867</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0003676870210221221</v>
       </c>
       <c r="T29" t="n">
-        <v>20.34333091812611</v>
+        <v>12.87175050273751</v>
       </c>
       <c r="U29" t="n">
-        <v>7415.719595981607</v>
+        <v>2171.613986592321</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (max)</t>
+          <t>Grok 4.7 (Xhigh)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5466356905615291</v>
+        <v>0.465968752688172</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02206122126132733</v>
+        <v>0.01302767878143769</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.591397849462366</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J30" t="n">
-        <v>7.03615822479963</v>
+        <v>9.479356533441949</v>
       </c>
       <c r="K30" t="n">
-        <v>1486.68747959053</v>
+        <v>2146.05576560009</v>
       </c>
       <c r="L30" t="n">
-        <v>39.3501020962311</v>
+        <v>169.916321277289</v>
       </c>
       <c r="M30" t="n">
-        <v>3228511.32437048</v>
+        <v>15914547.7950299</v>
       </c>
       <c r="N30" t="n">
-        <v>3187374.52012585</v>
+        <v>15798913.4163495</v>
       </c>
       <c r="O30" t="n">
-        <v>41136.8042446321</v>
+        <v>115634.378680352</v>
       </c>
       <c r="P30" t="n">
-        <v>0.928466255516988</v>
+        <v>0.9420679200051389</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.07768951082351416</v>
+        <v>0.04915615854771305</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001693150915826867</v>
+        <v>2.927942148841287e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0003676870210221221</v>
+        <v>0.0002171279796906282</v>
       </c>
       <c r="T30" t="n">
-        <v>12.87175050273751</v>
+        <v>20.34333091812611</v>
       </c>
       <c r="U30" t="n">
-        <v>2171.613986592321</v>
+        <v>7415.719595981607</v>
       </c>
     </row>
     <row r="31">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Opus 5.5 (max)</t>
+          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,391 +526,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Max)</t>
+          <t>Gemini 4 Argon (High)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.481004244053438</v>
+        <v>0.532462665363311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01839650049939798</v>
+        <v>0.01534920015815749</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.540322580645161</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J2" t="n">
-        <v>1.24038465572461</v>
+        <v>11.7318632341125</v>
       </c>
       <c r="K2" t="n">
-        <v>1568.79046882589</v>
+        <v>2081.39574652818</v>
       </c>
       <c r="L2" t="n">
-        <v>100.428485934615</v>
+        <v>166.081847507331</v>
       </c>
       <c r="M2" t="n">
-        <v>12280717.4101086</v>
+        <v>13865930.859975</v>
       </c>
       <c r="N2" t="n">
-        <v>12207751.9070045</v>
+        <v>13756695.0153003</v>
       </c>
       <c r="O2" t="n">
-        <v>72965.5031041599</v>
+        <v>109235.844674704</v>
       </c>
       <c r="P2" t="n">
-        <v>0.967020333857851</v>
+        <v>0.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3877863546872434</v>
+        <v>0.04538602732898216</v>
       </c>
       <c r="R2" t="n">
-        <v>3.916743851279486e-05</v>
+        <v>3.840078756632939e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000306608341656633</v>
+        <v>0.0002558200026359581</v>
       </c>
       <c r="T2" t="n">
-        <v>2.578739524773938</v>
+        <v>22.03321283776317</v>
       </c>
       <c r="U2" t="n">
-        <v>7828.143817892839</v>
+        <v>6661.842603985196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>GPT-6.1 Terra (Medium)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.431274491691105</v>
+        <v>0.420492375909634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.04130896078448847</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.586021505376344</v>
+        <v>0.470430107526882</v>
       </c>
       <c r="J3" t="n">
-        <v>1.84006320525524</v>
+        <v>0.394994482142174</v>
       </c>
       <c r="K3" t="n">
-        <v>3665.13740781145</v>
+        <v>610.752293823178</v>
       </c>
       <c r="L3" t="n">
-        <v>142.091813837298</v>
+        <v>57.9985804279353</v>
       </c>
       <c r="M3" t="n">
-        <v>22141655.7546106</v>
+        <v>4075423.19637776</v>
       </c>
       <c r="N3" t="n">
-        <v>21997509.2781069</v>
+        <v>4056826.27165961</v>
       </c>
       <c r="O3" t="n">
-        <v>144146.476503747</v>
+        <v>18596.9247181492</v>
       </c>
       <c r="P3" t="n">
-        <v>0.984007673153142</v>
+        <v>0.9421388881635679</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2343802595798777</v>
+        <v>1.064552531542155</v>
       </c>
       <c r="R3" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>0.0001031775979199824</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0006884826797414745</v>
       </c>
       <c r="T3" t="n">
-        <v>4.266570921085596</v>
+        <v>0.9393618166980995</v>
       </c>
       <c r="U3" t="n">
-        <v>6041.152974898141</v>
+        <v>6672.792288452144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash (Max)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.473001334419464</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.610215053763441</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J4" t="n">
-        <v>0.38619359563592</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K4" t="n">
-        <v>2283.94687962311</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L4" t="n">
-        <v>142.882443792766</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M4" t="n">
-        <v>27235627.5942381</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N4" t="n">
-        <v>27078637.1644444</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O4" t="n">
-        <v>156990.429793635</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22477777923946</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R4" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8164746429519335</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U4" t="n">
-        <v>11924.80781283864</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (High)</t>
+          <t>GPT-6.1 Terra (Low)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.33272301118714</v>
+        <v>0.3485683422396</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.05511407534171487</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.443548387096774</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="J5" t="n">
-        <v>2.51071545979138</v>
+        <v>0.198820047696481</v>
       </c>
       <c r="K5" t="n">
-        <v>786.045572632779</v>
+        <v>379.469317133703</v>
       </c>
       <c r="L5" t="n">
-        <v>202.504982078853</v>
+        <v>42.7471271858369</v>
       </c>
       <c r="M5" t="n">
-        <v>14251510.9748887</v>
+        <v>1886086.8732888</v>
       </c>
       <c r="N5" t="n">
-        <v>14138882.8572119</v>
+        <v>1877408.29673401</v>
       </c>
       <c r="O5" t="n">
-        <v>112628.117676768</v>
+        <v>8678.576554795271</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.925808219461337</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1325211942634019</v>
+        <v>1.753185085096272</v>
       </c>
       <c r="R5" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>0.0001848103325335146</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0009185679223619145</v>
       </c>
       <c r="T5" t="n">
-        <v>7.545962783978378</v>
+        <v>0.5703904331042647</v>
       </c>
       <c r="U5" t="n">
-        <v>18130.64212950749</v>
+        <v>4970.327739631851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
+          <t>GPT-6.1 Terra (High)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.463051957532312</v>
+        <v>0.462787772238514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.03657118285941164</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.615591397849462</v>
+        <v>0.529569892473118</v>
       </c>
       <c r="J6" t="n">
-        <v>0.29627468390668</v>
+        <v>0.544031579042956</v>
       </c>
       <c r="K6" t="n">
-        <v>1284.94041000543</v>
+        <v>759.266290102096</v>
       </c>
       <c r="L6" t="n">
-        <v>101.530045617465</v>
+        <v>66.77620831975671</v>
       </c>
       <c r="M6" t="n">
-        <v>16739365.2564321</v>
+        <v>5600133.87243293</v>
       </c>
       <c r="N6" t="n">
-        <v>16633748.9354947</v>
+        <v>5573162.88381014</v>
       </c>
       <c r="O6" t="n">
-        <v>105616.32093733</v>
+        <v>26970.988622787</v>
       </c>
       <c r="P6" t="n">
-        <v>0.967966386781858</v>
+        <v>0.949839928351402</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.56291435848148</v>
+        <v>0.8506634358480373</v>
       </c>
       <c r="R6" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>8.263869807052661e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0006095197143235273</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6398303237623303</v>
+        <v>1.175553054073715</v>
       </c>
       <c r="U6" t="n">
-        <v>13027.34751439669</v>
+        <v>7375.717775748873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>GLM-5.3 (Max)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.530769734767025</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.602150537634409</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J7" t="n">
-        <v>4.33822148437056</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K7" t="n">
-        <v>1270.3477207201</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L7" t="n">
-        <v>58.8586738351254</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M7" t="n">
-        <v>3625399.81721408</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N7" t="n">
-        <v>3585782.97351906</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O7" t="n">
-        <v>39616.8436950147</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P7" t="n">
-        <v>0.91270190622461</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1223473113761584</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001464030897356012</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T7" t="n">
-        <v>8.173453006461965</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U7" t="n">
-        <v>2853.864149226019</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="8">
@@ -921,7 +921,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Low)</t>
+          <t>GPT-6.1 Terra (Max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -931,311 +931,311 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3485683422396</v>
+        <v>0.481004244053438</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05511407534171487</v>
+        <v>0.01839650049939798</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.387096774193548</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J8" t="n">
-        <v>0.198820047696481</v>
+        <v>1.24038465572461</v>
       </c>
       <c r="K8" t="n">
-        <v>379.469317133703</v>
+        <v>1568.79046882589</v>
       </c>
       <c r="L8" t="n">
-        <v>42.7471271858369</v>
+        <v>100.428485934615</v>
       </c>
       <c r="M8" t="n">
-        <v>1886086.8732888</v>
+        <v>12280717.4101086</v>
       </c>
       <c r="N8" t="n">
-        <v>1877408.29673401</v>
+        <v>12207751.9070045</v>
       </c>
       <c r="O8" t="n">
-        <v>8678.576554795271</v>
+        <v>72965.5031041599</v>
       </c>
       <c r="P8" t="n">
-        <v>0.925808219461337</v>
+        <v>0.967020333857851</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.753185085096272</v>
+        <v>0.3877863546872434</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001848103325335146</v>
+        <v>3.916743851279486e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0009185679223619145</v>
+        <v>0.000306608341656633</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5703904331042647</v>
+        <v>2.578739524773938</v>
       </c>
       <c r="U8" t="n">
-        <v>4970.327739631851</v>
+        <v>7828.143817892839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muse Spark Open (Xhigh)</t>
+          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.263007023894863</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.508064516129032</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J9" t="n">
-        <v>3.54324946048794</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K9" t="n">
-        <v>1558.86632482568</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L9" t="n">
-        <v>161.39889866406</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M9" t="n">
-        <v>13336678.8257109</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N9" t="n">
-        <v>13239522.4765722</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O9" t="n">
-        <v>97156.3491386988</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P9" t="n">
-        <v>0.951550733530632</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07422763393538889</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R9" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001687168551314198</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T9" t="n">
-        <v>13.47207161244619</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U9" t="n">
-        <v>8555.370408172921</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark Open (Xhigh)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.392199207885305</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.561827956989248</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J10" t="n">
-        <v>3.79584401482699</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K10" t="n">
-        <v>4568.4135207125</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L10" t="n">
-        <v>114.796515026192</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M10" t="n">
-        <v>9153421.029330021</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N10" t="n">
-        <v>9032702.304066719</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O10" t="n">
-        <v>120718.725263303</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P10" t="n">
-        <v>0.947205701820927</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R10" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T10" t="n">
-        <v>9.678357167761158</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U10" t="n">
-        <v>2003.632330530016</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>GitHub Copilot</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Copilot Fusion (Max)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>github</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.615117219506897</v>
+        <v>0.598570672857608</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.01657120364261475</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.682795698924731</v>
+        <v>0.56989247311828</v>
       </c>
       <c r="J11" t="n">
-        <v>7.99768820548534</v>
+        <v>5.58738499550885</v>
       </c>
       <c r="K11" t="n">
-        <v>3067.08119502552</v>
+        <v>2167.26806006408</v>
       </c>
       <c r="L11" t="n">
-        <v>99.46435538177469</v>
+        <v>171.026594982079</v>
       </c>
       <c r="M11" t="n">
-        <v>10463266.3479852</v>
+        <v>7339450.14544803</v>
       </c>
       <c r="N11" t="n">
-        <v>10202564.6581949</v>
+        <v>7044588.60246008</v>
       </c>
       <c r="O11" t="n">
-        <v>260701.689790377</v>
+        <v>129476.420638645</v>
       </c>
       <c r="P11" t="n">
-        <v>0.870466942043008</v>
+        <v>0.972717072404472</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07691187799556992</v>
+        <v>0.1071289473230751</v>
       </c>
       <c r="R11" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>8.15552474634418e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002005545925893816</v>
+        <v>0.0002761867273769124</v>
       </c>
       <c r="T11" t="n">
-        <v>13.00189289432771</v>
+        <v>9.33454519051924</v>
       </c>
       <c r="U11" t="n">
-        <v>3411.473541996706</v>
+        <v>3386.498551190305</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Non-reasoning)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.392151614641034</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04110338068613622</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.462365591397849</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J12" t="n">
-        <v>0.454255643441512</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K12" t="n">
-        <v>572.437023079179</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L12" t="n">
-        <v>81.50919734984249</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M12" t="n">
-        <v>5776354.240164</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N12" t="n">
-        <v>5762448.0127566</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O12" t="n">
-        <v>13906.2274074074</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P12" t="n">
-        <v>0.947531776215516</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8632839686261944</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R12" t="n">
-        <v>6.788912146598201e-05</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.000685056344768937</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.158367392819041</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U12" t="n">
-        <v>10090.81175269305</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.586619030954708</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1267,170 +1267,170 @@
         <v>0.682795698924731</v>
       </c>
       <c r="J13" t="n">
-        <v>8.19825160322711</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K13" t="n">
-        <v>2253.66843252199</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L13" t="n">
-        <v>92.38415770609321</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M13" t="n">
-        <v>9809458.18526447</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N13" t="n">
-        <v>9713403.98470946</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O13" t="n">
-        <v>96054.2005550125</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P13" t="n">
-        <v>0.957829308304356</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07155416292954402</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R13" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T13" t="n">
-        <v>13.97542727157122</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U13" t="n">
-        <v>4352.662549515813</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>GPT-6.1 Terra (Non-reasoning)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.20478987379168</v>
+        <v>0.392151614641034</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.04110338068613622</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.376344086021506</v>
+        <v>0.462365591397849</v>
       </c>
       <c r="J14" t="n">
-        <v>0.319490234063365</v>
+        <v>0.454255643441512</v>
       </c>
       <c r="K14" t="n">
-        <v>2321.25393509395</v>
+        <v>572.437023079179</v>
       </c>
       <c r="L14" t="n">
-        <v>92.9845715216683</v>
+        <v>81.50919734984249</v>
       </c>
       <c r="M14" t="n">
-        <v>4890063.07487998</v>
+        <v>5776354.240164</v>
       </c>
       <c r="N14" t="n">
-        <v>4852363.14787444</v>
+        <v>5762448.0127566</v>
       </c>
       <c r="O14" t="n">
-        <v>37699.9270055393</v>
+        <v>13906.2274074074</v>
       </c>
       <c r="P14" t="n">
-        <v>0.95239449990423</v>
+        <v>0.947531776215516</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6409894637063107</v>
+        <v>0.8632839686261944</v>
       </c>
       <c r="R14" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>6.788912146598201e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>8.82238133000263e-05</v>
+        <v>0.000685056344768937</v>
       </c>
       <c r="T14" t="n">
-        <v>1.560088046093346</v>
+        <v>1.158367392819041</v>
       </c>
       <c r="U14" t="n">
-        <v>2106.647187948466</v>
+        <v>10090.81175269305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Xhigh)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.482238344954925</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02947324998862232</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.5376344086021499</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J15" t="n">
-        <v>0.690844449567775</v>
+        <v>8.19825160322711</v>
       </c>
       <c r="K15" t="n">
-        <v>981.713951073096</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L15" t="n">
-        <v>71.9594569349408</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M15" t="n">
-        <v>6886239.03807863</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N15" t="n">
-        <v>6849711.54192788</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O15" t="n">
-        <v>36527.4961507549</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P15" t="n">
-        <v>0.956934601768947</v>
+        <v>0.957829308304356</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6980418605905224</v>
+        <v>0.07155416292954402</v>
       </c>
       <c r="R15" t="n">
-        <v>7.002927756186012e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0004912208331437053</v>
+        <v>0.0002602951802888973</v>
       </c>
       <c r="T15" t="n">
-        <v>1.432578841552611</v>
+        <v>13.97542727157122</v>
       </c>
       <c r="U15" t="n">
-        <v>7014.506649876363</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="16">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Claude Haiku 5.5 (Max)</t>
+          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1451,116 +1451,116 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.373496050722277</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.338709677419355</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J16" t="n">
-        <v>2.67388407176395</v>
+        <v>11.5301045391259</v>
       </c>
       <c r="K16" t="n">
-        <v>4255.92477550559</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L16" t="n">
-        <v>114.307695231889</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M16" t="n">
-        <v>16053233.8058097</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N16" t="n">
-        <v>15314914.0867177</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O16" t="n">
-        <v>738319.719091995</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P16" t="n">
-        <v>0.918420370906708</v>
+        <v>0.923288749508769</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.04997354913195912</v>
       </c>
       <c r="R16" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>0.0002723640979209027</v>
       </c>
       <c r="T16" t="n">
-        <v>7.159069196563442</v>
+        <v>20.01058594736629</v>
       </c>
       <c r="U16" t="n">
-        <v>3771.973108688846</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (Max)</t>
+          <t>Kimi K3 (Max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.311260251113284</v>
+        <v>0.41417319257087</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.006586839388819422</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.381720430107527</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J17" t="n">
-        <v>0.159155559086193</v>
+        <v>5.16526976917945</v>
       </c>
       <c r="K17" t="n">
-        <v>1275.79489619203</v>
+        <v>3772.73379345389</v>
       </c>
       <c r="L17" t="n">
-        <v>81.3609199522103</v>
+        <v>185.884007277072</v>
       </c>
       <c r="M17" t="n">
-        <v>8885939.032378631</v>
+        <v>9010345.58218855</v>
       </c>
       <c r="N17" t="n">
-        <v>8794707.77057673</v>
+        <v>8910048.672052789</v>
       </c>
       <c r="O17" t="n">
-        <v>91231.26180188989</v>
+        <v>100296.910135766</v>
       </c>
       <c r="P17" t="n">
-        <v>0.954514555274975</v>
+        <v>0.9600647788144701</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95569826715708</v>
+        <v>0.08018423259172099</v>
       </c>
       <c r="R17" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>4.596640481688052e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.0001097806564803237</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5113263210350233</v>
+        <v>12.47127979751034</v>
       </c>
       <c r="U17" t="n">
-        <v>6965.021618209341</v>
+        <v>2388.280243313879</v>
       </c>
     </row>
     <row r="18">
@@ -1631,155 +1631,155 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kimi K3 (Max)</t>
+          <t>GPT-6 Luna (Max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.41417319257087</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F19" t="n">
-        <v>0.006586839388819422</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.599462365591398</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J19" t="n">
-        <v>5.16526976917945</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K19" t="n">
-        <v>3772.73379345389</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L19" t="n">
-        <v>185.884007277072</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M19" t="n">
-        <v>9010345.58218855</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N19" t="n">
-        <v>8910048.672052789</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O19" t="n">
-        <v>100296.910135766</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9600647788144701</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.08018423259172099</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R19" t="n">
-        <v>4.596640481688052e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0001097806564803237</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T19" t="n">
-        <v>12.47127979751034</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U19" t="n">
-        <v>2388.280243313879</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.663978494623656</v>
+        <v>0.376344086021506</v>
       </c>
       <c r="J20" t="n">
-        <v>11.5301045391259</v>
+        <v>0.319490234063365</v>
       </c>
       <c r="K20" t="n">
-        <v>2115.55138904529</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L20" t="n">
-        <v>42.2762050613663</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M20" t="n">
-        <v>5989151.58443575</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N20" t="n">
-        <v>5863350.62589986</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O20" t="n">
-        <v>125800.958535897</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P20" t="n">
-        <v>0.923288749508769</v>
+        <v>0.95239449990423</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.04997354913195912</v>
+        <v>0.6409894637063107</v>
       </c>
       <c r="R20" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0002723640979209027</v>
+        <v>8.82238133000263e-05</v>
       </c>
       <c r="T20" t="n">
-        <v>20.01058594736629</v>
+        <v>1.560088046093346</v>
       </c>
       <c r="U20" t="n">
-        <v>2831.01210183249</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GLM-5.3 (Max)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.489161690344303</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1787,40 +1787,40 @@
         <v>0.586021505376344</v>
       </c>
       <c r="J21" t="n">
-        <v>5.23102713863476</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K21" t="n">
-        <v>3369.69557528728</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L21" t="n">
-        <v>111.53421852938</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M21" t="n">
-        <v>15908435.1191376</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N21" t="n">
-        <v>15798476.017074</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O21" t="n">
-        <v>109959.102063647</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P21" t="n">
-        <v>0.949845583680754</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.09351159483220896</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R21" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001451649501906712</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T21" t="n">
-        <v>10.69386103182535</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U21" t="n">
-        <v>4721.030361260851</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="22">
@@ -1831,61 +1831,61 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (High)</t>
+          <t>DeepSeek V4.1 Flash (Max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.462787772238514</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F22" t="n">
-        <v>0.03657118285941164</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.529569892473118</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J22" t="n">
-        <v>0.544031579042956</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K22" t="n">
-        <v>759.266290102096</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L22" t="n">
-        <v>66.77620831975671</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M22" t="n">
-        <v>5600133.87243293</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N22" t="n">
-        <v>5573162.88381014</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O22" t="n">
-        <v>26970.988622787</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P22" t="n">
-        <v>0.949839928351402</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8506634358480373</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R22" t="n">
-        <v>8.263869807052661e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0006095197143235273</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T22" t="n">
-        <v>1.175553054073715</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U22" t="n">
-        <v>7375.717775748873</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="23">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Medium)</t>
+          <t>GPT-6.1 Terra (Xhigh)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1906,246 +1906,246 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.420492375909634</v>
+        <v>0.482238344954925</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04130896078448847</v>
+        <v>0.02947324998862232</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.470430107526882</v>
+        <v>0.5376344086021499</v>
       </c>
       <c r="J23" t="n">
-        <v>0.394994482142174</v>
+        <v>0.690844449567775</v>
       </c>
       <c r="K23" t="n">
-        <v>610.752293823178</v>
+        <v>981.713951073096</v>
       </c>
       <c r="L23" t="n">
-        <v>57.9985804279353</v>
+        <v>71.9594569349408</v>
       </c>
       <c r="M23" t="n">
-        <v>4075423.19637776</v>
+        <v>6886239.03807863</v>
       </c>
       <c r="N23" t="n">
-        <v>4056826.27165961</v>
+        <v>6849711.54192788</v>
       </c>
       <c r="O23" t="n">
-        <v>18596.9247181492</v>
+        <v>36527.4961507549</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9421388881635679</v>
+        <v>0.956934601768947</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.064552531542155</v>
+        <v>0.6980418605905224</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0001031775979199824</v>
+        <v>7.002927756186012e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0006884826797414745</v>
+        <v>0.0004912208331437053</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9393618166980995</v>
+        <v>1.432578841552611</v>
       </c>
       <c r="U23" t="n">
-        <v>6672.792288452144</v>
+        <v>7014.506649876363</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon (High)</t>
+          <t>Claude Haiku 5.5 (Max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.532462665363311</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01534920015815749</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.551075268817204</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="J24" t="n">
-        <v>5.86148606882067</v>
+        <v>2.67388407176395</v>
       </c>
       <c r="K24" t="n">
-        <v>2081.39574652818</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L24" t="n">
-        <v>166.081847507331</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M24" t="n">
-        <v>13865930.859975</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N24" t="n">
-        <v>13756695.0153003</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O24" t="n">
-        <v>109235.844674704</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P24" t="n">
-        <v>0.87</v>
+        <v>0.918420370906708</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.09084089923810779</v>
+        <v>0.1396829633215486</v>
       </c>
       <c r="R24" t="n">
-        <v>3.840078756632939e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0002558200026359581</v>
+        <v>8.775908185029112e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>11.00825738612349</v>
+        <v>7.159069196563442</v>
       </c>
       <c r="U24" t="n">
-        <v>6661.842603985196</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
+          <t>Gemini 3.8 Flash (High)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.593374426631911</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F25" t="n">
-        <v>0.007440989482023622</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.64247311827957</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J25" t="n">
-        <v>13.3015082635468</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K25" t="n">
-        <v>4784.64130125774</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L25" t="n">
-        <v>232.941984902791</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M25" t="n">
-        <v>24129277.9119089</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N25" t="n">
-        <v>23634722.0822716</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O25" t="n">
-        <v>494555.829637233</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P25" t="n">
-        <v>0.952959879951284</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.04460955967362529</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R25" t="n">
-        <v>2.459147052797024e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0001240164913670604</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T25" t="n">
-        <v>22.41671980885376</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U25" t="n">
-        <v>5043.069353091532</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Muse Wonder (Max)</t>
+          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.519768236993592</v>
+        <v>0.593374426631911</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02117889017131678</v>
+        <v>0.007440989482023622</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.615591397849462</v>
+        <v>0.64247311827957</v>
       </c>
       <c r="J26" t="n">
-        <v>8.04811220428196</v>
+        <v>13.3015082635468</v>
       </c>
       <c r="K26" t="n">
-        <v>1472.5084254817</v>
+        <v>4784.64130125774</v>
       </c>
       <c r="L26" t="n">
-        <v>200.877049903502</v>
+        <v>232.941984902791</v>
       </c>
       <c r="M26" t="n">
-        <v>14479705.3019539</v>
+        <v>24129277.9119089</v>
       </c>
       <c r="N26" t="n">
-        <v>14384183.420164</v>
+        <v>23634722.0822716</v>
       </c>
       <c r="O26" t="n">
-        <v>95521.8817899424</v>
+        <v>494555.829637233</v>
       </c>
       <c r="P26" t="n">
-        <v>0.939000029822895</v>
+        <v>0.952959879951284</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.06458262804997322</v>
+        <v>0.04460955967362529</v>
       </c>
       <c r="R26" t="n">
-        <v>3.589632704219845e-05</v>
+        <v>2.459147052797024e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003529815028552796</v>
+        <v>0.0001240164913670604</v>
       </c>
       <c r="T26" t="n">
-        <v>15.48404006145759</v>
+        <v>22.41671980885376</v>
       </c>
       <c r="U26" t="n">
-        <v>9833.35989892022</v>
+        <v>5043.069353091532</v>
       </c>
     </row>
     <row r="27">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (Max)</t>
+          <t>Muse Wonder (Max)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -2166,305 +2166,435 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.588804489084392</v>
+        <v>0.519768236993592</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01685280599548879</v>
+        <v>0.02117889017131678</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.688172043010753</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>0.615591397849462</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8.04811220428196</v>
+      </c>
       <c r="K27" t="n">
-        <v>2096.2841057163</v>
+        <v>1472.5084254817</v>
       </c>
       <c r="L27" t="n">
-        <v>194.874971760617</v>
+        <v>200.877049903502</v>
       </c>
       <c r="M27" t="n">
-        <v>14497965.3172412</v>
+        <v>14479705.3019539</v>
       </c>
       <c r="N27" t="n">
-        <v>14414434.4559639</v>
+        <v>14384183.420164</v>
       </c>
       <c r="O27" t="n">
-        <v>83530.861277289</v>
+        <v>95521.8817899424</v>
       </c>
       <c r="P27" t="n">
-        <v>0.962325196630197</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+        <v>0.939000029822895</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.06458262804997322</v>
+      </c>
       <c r="R27" t="n">
-        <v>4.061290506635278e-05</v>
+        <v>3.589632704219845e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0002808800999248132</v>
-      </c>
-      <c r="T27" t="inlineStr"/>
+        <v>0.0003529815028552796</v>
+      </c>
+      <c r="T27" t="n">
+        <v>15.48404006145759</v>
+      </c>
       <c r="U27" t="n">
-        <v>6916.030741113332</v>
+        <v>9833.35989892022</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (Max)</t>
+          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.541279798631476</v>
+        <v>0.616528649505811</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02284798697058158</v>
+        <v>0.01010368064401798</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.599462365591398</v>
+        <v>0.658602150537634</v>
       </c>
       <c r="J28" t="n">
-        <v>1.5046389983744</v>
+        <v>11.4227202144224</v>
       </c>
       <c r="K28" t="n">
-        <v>1421.42885321603</v>
+        <v>3661.21221302161</v>
       </c>
       <c r="L28" t="n">
-        <v>40.6271304442272</v>
+        <v>146.351117627892</v>
       </c>
       <c r="M28" t="n">
-        <v>3944222.64509301</v>
+        <v>14517552.0207549</v>
       </c>
       <c r="N28" t="n">
-        <v>3888998.33558647</v>
+        <v>14238131.763253</v>
       </c>
       <c r="O28" t="n">
-        <v>55224.3095065408</v>
+        <v>279420.257501901</v>
       </c>
       <c r="P28" t="n">
-        <v>0.921352278288341</v>
+        <v>0.9532457550498</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3597406415866333</v>
+        <v>0.05397389045101341</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001372335811987895</v>
+        <v>4.246781059398966e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0003807997828430263</v>
+        <v>0.0001683946774002996</v>
       </c>
       <c r="T28" t="n">
-        <v>2.779780442903275</v>
+        <v>18.5274767418813</v>
       </c>
       <c r="U28" t="n">
-        <v>2774.82945148403</v>
+        <v>3965.2309606969</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (Max)</t>
+          <t>Muse Wonder Full (Max)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5466356905615291</v>
+        <v>0.588804489084392</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02206122126132733</v>
+        <v>0.01685280599548879</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.591397849462366</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7.03615822479963</v>
-      </c>
+        <v>0.688172043010753</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>1486.68747959053</v>
+        <v>2096.2841057163</v>
       </c>
       <c r="L29" t="n">
-        <v>39.3501020962311</v>
+        <v>194.874971760617</v>
       </c>
       <c r="M29" t="n">
-        <v>3228511.32437048</v>
+        <v>14497965.3172412</v>
       </c>
       <c r="N29" t="n">
-        <v>3187374.52012585</v>
+        <v>14414434.4559639</v>
       </c>
       <c r="O29" t="n">
-        <v>41136.8042446321</v>
+        <v>83530.861277289</v>
       </c>
       <c r="P29" t="n">
-        <v>0.928466255516987</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.07768951082351416</v>
-      </c>
+        <v>0.962325196630197</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>0.0001693150915826867</v>
+        <v>4.061290506635278e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003676870210221221</v>
-      </c>
-      <c r="T29" t="n">
-        <v>12.87175050273751</v>
-      </c>
+        <v>0.0002808800999248132</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>2171.613986592321</v>
+        <v>6916.030741113332</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grok 4.7 (Xhigh)</t>
+          <t>GPT-6.1 Sol (Max)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.465968752688172</v>
+        <v>0.541279798631476</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.02284798697058158</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.629032258064516</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J30" t="n">
-        <v>9.479356533441949</v>
+        <v>1.5046389983744</v>
       </c>
       <c r="K30" t="n">
-        <v>2146.05576560009</v>
+        <v>1421.42885321603</v>
       </c>
       <c r="L30" t="n">
-        <v>169.916321277289</v>
+        <v>40.6271304442272</v>
       </c>
       <c r="M30" t="n">
-        <v>15914547.7950299</v>
+        <v>3944222.64509301</v>
       </c>
       <c r="N30" t="n">
-        <v>15798913.4163495</v>
+        <v>3888998.33558647</v>
       </c>
       <c r="O30" t="n">
-        <v>115634.378680352</v>
+        <v>55224.3095065408</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.921352278288341</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.3597406415866333</v>
       </c>
       <c r="R30" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>0.0001372335811987895</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0003807997828430263</v>
       </c>
       <c r="T30" t="n">
-        <v>20.34333091812611</v>
+        <v>2.779780442903275</v>
       </c>
       <c r="U30" t="n">
-        <v>7415.719595981607</v>
+        <v>2774.82945148403</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
+          <t>Grok 4.7 (Xhigh)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.616528649505811</v>
+        <v>0.465968752688172</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01010368064401798</v>
+        <v>0.01302767878143769</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.658602150537634</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J31" t="n">
-        <v>11.4227202144224</v>
+        <v>9.479356533441949</v>
       </c>
       <c r="K31" t="n">
-        <v>3661.21221302161</v>
+        <v>2146.05576560009</v>
       </c>
       <c r="L31" t="n">
-        <v>146.351117627892</v>
+        <v>169.916321277289</v>
       </c>
       <c r="M31" t="n">
-        <v>14517552.0207549</v>
+        <v>15914547.7950299</v>
       </c>
       <c r="N31" t="n">
-        <v>14238131.763253</v>
+        <v>15798913.4163495</v>
       </c>
       <c r="O31" t="n">
-        <v>279420.257501901</v>
+        <v>115634.378680352</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9532457550498</v>
+        <v>0.9420679200051389</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.05397389045101341</v>
+        <v>0.04915615854771305</v>
       </c>
       <c r="R31" t="n">
-        <v>4.246781059398966e-05</v>
+        <v>2.927942148841287e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0001683946774002996</v>
+        <v>0.0002171279796906282</v>
       </c>
       <c r="T31" t="n">
-        <v>18.5274767418813</v>
+        <v>20.34333091812611</v>
       </c>
       <c r="U31" t="n">
-        <v>3965.2309606969</v>
+        <v>7415.719595981607</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Antigravity CLI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gemini 4 Carbon (High)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.594049025741284</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.01991340695931401</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>0.637096774193548</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7.7432202900257</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1789.89670714312</v>
+      </c>
+      <c r="L32" t="n">
+        <v>177.827079034068</v>
+      </c>
+      <c r="M32" t="n">
+        <v>12548516.9639495</v>
+      </c>
+      <c r="N32" t="n">
+        <v>12439485.9861971</v>
+      </c>
+      <c r="O32" t="n">
+        <v>109030.977752435</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.951903021414925</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.07671860072307363</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4.734017792285105e-05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.0003318901159885669</v>
+      </c>
+      <c r="T32" t="n">
+        <v>13.0346485803311</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7010.74923143379</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra (Max)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5466356905615291</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.02206122126132733</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0.591397849462366</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7.03615822479963</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1486.68747959053</v>
+      </c>
+      <c r="L33" t="n">
+        <v>39.3501020962311</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3228511.32437048</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3187374.52012585</v>
+      </c>
+      <c r="O33" t="n">
+        <v>41136.8042446321</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.928466255516987</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.07768951082351416</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.0001693150915826867</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.0003676870210221221</v>
+      </c>
+      <c r="T33" t="n">
+        <v>12.87175050273751</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2171.613986592321</v>
       </c>
     </row>
   </sheetData>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,66 +526,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon (High)</t>
+          <t>GPT-6.1 Terra (Max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.532462665363311</v>
+        <v>0.481004244053438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01534920015815749</v>
+        <v>0.01839650049939798</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.551075268817204</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J2" t="n">
-        <v>11.7318632341125</v>
+        <v>1.24038465572461</v>
       </c>
       <c r="K2" t="n">
-        <v>2081.39574652818</v>
+        <v>1568.79046882589</v>
       </c>
       <c r="L2" t="n">
-        <v>166.081847507331</v>
+        <v>100.428485934615</v>
       </c>
       <c r="M2" t="n">
-        <v>13865930.859975</v>
+        <v>12280717.4101086</v>
       </c>
       <c r="N2" t="n">
-        <v>13756695.0153003</v>
+        <v>12207751.9070045</v>
       </c>
       <c r="O2" t="n">
-        <v>109235.844674704</v>
+        <v>72965.5031041599</v>
       </c>
       <c r="P2" t="n">
-        <v>0.87</v>
+        <v>0.967020333857851</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04538602732898216</v>
+        <v>0.3877863546872434</v>
       </c>
       <c r="R2" t="n">
-        <v>3.840078756632939e-05</v>
+        <v>3.916743851279486e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002558200026359581</v>
+        <v>0.000306608341656633</v>
       </c>
       <c r="T2" t="n">
-        <v>22.03321283776317</v>
+        <v>2.578739524773938</v>
       </c>
       <c r="U2" t="n">
-        <v>6661.842603985196</v>
+        <v>7828.143817892839</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Medium)</t>
+          <t>GPT-6 Luna (Max)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -606,181 +606,181 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.420492375909634</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04130896078448847</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.470430107526882</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J3" t="n">
-        <v>0.394994482142174</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K3" t="n">
-        <v>610.752293823178</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L3" t="n">
-        <v>57.9985804279353</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M3" t="n">
-        <v>4075423.19637776</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N3" t="n">
-        <v>4056826.27165961</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O3" t="n">
-        <v>18596.9247181492</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9421388881635679</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.064552531542155</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001031775979199824</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006884826797414745</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9393618166980995</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U3" t="n">
-        <v>6672.792288452144</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Mistral Vibe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Mistral Large 4 (Medium)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.530769734767025</v>
+        <v>0.354072051699794</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.009117463014941153</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.602150537634409</v>
+        <v>0.446236559139785</v>
       </c>
       <c r="J4" t="n">
-        <v>4.33822148437056</v>
+        <v>0.782666187098099</v>
       </c>
       <c r="K4" t="n">
-        <v>1270.3477207201</v>
+        <v>2330.06956728793</v>
       </c>
       <c r="L4" t="n">
-        <v>58.8586738351254</v>
+        <v>80.7014391224069</v>
       </c>
       <c r="M4" t="n">
-        <v>3625399.81721408</v>
+        <v>5758751.98349191</v>
       </c>
       <c r="N4" t="n">
-        <v>3585782.97351906</v>
+        <v>5679971.53044205</v>
       </c>
       <c r="O4" t="n">
-        <v>39616.8436950147</v>
+        <v>78780.4530498534</v>
       </c>
       <c r="P4" t="n">
-        <v>0.91270190622461</v>
+        <v>0.922890846004726</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1223473113761584</v>
+        <v>0.4523921660811633</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001464030897356012</v>
+        <v>6.148416405408328e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0001519577169156859</v>
       </c>
       <c r="T4" t="n">
-        <v>8.173453006461965</v>
+        <v>2.210471522224792</v>
       </c>
       <c r="U4" t="n">
-        <v>2853.864149226019</v>
+        <v>2471.493582998371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Low)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3485683422396</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05511407534171487</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.387096774193548</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J5" t="n">
-        <v>0.198820047696481</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K5" t="n">
-        <v>379.469317133703</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L5" t="n">
-        <v>42.7471271858369</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M5" t="n">
-        <v>1886086.8732888</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N5" t="n">
-        <v>1877408.29673401</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O5" t="n">
-        <v>8678.576554795271</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P5" t="n">
-        <v>0.925808219461337</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.753185085096272</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001848103325335146</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0009185679223619145</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5703904331042647</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U5" t="n">
-        <v>4970.327739631851</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="6">
@@ -791,581 +791,581 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (High)</t>
+          <t>DeepSeek V4.1 Flash (Max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.462787772238514</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03657118285941164</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.529569892473118</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J6" t="n">
-        <v>0.544031579042956</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K6" t="n">
-        <v>759.266290102096</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L6" t="n">
-        <v>66.77620831975671</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M6" t="n">
-        <v>5600133.87243293</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N6" t="n">
-        <v>5573162.88381014</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O6" t="n">
-        <v>26970.988622787</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P6" t="n">
-        <v>0.949839928351402</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8506634358480373</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R6" t="n">
-        <v>8.263869807052661e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0006095197143235273</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T6" t="n">
-        <v>1.175553054073715</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U6" t="n">
-        <v>7375.717775748873</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GLM-5.3 (Max)</t>
+          <t>Gemini 3.8 Flash (High)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.489161690344303</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.586021505376344</v>
+        <v>0.443548387096774</v>
       </c>
       <c r="J7" t="n">
-        <v>5.23102713863476</v>
+        <v>2.51071545979138</v>
       </c>
       <c r="K7" t="n">
-        <v>3369.69557528728</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L7" t="n">
-        <v>111.53421852938</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M7" t="n">
-        <v>15908435.1191376</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N7" t="n">
-        <v>15798476.017074</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O7" t="n">
-        <v>109959.102063647</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P7" t="n">
-        <v>0.949845583680754</v>
+        <v>0.8791986451773121</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09351159483220896</v>
+        <v>0.1325211942634019</v>
       </c>
       <c r="R7" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001451649501906712</v>
+        <v>0.0004232871766871206</v>
       </c>
       <c r="T7" t="n">
-        <v>10.69386103182535</v>
+        <v>7.545962783978378</v>
       </c>
       <c r="U7" t="n">
-        <v>4721.030361260851</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Max)</t>
+          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.481004244053438</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01839650049939798</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.540322580645161</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J8" t="n">
-        <v>1.24038465572461</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K8" t="n">
-        <v>1568.79046882589</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L8" t="n">
-        <v>100.428485934615</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M8" t="n">
-        <v>12280717.4101086</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N8" t="n">
-        <v>12207751.9070045</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O8" t="n">
-        <v>72965.5031041599</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.967020333857851</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3877863546872434</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R8" t="n">
-        <v>3.916743851279486e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000306608341656633</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T8" t="n">
-        <v>2.578739524773938</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U8" t="n">
-        <v>7828.143817892839</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
+          <t>Gemini 4 Argon (High)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.463051957532312</v>
+        <v>0.532462665363311</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.01534920015815749</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.615591397849462</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J9" t="n">
-        <v>0.29627468390668</v>
+        <v>11.7318632341125</v>
       </c>
       <c r="K9" t="n">
-        <v>1284.94041000543</v>
+        <v>2081.39574652818</v>
       </c>
       <c r="L9" t="n">
-        <v>101.530045617465</v>
+        <v>166.081847507331</v>
       </c>
       <c r="M9" t="n">
-        <v>16739365.2564321</v>
+        <v>13865930.859975</v>
       </c>
       <c r="N9" t="n">
-        <v>16633748.9354947</v>
+        <v>13756695.0153003</v>
       </c>
       <c r="O9" t="n">
-        <v>105616.32093733</v>
+        <v>109235.844674704</v>
       </c>
       <c r="P9" t="n">
-        <v>0.967966386781858</v>
+        <v>0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56291435848148</v>
+        <v>0.04538602732898216</v>
       </c>
       <c r="R9" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>3.840078756632939e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0002558200026359581</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6398303237623303</v>
+        <v>22.03321283776317</v>
       </c>
       <c r="U9" t="n">
-        <v>13027.34751439669</v>
+        <v>6661.842603985196</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muse Spark Open (Xhigh)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.263007023894863</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.508064516129032</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J10" t="n">
-        <v>3.54324946048794</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K10" t="n">
-        <v>1558.86632482568</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L10" t="n">
-        <v>161.39889866406</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M10" t="n">
-        <v>13336678.8257109</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N10" t="n">
-        <v>13239522.4765722</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O10" t="n">
-        <v>97156.3491386988</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P10" t="n">
-        <v>0.951550733530632</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07422763393538889</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R10" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001687168551314198</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T10" t="n">
-        <v>13.47207161244619</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U10" t="n">
-        <v>8555.370408172921</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GitHub Copilot</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Copilot Fusion (Max)</t>
+          <t>GPT-6.1 Terra (Low)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.598570672857608</v>
+        <v>0.3485683422396</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01657120364261475</v>
+        <v>0.05511407534171487</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.56989247311828</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="J11" t="n">
-        <v>5.58738499550885</v>
+        <v>0.198820047696481</v>
       </c>
       <c r="K11" t="n">
-        <v>2167.26806006408</v>
+        <v>379.469317133703</v>
       </c>
       <c r="L11" t="n">
-        <v>171.026594982079</v>
+        <v>42.7471271858369</v>
       </c>
       <c r="M11" t="n">
-        <v>7339450.14544803</v>
+        <v>1886086.8732888</v>
       </c>
       <c r="N11" t="n">
-        <v>7044588.60246008</v>
+        <v>1877408.29673401</v>
       </c>
       <c r="O11" t="n">
-        <v>129476.420638645</v>
+        <v>8678.576554795271</v>
       </c>
       <c r="P11" t="n">
-        <v>0.972717072404472</v>
+        <v>0.925808219461337</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1071289473230751</v>
+        <v>1.753185085096272</v>
       </c>
       <c r="R11" t="n">
-        <v>8.15552474634418e-05</v>
+        <v>0.0001848103325335146</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002761867273769124</v>
+        <v>0.0009185679223619145</v>
       </c>
       <c r="T11" t="n">
-        <v>9.33454519051924</v>
+        <v>0.5703904331042647</v>
       </c>
       <c r="U11" t="n">
-        <v>3386.498551190305</v>
+        <v>4970.327739631851</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Muse Spark Open (Xhigh)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.392199207885305</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.561827956989248</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J12" t="n">
-        <v>3.79584401482699</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K12" t="n">
-        <v>4568.4135207125</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L12" t="n">
-        <v>114.796515026192</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M12" t="n">
-        <v>9153421.029330021</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N12" t="n">
-        <v>9032702.304066719</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O12" t="n">
-        <v>120718.725263303</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P12" t="n">
-        <v>0.947205701820927</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R12" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T12" t="n">
-        <v>9.678357167761158</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U12" t="n">
-        <v>2003.632330530016</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>GitHub Copilot</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>Copilot Fusion (max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>github</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.615117219506897</v>
+        <v>0.598570672857608</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.01657120364261475</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.682795698924731</v>
+        <v>0.56989247311828</v>
       </c>
       <c r="J13" t="n">
-        <v>7.99768820548534</v>
+        <v>5.58738499550885</v>
       </c>
       <c r="K13" t="n">
-        <v>3067.08119502552</v>
+        <v>2167.26806006408</v>
       </c>
       <c r="L13" t="n">
-        <v>99.46435538177469</v>
+        <v>171.026594982079</v>
       </c>
       <c r="M13" t="n">
-        <v>10463266.3479852</v>
+        <v>7339450.14544803</v>
       </c>
       <c r="N13" t="n">
-        <v>10202564.6581949</v>
+        <v>7044588.60246008</v>
       </c>
       <c r="O13" t="n">
-        <v>260701.689790377</v>
+        <v>129476.420638645</v>
       </c>
       <c r="P13" t="n">
-        <v>0.870466942043008</v>
+        <v>0.972717072404472</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07691187799556992</v>
+        <v>0.1071289473230751</v>
       </c>
       <c r="R13" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>8.15552474634418e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002005545925893816</v>
+        <v>0.0002761867273769124</v>
       </c>
       <c r="T13" t="n">
-        <v>13.00189289432771</v>
+        <v>9.33454519051924</v>
       </c>
       <c r="U13" t="n">
-        <v>3411.473541996706</v>
+        <v>3386.498551190305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Non-reasoning)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.392151614641034</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04110338068613622</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.462365591397849</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J14" t="n">
-        <v>0.454255643441512</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K14" t="n">
-        <v>572.437023079179</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L14" t="n">
-        <v>81.50919734984249</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M14" t="n">
-        <v>5776354.240164</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N14" t="n">
-        <v>5762448.0127566</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O14" t="n">
-        <v>13906.2274074074</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P14" t="n">
-        <v>0.947531776215516</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8632839686261944</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R14" t="n">
-        <v>6.788912146598201e-05</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.000685056344768937</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.158367392819041</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U14" t="n">
-        <v>10090.81175269305</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="15">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.586619030954708</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1397,170 +1397,170 @@
         <v>0.682795698924731</v>
       </c>
       <c r="J15" t="n">
-        <v>8.19825160322711</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K15" t="n">
-        <v>2253.66843252199</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L15" t="n">
-        <v>92.38415770609321</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M15" t="n">
-        <v>9809458.18526447</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N15" t="n">
-        <v>9713403.98470946</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O15" t="n">
-        <v>96054.2005550125</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P15" t="n">
-        <v>0.957829308304356</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07155416292954402</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R15" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T15" t="n">
-        <v>13.97542727157122</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U15" t="n">
-        <v>4352.662549515813</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
+          <t>GPT-6.1 Terra (Non-reasoning)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.392151614641034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.04110338068613622</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.663978494623656</v>
+        <v>0.462365591397849</v>
       </c>
       <c r="J16" t="n">
-        <v>11.5301045391259</v>
+        <v>0.454255643441512</v>
       </c>
       <c r="K16" t="n">
-        <v>2115.55138904529</v>
+        <v>572.437023079179</v>
       </c>
       <c r="L16" t="n">
-        <v>42.2762050613663</v>
+        <v>81.50919734984249</v>
       </c>
       <c r="M16" t="n">
-        <v>5989151.58443575</v>
+        <v>5776354.240164</v>
       </c>
       <c r="N16" t="n">
-        <v>5863350.62589986</v>
+        <v>5762448.0127566</v>
       </c>
       <c r="O16" t="n">
-        <v>125800.958535897</v>
+        <v>13906.2274074074</v>
       </c>
       <c r="P16" t="n">
-        <v>0.923288749508769</v>
+        <v>0.947531776215516</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.04997354913195912</v>
+        <v>0.8632839686261944</v>
       </c>
       <c r="R16" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>6.788912146598201e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0002723640979209027</v>
+        <v>0.000685056344768937</v>
       </c>
       <c r="T16" t="n">
-        <v>20.01058594736629</v>
+        <v>1.158367392819041</v>
       </c>
       <c r="U16" t="n">
-        <v>2831.01210183249</v>
+        <v>10090.81175269305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kimi K3 (Max)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.41417319257087</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006586839388819422</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.599462365591398</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J17" t="n">
-        <v>5.16526976917945</v>
+        <v>8.19825160322711</v>
       </c>
       <c r="K17" t="n">
-        <v>3772.73379345389</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L17" t="n">
-        <v>185.884007277072</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M17" t="n">
-        <v>9010345.58218855</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N17" t="n">
-        <v>8910048.672052789</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O17" t="n">
-        <v>100296.910135766</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9600647788144701</v>
+        <v>0.957829308304356</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.08018423259172099</v>
+        <v>0.07155416292954402</v>
       </c>
       <c r="R17" t="n">
-        <v>4.596640481688052e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001097806564803237</v>
+        <v>0.0002602951802888973</v>
       </c>
       <c r="T17" t="n">
-        <v>12.47127979751034</v>
+        <v>13.97542727157122</v>
       </c>
       <c r="U17" t="n">
-        <v>2388.280243313879</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="18">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (Max)</t>
+          <t>Muse Wonder Full (Max)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1581,181 +1581,175 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.457077885630498</v>
+        <v>0.588804489084392</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.01685280599548879</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.586021505376344</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.91029139020419</v>
-      </c>
+        <v>0.688172043010753</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>1398.49826969262</v>
+        <v>2096.2841057163</v>
       </c>
       <c r="L18" t="n">
-        <v>208.319377647442</v>
+        <v>194.874971760617</v>
       </c>
       <c r="M18" t="n">
-        <v>17824340.6533789</v>
+        <v>14497965.3172412</v>
       </c>
       <c r="N18" t="n">
-        <v>17642872.3721332</v>
+        <v>14414434.4559639</v>
       </c>
       <c r="O18" t="n">
-        <v>181468.281245791</v>
+        <v>83530.861277289</v>
       </c>
       <c r="P18" t="n">
-        <v>0.966617846464586</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1168910037690644</v>
-      </c>
+        <v>0.962325196630197</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>4.061290506635278e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.000326834788098065</v>
-      </c>
-      <c r="T18" t="n">
-        <v>8.554978293929695</v>
-      </c>
+        <v>0.0002808800999248132</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>12745.34337271405</v>
+        <v>6916.030741113332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (Max)</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.311260251113284</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.381720430107527</v>
+        <v>0.376344086021506</v>
       </c>
       <c r="J19" t="n">
-        <v>0.159155559086193</v>
+        <v>0.319490234063365</v>
       </c>
       <c r="K19" t="n">
-        <v>1275.79489619203</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L19" t="n">
-        <v>81.3609199522103</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M19" t="n">
-        <v>8885939.032378631</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N19" t="n">
-        <v>8794707.77057673</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O19" t="n">
-        <v>91231.26180188989</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P19" t="n">
-        <v>0.954514555274975</v>
+        <v>0.95239449990423</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95569826715708</v>
+        <v>0.6409894637063107</v>
       </c>
       <c r="R19" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0002439735823072565</v>
+        <v>8.82238133000263e-05</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5113263210350233</v>
+        <v>1.560088046093346</v>
       </c>
       <c r="U19" t="n">
-        <v>6965.021618209341</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>GPT-6.1 Terra (Xhigh)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.20478987379168</v>
+        <v>0.482238344954925</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.02947324998862232</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.376344086021506</v>
+        <v>0.5376344086021499</v>
       </c>
       <c r="J20" t="n">
-        <v>0.319490234063365</v>
+        <v>0.690844449567775</v>
       </c>
       <c r="K20" t="n">
-        <v>2321.25393509395</v>
+        <v>981.713951073096</v>
       </c>
       <c r="L20" t="n">
-        <v>92.9845715216683</v>
+        <v>71.9594569349408</v>
       </c>
       <c r="M20" t="n">
-        <v>4890063.07487998</v>
+        <v>6886239.03807863</v>
       </c>
       <c r="N20" t="n">
-        <v>4852363.14787444</v>
+        <v>6849711.54192788</v>
       </c>
       <c r="O20" t="n">
-        <v>37699.9270055393</v>
+        <v>36527.4961507549</v>
       </c>
       <c r="P20" t="n">
-        <v>0.95239449990423</v>
+        <v>0.956934601768947</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6409894637063107</v>
+        <v>0.6980418605905224</v>
       </c>
       <c r="R20" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>7.002927756186012e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>8.82238133000263e-05</v>
+        <v>0.0004912208331437053</v>
       </c>
       <c r="T20" t="n">
-        <v>1.560088046093346</v>
+        <v>1.432578841552611</v>
       </c>
       <c r="U20" t="n">
-        <v>2106.647187948466</v>
+        <v>7014.506649876363</v>
       </c>
     </row>
     <row r="21">
@@ -1766,191 +1760,191 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>Claude Haiku 5.5 (Max)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.431274491691105</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F21" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.586021505376344</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="J21" t="n">
-        <v>1.84006320525524</v>
+        <v>2.67388407176395</v>
       </c>
       <c r="K21" t="n">
-        <v>3665.13740781145</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L21" t="n">
-        <v>142.091813837298</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M21" t="n">
-        <v>22141655.7546106</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N21" t="n">
-        <v>21997509.2781069</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O21" t="n">
-        <v>144146.476503747</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P21" t="n">
-        <v>0.984007673153142</v>
+        <v>0.918420370906708</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2343802595798777</v>
+        <v>0.1396829633215486</v>
       </c>
       <c r="R21" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001176693923594615</v>
+        <v>8.775908185029112e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>4.266570921085596</v>
+        <v>7.159069196563442</v>
       </c>
       <c r="U21" t="n">
-        <v>6041.152974898141</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash (Max)</t>
+          <t>Muse Spark 1.3 (Max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.473001334419464</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.610215053763441</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J22" t="n">
-        <v>0.38619359563592</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K22" t="n">
-        <v>2283.94687962311</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L22" t="n">
-        <v>142.882443792766</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M22" t="n">
-        <v>27235627.5942381</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N22" t="n">
-        <v>27078637.1644444</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O22" t="n">
-        <v>156990.429793635</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.22477777923946</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R22" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8164746429519335</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U22" t="n">
-        <v>11924.80781283864</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Xhigh)</t>
+          <t>Kimi K3 (Max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.482238344954925</v>
+        <v>0.41417319257087</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02947324998862232</v>
+        <v>0.006586839388819422</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.5376344086021499</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J23" t="n">
-        <v>0.690844449567775</v>
+        <v>5.16526976917945</v>
       </c>
       <c r="K23" t="n">
-        <v>981.713951073096</v>
+        <v>3772.73379345389</v>
       </c>
       <c r="L23" t="n">
-        <v>71.9594569349408</v>
+        <v>185.884007277072</v>
       </c>
       <c r="M23" t="n">
-        <v>6886239.03807863</v>
+        <v>9010345.58218855</v>
       </c>
       <c r="N23" t="n">
-        <v>6849711.54192788</v>
+        <v>8910048.672052789</v>
       </c>
       <c r="O23" t="n">
-        <v>36527.4961507549</v>
+        <v>100296.910135766</v>
       </c>
       <c r="P23" t="n">
-        <v>0.956934601768947</v>
+        <v>0.9600647788144701</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6980418605905224</v>
+        <v>0.08018423259172099</v>
       </c>
       <c r="R23" t="n">
-        <v>7.002927756186012e-05</v>
+        <v>4.596640481688052e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0004912208331437053</v>
+        <v>0.0001097806564803237</v>
       </c>
       <c r="T23" t="n">
-        <v>1.432578841552611</v>
+        <v>12.47127979751034</v>
       </c>
       <c r="U23" t="n">
-        <v>7014.506649876363</v>
+        <v>2388.280243313879</v>
       </c>
     </row>
     <row r="24">
@@ -1961,7 +1955,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claude Haiku 5.5 (Max)</t>
+          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1971,246 +1965,246 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.373496050722277</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F24" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.338709677419355</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J24" t="n">
-        <v>2.67388407176395</v>
+        <v>11.5301045391259</v>
       </c>
       <c r="K24" t="n">
-        <v>4255.92477550559</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L24" t="n">
-        <v>114.307695231889</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M24" t="n">
-        <v>16053233.8058097</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N24" t="n">
-        <v>15314914.0867177</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O24" t="n">
-        <v>738319.719091995</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P24" t="n">
-        <v>0.918420370906708</v>
+        <v>0.923288749508769</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.04997354913195912</v>
       </c>
       <c r="R24" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>0.0002723640979209027</v>
       </c>
       <c r="T24" t="n">
-        <v>7.159069196563442</v>
+        <v>20.01058594736629</v>
       </c>
       <c r="U24" t="n">
-        <v>3771.973108688846</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (High)</t>
+          <t>GLM-5.3 (Max)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.33272301118714</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.443548387096774</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J25" t="n">
-        <v>2.51071545979138</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K25" t="n">
-        <v>786.045572632779</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L25" t="n">
-        <v>202.504982078853</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M25" t="n">
-        <v>14251510.9748887</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N25" t="n">
-        <v>14138882.8572119</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O25" t="n">
-        <v>112628.117676768</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1325211942634019</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R25" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T25" t="n">
-        <v>7.545962783978378</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U25" t="n">
-        <v>18130.64212950749</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
+          <t>GPT-6.1 Terra (High)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.593374426631911</v>
+        <v>0.462787772238514</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007440989482023622</v>
+        <v>0.03657118285941164</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0.64247311827957</v>
+        <v>0.529569892473118</v>
       </c>
       <c r="J26" t="n">
-        <v>13.3015082635468</v>
+        <v>0.544031579042956</v>
       </c>
       <c r="K26" t="n">
-        <v>4784.64130125774</v>
+        <v>759.266290102096</v>
       </c>
       <c r="L26" t="n">
-        <v>232.941984902791</v>
+        <v>66.77620831975671</v>
       </c>
       <c r="M26" t="n">
-        <v>24129277.9119089</v>
+        <v>5600133.87243293</v>
       </c>
       <c r="N26" t="n">
-        <v>23634722.0822716</v>
+        <v>5573162.88381014</v>
       </c>
       <c r="O26" t="n">
-        <v>494555.829637233</v>
+        <v>26970.988622787</v>
       </c>
       <c r="P26" t="n">
-        <v>0.952959879951284</v>
+        <v>0.949839928351402</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.04460955967362529</v>
+        <v>0.8506634358480373</v>
       </c>
       <c r="R26" t="n">
-        <v>2.459147052797024e-05</v>
+        <v>8.263869807052661e-05</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0001240164913670604</v>
+        <v>0.0006095197143235273</v>
       </c>
       <c r="T26" t="n">
-        <v>22.41671980885376</v>
+        <v>1.175553054073715</v>
       </c>
       <c r="U26" t="n">
-        <v>5043.069353091532</v>
+        <v>7375.717775748873</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Muse Wonder (Max)</t>
+          <t>GPT-6.1 Terra (Medium)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.519768236993592</v>
+        <v>0.420492375909634</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02117889017131678</v>
+        <v>0.04130896078448847</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>0.615591397849462</v>
+        <v>0.470430107526882</v>
       </c>
       <c r="J27" t="n">
-        <v>8.04811220428196</v>
+        <v>0.394994482142174</v>
       </c>
       <c r="K27" t="n">
-        <v>1472.5084254817</v>
+        <v>610.752293823178</v>
       </c>
       <c r="L27" t="n">
-        <v>200.877049903502</v>
+        <v>57.9985804279353</v>
       </c>
       <c r="M27" t="n">
-        <v>14479705.3019539</v>
+        <v>4075423.19637776</v>
       </c>
       <c r="N27" t="n">
-        <v>14384183.420164</v>
+        <v>4056826.27165961</v>
       </c>
       <c r="O27" t="n">
-        <v>95521.8817899424</v>
+        <v>18596.9247181492</v>
       </c>
       <c r="P27" t="n">
-        <v>0.939000029822895</v>
+        <v>0.9421388881635679</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.06458262804997322</v>
+        <v>1.064552531542155</v>
       </c>
       <c r="R27" t="n">
-        <v>3.589632704219845e-05</v>
+        <v>0.0001031775979199824</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0003529815028552796</v>
+        <v>0.0006884826797414745</v>
       </c>
       <c r="T27" t="n">
-        <v>15.48404006145759</v>
+        <v>0.9393618166980995</v>
       </c>
       <c r="U27" t="n">
-        <v>9833.35989892022</v>
+        <v>6672.792288452144</v>
       </c>
     </row>
     <row r="28">
@@ -2221,7 +2215,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
+          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2231,51 +2225,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.616528649505811</v>
+        <v>0.593374426631911</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01010368064401798</v>
+        <v>0.007440989482023622</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.658602150537634</v>
+        <v>0.64247311827957</v>
       </c>
       <c r="J28" t="n">
-        <v>11.4227202144224</v>
+        <v>13.3015082635468</v>
       </c>
       <c r="K28" t="n">
-        <v>3661.21221302161</v>
+        <v>4784.64130125774</v>
       </c>
       <c r="L28" t="n">
-        <v>146.351117627892</v>
+        <v>232.941984902791</v>
       </c>
       <c r="M28" t="n">
-        <v>14517552.0207549</v>
+        <v>24129277.9119089</v>
       </c>
       <c r="N28" t="n">
-        <v>14238131.763253</v>
+        <v>23634722.0822716</v>
       </c>
       <c r="O28" t="n">
-        <v>279420.257501901</v>
+        <v>494555.829637233</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9532457550498</v>
+        <v>0.952959879951284</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.05397389045101341</v>
+        <v>0.04460955967362529</v>
       </c>
       <c r="R28" t="n">
-        <v>4.246781059398966e-05</v>
+        <v>2.459147052797024e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0001683946774002996</v>
+        <v>0.0001240164913670604</v>
       </c>
       <c r="T28" t="n">
-        <v>18.5274767418813</v>
+        <v>22.41671980885376</v>
       </c>
       <c r="U28" t="n">
-        <v>3965.2309606969</v>
+        <v>5043.069353091532</v>
       </c>
     </row>
     <row r="29">
@@ -2286,7 +2280,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (Max)</t>
+          <t>Muse Wonder (Max)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2296,45 +2290,51 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.588804489084392</v>
+        <v>0.519768236993592</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01685280599548879</v>
+        <v>0.02117889017131678</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.688172043010753</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>0.615591397849462</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8.04811220428196</v>
+      </c>
       <c r="K29" t="n">
-        <v>2096.2841057163</v>
+        <v>1472.5084254817</v>
       </c>
       <c r="L29" t="n">
-        <v>194.874971760617</v>
+        <v>200.877049903501</v>
       </c>
       <c r="M29" t="n">
-        <v>14497965.3172412</v>
+        <v>14479705.3019539</v>
       </c>
       <c r="N29" t="n">
-        <v>14414434.4559639</v>
+        <v>14384183.420164</v>
       </c>
       <c r="O29" t="n">
-        <v>83530.861277289</v>
+        <v>95521.8817899424</v>
       </c>
       <c r="P29" t="n">
-        <v>0.962325196630197</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>0.939000029822895</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.06458262804997322</v>
+      </c>
       <c r="R29" t="n">
-        <v>4.061290506635278e-05</v>
+        <v>3.589632704219845e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0002808800999248132</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
+        <v>0.0003529815028552796</v>
+      </c>
+      <c r="T29" t="n">
+        <v>15.48404006145759</v>
+      </c>
       <c r="U29" t="n">
-        <v>6916.030741113332</v>
+        <v>9833.35989892022</v>
       </c>
     </row>
     <row r="30">
@@ -2405,131 +2405,131 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grok 4.7 (Xhigh)</t>
+          <t>Gemini 4 Carbon (High)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.465968752688172</v>
+        <v>0.594049025741284</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.01991340695931401</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.629032258064516</v>
+        <v>0.637096774193548</v>
       </c>
       <c r="J31" t="n">
-        <v>9.479356533441949</v>
+        <v>7.7432202900257</v>
       </c>
       <c r="K31" t="n">
-        <v>2146.05576560009</v>
+        <v>1789.89670714312</v>
       </c>
       <c r="L31" t="n">
-        <v>169.916321277289</v>
+        <v>177.827079034068</v>
       </c>
       <c r="M31" t="n">
-        <v>15914547.7950299</v>
+        <v>12548516.9639495</v>
       </c>
       <c r="N31" t="n">
-        <v>15798913.4163495</v>
+        <v>12439485.9861971</v>
       </c>
       <c r="O31" t="n">
-        <v>115634.378680352</v>
+        <v>109030.977752435</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.951903021414925</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.07671860072307363</v>
       </c>
       <c r="R31" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>4.734017792285105e-05</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0003318901159885669</v>
       </c>
       <c r="T31" t="n">
-        <v>20.34333091812611</v>
+        <v>13.0346485803311</v>
       </c>
       <c r="U31" t="n">
-        <v>7415.719595981607</v>
+        <v>7010.74923143379</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Mistral Vibe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gemini 4 Carbon (High)</t>
+          <t>Mistral Large 4 (High)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.594049025741284</v>
+        <v>0.482774919409145</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01991340695931401</v>
+        <v>0.009974980957003318</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.637096774193548</v>
+        <v>0.588709677419355</v>
       </c>
       <c r="J32" t="n">
-        <v>7.7432202900257</v>
+        <v>1.25944220793442</v>
       </c>
       <c r="K32" t="n">
-        <v>1789.89670714312</v>
+        <v>2903.91483346258</v>
       </c>
       <c r="L32" t="n">
-        <v>177.827079034068</v>
+        <v>100.100451830129</v>
       </c>
       <c r="M32" t="n">
-        <v>12548516.9639495</v>
+        <v>8453863.202892359</v>
       </c>
       <c r="N32" t="n">
-        <v>12439485.9861971</v>
+        <v>8330596.8209395</v>
       </c>
       <c r="O32" t="n">
-        <v>109030.977752435</v>
+        <v>123266.381952862</v>
       </c>
       <c r="P32" t="n">
-        <v>0.951903021414925</v>
+        <v>0.911751306302099</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.07671860072307363</v>
+        <v>0.3833243926300772</v>
       </c>
       <c r="R32" t="n">
-        <v>4.734017792285105e-05</v>
+        <v>5.710701815519928e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0003318901159885669</v>
+        <v>0.000166249682616722</v>
       </c>
       <c r="T32" t="n">
-        <v>13.0346485803311</v>
+        <v>2.608756497698383</v>
       </c>
       <c r="U32" t="n">
-        <v>7010.74923143379</v>
+        <v>2911.195295907529</v>
       </c>
     </row>
     <row r="33">
@@ -2597,6 +2597,136 @@
         <v>2171.613986592321</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Grok Build</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Grok 4.7 (Xhigh)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>xai</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.465968752688172</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.01302767878143769</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0.629032258064516</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9.479356533441949</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2146.05576560009</v>
+      </c>
+      <c r="L34" t="n">
+        <v>169.916321277289</v>
+      </c>
+      <c r="M34" t="n">
+        <v>15914547.7950299</v>
+      </c>
+      <c r="N34" t="n">
+        <v>15798913.4163495</v>
+      </c>
+      <c r="O34" t="n">
+        <v>115634.378680352</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9420679200051389</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.04915615854771305</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.927942148841287e-05</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.0002171279796906282</v>
+      </c>
+      <c r="T34" t="n">
+        <v>20.34333091812611</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7415.719595981607</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.616528649505811</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.01010368064401798</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.658602150537634</v>
+      </c>
+      <c r="J35" t="n">
+        <v>11.4227202144224</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3661.21221302161</v>
+      </c>
+      <c r="L35" t="n">
+        <v>146.351117627892</v>
+      </c>
+      <c r="M35" t="n">
+        <v>14517552.0207549</v>
+      </c>
+      <c r="N35" t="n">
+        <v>14238131.763253</v>
+      </c>
+      <c r="O35" t="n">
+        <v>279420.257501901</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.9532457550498</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.05397389045101341</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4.246781059398966e-05</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0001683946774002996</v>
+      </c>
+      <c r="T35" t="n">
+        <v>18.5274767418813</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3965.2309606969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/artificial_analysis_coding_agents.xlsx
+++ b/data/artificial_analysis_coding_agents.xlsx
@@ -526,261 +526,261 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Opencode</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Max)</t>
+          <t>GLM-5.3 (Max)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>zai</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.481004244053438</v>
+        <v>0.489161690344303</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01839650049939798</v>
+        <v>0.00870989701144027</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0.540322580645161</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J2" t="n">
-        <v>1.24038465572461</v>
+        <v>5.23102713863476</v>
       </c>
       <c r="K2" t="n">
-        <v>1568.79046882589</v>
+        <v>3369.69557528728</v>
       </c>
       <c r="L2" t="n">
-        <v>100.428485934615</v>
+        <v>111.53421852938</v>
       </c>
       <c r="M2" t="n">
-        <v>12280717.4101086</v>
+        <v>15908435.1191376</v>
       </c>
       <c r="N2" t="n">
-        <v>12207751.9070045</v>
+        <v>15798476.017074</v>
       </c>
       <c r="O2" t="n">
-        <v>72965.5031041599</v>
+        <v>109959.102063647</v>
       </c>
       <c r="P2" t="n">
-        <v>0.967020333857851</v>
+        <v>0.949845583680754</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3877863546872434</v>
+        <v>0.09351159483220896</v>
       </c>
       <c r="R2" t="n">
-        <v>3.916743851279486e-05</v>
+        <v>3.074857373971681e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000306608341656633</v>
+        <v>0.0001451649501906712</v>
       </c>
       <c r="T2" t="n">
-        <v>2.578739524773938</v>
+        <v>10.69386103182535</v>
       </c>
       <c r="U2" t="n">
-        <v>7828.143817892839</v>
+        <v>4721.030361260851</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-6 Luna (Max)</t>
+          <t>Gemini 4 Argon (High)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.311260251113284</v>
+        <v>0.532462665363311</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01463841493843539</v>
+        <v>0.01534920015815749</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.381720430107527</v>
+        <v>0.551075268817204</v>
       </c>
       <c r="J3" t="n">
-        <v>0.159155559086193</v>
+        <v>11.7318632341125</v>
       </c>
       <c r="K3" t="n">
-        <v>1275.79489619203</v>
+        <v>2081.39574652818</v>
       </c>
       <c r="L3" t="n">
-        <v>81.3609199522103</v>
+        <v>166.081847507331</v>
       </c>
       <c r="M3" t="n">
-        <v>8885939.032378631</v>
+        <v>13865930.859975</v>
       </c>
       <c r="N3" t="n">
-        <v>8794707.77057673</v>
+        <v>13756695.0153003</v>
       </c>
       <c r="O3" t="n">
-        <v>91231.26180188989</v>
+        <v>109235.844674704</v>
       </c>
       <c r="P3" t="n">
-        <v>0.954514555274975</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95569826715708</v>
+        <v>0.04538602732898216</v>
       </c>
       <c r="R3" t="n">
-        <v>3.502840273595309e-05</v>
+        <v>3.840078756632939e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002439735823072565</v>
+        <v>0.0002558200026359581</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5113263210350233</v>
+        <v>22.03321283776317</v>
       </c>
       <c r="U3" t="n">
-        <v>6965.021618209341</v>
+        <v>6661.842603985196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mistral Vibe</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mistral Large 4 (Medium)</t>
+          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.354072051699794</v>
+        <v>0.530769734767025</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009117463014941153</v>
+        <v>0.02506887174794111</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.446236559139785</v>
+        <v>0.602150537634409</v>
       </c>
       <c r="J4" t="n">
-        <v>0.782666187098099</v>
+        <v>4.33822148437056</v>
       </c>
       <c r="K4" t="n">
-        <v>2330.06956728793</v>
+        <v>1270.3477207201</v>
       </c>
       <c r="L4" t="n">
-        <v>80.7014391224069</v>
+        <v>58.8586738351254</v>
       </c>
       <c r="M4" t="n">
-        <v>5758751.98349191</v>
+        <v>3625399.81721408</v>
       </c>
       <c r="N4" t="n">
-        <v>5679971.53044205</v>
+        <v>3585782.97351906</v>
       </c>
       <c r="O4" t="n">
-        <v>78780.4530498534</v>
+        <v>39616.8436950147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.922890846004726</v>
+        <v>0.91270190622461</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4523921660811633</v>
+        <v>0.1223473113761584</v>
       </c>
       <c r="R4" t="n">
-        <v>6.148416405408328e-05</v>
+        <v>0.0001464030897356012</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001519577169156859</v>
+        <v>0.0004178145291323519</v>
       </c>
       <c r="T4" t="n">
-        <v>2.210471522224792</v>
+        <v>8.173453006461965</v>
       </c>
       <c r="U4" t="n">
-        <v>2471.493582998371</v>
+        <v>2853.864149226019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Step 5 Preview</t>
+          <t>GPT-6.1 Terra (Low)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>stepfun</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.431274491691105</v>
+        <v>0.3485683422396</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007060163541567688</v>
+        <v>0.05511407534171487</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.586021505376344</v>
+        <v>0.387096774193548</v>
       </c>
       <c r="J5" t="n">
-        <v>1.84006320525524</v>
+        <v>0.198820047696481</v>
       </c>
       <c r="K5" t="n">
-        <v>3665.13740781145</v>
+        <v>379.469317133703</v>
       </c>
       <c r="L5" t="n">
-        <v>142.091813837298</v>
+        <v>42.7471271858369</v>
       </c>
       <c r="M5" t="n">
-        <v>22141655.7546106</v>
+        <v>1886086.8732888</v>
       </c>
       <c r="N5" t="n">
-        <v>21997509.2781069</v>
+        <v>1877408.29673401</v>
       </c>
       <c r="O5" t="n">
-        <v>144146.476503747</v>
+        <v>8678.576554795271</v>
       </c>
       <c r="P5" t="n">
-        <v>0.984007673153142</v>
+        <v>0.925808219461337</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2343802595798777</v>
+        <v>1.753185085096272</v>
       </c>
       <c r="R5" t="n">
-        <v>1.947796932943011e-05</v>
+        <v>0.0001848103325335146</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001176693923594615</v>
+        <v>0.0009185679223619145</v>
       </c>
       <c r="T5" t="n">
-        <v>4.266570921085596</v>
+        <v>0.5703904331042647</v>
       </c>
       <c r="U5" t="n">
-        <v>6041.152974898141</v>
+        <v>4970.327739631851</v>
       </c>
     </row>
     <row r="6">
@@ -791,256 +791,256 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash (Max)</t>
+          <t>GPT-6.1 Terra (Max)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.473001334419464</v>
+        <v>0.481004244053438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01242589322823963</v>
+        <v>0.01839650049939798</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0.610215053763441</v>
+        <v>0.540322580645161</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38619359563592</v>
+        <v>1.24038465572461</v>
       </c>
       <c r="K6" t="n">
-        <v>2283.94687962311</v>
+        <v>1568.79046882589</v>
       </c>
       <c r="L6" t="n">
-        <v>142.882443792766</v>
+        <v>100.428485934615</v>
       </c>
       <c r="M6" t="n">
-        <v>27235627.5942381</v>
+        <v>12280717.4101086</v>
       </c>
       <c r="N6" t="n">
-        <v>27078637.1644444</v>
+        <v>12207751.9070045</v>
       </c>
       <c r="O6" t="n">
-        <v>156990.429793635</v>
+        <v>72965.5031041599</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9831236432716099</v>
+        <v>0.967020333857851</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.22477777923946</v>
+        <v>0.3877863546872434</v>
       </c>
       <c r="R6" t="n">
-        <v>1.736700697580147e-05</v>
+        <v>3.916743851279486e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002070982204706605</v>
+        <v>0.000306608341656633</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8164746429519335</v>
+        <v>2.578739524773938</v>
       </c>
       <c r="U6" t="n">
-        <v>11924.80781283864</v>
+        <v>7828.143817892839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antigravity SDK v0.1.12</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini 3.8 Flash (High)</t>
+          <t>Muse Spark Open (Xhigh)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.33272301118714</v>
+        <v>0.263007023894863</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02539723060122723</v>
+        <v>0.01012301130788519</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.443548387096774</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="J7" t="n">
-        <v>2.51071545979138</v>
+        <v>3.54324946048794</v>
       </c>
       <c r="K7" t="n">
-        <v>786.045572632779</v>
+        <v>1558.86632482568</v>
       </c>
       <c r="L7" t="n">
-        <v>202.504982078853</v>
+        <v>161.39889866406</v>
       </c>
       <c r="M7" t="n">
-        <v>14251510.9748887</v>
+        <v>13336678.8257109</v>
       </c>
       <c r="N7" t="n">
-        <v>14138882.8572119</v>
+        <v>13239522.4765722</v>
       </c>
       <c r="O7" t="n">
-        <v>112628.117676768</v>
+        <v>97156.3491386988</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8791986451773121</v>
+        <v>0.951550733530632</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1325211942634019</v>
+        <v>0.07422763393538889</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33465077333485e-05</v>
+        <v>1.972057866369468e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004232871766871206</v>
+        <v>0.0001687168551314198</v>
       </c>
       <c r="T7" t="n">
-        <v>7.545962783978378</v>
+        <v>13.47207161244619</v>
       </c>
       <c r="U7" t="n">
-        <v>18130.64212950749</v>
+        <v>8555.370408172921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>GitHub Copilot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
+          <t>Copilot Fusion (max)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>github</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.463051957532312</v>
+        <v>0.598570672857608</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02162210576895259</v>
+        <v>0.01657120364261475</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.615591397849462</v>
+        <v>0.56989247311828</v>
       </c>
       <c r="J8" t="n">
-        <v>0.29627468390668</v>
+        <v>5.58738499550885</v>
       </c>
       <c r="K8" t="n">
-        <v>1284.94041000543</v>
+        <v>2167.26806006408</v>
       </c>
       <c r="L8" t="n">
-        <v>101.530045617465</v>
+        <v>171.026594982079</v>
       </c>
       <c r="M8" t="n">
-        <v>16739365.2564321</v>
+        <v>7339450.14544803</v>
       </c>
       <c r="N8" t="n">
-        <v>16633748.9354947</v>
+        <v>7044588.60246008</v>
       </c>
       <c r="O8" t="n">
-        <v>105616.32093733</v>
+        <v>129476.420638645</v>
       </c>
       <c r="P8" t="n">
-        <v>0.967966386781858</v>
+        <v>0.972717072404472</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56291435848148</v>
+        <v>0.1071289473230751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.766245615880712e-05</v>
+        <v>8.15552474634418e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003603684294825432</v>
+        <v>0.0002761867273769124</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6398303237623303</v>
+        <v>9.33454519051924</v>
       </c>
       <c r="U8" t="n">
-        <v>13027.34751439669</v>
+        <v>3386.498551190305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gemini 4 Argon (High)</t>
+          <t>Qwen3.8 Max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>alibaba_cloud</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.532462665363311</v>
+        <v>0.392199207885305</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01534920015815749</v>
+        <v>0.005151011913967062</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0.551075268817204</v>
+        <v>0.561827956989248</v>
       </c>
       <c r="J9" t="n">
-        <v>11.7318632341125</v>
+        <v>3.79584401482699</v>
       </c>
       <c r="K9" t="n">
-        <v>2081.39574652818</v>
+        <v>4568.4135207125</v>
       </c>
       <c r="L9" t="n">
-        <v>166.081847507331</v>
+        <v>114.796515026192</v>
       </c>
       <c r="M9" t="n">
-        <v>13865930.859975</v>
+        <v>9153421.029330021</v>
       </c>
       <c r="N9" t="n">
-        <v>13756695.0153003</v>
+        <v>9032702.304066719</v>
       </c>
       <c r="O9" t="n">
-        <v>109235.844674704</v>
+        <v>120718.725263303</v>
       </c>
       <c r="P9" t="n">
-        <v>0.87</v>
+        <v>0.947205701820927</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04538602732898216</v>
+        <v>0.1033233205456629</v>
       </c>
       <c r="R9" t="n">
-        <v>3.840078756632939e-05</v>
+        <v>4.284728153862838e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0002558200026359581</v>
+        <v>8.58501985661177e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>22.03321283776317</v>
+        <v>9.678357167761158</v>
       </c>
       <c r="U9" t="n">
-        <v>6661.842603985196</v>
+        <v>2003.632330530016</v>
       </c>
     </row>
     <row r="10">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-6 Astra XHigh + SWE-2 Medium</t>
+          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1061,51 +1061,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.530769734767025</v>
+        <v>0.615117219506897</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02506887174794111</v>
+        <v>0.0120332755553629</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0.602150537634409</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J10" t="n">
-        <v>4.33822148437056</v>
+        <v>7.99768820548534</v>
       </c>
       <c r="K10" t="n">
-        <v>1270.3477207201</v>
+        <v>3067.08119502552</v>
       </c>
       <c r="L10" t="n">
-        <v>58.8586738351254</v>
+        <v>99.46435538177469</v>
       </c>
       <c r="M10" t="n">
-        <v>3625399.81721408</v>
+        <v>10463266.3479852</v>
       </c>
       <c r="N10" t="n">
-        <v>3585782.97351906</v>
+        <v>10202564.6581949</v>
       </c>
       <c r="O10" t="n">
-        <v>39616.8436950147</v>
+        <v>260701.689790377</v>
       </c>
       <c r="P10" t="n">
-        <v>0.91270190622461</v>
+        <v>0.870466942043008</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1223473113761584</v>
+        <v>0.07691187799556992</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001464030897356012</v>
+        <v>5.878825971254604e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004178145291323519</v>
+        <v>0.0002005545925893816</v>
       </c>
       <c r="T10" t="n">
-        <v>8.173453006461965</v>
+        <v>13.00189289432771</v>
       </c>
       <c r="U10" t="n">
-        <v>2853.864149226019</v>
+        <v>3411.473541996706</v>
       </c>
     </row>
     <row r="11">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Low)</t>
+          <t>GPT-6.1 Terra (Non-reasoning)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1126,955 +1126,955 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.3485683422396</v>
+        <v>0.392151614641034</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05511407534171487</v>
+        <v>0.04110338068613622</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.387096774193548</v>
+        <v>0.462365591397849</v>
       </c>
       <c r="J11" t="n">
-        <v>0.198820047696481</v>
+        <v>0.454255643441512</v>
       </c>
       <c r="K11" t="n">
-        <v>379.469317133703</v>
+        <v>572.437023079179</v>
       </c>
       <c r="L11" t="n">
-        <v>42.7471271858369</v>
+        <v>81.50919734984249</v>
       </c>
       <c r="M11" t="n">
-        <v>1886086.8732888</v>
+        <v>5776354.240164</v>
       </c>
       <c r="N11" t="n">
-        <v>1877408.29673401</v>
+        <v>5762448.0127566</v>
       </c>
       <c r="O11" t="n">
-        <v>8678.576554795271</v>
+        <v>13906.2274074074</v>
       </c>
       <c r="P11" t="n">
-        <v>0.925808219461337</v>
+        <v>0.947531776215516</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.753185085096272</v>
+        <v>0.8632839686261944</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001848103325335146</v>
+        <v>6.788912146598201e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0009185679223619145</v>
+        <v>0.000685056344768937</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5703904331042647</v>
+        <v>1.158367392819041</v>
       </c>
       <c r="U11" t="n">
-        <v>4970.327739631851</v>
+        <v>10090.81175269305</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Devin Fusion CLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muse Spark Open (Xhigh)</t>
+          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>cognition</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.263007023894863</v>
+        <v>0.586619030954708</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01012301130788519</v>
+        <v>0.01561771081733384</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>0.508064516129032</v>
+        <v>0.682795698924731</v>
       </c>
       <c r="J12" t="n">
-        <v>3.54324946048794</v>
+        <v>8.19825160322711</v>
       </c>
       <c r="K12" t="n">
-        <v>1558.86632482568</v>
+        <v>2253.66843252199</v>
       </c>
       <c r="L12" t="n">
-        <v>161.39889866406</v>
+        <v>92.38415770609321</v>
       </c>
       <c r="M12" t="n">
-        <v>13336678.8257109</v>
+        <v>9809458.18526447</v>
       </c>
       <c r="N12" t="n">
-        <v>13239522.4765722</v>
+        <v>9713403.98470946</v>
       </c>
       <c r="O12" t="n">
-        <v>97156.3491386988</v>
+        <v>96054.2005550125</v>
       </c>
       <c r="P12" t="n">
-        <v>0.951550733530632</v>
+        <v>0.957829308304356</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07422763393538889</v>
+        <v>0.07155416292954402</v>
       </c>
       <c r="R12" t="n">
-        <v>1.972057866369468e-05</v>
+        <v>5.980136923728498e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001687168551314198</v>
+        <v>0.0002602951802888973</v>
       </c>
       <c r="T12" t="n">
-        <v>13.47207161244619</v>
+        <v>13.97542727157122</v>
       </c>
       <c r="U12" t="n">
-        <v>8555.370408172921</v>
+        <v>4352.662549515813</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GitHub Copilot</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Copilot Fusion (max)</t>
+          <t>Muse Wonder Full (Max)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.598570672857608</v>
+        <v>0.588804489084392</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01657120364261475</v>
+        <v>0.01685280599548879</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0.56989247311828</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.58738499550885</v>
-      </c>
+        <v>0.688172043010753</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>2167.26806006408</v>
+        <v>2096.2841057163</v>
       </c>
       <c r="L13" t="n">
-        <v>171.026594982079</v>
+        <v>194.874971760617</v>
       </c>
       <c r="M13" t="n">
-        <v>7339450.14544803</v>
+        <v>14497965.3172412</v>
       </c>
       <c r="N13" t="n">
-        <v>7044588.60246008</v>
+        <v>14414434.4559639</v>
       </c>
       <c r="O13" t="n">
-        <v>129476.420638645</v>
+        <v>83530.861277289</v>
       </c>
       <c r="P13" t="n">
-        <v>0.972717072404472</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1071289473230751</v>
-      </c>
+        <v>0.962325196630197</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>8.15552474634418e-05</v>
+        <v>4.061290506635278e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0002761867273769124</v>
-      </c>
-      <c r="T13" t="n">
-        <v>9.33454519051924</v>
-      </c>
+        <v>0.0002808800999248132</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>3386.498551190305</v>
+        <v>6916.030741113332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mirror</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3.8 Max</t>
+          <t>Beam 1.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>alibaba_cloud</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.392199207885305</v>
+        <v>0.20478987379168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005151011913967062</v>
+        <v>0.005293428798001577</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.561827956989248</v>
+        <v>0.376344086021506</v>
       </c>
       <c r="J14" t="n">
-        <v>3.79584401482699</v>
+        <v>0.319490234063365</v>
       </c>
       <c r="K14" t="n">
-        <v>4568.4135207125</v>
+        <v>2321.25393509395</v>
       </c>
       <c r="L14" t="n">
-        <v>114.796515026192</v>
+        <v>92.9845715216683</v>
       </c>
       <c r="M14" t="n">
-        <v>9153421.029330021</v>
+        <v>4890063.07487998</v>
       </c>
       <c r="N14" t="n">
-        <v>9032702.304066719</v>
+        <v>4852363.14787444</v>
       </c>
       <c r="O14" t="n">
-        <v>120718.725263303</v>
+        <v>37699.9270055393</v>
       </c>
       <c r="P14" t="n">
-        <v>0.947205701820927</v>
+        <v>0.95239449990423</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1033233205456629</v>
+        <v>0.6409894637063107</v>
       </c>
       <c r="R14" t="n">
-        <v>4.284728153862838e-05</v>
+        <v>4.187877960995551e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>8.58501985661177e-05</v>
+        <v>8.82238133000263e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>9.678357167761158</v>
+        <v>1.560088046093346</v>
       </c>
       <c r="U14" t="n">
-        <v>2003.632330530016</v>
+        <v>2106.647187948466</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 Max + GPT-6 Luna High</t>
+          <t>GPT-6.1 Terra (Xhigh)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.615117219506897</v>
+        <v>0.482238344954925</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0120332755553629</v>
+        <v>0.02947324998862232</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0.682795698924731</v>
+        <v>0.5376344086021499</v>
       </c>
       <c r="J15" t="n">
-        <v>7.99768820548534</v>
+        <v>0.690844449567775</v>
       </c>
       <c r="K15" t="n">
-        <v>3067.08119502552</v>
+        <v>981.713951073096</v>
       </c>
       <c r="L15" t="n">
-        <v>99.46435538177469</v>
+        <v>71.9594569349408</v>
       </c>
       <c r="M15" t="n">
-        <v>10463266.3479852</v>
+        <v>6886239.03807863</v>
       </c>
       <c r="N15" t="n">
-        <v>10202564.6581949</v>
+        <v>6849711.54192788</v>
       </c>
       <c r="O15" t="n">
-        <v>260701.689790377</v>
+        <v>36527.4961507549</v>
       </c>
       <c r="P15" t="n">
-        <v>0.870466942043008</v>
+        <v>0.956934601768947</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07691187799556992</v>
+        <v>0.6980418605905224</v>
       </c>
       <c r="R15" t="n">
-        <v>5.878825971254604e-05</v>
+        <v>7.002927756186012e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002005545925893816</v>
+        <v>0.0004912208331437053</v>
       </c>
       <c r="T15" t="n">
-        <v>13.00189289432771</v>
+        <v>1.432578841552611</v>
       </c>
       <c r="U15" t="n">
-        <v>3411.473541996706</v>
+        <v>7014.506649876363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Non-reasoning)</t>
+          <t>Claude Haiku 5.5 (Max)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.392151614641034</v>
+        <v>0.373496050722277</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04110338068613622</v>
+        <v>0.005265544911017467</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0.462365591397849</v>
+        <v>0.338709677419355</v>
       </c>
       <c r="J16" t="n">
-        <v>0.454255643441512</v>
+        <v>2.67388407176395</v>
       </c>
       <c r="K16" t="n">
-        <v>572.437023079179</v>
+        <v>4255.92477550559</v>
       </c>
       <c r="L16" t="n">
-        <v>81.50919734984249</v>
+        <v>114.307695231889</v>
       </c>
       <c r="M16" t="n">
-        <v>5776354.240164</v>
+        <v>16053233.8058097</v>
       </c>
       <c r="N16" t="n">
-        <v>5762448.0127566</v>
+        <v>15314914.0867177</v>
       </c>
       <c r="O16" t="n">
-        <v>13906.2274074074</v>
+        <v>738319.719091995</v>
       </c>
       <c r="P16" t="n">
-        <v>0.947531776215516</v>
+        <v>0.918420370906708</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8632839686261944</v>
+        <v>0.1396829633215486</v>
       </c>
       <c r="R16" t="n">
-        <v>6.788912146598201e-05</v>
+        <v>2.326609424869324e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.000685056344768937</v>
+        <v>8.775908185029112e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.158367392819041</v>
+        <v>7.159069196563442</v>
       </c>
       <c r="U16" t="n">
-        <v>10090.81175269305</v>
+        <v>3771.973108688846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Devin Fusion CLI</t>
+          <t>DeepSeek Harness</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 XHigh + SWE-2 Medium</t>
+          <t>DeepSeek V4.1 Flash 1017 (Max)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>cognition</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.586619030954708</v>
+        <v>0.463051957532312</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01561771081733384</v>
+        <v>0.02162210576895259</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.682795698924731</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J17" t="n">
-        <v>8.19825160322711</v>
+        <v>0.29627468390668</v>
       </c>
       <c r="K17" t="n">
-        <v>2253.66843252199</v>
+        <v>1284.94041000543</v>
       </c>
       <c r="L17" t="n">
-        <v>92.38415770609321</v>
+        <v>101.530045617465</v>
       </c>
       <c r="M17" t="n">
-        <v>9809458.18526447</v>
+        <v>16739365.2564321</v>
       </c>
       <c r="N17" t="n">
-        <v>9713403.98470946</v>
+        <v>16633748.9354947</v>
       </c>
       <c r="O17" t="n">
-        <v>96054.2005550125</v>
+        <v>105616.32093733</v>
       </c>
       <c r="P17" t="n">
-        <v>0.957829308304356</v>
+        <v>0.967966386781858</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.07155416292954402</v>
+        <v>1.56291435848148</v>
       </c>
       <c r="R17" t="n">
-        <v>5.980136923728498e-05</v>
+        <v>2.766245615880712e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0002602951802888973</v>
+        <v>0.0003603684294825432</v>
       </c>
       <c r="T17" t="n">
-        <v>13.97542727157122</v>
+        <v>0.6398303237623303</v>
       </c>
       <c r="U17" t="n">
-        <v>4352.662549515813</v>
+        <v>13027.34751439669</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Antigravity SDK v0.1.12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Muse Wonder Full (Max)</t>
+          <t>Gemini 3.8 Flash (High)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.588804489084392</v>
+        <v>0.33272301118714</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01685280599548879</v>
+        <v>0.02539723060122723</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0.688172043010753</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>0.443548387096774</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.51071545979138</v>
+      </c>
       <c r="K18" t="n">
-        <v>2096.2841057163</v>
+        <v>786.045572632779</v>
       </c>
       <c r="L18" t="n">
-        <v>194.874971760617</v>
+        <v>202.504982078853</v>
       </c>
       <c r="M18" t="n">
-        <v>14497965.3172412</v>
+        <v>14251510.9748887</v>
       </c>
       <c r="N18" t="n">
-        <v>14414434.4559639</v>
+        <v>14138882.8572119</v>
       </c>
       <c r="O18" t="n">
-        <v>83530.861277289</v>
+        <v>112628.117676768</v>
       </c>
       <c r="P18" t="n">
-        <v>0.962325196630197</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>0.8791986451773121</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1325211942634019</v>
+      </c>
       <c r="R18" t="n">
-        <v>4.061290506635278e-05</v>
+        <v>2.33465077333485e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002808800999248132</v>
-      </c>
-      <c r="T18" t="inlineStr"/>
+        <v>0.0004232871766871206</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7.545962783978378</v>
+      </c>
       <c r="U18" t="n">
-        <v>6916.030741113332</v>
+        <v>18130.64212950749</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mirror</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Beam 1.0</t>
+          <t>DeepSeek V4.1 Flash (Max)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.20478987379168</v>
+        <v>0.473001334419464</v>
       </c>
       <c r="F19" t="n">
-        <v>0.005293428798001577</v>
+        <v>0.01242589322823963</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.376344086021506</v>
+        <v>0.610215053763441</v>
       </c>
       <c r="J19" t="n">
-        <v>0.319490234063365</v>
+        <v>0.38619359563592</v>
       </c>
       <c r="K19" t="n">
-        <v>2321.25393509395</v>
+        <v>2283.94687962311</v>
       </c>
       <c r="L19" t="n">
-        <v>92.9845715216683</v>
+        <v>142.882443792766</v>
       </c>
       <c r="M19" t="n">
-        <v>4890063.07487998</v>
+        <v>27235627.5942381</v>
       </c>
       <c r="N19" t="n">
-        <v>4852363.14787444</v>
+        <v>27078637.1644444</v>
       </c>
       <c r="O19" t="n">
-        <v>37699.9270055393</v>
+        <v>156990.429793635</v>
       </c>
       <c r="P19" t="n">
-        <v>0.95239449990423</v>
+        <v>0.9831236432716099</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6409894637063107</v>
+        <v>1.22477777923946</v>
       </c>
       <c r="R19" t="n">
-        <v>4.187877960995551e-05</v>
+        <v>1.736700697580147e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>8.82238133000263e-05</v>
+        <v>0.0002070982204706605</v>
       </c>
       <c r="T19" t="n">
-        <v>1.560088046093346</v>
+        <v>0.8164746429519335</v>
       </c>
       <c r="U19" t="n">
-        <v>2106.647187948466</v>
+        <v>11924.80781283864</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-6.1 Terra (Xhigh)</t>
+          <t>Step 5 Preview</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>stepfun</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.482238344954925</v>
+        <v>0.431274491691105</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02947324998862232</v>
+        <v>0.007060163541567688</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0.5376344086021499</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J20" t="n">
-        <v>0.690844449567775</v>
+        <v>1.84006320525524</v>
       </c>
       <c r="K20" t="n">
-        <v>981.713951073096</v>
+        <v>3665.13740781145</v>
       </c>
       <c r="L20" t="n">
-        <v>71.9594569349408</v>
+        <v>142.091813837298</v>
       </c>
       <c r="M20" t="n">
-        <v>6886239.03807863</v>
+        <v>22141655.7546106</v>
       </c>
       <c r="N20" t="n">
-        <v>6849711.54192788</v>
+        <v>21997509.2781069</v>
       </c>
       <c r="O20" t="n">
-        <v>36527.4961507549</v>
+        <v>144146.476503747</v>
       </c>
       <c r="P20" t="n">
-        <v>0.956934601768947</v>
+        <v>0.984007673153142</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6980418605905224</v>
+        <v>0.2343802595798777</v>
       </c>
       <c r="R20" t="n">
-        <v>7.002927756186012e-05</v>
+        <v>1.947796932943011e-05</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0004912208331437053</v>
+        <v>0.0001176693923594615</v>
       </c>
       <c r="T20" t="n">
-        <v>1.432578841552611</v>
+        <v>4.266570921085596</v>
       </c>
       <c r="U20" t="n">
-        <v>7014.506649876363</v>
+        <v>6041.152974898141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Mistral Vibe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Claude Haiku 5.5 (Max)</t>
+          <t>Mistral Large 4 (Medium)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.373496050722277</v>
+        <v>0.354072051699794</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005265544911017467</v>
+        <v>0.009117463014941153</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.338709677419355</v>
+        <v>0.446236559139785</v>
       </c>
       <c r="J21" t="n">
-        <v>2.67388407176395</v>
+        <v>0.782666187098099</v>
       </c>
       <c r="K21" t="n">
-        <v>4255.92477550559</v>
+        <v>2330.06956728793</v>
       </c>
       <c r="L21" t="n">
-        <v>114.307695231889</v>
+        <v>80.7014391224069</v>
       </c>
       <c r="M21" t="n">
-        <v>16053233.8058097</v>
+        <v>5758751.98349191</v>
       </c>
       <c r="N21" t="n">
-        <v>15314914.0867177</v>
+        <v>5679971.53044205</v>
       </c>
       <c r="O21" t="n">
-        <v>738319.719091995</v>
+        <v>78780.4530498534</v>
       </c>
       <c r="P21" t="n">
-        <v>0.918420370906708</v>
+        <v>0.922890846004726</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1396829633215486</v>
+        <v>0.4523921660811633</v>
       </c>
       <c r="R21" t="n">
-        <v>2.326609424869324e-05</v>
+        <v>6.148416405408328e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>8.775908185029112e-05</v>
+        <v>0.0001519577169156859</v>
       </c>
       <c r="T21" t="n">
-        <v>7.159069196563442</v>
+        <v>2.210471522224792</v>
       </c>
       <c r="U21" t="n">
-        <v>3771.973108688846</v>
+        <v>2471.493582998371</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muse Spark 1.3 (Max)</t>
+          <t>GPT-6 Luna (Max)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.457077885630498</v>
+        <v>0.311260251113284</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0196100872858839</v>
+        <v>0.01463841493843539</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.586021505376344</v>
+        <v>0.381720430107527</v>
       </c>
       <c r="J22" t="n">
-        <v>3.91029139020419</v>
+        <v>0.159155559086193</v>
       </c>
       <c r="K22" t="n">
-        <v>1398.49826969262</v>
+        <v>1275.79489619203</v>
       </c>
       <c r="L22" t="n">
-        <v>208.319377647442</v>
+        <v>81.3609199522103</v>
       </c>
       <c r="M22" t="n">
-        <v>17824340.6533789</v>
+        <v>8885939.032378631</v>
       </c>
       <c r="N22" t="n">
-        <v>17642872.3721332</v>
+        <v>8794707.77057673</v>
       </c>
       <c r="O22" t="n">
-        <v>181468.281245791</v>
+        <v>91231.26180188989</v>
       </c>
       <c r="P22" t="n">
-        <v>0.966617846464586</v>
+        <v>0.954514555274975</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1168910037690644</v>
+        <v>1.95569826715708</v>
       </c>
       <c r="R22" t="n">
-        <v>2.564346667958522e-05</v>
+        <v>3.502840273595309e-05</v>
       </c>
       <c r="S22" t="n">
-        <v>0.000326834788098065</v>
+        <v>0.0002439735823072565</v>
       </c>
       <c r="T22" t="n">
-        <v>8.554978293929695</v>
+        <v>0.5113263210350233</v>
       </c>
       <c r="U22" t="n">
-        <v>12745.34337271405</v>
+        <v>6965.021618209341</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kimi Code CLI</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kimi K3 (Max)</t>
+          <t>Muse Spark 1.3 (Max)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>moonshotai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.41417319257087</v>
+        <v>0.457077885630498</v>
       </c>
       <c r="F23" t="n">
-        <v>0.006586839388819422</v>
+        <v>0.0196100872858839</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>0.599462365591398</v>
+        <v>0.586021505376344</v>
       </c>
       <c r="J23" t="n">
-        <v>5.16526976917945</v>
+        <v>3.91029139020419</v>
       </c>
       <c r="K23" t="n">
-        <v>3772.73379345389</v>
+        <v>1398.49826969262</v>
       </c>
       <c r="L23" t="n">
-        <v>185.884007277072</v>
+        <v>208.319377647442</v>
       </c>
       <c r="M23" t="n">
-        <v>9010345.58218855</v>
+        <v>17824340.6533789</v>
       </c>
       <c r="N23" t="n">
-        <v>8910048.672052789</v>
+        <v>17642872.3721332</v>
       </c>
       <c r="O23" t="n">
-        <v>100296.910135766</v>
+        <v>181468.281245791</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9600647788144701</v>
+        <v>0.966617846464586</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.08018423259172099</v>
+        <v>0.1168910037690644</v>
       </c>
       <c r="R23" t="n">
-        <v>4.596640481688052e-05</v>
+        <v>2.564346667958522e-05</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0001097806564803237</v>
+        <v>0.000326834788098065</v>
       </c>
       <c r="T23" t="n">
-        <v>12.47127979751034</v>
+        <v>8.554978293929695</v>
       </c>
       <c r="U23" t="n">
-        <v>2388.280243313879</v>
+        <v>12745.34337271405</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Kimi Code CLI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
+          <t>Kimi K3 (Max)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>moonshotai</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5762002456826329</v>
+        <v>0.41417319257087</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01634184587525416</v>
+        <v>0.006586839388819422</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>0.663978494623656</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J24" t="n">
-        <v>11.5301045391259</v>
+        <v>5.16526976917945</v>
       </c>
       <c r="K24" t="n">
-        <v>2115.55138904529</v>
+        <v>3772.73379345389</v>
       </c>
       <c r="L24" t="n">
-        <v>42.2762050613663</v>
+        <v>185.884007277072</v>
       </c>
       <c r="M24" t="n">
-        <v>5989151.58443575</v>
+        <v>9010345.58218855</v>
       </c>
       <c r="N24" t="n">
-        <v>5863350.62589986</v>
+        <v>8910048.672052789</v>
       </c>
       <c r="O24" t="n">
-        <v>125800.958535897</v>
+        <v>100296.910135766</v>
       </c>
       <c r="P24" t="n">
-        <v>0.923288749508769</v>
+        <v>0.9600647788144701</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.04997354913195912</v>
+        <v>0.08018423259172099</v>
       </c>
       <c r="R24" t="n">
-        <v>9.620732378522992e-05</v>
+        <v>4.596640481688052e-05</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0002723640979209027</v>
+        <v>0.0001097806564803237</v>
       </c>
       <c r="T24" t="n">
-        <v>20.01058594736629</v>
+        <v>12.47127979751034</v>
       </c>
       <c r="U24" t="n">
-        <v>2831.01210183249</v>
+        <v>2388.280243313879</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Opencode</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GLM-5.3 (Max)</t>
+          <t>Claude Fable 5.1 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>zai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.489161690344303</v>
+        <v>0.5762002456826329</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00870989701144027</v>
+        <v>0.01634184587525416</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.586021505376344</v>
+        <v>0.663978494623656</v>
       </c>
       <c r="J25" t="n">
-        <v>5.23102713863476</v>
+        <v>11.5301045391259</v>
       </c>
       <c r="K25" t="n">
-        <v>3369.69557528728</v>
+        <v>2115.55138904529</v>
       </c>
       <c r="L25" t="n">
-        <v>111.53421852938</v>
+        <v>42.2762050613663</v>
       </c>
       <c r="M25" t="n">
-        <v>15908435.1191376</v>
+        <v>5989151.58443575</v>
       </c>
       <c r="N25" t="n">
-        <v>15798476.017074</v>
+        <v>5863350.62589986</v>
       </c>
       <c r="O25" t="n">
-        <v>109959.102063647</v>
+        <v>125800.958535897</v>
       </c>
       <c r="P25" t="n">
-        <v>0.949845583680754</v>
+        <v>0.923288749508769</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.09351159483220896</v>
+        <v>0.04997354913195912</v>
       </c>
       <c r="R25" t="n">
-        <v>3.074857373971681e-05</v>
+        <v>9.620732378522992e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0001451649501906712</v>
+        <v>0.0002723640979209027</v>
       </c>
       <c r="T25" t="n">
-        <v>10.69386103182535</v>
+        <v>20.01058594736629</v>
       </c>
       <c r="U25" t="n">
-        <v>4721.030361260851</v>
+        <v>2831.01210183249</v>
       </c>
     </row>
     <row r="26">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
+          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2225,506 +2225,506 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.593374426631911</v>
+        <v>0.616528649505811</v>
       </c>
       <c r="F28" t="n">
-        <v>0.007440989482023622</v>
+        <v>0.01010368064401798</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>0.64247311827957</v>
+        <v>0.658602150537634</v>
       </c>
       <c r="J28" t="n">
-        <v>13.3015082635468</v>
+        <v>11.4227202144224</v>
       </c>
       <c r="K28" t="n">
-        <v>4784.64130125774</v>
+        <v>3661.21221302161</v>
       </c>
       <c r="L28" t="n">
-        <v>232.941984902791</v>
+        <v>146.351117627892</v>
       </c>
       <c r="M28" t="n">
-        <v>24129277.9119089</v>
+        <v>14517552.0207549</v>
       </c>
       <c r="N28" t="n">
-        <v>23634722.0822716</v>
+        <v>14238131.763253</v>
       </c>
       <c r="O28" t="n">
-        <v>494555.829637233</v>
+        <v>279420.257501901</v>
       </c>
       <c r="P28" t="n">
-        <v>0.952959879951284</v>
+        <v>0.9532457550498</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.04460955967362529</v>
+        <v>0.05397389045101341</v>
       </c>
       <c r="R28" t="n">
-        <v>2.459147052797024e-05</v>
+        <v>4.246781059398966e-05</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0001240164913670604</v>
+        <v>0.0001683946774002996</v>
       </c>
       <c r="T28" t="n">
-        <v>22.41671980885376</v>
+        <v>18.5274767418813</v>
       </c>
       <c r="U28" t="n">
-        <v>5043.069353091532</v>
+        <v>3965.2309606969</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Muse Code</t>
+          <t>Claude Code</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Muse Wonder (Max)</t>
+          <t>Claude Sonnet 5.5 (Max, Default Fallback)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.519768236993592</v>
+        <v>0.593374426631911</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02117889017131678</v>
+        <v>0.007440989482023622</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.615591397849462</v>
+        <v>0.64247311827957</v>
       </c>
       <c r="J29" t="n">
-        <v>8.04811220428196</v>
+        <v>13.3015082635468</v>
       </c>
       <c r="K29" t="n">
-        <v>1472.5084254817</v>
+        <v>4784.64130125774</v>
       </c>
       <c r="L29" t="n">
-        <v>200.877049903501</v>
+        <v>232.941984902791</v>
       </c>
       <c r="M29" t="n">
-        <v>14479705.3019539</v>
+        <v>24129277.9119089</v>
       </c>
       <c r="N29" t="n">
-        <v>14384183.420164</v>
+        <v>23634722.0822716</v>
       </c>
       <c r="O29" t="n">
-        <v>95521.8817899424</v>
+        <v>494555.829637232</v>
       </c>
       <c r="P29" t="n">
-        <v>0.939000029822895</v>
+        <v>0.952959879951284</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06458262804997322</v>
+        <v>0.04460955967362529</v>
       </c>
       <c r="R29" t="n">
-        <v>3.589632704219845e-05</v>
+        <v>2.459147052797024e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0003529815028552796</v>
+        <v>0.0001240164913670604</v>
       </c>
       <c r="T29" t="n">
-        <v>15.48404006145759</v>
+        <v>22.41671980885376</v>
       </c>
       <c r="U29" t="n">
-        <v>9833.35989892022</v>
+        <v>5043.069353091532</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Muse Code</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-6.1 Sol (Max)</t>
+          <t>Muse Wonder (Max)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.541279798631476</v>
+        <v>0.519768236993592</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02284798697058158</v>
+        <v>0.02117889017131678</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0.599462365591398</v>
+        <v>0.615591397849462</v>
       </c>
       <c r="J30" t="n">
-        <v>1.5046389983744</v>
+        <v>8.04811220428196</v>
       </c>
       <c r="K30" t="n">
-        <v>1421.42885321603</v>
+        <v>1472.5084254817</v>
       </c>
       <c r="L30" t="n">
-        <v>40.6271304442272</v>
+        <v>200.877049903501</v>
       </c>
       <c r="M30" t="n">
-        <v>3944222.64509301</v>
+        <v>14479705.3019539</v>
       </c>
       <c r="N30" t="n">
-        <v>3888998.33558647</v>
+        <v>14384183.420164</v>
       </c>
       <c r="O30" t="n">
-        <v>55224.3095065408</v>
+        <v>95521.8817899424</v>
       </c>
       <c r="P30" t="n">
-        <v>0.921352278288341</v>
+        <v>0.939000029822895</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3597406415866333</v>
+        <v>0.06458262804997322</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001372335811987895</v>
+        <v>3.589632704219845e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0003807997828430263</v>
+        <v>0.0003529815028552796</v>
       </c>
       <c r="T30" t="n">
-        <v>2.779780442903275</v>
+        <v>15.48404006145759</v>
       </c>
       <c r="U30" t="n">
-        <v>2774.82945148403</v>
+        <v>9833.35989892022</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Antigravity CLI</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gemini 4 Carbon (High)</t>
+          <t>GPT-6.1 Sol (Max)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.594049025741284</v>
+        <v>0.541279798631476</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01991340695931401</v>
+        <v>0.02284798697058158</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.637096774193548</v>
+        <v>0.599462365591398</v>
       </c>
       <c r="J31" t="n">
-        <v>7.7432202900257</v>
+        <v>1.5046389983744</v>
       </c>
       <c r="K31" t="n">
-        <v>1789.89670714312</v>
+        <v>1421.42885321603</v>
       </c>
       <c r="L31" t="n">
-        <v>177.827079034068</v>
+        <v>40.6271304442272</v>
       </c>
       <c r="M31" t="n">
-        <v>12548516.9639495</v>
+        <v>3944222.64509301</v>
       </c>
       <c r="N31" t="n">
-        <v>12439485.9861971</v>
+        <v>3888998.33558647</v>
       </c>
       <c r="O31" t="n">
-        <v>109030.977752435</v>
+        <v>55224.3095065408</v>
       </c>
       <c r="P31" t="n">
-        <v>0.951903021414925</v>
+        <v>0.921352278288341</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.07671860072307363</v>
+        <v>0.3597406415866333</v>
       </c>
       <c r="R31" t="n">
-        <v>4.734017792285105e-05</v>
+        <v>0.0001372335811987895</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0003318901159885669</v>
+        <v>0.0003807997828430263</v>
       </c>
       <c r="T31" t="n">
-        <v>13.0346485803311</v>
+        <v>2.779780442903275</v>
       </c>
       <c r="U31" t="n">
-        <v>7010.74923143379</v>
+        <v>2774.82945148403</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mistral Vibe</t>
+          <t>Antigravity CLI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mistral Large 4 (High)</t>
+          <t>Gemini 4 Carbon (High)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>mistral</t>
+          <t>google</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.482774919409145</v>
+        <v>0.594049025741284</v>
       </c>
       <c r="F32" t="n">
-        <v>0.009974980957003318</v>
+        <v>0.01991340695931401</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.588709677419355</v>
+        <v>0.637096774193548</v>
       </c>
       <c r="J32" t="n">
-        <v>1.25944220793442</v>
+        <v>7.7432202900257</v>
       </c>
       <c r="K32" t="n">
-        <v>2903.91483346258</v>
+        <v>1789.89670714312</v>
       </c>
       <c r="L32" t="n">
-        <v>100.100451830129</v>
+        <v>177.827079034068</v>
       </c>
       <c r="M32" t="n">
-        <v>8453863.202892359</v>
+        <v>12548516.9639495</v>
       </c>
       <c r="N32" t="n">
-        <v>8330596.8209395</v>
+        <v>12439485.9861971</v>
       </c>
       <c r="O32" t="n">
-        <v>123266.381952862</v>
+        <v>109030.977752435</v>
       </c>
       <c r="P32" t="n">
-        <v>0.911751306302099</v>
+        <v>0.951903021414925</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3833243926300772</v>
+        <v>0.07671860072307363</v>
       </c>
       <c r="R32" t="n">
-        <v>5.710701815519928e-05</v>
+        <v>4.734017792285105e-05</v>
       </c>
       <c r="S32" t="n">
-        <v>0.000166249682616722</v>
+        <v>0.0003318901159885669</v>
       </c>
       <c r="T32" t="n">
-        <v>2.608756497698383</v>
+        <v>13.0346485803311</v>
       </c>
       <c r="U32" t="n">
-        <v>2911.195295907529</v>
+        <v>7010.74923143379</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Mistral Vibe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-6 Astra (Max)</t>
+          <t>Mistral Large 4 (High)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>mistral</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5466356905615291</v>
+        <v>0.482774919409145</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02206122126132733</v>
+        <v>0.009974980957003318</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.591397849462366</v>
+        <v>0.588709677419355</v>
       </c>
       <c r="J33" t="n">
-        <v>7.03615822479963</v>
+        <v>1.25944220793442</v>
       </c>
       <c r="K33" t="n">
-        <v>1486.68747959053</v>
+        <v>2903.91483346258</v>
       </c>
       <c r="L33" t="n">
-        <v>39.3501020962311</v>
+        <v>100.100451830129</v>
       </c>
       <c r="M33" t="n">
-        <v>3228511.32437048</v>
+        <v>8453863.202892359</v>
       </c>
       <c r="N33" t="n">
-        <v>3187374.52012585</v>
+        <v>8330596.8209395</v>
       </c>
       <c r="O33" t="n">
-        <v>41136.8042446321</v>
+        <v>123266.381952862</v>
       </c>
       <c r="P33" t="n">
-        <v>0.928466255516987</v>
+        <v>0.911751306302099</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.07768951082351416</v>
+        <v>0.3833243926300772</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0001693150915826867</v>
+        <v>5.710701815519928e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0003676870210221221</v>
+        <v>0.000166249682616722</v>
       </c>
       <c r="T33" t="n">
-        <v>12.87175050273751</v>
+        <v>2.608756497698383</v>
       </c>
       <c r="U33" t="n">
-        <v>2171.613986592321</v>
+        <v>2911.195295907529</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grok Build</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Grok 4.7 (Xhigh)</t>
+          <t>GPT-6 Astra (Max)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>xai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.465968752688172</v>
+        <v>0.5466356905615291</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01302767878143769</v>
+        <v>0.02206122126132733</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.629032258064516</v>
+        <v>0.591397849462366</v>
       </c>
       <c r="J34" t="n">
-        <v>9.479356533441949</v>
+        <v>7.03615822479963</v>
       </c>
       <c r="K34" t="n">
-        <v>2146.05576560009</v>
+        <v>1486.68747959053</v>
       </c>
       <c r="L34" t="n">
-        <v>169.916321277289</v>
+        <v>39.3501020962311</v>
       </c>
       <c r="M34" t="n">
-        <v>15914547.7950299</v>
+        <v>3228511.32437048</v>
       </c>
       <c r="N34" t="n">
-        <v>15798913.4163495</v>
+        <v>3187374.52012585</v>
       </c>
       <c r="O34" t="n">
-        <v>115634.378680352</v>
+        <v>41136.8042446321</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9420679200051389</v>
+        <v>0.928466255516988</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.04915615854771305</v>
+        <v>0.07768951082351416</v>
       </c>
       <c r="R34" t="n">
-        <v>2.927942148841287e-05</v>
+        <v>0.0001693150915826867</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0002171279796906282</v>
+        <v>0.0003676870210221221</v>
       </c>
       <c r="T34" t="n">
-        <v>20.34333091812611</v>
+        <v>12.87175050273751</v>
       </c>
       <c r="U34" t="n">
-        <v>7415.719595981607</v>
+        <v>2171.613986592321</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Claude Code</t>
+          <t>Grok Build</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 (Max, Default Fallback)</t>
+          <t>Grok 4.7 (Xhigh)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.616528649505811</v>
+        <v>0.465968752688172</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01010368064401798</v>
+        <v>0.01302767878143769</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>0.658602150537634</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="J35" t="n">
-        <v>11.4227202144224</v>
+        <v>9.479356533441949</v>
       </c>
       <c r="K35" t="n">
-        <v>3661.21221302161</v>
+        <v>2146.05576560009</v>
       </c>
       <c r="L35" t="n">
-        <v>146.351117627892</v>
+        <v>169.916321277289</v>
       </c>
       <c r="M35" t="n">
-        <v>14517552.0207549</v>
+        <v>15914547.7950299</v>
       </c>
       <c r="N35" t="n">
-        <v>14238131.763253</v>
+        <v>15798913.4163495</v>
       </c>
       <c r="O35" t="n">
-        <v>279420.257501901</v>
+        <v>115634.378680352</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9532457550498</v>
+        <v>0.9420679200051389</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.05397389045101341</v>
+        <v>0.04915615854771305</v>
       </c>
       <c r="R35" t="n">
-        <v>4.246781059398966e-05</v>
+        <v>2.927942148841287e-05</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0001683946774002996</v>
+        <v>0.0002171279796906282</v>
       </c>
       <c r="T35" t="n">
-        <v>18.5274767418813</v>
+        <v>20.34333091812611</v>
       </c>
       <c r="U35" t="n">
-        <v>3965.2309606969</v>
+        <v>7415.719595981607</v>
       </c>
     </row>
   </sheetData>
